--- a/egais.xlsx
+++ b/egais.xlsx
@@ -7820,7 +7820,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK62"/>
+  <dimension ref="A1:AK82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28.33" customWidth="1" min="1" max="1"/>
@@ -15874,6 +15874,2526 @@
       <c r="AK62" t="inlineStr">
         <is>
           <t>2026-10-11T12:00:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>7772328806</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>79852671426</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Сосна пиловочник, ЭСД выдаём за 15 минут</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;&lt;strong&gt;Лес у вас есть, а в системе его нет: сделаем так, чтобы партию можно было вывезти и продать.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Оформляем вашу древесину договором купли-продажи от нашего объёма, заводим кубатуру в ФГИС ЛК и выписываем ЭСД с QR на каждый рейс. На документ уходит 15 минут.&lt;/p&gt;&lt;p&gt;Кабинет в системе и электронная подпись вам не нужны, от вас только порода, объём и маршрут. Работа от 1400 руб.&lt;/p&gt;&lt;p&gt;Сосновый пиловочник 4 и 6 метров, диаметр от 18 см.&lt;/p&gt;&lt;p&gt;Южский район, Ивановская область.&lt;/p&gt;&lt;p&gt;Напишите, сколько машин в неделю.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_01_yuzha_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_01_yuzha_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_01_yuzha_3.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_01_yuzha_4.jpg</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>В сообщениях</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>Южа, Ивановская обл., ул. Советская, 21</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>ПВЗ</t>
+        </is>
+      </c>
+      <c r="P63" t="n">
+        <v>1400</v>
+      </c>
+      <c r="Q63" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R63" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S63" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Сосна</t>
+        </is>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB63" t="n">
+        <v>6000</v>
+      </c>
+      <c r="AC63" t="n">
+        <v>18</v>
+      </c>
+      <c r="AE63" t="inlineStr">
+        <is>
+          <t>orbizona-shop@yandex.ru</t>
+        </is>
+      </c>
+      <c r="AF63" t="inlineStr">
+        <is>
+          <t>ЕГАИС ЛЕС документация</t>
+        </is>
+      </c>
+      <c r="AG63" t="inlineStr">
+        <is>
+          <t>2026-10-15T07:20:00+03:00</t>
+        </is>
+      </c>
+      <c r="AJ63" t="inlineStr">
+        <is>
+          <t>2026-09-15T09:20:00+03:00</t>
+        </is>
+      </c>
+      <c r="AK63" t="inlineStr">
+        <is>
+          <t>2026-10-15T07:20:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>9833881860</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>79852671426</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Баланс берёзовый, накладная на перевозку</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;&lt;strong&gt;Довезём вашу партию до покупателя по бумагам, которые он примет без вопросов.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Что делаем:&lt;br&gt;- договор купли-продажи от нашего объёма на вашу древесину&lt;br&gt;- постановка кубатуры в ФГИС ЛК&lt;br&gt;- накладная с QR на каждую машину, 15 минут на документ&lt;br&gt;- декларация о сделке и отчёт 1-ИЛ&lt;/p&gt;&lt;p&gt;От вас порода, объём и маршрут, от 950 руб. Электронная подпись не понадобится.&lt;/p&gt;&lt;p&gt;Берёзовый баланс 2 и 3 метра, диаметр от 6 см.&lt;/p&gt;&lt;p&gt;Меленковский район, Владимирская область.&lt;/p&gt;&lt;p&gt;Напишите, сколько кубов набирается.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_03_melenki_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_03_melenki_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_03_melenki_3.jpg</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>В сообщениях</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>Меленки, Владимирская обл., ул. Первомайская, 108</t>
+        </is>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>ПВЗ</t>
+        </is>
+      </c>
+      <c r="P64" t="n">
+        <v>950</v>
+      </c>
+      <c r="Q64" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R64" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S64" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Берёза</t>
+        </is>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB64" t="n">
+        <v>3000</v>
+      </c>
+      <c r="AC64" t="n">
+        <v>6</v>
+      </c>
+      <c r="AE64" t="inlineStr">
+        <is>
+          <t>orbizona-shop@yandex.ru</t>
+        </is>
+      </c>
+      <c r="AF64" t="inlineStr">
+        <is>
+          <t>ЕГАИС ЛЕС документация</t>
+        </is>
+      </c>
+      <c r="AG64" t="inlineStr">
+        <is>
+          <t>2026-10-15T09:40:00+03:00</t>
+        </is>
+      </c>
+      <c r="AJ64" t="inlineStr">
+        <is>
+          <t>2026-09-15T11:40:00+03:00</t>
+        </is>
+      </c>
+      <c r="AK64" t="inlineStr">
+        <is>
+          <t>2026-10-15T09:40:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>4102655995</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>79852671426</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Пиловочник сосна, ЭСД и договор на груз</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;&lt;strong&gt;На руках будет комплект, с которым партию принимают и на комбинате, и на посту.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Оформляем вашу древесину договором купли-продажи от нашего объёма, ставим её на учёт в ФГИС ЛК и выписываем ЭСД с QR на рейс за 15 минут. Декларацию о сделке и отчёт 1-ИЛ закрываем сами.&lt;/p&gt;&lt;p&gt;Работаем удалённо, от 2000 руб. Свой кабинет заводить не нужно.&lt;/p&gt;&lt;p&gt;Сосновый пиловочник 6 метров, диаметр от 20 см.&lt;/p&gt;&lt;p&gt;Кукморский район, Татарстан.&lt;/p&gt;&lt;p&gt;Напишите, сколько машин в неделю.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_10_kukmor_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_10_kukmor_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_10_kukmor_3.jpg</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>В сообщениях</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>Кукмор, Республика Татарстан, ул. Ленина, 15</t>
+        </is>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>ПВЗ</t>
+        </is>
+      </c>
+      <c r="P65" t="n">
+        <v>2000</v>
+      </c>
+      <c r="Q65" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R65" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S65" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Сосна</t>
+        </is>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB65" t="n">
+        <v>6000</v>
+      </c>
+      <c r="AC65" t="n">
+        <v>20</v>
+      </c>
+      <c r="AE65" t="inlineStr">
+        <is>
+          <t>orbizona-shop@yandex.ru</t>
+        </is>
+      </c>
+      <c r="AF65" t="inlineStr">
+        <is>
+          <t>ЕГАИС ЛЕС документация</t>
+        </is>
+      </c>
+      <c r="AG65" t="inlineStr">
+        <is>
+          <t>2026-10-15T12:10:00+03:00</t>
+        </is>
+      </c>
+      <c r="AJ65" t="inlineStr">
+        <is>
+          <t>2026-09-15T14:10:00+03:00</t>
+        </is>
+      </c>
+      <c r="AK65" t="inlineStr">
+        <is>
+          <t>2026-10-15T12:10:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>9814763638</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>79852671426</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Пиловочник сосна от заготовителя, ЭСД</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;&lt;strong&gt;Работаем с теми, кто пилит сам: доведём вашу заготовку до бумаг, с которыми её купят.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Оформляем древесину договором купли-продажи от нашего объёма, ставим кубатуру в ФГИС ЛК и выдаём ЭСД с QR на рейс за 15 минут. Декларация о сделке и отчёт 1-ИЛ на нас.&lt;/p&gt;&lt;p&gt;Свой кабинет и подпись заводить не нужно, от 1850 руб.&lt;/p&gt;&lt;p&gt;Сосновый пиловочник 4 и 6 метров, диаметр от 18 см.&lt;/p&gt;&lt;p&gt;Караидельский район, Башкортостан.&lt;/p&gt;&lt;p&gt;Напишите, какой объём пилите в месяц.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_19_karaidel_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_19_karaidel_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_19_karaidel_3.jpg</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>В сообщениях</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>Караидель, Республика Башкортостан, ул. Ленина, 24</t>
+        </is>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>ПВЗ</t>
+        </is>
+      </c>
+      <c r="P66" t="n">
+        <v>1850</v>
+      </c>
+      <c r="Q66" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R66" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S66" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Сосна</t>
+        </is>
+      </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB66" t="n">
+        <v>6000</v>
+      </c>
+      <c r="AC66" t="n">
+        <v>18</v>
+      </c>
+      <c r="AE66" t="inlineStr">
+        <is>
+          <t>orbizona-shop@yandex.ru</t>
+        </is>
+      </c>
+      <c r="AF66" t="inlineStr">
+        <is>
+          <t>ЕГАИС ЛЕС документация</t>
+        </is>
+      </c>
+      <c r="AG66" t="inlineStr">
+        <is>
+          <t>2026-10-15T14:30:00+03:00</t>
+        </is>
+      </c>
+      <c r="AJ66" t="inlineStr">
+        <is>
+          <t>2026-09-15T16:30:00+03:00</t>
+        </is>
+      </c>
+      <c r="AK66" t="inlineStr">
+        <is>
+          <t>2026-10-15T14:30:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>4647399772</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>79852671426</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Лес кругляк ель (QR код на каждый рейс)</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;&lt;strong&gt;Машина уедет с площадки только с рабочим QR, и ни один пост её не развернёт.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Берём вашу древесину на свой объём по договору купли-продажи, ставим кубатуру в ФГИС ЛК и выдаём электронный сопроводительный документ на рейс. QR живой, проверяется телефоном за пару секунд.&lt;/p&gt;&lt;p&gt;Ни кабинета, ни подписи заводить не надо, работа от 850 руб.&lt;/p&gt;&lt;p&gt;Еловый кругляк 4 и 6 метров, диаметр от 14 см.&lt;/p&gt;&lt;p&gt;Пестяковский район, Ивановская область.&lt;/p&gt;&lt;p&gt;Напишите, куда идёт груз.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_02_pestyaki_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_02_pestyaki_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_02_pestyaki_3.jpg</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>В сообщениях</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>Пестяки, Ивановская обл., ул. Ленина, 14</t>
+        </is>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>ПВЗ</t>
+        </is>
+      </c>
+      <c r="P67" t="n">
+        <v>850</v>
+      </c>
+      <c r="Q67" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R67" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S67" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Ель</t>
+        </is>
+      </c>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB67" t="n">
+        <v>6000</v>
+      </c>
+      <c r="AC67" t="n">
+        <v>14</v>
+      </c>
+      <c r="AE67" t="inlineStr">
+        <is>
+          <t>orbizona-shop@yandex.ru</t>
+        </is>
+      </c>
+      <c r="AF67" t="inlineStr">
+        <is>
+          <t>ЕГАИС ЛЕС документация</t>
+        </is>
+      </c>
+      <c r="AG67" t="inlineStr">
+        <is>
+          <t>2026-10-16T07:20:00+03:00</t>
+        </is>
+      </c>
+      <c r="AJ67" t="inlineStr">
+        <is>
+          <t>2026-09-16T09:20:00+03:00</t>
+        </is>
+      </c>
+      <c r="AK67" t="inlineStr">
+        <is>
+          <t>2026-10-16T07:20:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>5381421624</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>79852671426</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Пиловочник сосна, заведём объём в ФГИС ЛК</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;&lt;strong&gt;Кубатура начнёт числиться за вами, и партию можно будет спокойно продавать.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Разбираем ситуацию в день обращения, оформляем древесину договором купли-продажи от нашего объёма и заводим её в ФГИС ЛК. Дальше выписываем ЭСД на рейсы, подаём декларацию о сделке и закрываем отчёт 1-ИЛ.&lt;/p&gt;&lt;p&gt;Свой кабинет вам не нужен, от 1700 руб. Срок по учёту называем после разбора ситуации.&lt;/p&gt;&lt;p&gt;Сосновый пиловочник 6 метров, диаметр от 20 см.&lt;/p&gt;&lt;p&gt;Судогодский район, Владимирская область.&lt;/p&gt;&lt;p&gt;Напишите, что уже есть по документам.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_04_sudogda_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_04_sudogda_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_04_sudogda_3.jpg</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>В сообщениях</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>Судогда, Владимирская обл., ул. Ленина, 40</t>
+        </is>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>ПВЗ</t>
+        </is>
+      </c>
+      <c r="P68" t="n">
+        <v>1700</v>
+      </c>
+      <c r="Q68" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R68" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S68" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Сосна</t>
+        </is>
+      </c>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB68" t="n">
+        <v>6000</v>
+      </c>
+      <c r="AC68" t="n">
+        <v>20</v>
+      </c>
+      <c r="AE68" t="inlineStr">
+        <is>
+          <t>orbizona-shop@yandex.ru</t>
+        </is>
+      </c>
+      <c r="AF68" t="inlineStr">
+        <is>
+          <t>ЕГАИС ЛЕС документация</t>
+        </is>
+      </c>
+      <c r="AG68" t="inlineStr">
+        <is>
+          <t>2026-10-16T09:40:00+03:00</t>
+        </is>
+      </c>
+      <c r="AJ68" t="inlineStr">
+        <is>
+          <t>2026-09-16T11:40:00+03:00</t>
+        </is>
+      </c>
+      <c r="AK68" t="inlineStr">
+        <is>
+          <t>2026-10-16T09:40:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>7245708048</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>79852671426</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Балансы еловые (объём встанет на баланс)</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;&lt;strong&gt;Кубы, которых сейчас за вами нет, появятся на балансе и станут товаром.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Работаем так: договор купли-продажи от нашего объёма на вашу древесину, постановка в ФГИС ЛК, ЭСД с QR на каждый рейс за 15 минут, декларация о сделке, отчёт 1-ИЛ и места складирования.&lt;/p&gt;&lt;p&gt;Электронная подпись и свой кабинет не понадобятся, от 900 руб.&lt;/p&gt;&lt;p&gt;Еловый баланс 2 и 3 метра, диаметр от 6 см.&lt;/p&gt;&lt;p&gt;Кезский район, Удмуртия.&lt;/p&gt;&lt;p&gt;Напишите, сколько кубов на руках.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_08_kez_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_08_kez_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_08_kez_3.jpg</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>В сообщениях</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>Кез, Удмуртская Республика, ул. Кирова, 10</t>
+        </is>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>ПВЗ</t>
+        </is>
+      </c>
+      <c r="P69" t="n">
+        <v>900</v>
+      </c>
+      <c r="Q69" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R69" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S69" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Ель</t>
+        </is>
+      </c>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB69" t="n">
+        <v>3000</v>
+      </c>
+      <c r="AC69" t="n">
+        <v>6</v>
+      </c>
+      <c r="AE69" t="inlineStr">
+        <is>
+          <t>orbizona-shop@yandex.ru</t>
+        </is>
+      </c>
+      <c r="AF69" t="inlineStr">
+        <is>
+          <t>ЕГАИС ЛЕС документация</t>
+        </is>
+      </c>
+      <c r="AG69" t="inlineStr">
+        <is>
+          <t>2026-10-16T12:10:00+03:00</t>
+        </is>
+      </c>
+      <c r="AJ69" t="inlineStr">
+        <is>
+          <t>2026-09-16T14:10:00+03:00</t>
+        </is>
+      </c>
+      <c r="AK69" t="inlineStr">
+        <is>
+          <t>2026-10-16T12:10:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>3846915680</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>79852671426</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Пиловочник ель (ЭСД на каждую машину)</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;&lt;strong&gt;Сколько машин уйдёт, столько документов и будет, задержек по бумагам не случится.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Оформляем вашу древесину договором купли-продажи от нашего объёма, заводим в ФГИС ЛК и выписываем ЭСД с QR на рейс за 15 минут. Декларация о сделке и отчёт 1-ИЛ на нас.&lt;/p&gt;&lt;p&gt;Кабинет и электронная подпись вам не понадобятся, от 1550 руб.&lt;/p&gt;&lt;p&gt;Еловый пиловочник 4 и 6 метров, диаметр от 16 см.&lt;/p&gt;&lt;p&gt;Маслянинский район, Новосибирская область.&lt;/p&gt;&lt;p&gt;Напишите, сколько рейсов в неделю.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_15_maslyanino_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_15_maslyanino_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_15_maslyanino_3.jpg</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>В сообщениях</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>Маслянино, Новосибирская обл., ул. Коммунистическая, 3</t>
+        </is>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>ПВЗ</t>
+        </is>
+      </c>
+      <c r="P70" t="n">
+        <v>1550</v>
+      </c>
+      <c r="Q70" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R70" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S70" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Ель</t>
+        </is>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB70" t="n">
+        <v>6000</v>
+      </c>
+      <c r="AC70" t="n">
+        <v>16</v>
+      </c>
+      <c r="AE70" t="inlineStr">
+        <is>
+          <t>orbizona-shop@yandex.ru</t>
+        </is>
+      </c>
+      <c r="AF70" t="inlineStr">
+        <is>
+          <t>ЕГАИС ЛЕС документация</t>
+        </is>
+      </c>
+      <c r="AG70" t="inlineStr">
+        <is>
+          <t>2026-10-16T14:30:00+03:00</t>
+        </is>
+      </c>
+      <c r="AJ70" t="inlineStr">
+        <is>
+          <t>2026-09-16T16:30:00+03:00</t>
+        </is>
+      </c>
+      <c r="AK70" t="inlineStr">
+        <is>
+          <t>2026-10-16T14:30:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>1403662800</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>79852671426</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Ель пиловочник, ЭСД на вывоз с площадки</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;&lt;strong&gt;Отгрузка не встанет из-за бумаг: документ на рейс будет у водителя раньше, чем он заведёт машину.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Оформляем вашу древесину на наш объём договором купли-продажи, ставим её в ФГИС ЛК и выписываем ЭСД с QR. На документ уходит 15 минут, дальше подаём декларацию о сделке и закрываем 1-ИЛ.&lt;/p&gt;&lt;p&gt;От вас порода, объём и маршрут, от 1100 руб. Подпись и кабинет не нужны.&lt;/p&gt;&lt;p&gt;Еловый пиловочник 4 и 6 метров, диаметр от 16 см.&lt;/p&gt;&lt;p&gt;Западнодвинский округ, Тверская область.&lt;/p&gt;&lt;p&gt;Напишите, сколько машин в день.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_06_zapdvina_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_06_zapdvina_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_06_zapdvina_3.jpg</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>В сообщениях</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>Западная Двина, Тверская обл., ул. Кирова, 10</t>
+        </is>
+      </c>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>ПВЗ</t>
+        </is>
+      </c>
+      <c r="P71" t="n">
+        <v>1100</v>
+      </c>
+      <c r="Q71" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R71" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S71" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Ель</t>
+        </is>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB71" t="n">
+        <v>6000</v>
+      </c>
+      <c r="AC71" t="n">
+        <v>16</v>
+      </c>
+      <c r="AE71" t="inlineStr">
+        <is>
+          <t>orbizona-shop@yandex.ru</t>
+        </is>
+      </c>
+      <c r="AF71" t="inlineStr">
+        <is>
+          <t>ЕГАИС ЛЕС документация</t>
+        </is>
+      </c>
+      <c r="AG71" t="inlineStr">
+        <is>
+          <t>2026-10-17T07:20:00+03:00</t>
+        </is>
+      </c>
+      <c r="AJ71" t="inlineStr">
+        <is>
+          <t>2026-09-17T09:20:00+03:00</t>
+        </is>
+      </c>
+      <c r="AK71" t="inlineStr">
+        <is>
+          <t>2026-10-17T07:20:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>3459366177</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>79852671426</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Берёза дровяная (поставим на учёт в ЛК)</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;&lt;strong&gt;Даже дровяная древесина должна числиться за вами, иначе её не продать и не вывезти.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Ставим вашу кубатуру в ФГИС ЛК через договор купли-продажи от нашего объёма, выписываем ЭСД с QR на рейс за 15 минут и подаём декларацию о сделке.&lt;/p&gt;&lt;p&gt;От вас порода, объём и маршрут, работа от 350 руб. Подпись и кабинет не понадобятся.&lt;/p&gt;&lt;p&gt;Берёзовые дрова и баланс 1 и 2 метра, диаметр от 6 см.&lt;/p&gt;&lt;p&gt;Балтасинский район, Татарстан.&lt;/p&gt;&lt;p&gt;Напишите, сколько кубов.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_11_baltasi_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_11_baltasi_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_11_baltasi_3.jpg</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>В сообщениях</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>Балтаси, Республика Татарстан, ул. Советская, 20</t>
+        </is>
+      </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>ПВЗ</t>
+        </is>
+      </c>
+      <c r="P72" t="n">
+        <v>350</v>
+      </c>
+      <c r="Q72" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R72" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S72" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Берёза</t>
+        </is>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB72" t="n">
+        <v>2000</v>
+      </c>
+      <c r="AC72" t="n">
+        <v>6</v>
+      </c>
+      <c r="AE72" t="inlineStr">
+        <is>
+          <t>orbizona-shop@yandex.ru</t>
+        </is>
+      </c>
+      <c r="AF72" t="inlineStr">
+        <is>
+          <t>ЕГАИС ЛЕС документация</t>
+        </is>
+      </c>
+      <c r="AG72" t="inlineStr">
+        <is>
+          <t>2026-10-17T09:40:00+03:00</t>
+        </is>
+      </c>
+      <c r="AJ72" t="inlineStr">
+        <is>
+          <t>2026-09-17T11:40:00+03:00</t>
+        </is>
+      </c>
+      <c r="AK72" t="inlineStr">
+        <is>
+          <t>2026-10-17T09:40:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>1944067370</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>79852671426</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>Ель пиловочник, ЭСД за 15 минут на рейс</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;&lt;strong&gt;Документ на вывоз будет у вас в тот же день, когда вы напишете.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Берём вашу древесину на свой объём по договору купли-продажи, ставим кубатуру в ФГИС ЛК и выпускаем ЭСД с QR на рейс. Дальше подаём декларацию о сделке и закрываем отчёт 1-ИЛ.&lt;/p&gt;&lt;p&gt;Работаем удалённо по всей стране, от 2450 руб. Ни кабинета, ни подписи заводить не надо.&lt;/p&gt;&lt;p&gt;Еловый пиловочник 6 метров, диаметр от 20 см.&lt;/p&gt;&lt;p&gt;Варнавинский район, Нижегородская область.&lt;/p&gt;&lt;p&gt;Напишите, когда нужна первая машина.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_17_varnavino_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_17_varnavino_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_17_varnavino_3.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_17_varnavino_4.jpg</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>В сообщениях</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>Варнавино, Нижегородская обл., ул. Советская, 1</t>
+        </is>
+      </c>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>ПВЗ</t>
+        </is>
+      </c>
+      <c r="P73" t="n">
+        <v>2450</v>
+      </c>
+      <c r="Q73" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R73" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S73" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Ель</t>
+        </is>
+      </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB73" t="n">
+        <v>6000</v>
+      </c>
+      <c r="AC73" t="n">
+        <v>20</v>
+      </c>
+      <c r="AE73" t="inlineStr">
+        <is>
+          <t>orbizona-shop@yandex.ru</t>
+        </is>
+      </c>
+      <c r="AF73" t="inlineStr">
+        <is>
+          <t>ЕГАИС ЛЕС документация</t>
+        </is>
+      </c>
+      <c r="AG73" t="inlineStr">
+        <is>
+          <t>2026-10-17T12:10:00+03:00</t>
+        </is>
+      </c>
+      <c r="AJ73" t="inlineStr">
+        <is>
+          <t>2026-09-17T14:10:00+03:00</t>
+        </is>
+      </c>
+      <c r="AK73" t="inlineStr">
+        <is>
+          <t>2026-10-17T12:10:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>4328655612</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>79852671426</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>Кряж берёзовый (декларация о сделке)</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;&lt;strong&gt;Сделка станет видимой в системе, и вы перестанете зависеть от того, проверят вас или нет.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Заводим вашу древесину через договор купли-продажи от нашего объёма, подаём декларацию о сделке в ФГИС ЛК и выпускаем ЭСД с QR на каждую отгрузку за 15 минут.&lt;/p&gt;&lt;p&gt;Работаем удалённо, кабинет и подпись заводить не нужно. Работа от 620 руб.&lt;/p&gt;&lt;p&gt;Берёзовый кряж 3 и 4 метра, диаметр от 16 см.&lt;/p&gt;&lt;p&gt;Кузоватовский район, Ульяновская область.&lt;/p&gt;&lt;p&gt;Напишите объём и породу.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_05_kuzovatovo_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_05_kuzovatovo_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_05_kuzovatovo_3.jpg</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>В сообщениях</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>Кузоватово, Ульяновская обл., ул. Октябрьская, 4</t>
+        </is>
+      </c>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>ПВЗ</t>
+        </is>
+      </c>
+      <c r="P74" t="n">
+        <v>620</v>
+      </c>
+      <c r="Q74" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R74" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S74" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Берёза</t>
+        </is>
+      </c>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB74" t="n">
+        <v>4000</v>
+      </c>
+      <c r="AC74" t="n">
+        <v>16</v>
+      </c>
+      <c r="AE74" t="inlineStr">
+        <is>
+          <t>orbizona-shop@yandex.ru</t>
+        </is>
+      </c>
+      <c r="AF74" t="inlineStr">
+        <is>
+          <t>ЕГАИС ЛЕС документация</t>
+        </is>
+      </c>
+      <c r="AG74" t="inlineStr">
+        <is>
+          <t>2026-10-17T14:30:00+03:00</t>
+        </is>
+      </c>
+      <c r="AJ74" t="inlineStr">
+        <is>
+          <t>2026-09-17T16:30:00+03:00</t>
+        </is>
+      </c>
+      <c r="AK74" t="inlineStr">
+        <is>
+          <t>2026-10-17T14:30:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2873722762</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>79852671426</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>Лес кругляк сосна, документы ФГИС ЛК</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;&lt;strong&gt;Купили лес у населения или взяли по билету, а в системе пусто: доведём партию до законной отгрузки.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Оформляем происхождение древесины договором купли-продажи от нашего объёма, заводим кубатуру в ФГИС ЛК, выдаём ЭСД с QR на рейс за 15 минут, подаём декларацию и закрываем отчёт 1-ИЛ.&lt;/p&gt;&lt;p&gt;Кабинет в системе вам заводить не надо, работа от 750 руб.&lt;/p&gt;&lt;p&gt;Сосновый кругляк 4 и 6 метров, диаметр от 18 см.&lt;/p&gt;&lt;p&gt;Зубово-Полянский район, Мордовия.&lt;/p&gt;&lt;p&gt;Напишите, откуда древесина.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_07_zubovapolyana_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_07_zubovapolyana_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_07_zubovapolyana_3.jpg</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>В сообщениях</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>Зубова Поляна, Республика Мордовия, ул. Ленина, 6</t>
+        </is>
+      </c>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>ПВЗ</t>
+        </is>
+      </c>
+      <c r="P75" t="n">
+        <v>750</v>
+      </c>
+      <c r="Q75" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R75" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S75" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>Сосна</t>
+        </is>
+      </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB75" t="n">
+        <v>6000</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>18</v>
+      </c>
+      <c r="AE75" t="inlineStr">
+        <is>
+          <t>orbizona-shop@yandex.ru</t>
+        </is>
+      </c>
+      <c r="AF75" t="inlineStr">
+        <is>
+          <t>ЕГАИС ЛЕС документация</t>
+        </is>
+      </c>
+      <c r="AG75" t="inlineStr">
+        <is>
+          <t>2026-10-18T07:20:00+03:00</t>
+        </is>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>2026-09-18T09:20:00+03:00</t>
+        </is>
+      </c>
+      <c r="AK75" t="inlineStr">
+        <is>
+          <t>2026-10-18T07:20:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>2564555725</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>79852671426</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>Доска обрезная сосна, QR код на вывоз</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;&lt;strong&gt;Покупатель заберёт партию спокойно: по бумагам древесина чистая и учтённая.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Заводим ваш объём в ФГИС ЛК через договор купли-продажи от нашей компании и выдаём документ с QR на каждую машину. Делаем за 15 минут, дальше декларация о сделке и отчёт 1-ИЛ на нас.&lt;/p&gt;&lt;p&gt;Кабинет и подпись не нужны, работа от 480 руб.&lt;/p&gt;&lt;p&gt;Сосновая доска и кругляк 4 и 6 метров, диаметр от 18 см.&lt;/p&gt;&lt;p&gt;Шиловский район, Рязанская область.&lt;/p&gt;&lt;p&gt;Напишите, какой объём и куда везёте.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_09_shilovo_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_09_shilovo_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_09_shilovo_3.jpg</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>В сообщениях</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>Шилово, Рязанская обл., ул. Советская, 14</t>
+        </is>
+      </c>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t>ПВЗ</t>
+        </is>
+      </c>
+      <c r="P76" t="n">
+        <v>480</v>
+      </c>
+      <c r="Q76" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R76" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S76" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>Сосна</t>
+        </is>
+      </c>
+      <c r="X76" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB76" t="n">
+        <v>6000</v>
+      </c>
+      <c r="AC76" t="n">
+        <v>18</v>
+      </c>
+      <c r="AE76" t="inlineStr">
+        <is>
+          <t>orbizona-shop@yandex.ru</t>
+        </is>
+      </c>
+      <c r="AF76" t="inlineStr">
+        <is>
+          <t>ЕГАИС ЛЕС документация</t>
+        </is>
+      </c>
+      <c r="AG76" t="inlineStr">
+        <is>
+          <t>2026-10-18T09:40:00+03:00</t>
+        </is>
+      </c>
+      <c r="AJ76" t="inlineStr">
+        <is>
+          <t>2026-09-18T11:40:00+03:00</t>
+        </is>
+      </c>
+      <c r="AK76" t="inlineStr">
+        <is>
+          <t>2026-10-18T09:40:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>3700275644</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>79852671426</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>Лес кругляк хвоя (QR на перевозку леса)</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;&lt;strong&gt;Машина с нашим QR доезжает до покупателя без разворотов на дороге.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Оформляем вашу древесину на наш объём по договору купли-продажи, заводим кубатуру в ФГИС ЛК и выдаём электронный сопроводительный документ на каждый рейс. 15 минут на документ, дальше декларация и 1-ИЛ.&lt;/p&gt;&lt;p&gt;Свой кабинет в системе не нужен, работа от 690 руб.&lt;/p&gt;&lt;p&gt;Хвойный кругляк 4 и 6 метров, диаметр от 16 см.&lt;/p&gt;&lt;p&gt;Тисульский район, Кемеровская область.&lt;/p&gt;&lt;p&gt;Напишите маршрут и объём.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_13_tisul_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_13_tisul_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_13_tisul_3.jpg</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>В сообщениях</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>Тисуль, Кемеровская обл., ул. Ленина, 53</t>
+        </is>
+      </c>
+      <c r="O77" t="inlineStr">
+        <is>
+          <t>ПВЗ</t>
+        </is>
+      </c>
+      <c r="P77" t="n">
+        <v>690</v>
+      </c>
+      <c r="Q77" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R77" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S77" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>Сосна</t>
+        </is>
+      </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB77" t="n">
+        <v>6000</v>
+      </c>
+      <c r="AC77" t="n">
+        <v>16</v>
+      </c>
+      <c r="AE77" t="inlineStr">
+        <is>
+          <t>orbizona-shop@yandex.ru</t>
+        </is>
+      </c>
+      <c r="AF77" t="inlineStr">
+        <is>
+          <t>ЕГАИС ЛЕС документация</t>
+        </is>
+      </c>
+      <c r="AG77" t="inlineStr">
+        <is>
+          <t>2026-10-18T12:10:00+03:00</t>
+        </is>
+      </c>
+      <c r="AJ77" t="inlineStr">
+        <is>
+          <t>2026-09-18T14:10:00+03:00</t>
+        </is>
+      </c>
+      <c r="AK77" t="inlineStr">
+        <is>
+          <t>2026-10-18T12:10:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>5906342724</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>79852671426</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>Лес кругляк сосна, склад и учёт объёма</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;&lt;strong&gt;Штабель на площадке перестанет быть проблемой: он встанет в систему как ваш законный объём.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Оформляем места складирования в ФГИС ЛК, заводим кубатуру договором купли-продажи от нашего объёма, выдаём ЭСД с QR на вывоз за 15 минут и подаём декларацию о сделке.&lt;/p&gt;&lt;p&gt;От вас адрес площадки, порода и объём, работа от 820 руб. Кабинет не нужен.&lt;/p&gt;&lt;p&gt;Сосновый кругляк 4 и 6 метров, диаметр от 18 см.&lt;/p&gt;&lt;p&gt;Нязепетровский район, Челябинская область.&lt;/p&gt;&lt;p&gt;Напишите, сколько кубов лежит.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_16_nyazepetrovsk_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_16_nyazepetrovsk_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_16_nyazepetrovsk_3.jpg</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>В сообщениях</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>Нязепетровск, Челябинская обл., ул. Свердлова, 8</t>
+        </is>
+      </c>
+      <c r="O78" t="inlineStr">
+        <is>
+          <t>ПВЗ</t>
+        </is>
+      </c>
+      <c r="P78" t="n">
+        <v>820</v>
+      </c>
+      <c r="Q78" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R78" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S78" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>Сосна</t>
+        </is>
+      </c>
+      <c r="X78" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB78" t="n">
+        <v>6000</v>
+      </c>
+      <c r="AC78" t="n">
+        <v>18</v>
+      </c>
+      <c r="AE78" t="inlineStr">
+        <is>
+          <t>orbizona-shop@yandex.ru</t>
+        </is>
+      </c>
+      <c r="AF78" t="inlineStr">
+        <is>
+          <t>ЕГАИС ЛЕС документация</t>
+        </is>
+      </c>
+      <c r="AG78" t="inlineStr">
+        <is>
+          <t>2026-10-18T14:30:00+03:00</t>
+        </is>
+      </c>
+      <c r="AJ78" t="inlineStr">
+        <is>
+          <t>2026-09-18T16:30:00+03:00</t>
+        </is>
+      </c>
+      <c r="AK78" t="inlineStr">
+        <is>
+          <t>2026-10-18T14:30:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>6811895387</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>79852671426</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>Сосна пиловочник, отчёт 1-ИЛ и ЭСД</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;&lt;strong&gt;Отчётность по лесу перестанет висеть на вас: сдадим сами и в срок.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Заводим вашу древесину в ФГИС ЛК договором купли-продажи от нашего объёма, выписываем ЭСД с QR на каждый рейс, подаём декларацию о сделке, закрываем отчёт 1-ИЛ и оформляем места складирования.&lt;/p&gt;&lt;p&gt;Кабинет и электронная подпись вам не нужны, от 1250 руб.&lt;/p&gt;&lt;p&gt;Сосновый пиловочник 4 и 6 метров, диаметр от 18 см.&lt;/p&gt;&lt;p&gt;Заринский район, Алтайский край.&lt;/p&gt;&lt;p&gt;Напишите, за какой период нужен отчёт.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_12_zarinsk_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_12_zarinsk_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_12_zarinsk_3.jpg</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>В сообщениях</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>Заринск, Алтайский край, ул. Ленина, 2</t>
+        </is>
+      </c>
+      <c r="O79" t="inlineStr">
+        <is>
+          <t>ПВЗ</t>
+        </is>
+      </c>
+      <c r="P79" t="n">
+        <v>1250</v>
+      </c>
+      <c r="Q79" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R79" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S79" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>Сосна</t>
+        </is>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB79" t="n">
+        <v>6000</v>
+      </c>
+      <c r="AC79" t="n">
+        <v>18</v>
+      </c>
+      <c r="AE79" t="inlineStr">
+        <is>
+          <t>orbizona-shop@yandex.ru</t>
+        </is>
+      </c>
+      <c r="AF79" t="inlineStr">
+        <is>
+          <t>ЕГАИС ЛЕС документация</t>
+        </is>
+      </c>
+      <c r="AG79" t="inlineStr">
+        <is>
+          <t>2026-10-19T07:20:00+03:00</t>
+        </is>
+      </c>
+      <c r="AJ79" t="inlineStr">
+        <is>
+          <t>2026-09-19T09:20:00+03:00</t>
+        </is>
+      </c>
+      <c r="AK79" t="inlineStr">
+        <is>
+          <t>2026-10-19T07:20:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>2189870291</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>79852671426</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>Сосна баланс, накладная на перевозку</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;&lt;strong&gt;Отдадим водителю бумагу, по которой груз примут на комбинате без споров.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Ставим вашу древесину на учёт в ФГИС ЛК через договор купли-продажи от нашего объёма и выписываем накладную с QR на рейс за 15 минут. Декларацию о сделке и отчёт 1-ИЛ берём на себя.&lt;/p&gt;&lt;p&gt;От вас порода, объём и маршрут, от 540 руб. Электронная подпись не нужна.&lt;/p&gt;&lt;p&gt;Сосновый баланс 2 и 3 метра, диаметр от 6 см.&lt;/p&gt;&lt;p&gt;Земетчинский район, Пензенская область.&lt;/p&gt;&lt;p&gt;Напишите, куда отгружаете.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_14_zemetchino_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_14_zemetchino_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_14_zemetchino_3.jpg</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>В сообщениях</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>Земетчино, Пензенская обл., ул. Первомайская, 2</t>
+        </is>
+      </c>
+      <c r="O80" t="inlineStr">
+        <is>
+          <t>ПВЗ</t>
+        </is>
+      </c>
+      <c r="P80" t="n">
+        <v>540</v>
+      </c>
+      <c r="Q80" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R80" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S80" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>Сосна</t>
+        </is>
+      </c>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB80" t="n">
+        <v>3000</v>
+      </c>
+      <c r="AC80" t="n">
+        <v>6</v>
+      </c>
+      <c r="AE80" t="inlineStr">
+        <is>
+          <t>orbizona-shop@yandex.ru</t>
+        </is>
+      </c>
+      <c r="AF80" t="inlineStr">
+        <is>
+          <t>ЕГАИС ЛЕС документация</t>
+        </is>
+      </c>
+      <c r="AG80" t="inlineStr">
+        <is>
+          <t>2026-10-19T09:40:00+03:00</t>
+        </is>
+      </c>
+      <c r="AJ80" t="inlineStr">
+        <is>
+          <t>2026-09-19T11:40:00+03:00</t>
+        </is>
+      </c>
+      <c r="AK80" t="inlineStr">
+        <is>
+          <t>2026-10-19T09:40:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>3309045417</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>79852671426</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>Баланс хвойный (декларация о сделке)</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;&lt;strong&gt;Сделку проведём так, чтобы к вам не было вопросов ни у покупателя, ни у проверяющих.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Оформляем вашу древесину через договор купли-продажи от нашего объёма, подаём декларацию о сделке в ФГИС ЛК, выписываем ЭСД с QR на каждый рейс за 15 минут и закрываем отчёт 1-ИЛ.&lt;/p&gt;&lt;p&gt;Электронная подпись вам не нужна, работа от 420 руб.&lt;/p&gt;&lt;p&gt;Хвойный баланс 2 и 3 метра, диаметр от 6 см.&lt;/p&gt;&lt;p&gt;Тоншаевский район, Нижегородская область.&lt;/p&gt;&lt;p&gt;Напишите объём и покупателя.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_18_tonshaevo_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_18_tonshaevo_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_18_tonshaevo_3.jpg</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>В сообщениях</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>Тоншаево, Нижегородская обл., ул. Ленина, 3</t>
+        </is>
+      </c>
+      <c r="O81" t="inlineStr">
+        <is>
+          <t>ПВЗ</t>
+        </is>
+      </c>
+      <c r="P81" t="n">
+        <v>420</v>
+      </c>
+      <c r="Q81" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R81" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S81" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>Сосна</t>
+        </is>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB81" t="n">
+        <v>3000</v>
+      </c>
+      <c r="AC81" t="n">
+        <v>6</v>
+      </c>
+      <c r="AE81" t="inlineStr">
+        <is>
+          <t>orbizona-shop@yandex.ru</t>
+        </is>
+      </c>
+      <c r="AF81" t="inlineStr">
+        <is>
+          <t>ЕГАИС ЛЕС документация</t>
+        </is>
+      </c>
+      <c r="AG81" t="inlineStr">
+        <is>
+          <t>2026-10-19T12:10:00+03:00</t>
+        </is>
+      </c>
+      <c r="AJ81" t="inlineStr">
+        <is>
+          <t>2026-09-19T14:10:00+03:00</t>
+        </is>
+      </c>
+      <c r="AK81" t="inlineStr">
+        <is>
+          <t>2026-10-19T12:10:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>5040251653</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>79852671426</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>Кругляк берёза (QR код на вывоз партии)</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;&lt;strong&gt;Партия уедет с площадки законно, с живым QR на каждой машине.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Заводим вашу древесину в ФГИС ЛК через договор купли-продажи от нашего объёма и выдаём документ с QR на рейс за 15 минут. Декларацию о сделке подаём сами, отчёт 1-ИЛ закрываем тоже.&lt;/p&gt;&lt;p&gt;От вас порода, объём и маршрут, от 2700 руб. Кабинет в системе не нужен.&lt;/p&gt;&lt;p&gt;Берёзовый кругляк 3 и 4 метра, диаметр от 16 см.&lt;/p&gt;&lt;p&gt;Ибресинский район, Чувашия.&lt;/p&gt;&lt;p&gt;Напишите, сколько машин готовите.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_20_ibresi_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_20_ibresi_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_20_ibresi_3.jpg</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>В сообщениях</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>Ибреси, Чувашская Республика, ул. Ленина, 26</t>
+        </is>
+      </c>
+      <c r="O82" t="inlineStr">
+        <is>
+          <t>ПВЗ</t>
+        </is>
+      </c>
+      <c r="P82" t="n">
+        <v>2700</v>
+      </c>
+      <c r="Q82" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R82" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S82" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>Берёза</t>
+        </is>
+      </c>
+      <c r="X82" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB82" t="n">
+        <v>4000</v>
+      </c>
+      <c r="AC82" t="n">
+        <v>16</v>
+      </c>
+      <c r="AE82" t="inlineStr">
+        <is>
+          <t>orbizona-shop@yandex.ru</t>
+        </is>
+      </c>
+      <c r="AF82" t="inlineStr">
+        <is>
+          <t>ЕГАИС ЛЕС документация</t>
+        </is>
+      </c>
+      <c r="AG82" t="inlineStr">
+        <is>
+          <t>2026-10-19T14:30:00+03:00</t>
+        </is>
+      </c>
+      <c r="AJ82" t="inlineStr">
+        <is>
+          <t>2026-09-19T16:30:00+03:00</t>
+        </is>
+      </c>
+      <c r="AK82" t="inlineStr">
+        <is>
+          <t>2026-10-19T14:30:00+03:00</t>
         </is>
       </c>
     </row>

--- a/egais.xlsx
+++ b/egais.xlsx
@@ -7820,7 +7820,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK82"/>
+  <dimension ref="A1:AK81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28.33" customWidth="1" min="1" max="1"/>
@@ -15250,7 +15250,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>7236924498</t>
+          <t>6686650421</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -15265,17 +15265,17 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Лес кругляк сосна, накладная на перевозку</t>
+          <t>Баланс еловый (декларация о сделке)</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;strong&gt;Поможем вывезти и продать лес законно, даже если сейчас в ФГИС ЛК по вам пусто.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;1. Разбираем, откуда у вас древесина и чего не хватает по бумагам&lt;br&gt;2. Оформляем её договором купли-продажи от нашего объёма, работа от 2500 руб&lt;br&gt;3. Выписываем накладную на перевозку с QR за 15 минут, подаём декларацию о сделке, закрываем 1-ИЛ&lt;/p&gt;&lt;p&gt;От вас данные по партии и маршруту, ни кабинета, ни подписи.&lt;/p&gt;&lt;p&gt;Сосновый и лиственничный кругляк 6 метров, диаметр от 20 см.&lt;/p&gt;&lt;p&gt;Белорецкий район, Башкортостан.&lt;/p&gt;&lt;p&gt;Напишите, куда идёт машина.&lt;/p&gt;</t>
+          <t>&lt;p&gt;&lt;strong&gt;Комбинат примет вашу партию с первого раза и не развернёт машину.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Пригодится, если:&lt;br&gt;- баланс лежит на площадке, а в системе его нет&lt;br&gt;- приёмка просит декларацию о сделке на каждую поставку&lt;br&gt;- некогда сидеть в ФГИС ЛК самому&lt;/p&gt;&lt;p&gt;Подадим декларацию о сделке, поставим кубатуру на баланс, выпишем ЭСД с QR на рейс за 15 минут, сдадим отчёт 1-ИЛ. Работа от 1200 руб, кабинет и подпись не нужны.&lt;/p&gt;&lt;p&gt;Еловый баланс 3 метра, диаметр от 6 см.&lt;/p&gt;&lt;p&gt;Игринский район, Удмуртия.&lt;/p&gt;&lt;p&gt;Напишите, на какой комбинат везёте.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-10/w1009_3_beloretsk.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/qr_1_1__image.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/tr_1__2.jpg</t>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-10/w1009_4_igra.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/reel_1__2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/inf_1_1__image2.jpg</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -15290,7 +15290,7 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>Белорецк, Белорецкий р-н, Республика Башкортостан, ул. Ленина, 71</t>
+          <t>Игра, Игринский р-н, Удмуртская Республика, ул. Советская, 30</t>
         </is>
       </c>
       <c r="O58" t="inlineStr">
@@ -15299,7 +15299,7 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>2500</v>
+        <v>1200</v>
       </c>
       <c r="Q58" t="inlineStr">
         <is>
@@ -15333,7 +15333,7 @@
       </c>
       <c r="W58" t="inlineStr">
         <is>
-          <t>Сосна</t>
+          <t>Ель</t>
         </is>
       </c>
       <c r="X58" t="inlineStr">
@@ -15342,10 +15342,10 @@
         </is>
       </c>
       <c r="AB58" t="n">
-        <v>6000</v>
+        <v>3000</v>
       </c>
       <c r="AC58" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="AE58" t="inlineStr">
         <is>
@@ -15359,24 +15359,24 @@
       </c>
       <c r="AG58" t="inlineStr">
         <is>
-          <t>2026-10-11T04:00:00+03:00</t>
+          <t>2026-10-11T06:30:00+03:00</t>
         </is>
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
-          <t>2026-09-11T06:00:00+03:00</t>
+          <t>2026-09-11T08:30:00+03:00</t>
         </is>
       </c>
       <c r="AK58" t="inlineStr">
         <is>
-          <t>2026-10-11T04:00:00+03:00</t>
+          <t>2026-10-11T06:30:00+03:00</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>6686650421</t>
+          <t>9980655614</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -15391,17 +15391,17 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Баланс еловый (декларация о сделке)</t>
+          <t>Сосна кругляк, поставим древесину на учёт</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;strong&gt;Комбинат примет вашу партию с первого раза и не развернёт машину.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Пригодится, если:&lt;br&gt;- баланс лежит на площадке, а в системе его нет&lt;br&gt;- приёмка просит декларацию о сделке на каждую поставку&lt;br&gt;- некогда сидеть в ФГИС ЛК самому&lt;/p&gt;&lt;p&gt;Подадим декларацию о сделке, поставим кубатуру на баланс, выпишем ЭСД с QR на рейс за 15 минут, сдадим отчёт 1-ИЛ. Работа от 1200 руб, кабинет и подпись не нужны.&lt;/p&gt;&lt;p&gt;Еловый баланс 3 метра, диаметр от 6 см.&lt;/p&gt;&lt;p&gt;Игринский район, Удмуртия.&lt;/p&gt;&lt;p&gt;Напишите, на какой комбинат везёте.&lt;/p&gt;</t>
+          <t>&lt;p&gt;&lt;strong&gt;Заберём лесные бумаги на себя: вы работаете в лесу и в рейсе, отчётность держим мы.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Поставим вашу древесину на учёт в ФГИС ЛК через договор купли-продажи от нашего объёма, дальше выпишем ЭСД с QR на каждый рейс за 15 минут, подадим декларацию о сделке и закроем отчёт 1-ИЛ. Работаем удалённо, от 1700 руб. Кабинет и электронная подпись вам не нужны, срок по учёту назовём после разбора ситуации.&lt;/p&gt;&lt;p&gt;Сосновый кругляк 4 и 6 метров, диаметр от 18 см.&lt;/p&gt;&lt;p&gt;Максатихинский район, Тверская область.&lt;/p&gt;&lt;p&gt;Напишите, сколько машин в неделю.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-10/w1009_4_igra.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/reel_1__2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/inf_1_1__image2.jpg</t>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-10/w1009_5_maksatiha.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/reel_2__2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/15_qr__3.jpg</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -15416,7 +15416,7 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>Игра, Игринский р-н, Удмуртская Республика, ул. Советская, 30</t>
+          <t>Максатиха, Максатихинский р-н, Тверская обл., ул. Больничная, 5</t>
         </is>
       </c>
       <c r="O59" t="inlineStr">
@@ -15425,7 +15425,7 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>1200</v>
+        <v>1700</v>
       </c>
       <c r="Q59" t="inlineStr">
         <is>
@@ -15459,7 +15459,7 @@
       </c>
       <c r="W59" t="inlineStr">
         <is>
-          <t>Ель</t>
+          <t>Сосна</t>
         </is>
       </c>
       <c r="X59" t="inlineStr">
@@ -15468,10 +15468,10 @@
         </is>
       </c>
       <c r="AB59" t="n">
-        <v>3000</v>
+        <v>6000</v>
       </c>
       <c r="AC59" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="AE59" t="inlineStr">
         <is>
@@ -15485,24 +15485,24 @@
       </c>
       <c r="AG59" t="inlineStr">
         <is>
-          <t>2026-10-11T06:30:00+03:00</t>
+          <t>2026-10-11T08:00:00+03:00</t>
         </is>
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>2026-09-11T08:30:00+03:00</t>
+          <t>2026-09-11T10:00:00+03:00</t>
         </is>
       </c>
       <c r="AK59" t="inlineStr">
         <is>
-          <t>2026-10-11T06:30:00+03:00</t>
+          <t>2026-10-11T08:00:00+03:00</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>9980655614</t>
+          <t>9642863659</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -15517,17 +15517,17 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Сосна кругляк, поставим древесину на учёт</t>
+          <t>Баланс берёзовый (документы ФГИС ЛК)</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;strong&gt;Заберём лесные бумаги на себя: вы работаете в лесу и в рейсе, отчётность держим мы.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Поставим вашу древесину на учёт в ФГИС ЛК через договор купли-продажи от нашего объёма, дальше выпишем ЭСД с QR на каждый рейс за 15 минут, подадим декларацию о сделке и закроем отчёт 1-ИЛ. Работаем удалённо, от 1700 руб. Кабинет и электронная подпись вам не нужны, срок по учёту назовём после разбора ситуации.&lt;/p&gt;&lt;p&gt;Сосновый кругляк 4 и 6 метров, диаметр от 18 см.&lt;/p&gt;&lt;p&gt;Максатихинский район, Тверская область.&lt;/p&gt;&lt;p&gt;Напишите, сколько машин в неделю.&lt;/p&gt;</t>
+          <t>&lt;p&gt;&lt;strong&gt;Ваш лес станет товаром, который можно спокойно продать и вывезти.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Что будет у вас на руках:&lt;br&gt;- документ с QR на каждый рейс, делаем за 15 минут&lt;br&gt;- проведённая декларация о сделке в ФГИС ЛК&lt;br&gt;- кубатура, которая числится за вами&lt;br&gt;- сданный отчёт 1-ИЛ и заведённые места складирования&lt;/p&gt;&lt;p&gt;От вас порода, объём и маршрут, работа от 950 руб. Заводить кабинет и покупать электронную подпись не нужно.&lt;/p&gt;&lt;p&gt;Берёзовый баланс 2 и 3 метра, диаметр от 6 см.&lt;/p&gt;&lt;p&gt;Гайнский район, Пермский край.&lt;/p&gt;&lt;p&gt;Напишите, сколько кубов набирается.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-10/w1009_5_maksatiha.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/reel_2__2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/15_qr__3.jpg</t>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-10/w1009_6_gayny.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/inf_1_1__image.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/12_qr__2.jpg</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -15542,7 +15542,7 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>Максатиха, Максатихинский р-н, Тверская обл., ул. Больничная, 5</t>
+          <t>Гайны, Гайнский р-н, Пермский край, ул. Кашина, 41</t>
         </is>
       </c>
       <c r="O60" t="inlineStr">
@@ -15551,7 +15551,7 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>1700</v>
+        <v>950</v>
       </c>
       <c r="Q60" t="inlineStr">
         <is>
@@ -15585,7 +15585,7 @@
       </c>
       <c r="W60" t="inlineStr">
         <is>
-          <t>Сосна</t>
+          <t>Берёза</t>
         </is>
       </c>
       <c r="X60" t="inlineStr">
@@ -15594,10 +15594,10 @@
         </is>
       </c>
       <c r="AB60" t="n">
-        <v>6000</v>
+        <v>3000</v>
       </c>
       <c r="AC60" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="AE60" t="inlineStr">
         <is>
@@ -15611,24 +15611,24 @@
       </c>
       <c r="AG60" t="inlineStr">
         <is>
-          <t>2026-10-11T08:00:00+03:00</t>
+          <t>2026-10-11T10:00:00+03:00</t>
         </is>
       </c>
       <c r="AJ60" t="inlineStr">
         <is>
-          <t>2026-09-11T10:00:00+03:00</t>
+          <t>2026-09-11T12:00:00+03:00</t>
         </is>
       </c>
       <c r="AK60" t="inlineStr">
         <is>
-          <t>2026-10-11T08:00:00+03:00</t>
+          <t>2026-10-11T10:00:00+03:00</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>9642863659</t>
+          <t>6060078734</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -15643,17 +15643,17 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Баланс берёзовый (документы ФГИС ЛК)</t>
+          <t>Кругляк берёза и осина, объём на баланс</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;strong&gt;Ваш лес станет товаром, который можно спокойно продать и вывезти.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Что будет у вас на руках:&lt;br&gt;- документ с QR на каждый рейс, делаем за 15 минут&lt;br&gt;- проведённая декларация о сделке в ФГИС ЛК&lt;br&gt;- кубатура, которая числится за вами&lt;br&gt;- сданный отчёт 1-ИЛ и заведённые места складирования&lt;/p&gt;&lt;p&gt;От вас порода, объём и маршрут, работа от 950 руб. Заводить кабинет и покупать электронную подпись не нужно.&lt;/p&gt;&lt;p&gt;Берёзовый баланс 2 и 3 метра, диаметр от 6 см.&lt;/p&gt;&lt;p&gt;Гайнский район, Пермский край.&lt;/p&gt;&lt;p&gt;Напишите, сколько кубов набирается.&lt;/p&gt;</t>
+          <t>&lt;p&gt;&lt;strong&gt;Даже если бумаг по лесу нет совсем, доведём партию до отгрузки.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;В день обращения разберём вашу ситуацию и оформим древесину договором купли-продажи от нашего объёма, чтобы кубатура встала на баланс.&lt;br&gt;В тот же день выпишем ЭСД с QR на рейс, на это уходит 15 минут.&lt;br&gt;Дальше подаём декларацию о сделке и закрываем отчёт 1-ИЛ, работа от 1100 руб.&lt;/p&gt;&lt;p&gt;Кабинет в системе и подпись вам не нужны.&lt;/p&gt;&lt;p&gt;Берёзовый и осиновый кругляк 3 метра, диаметр от 16 см.&lt;/p&gt;&lt;p&gt;Мамадышский район, Татарстан.&lt;/p&gt;&lt;p&gt;Напишите, куда отгружаете.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-10/w1009_6_gayny.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/inf_1_1__image.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/12_qr__2.jpg</t>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-10/w1009_7_mamadysh.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-07-29/egais_0729_15_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-07-29/egais_0729_15_3.jpg</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -15668,7 +15668,7 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>Гайны, Гайнский р-н, Пермский край, ул. Кашина, 41</t>
+          <t>Мамадыш, Мамадышский р-н, Республика Татарстан, ул. Давыдова, 21</t>
         </is>
       </c>
       <c r="O61" t="inlineStr">
@@ -15677,7 +15677,7 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>950</v>
+        <v>1100</v>
       </c>
       <c r="Q61" t="inlineStr">
         <is>
@@ -15723,7 +15723,7 @@
         <v>3000</v>
       </c>
       <c r="AC61" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="AE61" t="inlineStr">
         <is>
@@ -15737,24 +15737,24 @@
       </c>
       <c r="AG61" t="inlineStr">
         <is>
-          <t>2026-10-11T10:00:00+03:00</t>
+          <t>2026-10-11T12:00:00+03:00</t>
         </is>
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>2026-09-11T12:00:00+03:00</t>
+          <t>2026-09-11T14:00:00+03:00</t>
         </is>
       </c>
       <c r="AK61" t="inlineStr">
         <is>
-          <t>2026-10-11T10:00:00+03:00</t>
+          <t>2026-10-11T12:00:00+03:00</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>6060078734</t>
+          <t>7772328806</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -15769,17 +15769,17 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Кругляк берёза и осина, объём на баланс</t>
+          <t>Сосна пиловочник, ЭСД выдаём за 15 минут</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;strong&gt;Даже если бумаг по лесу нет совсем, доведём партию до отгрузки.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;В день обращения разберём вашу ситуацию и оформим древесину договором купли-продажи от нашего объёма, чтобы кубатура встала на баланс.&lt;br&gt;В тот же день выпишем ЭСД с QR на рейс, на это уходит 15 минут.&lt;br&gt;Дальше подаём декларацию о сделке и закрываем отчёт 1-ИЛ, работа от 1100 руб.&lt;/p&gt;&lt;p&gt;Кабинет в системе и подпись вам не нужны.&lt;/p&gt;&lt;p&gt;Берёзовый и осиновый кругляк 3 метра, диаметр от 16 см.&lt;/p&gt;&lt;p&gt;Мамадышский район, Татарстан.&lt;/p&gt;&lt;p&gt;Напишите, куда отгружаете.&lt;/p&gt;</t>
+          <t>&lt;p&gt;&lt;strong&gt;Лес у вас есть, а в системе его нет: сделаем так, чтобы партию можно было вывезти и продать.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Оформляем вашу древесину договором купли-продажи от нашего объёма, заводим кубатуру в ФГИС ЛК и выписываем ЭСД с QR на каждый рейс. На документ уходит 15 минут.&lt;/p&gt;&lt;p&gt;Кабинет в системе и электронная подпись вам не нужны, от вас только порода, объём и маршрут. Работа от 1400 руб.&lt;/p&gt;&lt;p&gt;Сосновый пиловочник 4 и 6 метров, диаметр от 18 см.&lt;/p&gt;&lt;p&gt;Южский район, Ивановская область.&lt;/p&gt;&lt;p&gt;Напишите, сколько машин в неделю.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-10/w1009_7_mamadysh.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-07-29/egais_0729_15_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-07-29/egais_0729_15_3.jpg</t>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_01_yuzha_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_01_yuzha_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_01_yuzha_3.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_01_yuzha_4.jpg</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -15794,7 +15794,7 @@
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>Мамадыш, Мамадышский р-н, Республика Татарстан, ул. Давыдова, 21</t>
+          <t>Южа, Ивановская обл., ул. Советская, 21</t>
         </is>
       </c>
       <c r="O62" t="inlineStr">
@@ -15803,7 +15803,7 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>1100</v>
+        <v>1400</v>
       </c>
       <c r="Q62" t="inlineStr">
         <is>
@@ -15837,7 +15837,7 @@
       </c>
       <c r="W62" t="inlineStr">
         <is>
-          <t>Берёза</t>
+          <t>Сосна</t>
         </is>
       </c>
       <c r="X62" t="inlineStr">
@@ -15846,10 +15846,10 @@
         </is>
       </c>
       <c r="AB62" t="n">
-        <v>3000</v>
+        <v>6000</v>
       </c>
       <c r="AC62" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AE62" t="inlineStr">
         <is>
@@ -15863,24 +15863,24 @@
       </c>
       <c r="AG62" t="inlineStr">
         <is>
-          <t>2026-10-11T12:00:00+03:00</t>
+          <t>2026-10-15T07:20:00+03:00</t>
         </is>
       </c>
       <c r="AJ62" t="inlineStr">
         <is>
-          <t>2026-09-11T14:00:00+03:00</t>
+          <t>2026-09-15T09:20:00+03:00</t>
         </is>
       </c>
       <c r="AK62" t="inlineStr">
         <is>
-          <t>2026-10-11T12:00:00+03:00</t>
+          <t>2026-10-15T07:20:00+03:00</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>7772328806</t>
+          <t>9833881860</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -15895,17 +15895,17 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Сосна пиловочник, ЭСД выдаём за 15 минут</t>
+          <t>Баланс берёзовый, накладная на перевозку</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;strong&gt;Лес у вас есть, а в системе его нет: сделаем так, чтобы партию можно было вывезти и продать.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Оформляем вашу древесину договором купли-продажи от нашего объёма, заводим кубатуру в ФГИС ЛК и выписываем ЭСД с QR на каждый рейс. На документ уходит 15 минут.&lt;/p&gt;&lt;p&gt;Кабинет в системе и электронная подпись вам не нужны, от вас только порода, объём и маршрут. Работа от 1400 руб.&lt;/p&gt;&lt;p&gt;Сосновый пиловочник 4 и 6 метров, диаметр от 18 см.&lt;/p&gt;&lt;p&gt;Южский район, Ивановская область.&lt;/p&gt;&lt;p&gt;Напишите, сколько машин в неделю.&lt;/p&gt;</t>
+          <t>&lt;p&gt;&lt;strong&gt;Довезём вашу партию до покупателя по бумагам, которые он примет без вопросов.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Что делаем:&lt;br&gt;- договор купли-продажи от нашего объёма на вашу древесину&lt;br&gt;- постановка кубатуры в ФГИС ЛК&lt;br&gt;- накладная с QR на каждую машину, 15 минут на документ&lt;br&gt;- декларация о сделке и отчёт 1-ИЛ&lt;/p&gt;&lt;p&gt;От вас порода, объём и маршрут, от 950 руб. Электронная подпись не понадобится.&lt;/p&gt;&lt;p&gt;Берёзовый баланс 2 и 3 метра, диаметр от 6 см.&lt;/p&gt;&lt;p&gt;Меленковский район, Владимирская область.&lt;/p&gt;&lt;p&gt;Напишите, сколько кубов набирается.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_01_yuzha_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_01_yuzha_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_01_yuzha_3.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_01_yuzha_4.jpg</t>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_03_melenki_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_03_melenki_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_03_melenki_3.jpg</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -15920,7 +15920,7 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>Южа, Ивановская обл., ул. Советская, 21</t>
+          <t>Меленки, Владимирская обл., ул. Первомайская, 108</t>
         </is>
       </c>
       <c r="O63" t="inlineStr">
@@ -15929,7 +15929,7 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>1400</v>
+        <v>950</v>
       </c>
       <c r="Q63" t="inlineStr">
         <is>
@@ -15963,7 +15963,7 @@
       </c>
       <c r="W63" t="inlineStr">
         <is>
-          <t>Сосна</t>
+          <t>Берёза</t>
         </is>
       </c>
       <c r="X63" t="inlineStr">
@@ -15972,10 +15972,10 @@
         </is>
       </c>
       <c r="AB63" t="n">
-        <v>6000</v>
+        <v>3000</v>
       </c>
       <c r="AC63" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="AE63" t="inlineStr">
         <is>
@@ -15989,24 +15989,24 @@
       </c>
       <c r="AG63" t="inlineStr">
         <is>
-          <t>2026-10-15T07:20:00+03:00</t>
+          <t>2026-10-15T09:40:00+03:00</t>
         </is>
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>2026-09-15T09:20:00+03:00</t>
+          <t>2026-09-15T11:40:00+03:00</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
         <is>
-          <t>2026-10-15T07:20:00+03:00</t>
+          <t>2026-10-15T09:40:00+03:00</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>9833881860</t>
+          <t>4102655995</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -16021,17 +16021,17 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Баланс берёзовый, накладная на перевозку</t>
+          <t>Пиловочник сосна, ЭСД и договор на груз</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;strong&gt;Довезём вашу партию до покупателя по бумагам, которые он примет без вопросов.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Что делаем:&lt;br&gt;- договор купли-продажи от нашего объёма на вашу древесину&lt;br&gt;- постановка кубатуры в ФГИС ЛК&lt;br&gt;- накладная с QR на каждую машину, 15 минут на документ&lt;br&gt;- декларация о сделке и отчёт 1-ИЛ&lt;/p&gt;&lt;p&gt;От вас порода, объём и маршрут, от 950 руб. Электронная подпись не понадобится.&lt;/p&gt;&lt;p&gt;Берёзовый баланс 2 и 3 метра, диаметр от 6 см.&lt;/p&gt;&lt;p&gt;Меленковский район, Владимирская область.&lt;/p&gt;&lt;p&gt;Напишите, сколько кубов набирается.&lt;/p&gt;</t>
+          <t>&lt;p&gt;&lt;strong&gt;На руках будет комплект, с которым партию принимают и на комбинате, и на посту.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Оформляем вашу древесину договором купли-продажи от нашего объёма, ставим её на учёт в ФГИС ЛК и выписываем ЭСД с QR на рейс за 15 минут. Декларацию о сделке и отчёт 1-ИЛ закрываем сами.&lt;/p&gt;&lt;p&gt;Работаем удалённо, от 2000 руб. Свой кабинет заводить не нужно.&lt;/p&gt;&lt;p&gt;Сосновый пиловочник 6 метров, диаметр от 20 см.&lt;/p&gt;&lt;p&gt;Кукморский район, Татарстан.&lt;/p&gt;&lt;p&gt;Напишите, сколько машин в неделю.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_03_melenki_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_03_melenki_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_03_melenki_3.jpg</t>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_10_kukmor_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_10_kukmor_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_10_kukmor_3.jpg</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -16046,7 +16046,7 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>Меленки, Владимирская обл., ул. Первомайская, 108</t>
+          <t>Кукмор, Республика Татарстан, ул. Ленина, 15</t>
         </is>
       </c>
       <c r="O64" t="inlineStr">
@@ -16055,7 +16055,7 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>950</v>
+        <v>2000</v>
       </c>
       <c r="Q64" t="inlineStr">
         <is>
@@ -16089,7 +16089,7 @@
       </c>
       <c r="W64" t="inlineStr">
         <is>
-          <t>Берёза</t>
+          <t>Сосна</t>
         </is>
       </c>
       <c r="X64" t="inlineStr">
@@ -16098,10 +16098,10 @@
         </is>
       </c>
       <c r="AB64" t="n">
-        <v>3000</v>
+        <v>6000</v>
       </c>
       <c r="AC64" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="AE64" t="inlineStr">
         <is>
@@ -16115,24 +16115,24 @@
       </c>
       <c r="AG64" t="inlineStr">
         <is>
-          <t>2026-10-15T09:40:00+03:00</t>
+          <t>2026-10-15T12:10:00+03:00</t>
         </is>
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
-          <t>2026-09-15T11:40:00+03:00</t>
+          <t>2026-09-15T14:10:00+03:00</t>
         </is>
       </c>
       <c r="AK64" t="inlineStr">
         <is>
-          <t>2026-10-15T09:40:00+03:00</t>
+          <t>2026-10-15T12:10:00+03:00</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>4102655995</t>
+          <t>9814763638</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -16147,17 +16147,17 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Пиловочник сосна, ЭСД и договор на груз</t>
+          <t>Пиловочник сосна от заготовителя, ЭСД</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;strong&gt;На руках будет комплект, с которым партию принимают и на комбинате, и на посту.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Оформляем вашу древесину договором купли-продажи от нашего объёма, ставим её на учёт в ФГИС ЛК и выписываем ЭСД с QR на рейс за 15 минут. Декларацию о сделке и отчёт 1-ИЛ закрываем сами.&lt;/p&gt;&lt;p&gt;Работаем удалённо, от 2000 руб. Свой кабинет заводить не нужно.&lt;/p&gt;&lt;p&gt;Сосновый пиловочник 6 метров, диаметр от 20 см.&lt;/p&gt;&lt;p&gt;Кукморский район, Татарстан.&lt;/p&gt;&lt;p&gt;Напишите, сколько машин в неделю.&lt;/p&gt;</t>
+          <t>&lt;p&gt;&lt;strong&gt;Работаем с теми, кто пилит сам: доведём вашу заготовку до бумаг, с которыми её купят.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Оформляем древесину договором купли-продажи от нашего объёма, ставим кубатуру в ФГИС ЛК и выдаём ЭСД с QR на рейс за 15 минут. Декларация о сделке и отчёт 1-ИЛ на нас.&lt;/p&gt;&lt;p&gt;Свой кабинет и подпись заводить не нужно, от 1850 руб.&lt;/p&gt;&lt;p&gt;Сосновый пиловочник 4 и 6 метров, диаметр от 18 см.&lt;/p&gt;&lt;p&gt;Караидельский район, Башкортостан.&lt;/p&gt;&lt;p&gt;Напишите, какой объём пилите в месяц.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_10_kukmor_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_10_kukmor_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_10_kukmor_3.jpg</t>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_19_karaidel_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_19_karaidel_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_19_karaidel_3.jpg</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -16172,7 +16172,7 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>Кукмор, Республика Татарстан, ул. Ленина, 15</t>
+          <t>Караидель, Республика Башкортостан, ул. Ленина, 24</t>
         </is>
       </c>
       <c r="O65" t="inlineStr">
@@ -16181,7 +16181,7 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>2000</v>
+        <v>1850</v>
       </c>
       <c r="Q65" t="inlineStr">
         <is>
@@ -16227,7 +16227,7 @@
         <v>6000</v>
       </c>
       <c r="AC65" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AE65" t="inlineStr">
         <is>
@@ -16241,24 +16241,24 @@
       </c>
       <c r="AG65" t="inlineStr">
         <is>
-          <t>2026-10-15T12:10:00+03:00</t>
+          <t>2026-10-15T14:30:00+03:00</t>
         </is>
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>2026-09-15T14:10:00+03:00</t>
+          <t>2026-09-15T16:30:00+03:00</t>
         </is>
       </c>
       <c r="AK65" t="inlineStr">
         <is>
-          <t>2026-10-15T12:10:00+03:00</t>
+          <t>2026-10-15T14:30:00+03:00</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>9814763638</t>
+          <t>4647399772</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -16273,17 +16273,17 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Пиловочник сосна от заготовителя, ЭСД</t>
+          <t>Лес кругляк ель (QR код на каждый рейс)</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;strong&gt;Работаем с теми, кто пилит сам: доведём вашу заготовку до бумаг, с которыми её купят.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Оформляем древесину договором купли-продажи от нашего объёма, ставим кубатуру в ФГИС ЛК и выдаём ЭСД с QR на рейс за 15 минут. Декларация о сделке и отчёт 1-ИЛ на нас.&lt;/p&gt;&lt;p&gt;Свой кабинет и подпись заводить не нужно, от 1850 руб.&lt;/p&gt;&lt;p&gt;Сосновый пиловочник 4 и 6 метров, диаметр от 18 см.&lt;/p&gt;&lt;p&gt;Караидельский район, Башкортостан.&lt;/p&gt;&lt;p&gt;Напишите, какой объём пилите в месяц.&lt;/p&gt;</t>
+          <t>&lt;p&gt;&lt;strong&gt;Машина уедет с площадки только с рабочим QR, и ни один пост её не развернёт.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Берём вашу древесину на свой объём по договору купли-продажи, ставим кубатуру в ФГИС ЛК и выдаём электронный сопроводительный документ на рейс. QR живой, проверяется телефоном за пару секунд.&lt;/p&gt;&lt;p&gt;Ни кабинета, ни подписи заводить не надо, работа от 850 руб.&lt;/p&gt;&lt;p&gt;Еловый кругляк 4 и 6 метров, диаметр от 14 см.&lt;/p&gt;&lt;p&gt;Пестяковский район, Ивановская область.&lt;/p&gt;&lt;p&gt;Напишите, куда идёт груз.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_19_karaidel_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_19_karaidel_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_19_karaidel_3.jpg</t>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_02_pestyaki_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_02_pestyaki_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_02_pestyaki_3.jpg</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -16298,7 +16298,7 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>Караидель, Республика Башкортостан, ул. Ленина, 24</t>
+          <t>Пестяки, Ивановская обл., ул. Ленина, 14</t>
         </is>
       </c>
       <c r="O66" t="inlineStr">
@@ -16307,7 +16307,7 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>1850</v>
+        <v>850</v>
       </c>
       <c r="Q66" t="inlineStr">
         <is>
@@ -16341,7 +16341,7 @@
       </c>
       <c r="W66" t="inlineStr">
         <is>
-          <t>Сосна</t>
+          <t>Ель</t>
         </is>
       </c>
       <c r="X66" t="inlineStr">
@@ -16353,7 +16353,7 @@
         <v>6000</v>
       </c>
       <c r="AC66" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="AE66" t="inlineStr">
         <is>
@@ -16367,24 +16367,24 @@
       </c>
       <c r="AG66" t="inlineStr">
         <is>
-          <t>2026-10-15T14:30:00+03:00</t>
+          <t>2026-10-16T07:20:00+03:00</t>
         </is>
       </c>
       <c r="AJ66" t="inlineStr">
         <is>
-          <t>2026-09-15T16:30:00+03:00</t>
+          <t>2026-09-16T09:20:00+03:00</t>
         </is>
       </c>
       <c r="AK66" t="inlineStr">
         <is>
-          <t>2026-10-15T14:30:00+03:00</t>
+          <t>2026-10-16T07:20:00+03:00</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>4647399772</t>
+          <t>5381421624</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -16399,17 +16399,17 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Лес кругляк ель (QR код на каждый рейс)</t>
+          <t>Пиловочник сосна, заведём объём в ФГИС ЛК</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;strong&gt;Машина уедет с площадки только с рабочим QR, и ни один пост её не развернёт.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Берём вашу древесину на свой объём по договору купли-продажи, ставим кубатуру в ФГИС ЛК и выдаём электронный сопроводительный документ на рейс. QR живой, проверяется телефоном за пару секунд.&lt;/p&gt;&lt;p&gt;Ни кабинета, ни подписи заводить не надо, работа от 850 руб.&lt;/p&gt;&lt;p&gt;Еловый кругляк 4 и 6 метров, диаметр от 14 см.&lt;/p&gt;&lt;p&gt;Пестяковский район, Ивановская область.&lt;/p&gt;&lt;p&gt;Напишите, куда идёт груз.&lt;/p&gt;</t>
+          <t>&lt;p&gt;&lt;strong&gt;Кубатура начнёт числиться за вами, и партию можно будет спокойно продавать.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Разбираем ситуацию в день обращения, оформляем древесину договором купли-продажи от нашего объёма и заводим её в ФГИС ЛК. Дальше выписываем ЭСД на рейсы, подаём декларацию о сделке и закрываем отчёт 1-ИЛ.&lt;/p&gt;&lt;p&gt;Свой кабинет вам не нужен, от 1700 руб. Срок по учёту называем после разбора ситуации.&lt;/p&gt;&lt;p&gt;Сосновый пиловочник 6 метров, диаметр от 20 см.&lt;/p&gt;&lt;p&gt;Судогодский район, Владимирская область.&lt;/p&gt;&lt;p&gt;Напишите, что уже есть по документам.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_02_pestyaki_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_02_pestyaki_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_02_pestyaki_3.jpg</t>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_04_sudogda_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_04_sudogda_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_04_sudogda_3.jpg</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -16424,7 +16424,7 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>Пестяки, Ивановская обл., ул. Ленина, 14</t>
+          <t>Судогда, Владимирская обл., ул. Ленина, 40</t>
         </is>
       </c>
       <c r="O67" t="inlineStr">
@@ -16433,7 +16433,7 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>850</v>
+        <v>1700</v>
       </c>
       <c r="Q67" t="inlineStr">
         <is>
@@ -16467,7 +16467,7 @@
       </c>
       <c r="W67" t="inlineStr">
         <is>
-          <t>Ель</t>
+          <t>Сосна</t>
         </is>
       </c>
       <c r="X67" t="inlineStr">
@@ -16479,7 +16479,7 @@
         <v>6000</v>
       </c>
       <c r="AC67" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="AE67" t="inlineStr">
         <is>
@@ -16493,24 +16493,24 @@
       </c>
       <c r="AG67" t="inlineStr">
         <is>
-          <t>2026-10-16T07:20:00+03:00</t>
+          <t>2026-10-16T09:40:00+03:00</t>
         </is>
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>2026-09-16T09:20:00+03:00</t>
+          <t>2026-09-16T11:40:00+03:00</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
         <is>
-          <t>2026-10-16T07:20:00+03:00</t>
+          <t>2026-10-16T09:40:00+03:00</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>5381421624</t>
+          <t>7245708048</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -16525,17 +16525,17 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Пиловочник сосна, заведём объём в ФГИС ЛК</t>
+          <t>Балансы еловые (объём встанет на баланс)</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;strong&gt;Кубатура начнёт числиться за вами, и партию можно будет спокойно продавать.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Разбираем ситуацию в день обращения, оформляем древесину договором купли-продажи от нашего объёма и заводим её в ФГИС ЛК. Дальше выписываем ЭСД на рейсы, подаём декларацию о сделке и закрываем отчёт 1-ИЛ.&lt;/p&gt;&lt;p&gt;Свой кабинет вам не нужен, от 1700 руб. Срок по учёту называем после разбора ситуации.&lt;/p&gt;&lt;p&gt;Сосновый пиловочник 6 метров, диаметр от 20 см.&lt;/p&gt;&lt;p&gt;Судогодский район, Владимирская область.&lt;/p&gt;&lt;p&gt;Напишите, что уже есть по документам.&lt;/p&gt;</t>
+          <t>&lt;p&gt;&lt;strong&gt;Кубы, которых сейчас за вами нет, появятся на балансе и станут товаром.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Работаем так: договор купли-продажи от нашего объёма на вашу древесину, постановка в ФГИС ЛК, ЭСД с QR на каждый рейс за 15 минут, декларация о сделке, отчёт 1-ИЛ и места складирования.&lt;/p&gt;&lt;p&gt;Электронная подпись и свой кабинет не понадобятся, от 900 руб.&lt;/p&gt;&lt;p&gt;Еловый баланс 2 и 3 метра, диаметр от 6 см.&lt;/p&gt;&lt;p&gt;Кезский район, Удмуртия.&lt;/p&gt;&lt;p&gt;Напишите, сколько кубов на руках.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_04_sudogda_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_04_sudogda_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_04_sudogda_3.jpg</t>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_08_kez_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_08_kez_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_08_kez_3.jpg</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -16550,7 +16550,7 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>Судогда, Владимирская обл., ул. Ленина, 40</t>
+          <t>Кез, Удмуртская Республика, ул. Кирова, 10</t>
         </is>
       </c>
       <c r="O68" t="inlineStr">
@@ -16559,7 +16559,7 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>1700</v>
+        <v>900</v>
       </c>
       <c r="Q68" t="inlineStr">
         <is>
@@ -16593,7 +16593,7 @@
       </c>
       <c r="W68" t="inlineStr">
         <is>
-          <t>Сосна</t>
+          <t>Ель</t>
         </is>
       </c>
       <c r="X68" t="inlineStr">
@@ -16602,10 +16602,10 @@
         </is>
       </c>
       <c r="AB68" t="n">
-        <v>6000</v>
+        <v>3000</v>
       </c>
       <c r="AC68" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="AE68" t="inlineStr">
         <is>
@@ -16619,24 +16619,24 @@
       </c>
       <c r="AG68" t="inlineStr">
         <is>
-          <t>2026-10-16T09:40:00+03:00</t>
+          <t>2026-10-16T12:10:00+03:00</t>
         </is>
       </c>
       <c r="AJ68" t="inlineStr">
         <is>
-          <t>2026-09-16T11:40:00+03:00</t>
+          <t>2026-09-16T14:10:00+03:00</t>
         </is>
       </c>
       <c r="AK68" t="inlineStr">
         <is>
-          <t>2026-10-16T09:40:00+03:00</t>
+          <t>2026-10-16T12:10:00+03:00</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>7245708048</t>
+          <t>3846915680</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -16651,17 +16651,17 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Балансы еловые (объём встанет на баланс)</t>
+          <t>Пиловочник ель (ЭСД на каждую машину)</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;strong&gt;Кубы, которых сейчас за вами нет, появятся на балансе и станут товаром.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Работаем так: договор купли-продажи от нашего объёма на вашу древесину, постановка в ФГИС ЛК, ЭСД с QR на каждый рейс за 15 минут, декларация о сделке, отчёт 1-ИЛ и места складирования.&lt;/p&gt;&lt;p&gt;Электронная подпись и свой кабинет не понадобятся, от 900 руб.&lt;/p&gt;&lt;p&gt;Еловый баланс 2 и 3 метра, диаметр от 6 см.&lt;/p&gt;&lt;p&gt;Кезский район, Удмуртия.&lt;/p&gt;&lt;p&gt;Напишите, сколько кубов на руках.&lt;/p&gt;</t>
+          <t>&lt;p&gt;&lt;strong&gt;Сколько машин уйдёт, столько документов и будет, задержек по бумагам не случится.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Оформляем вашу древесину договором купли-продажи от нашего объёма, заводим в ФГИС ЛК и выписываем ЭСД с QR на рейс за 15 минут. Декларация о сделке и отчёт 1-ИЛ на нас.&lt;/p&gt;&lt;p&gt;Кабинет и электронная подпись вам не понадобятся, от 1550 руб.&lt;/p&gt;&lt;p&gt;Еловый пиловочник 4 и 6 метров, диаметр от 16 см.&lt;/p&gt;&lt;p&gt;Маслянинский район, Новосибирская область.&lt;/p&gt;&lt;p&gt;Напишите, сколько рейсов в неделю.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_08_kez_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_08_kez_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_08_kez_3.jpg</t>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_15_maslyanino_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_15_maslyanino_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_15_maslyanino_3.jpg</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -16676,7 +16676,7 @@
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>Кез, Удмуртская Республика, ул. Кирова, 10</t>
+          <t>Маслянино, Новосибирская обл., ул. Коммунистическая, 3</t>
         </is>
       </c>
       <c r="O69" t="inlineStr">
@@ -16685,7 +16685,7 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>900</v>
+        <v>1550</v>
       </c>
       <c r="Q69" t="inlineStr">
         <is>
@@ -16728,10 +16728,10 @@
         </is>
       </c>
       <c r="AB69" t="n">
-        <v>3000</v>
+        <v>6000</v>
       </c>
       <c r="AC69" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="AE69" t="inlineStr">
         <is>
@@ -16745,24 +16745,24 @@
       </c>
       <c r="AG69" t="inlineStr">
         <is>
-          <t>2026-10-16T12:10:00+03:00</t>
+          <t>2026-10-16T14:30:00+03:00</t>
         </is>
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>2026-09-16T14:10:00+03:00</t>
+          <t>2026-09-16T16:30:00+03:00</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
         <is>
-          <t>2026-10-16T12:10:00+03:00</t>
+          <t>2026-10-16T14:30:00+03:00</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>3846915680</t>
+          <t>1403662800</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -16777,17 +16777,17 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Пиловочник ель (ЭСД на каждую машину)</t>
+          <t>Ель пиловочник, ЭСД на вывоз с площадки</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;strong&gt;Сколько машин уйдёт, столько документов и будет, задержек по бумагам не случится.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Оформляем вашу древесину договором купли-продажи от нашего объёма, заводим в ФГИС ЛК и выписываем ЭСД с QR на рейс за 15 минут. Декларация о сделке и отчёт 1-ИЛ на нас.&lt;/p&gt;&lt;p&gt;Кабинет и электронная подпись вам не понадобятся, от 1550 руб.&lt;/p&gt;&lt;p&gt;Еловый пиловочник 4 и 6 метров, диаметр от 16 см.&lt;/p&gt;&lt;p&gt;Маслянинский район, Новосибирская область.&lt;/p&gt;&lt;p&gt;Напишите, сколько рейсов в неделю.&lt;/p&gt;</t>
+          <t>&lt;p&gt;&lt;strong&gt;Отгрузка не встанет из-за бумаг: документ на рейс будет у водителя раньше, чем он заведёт машину.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Оформляем вашу древесину на наш объём договором купли-продажи, ставим её в ФГИС ЛК и выписываем ЭСД с QR. На документ уходит 15 минут, дальше подаём декларацию о сделке и закрываем 1-ИЛ.&lt;/p&gt;&lt;p&gt;От вас порода, объём и маршрут, от 1100 руб. Подпись и кабинет не нужны.&lt;/p&gt;&lt;p&gt;Еловый пиловочник 4 и 6 метров, диаметр от 16 см.&lt;/p&gt;&lt;p&gt;Западнодвинский округ, Тверская область.&lt;/p&gt;&lt;p&gt;Напишите, сколько машин в день.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_15_maslyanino_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_15_maslyanino_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_15_maslyanino_3.jpg</t>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_06_zapdvina_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_06_zapdvina_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_06_zapdvina_3.jpg</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -16802,7 +16802,7 @@
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>Маслянино, Новосибирская обл., ул. Коммунистическая, 3</t>
+          <t>Западная Двина, Тверская обл., ул. Кирова, 10</t>
         </is>
       </c>
       <c r="O70" t="inlineStr">
@@ -16811,7 +16811,7 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>1550</v>
+        <v>1100</v>
       </c>
       <c r="Q70" t="inlineStr">
         <is>
@@ -16871,24 +16871,24 @@
       </c>
       <c r="AG70" t="inlineStr">
         <is>
-          <t>2026-10-16T14:30:00+03:00</t>
+          <t>2026-10-17T07:20:00+03:00</t>
         </is>
       </c>
       <c r="AJ70" t="inlineStr">
         <is>
-          <t>2026-09-16T16:30:00+03:00</t>
+          <t>2026-09-17T09:20:00+03:00</t>
         </is>
       </c>
       <c r="AK70" t="inlineStr">
         <is>
-          <t>2026-10-16T14:30:00+03:00</t>
+          <t>2026-10-17T07:20:00+03:00</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>1403662800</t>
+          <t>3459366177</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -16903,17 +16903,17 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Ель пиловочник, ЭСД на вывоз с площадки</t>
+          <t>Берёза дровяная (поставим на учёт в ЛК)</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;strong&gt;Отгрузка не встанет из-за бумаг: документ на рейс будет у водителя раньше, чем он заведёт машину.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Оформляем вашу древесину на наш объём договором купли-продажи, ставим её в ФГИС ЛК и выписываем ЭСД с QR. На документ уходит 15 минут, дальше подаём декларацию о сделке и закрываем 1-ИЛ.&lt;/p&gt;&lt;p&gt;От вас порода, объём и маршрут, от 1100 руб. Подпись и кабинет не нужны.&lt;/p&gt;&lt;p&gt;Еловый пиловочник 4 и 6 метров, диаметр от 16 см.&lt;/p&gt;&lt;p&gt;Западнодвинский округ, Тверская область.&lt;/p&gt;&lt;p&gt;Напишите, сколько машин в день.&lt;/p&gt;</t>
+          <t>&lt;p&gt;&lt;strong&gt;Даже дровяная древесина должна числиться за вами, иначе её не продать и не вывезти.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Ставим вашу кубатуру в ФГИС ЛК через договор купли-продажи от нашего объёма, выписываем ЭСД с QR на рейс за 15 минут и подаём декларацию о сделке.&lt;/p&gt;&lt;p&gt;От вас порода, объём и маршрут, работа от 350 руб. Подпись и кабинет не понадобятся.&lt;/p&gt;&lt;p&gt;Берёзовые дрова и баланс 1 и 2 метра, диаметр от 6 см.&lt;/p&gt;&lt;p&gt;Балтасинский район, Татарстан.&lt;/p&gt;&lt;p&gt;Напишите, сколько кубов.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_06_zapdvina_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_06_zapdvina_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_06_zapdvina_3.jpg</t>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_11_baltasi_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_11_baltasi_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_11_baltasi_3.jpg</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -16928,7 +16928,7 @@
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>Западная Двина, Тверская обл., ул. Кирова, 10</t>
+          <t>Балтаси, Республика Татарстан, ул. Советская, 20</t>
         </is>
       </c>
       <c r="O71" t="inlineStr">
@@ -16937,7 +16937,7 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>1100</v>
+        <v>350</v>
       </c>
       <c r="Q71" t="inlineStr">
         <is>
@@ -16971,7 +16971,7 @@
       </c>
       <c r="W71" t="inlineStr">
         <is>
-          <t>Ель</t>
+          <t>Берёза</t>
         </is>
       </c>
       <c r="X71" t="inlineStr">
@@ -16980,10 +16980,10 @@
         </is>
       </c>
       <c r="AB71" t="n">
-        <v>6000</v>
+        <v>2000</v>
       </c>
       <c r="AC71" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="AE71" t="inlineStr">
         <is>
@@ -16997,24 +16997,24 @@
       </c>
       <c r="AG71" t="inlineStr">
         <is>
-          <t>2026-10-17T07:20:00+03:00</t>
+          <t>2026-10-17T09:40:00+03:00</t>
         </is>
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>2026-09-17T09:20:00+03:00</t>
+          <t>2026-09-17T11:40:00+03:00</t>
         </is>
       </c>
       <c r="AK71" t="inlineStr">
         <is>
-          <t>2026-10-17T07:20:00+03:00</t>
+          <t>2026-10-17T09:40:00+03:00</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>3459366177</t>
+          <t>1944067370</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -17029,17 +17029,17 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Берёза дровяная (поставим на учёт в ЛК)</t>
+          <t>Ель пиловочник, ЭСД за 15 минут на рейс</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;strong&gt;Даже дровяная древесина должна числиться за вами, иначе её не продать и не вывезти.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Ставим вашу кубатуру в ФГИС ЛК через договор купли-продажи от нашего объёма, выписываем ЭСД с QR на рейс за 15 минут и подаём декларацию о сделке.&lt;/p&gt;&lt;p&gt;От вас порода, объём и маршрут, работа от 350 руб. Подпись и кабинет не понадобятся.&lt;/p&gt;&lt;p&gt;Берёзовые дрова и баланс 1 и 2 метра, диаметр от 6 см.&lt;/p&gt;&lt;p&gt;Балтасинский район, Татарстан.&lt;/p&gt;&lt;p&gt;Напишите, сколько кубов.&lt;/p&gt;</t>
+          <t>&lt;p&gt;&lt;strong&gt;Документ на вывоз будет у вас в тот же день, когда вы напишете.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Берём вашу древесину на свой объём по договору купли-продажи, ставим кубатуру в ФГИС ЛК и выпускаем ЭСД с QR на рейс. Дальше подаём декларацию о сделке и закрываем отчёт 1-ИЛ.&lt;/p&gt;&lt;p&gt;Работаем удалённо по всей стране, от 2450 руб. Ни кабинета, ни подписи заводить не надо.&lt;/p&gt;&lt;p&gt;Еловый пиловочник 6 метров, диаметр от 20 см.&lt;/p&gt;&lt;p&gt;Варнавинский район, Нижегородская область.&lt;/p&gt;&lt;p&gt;Напишите, когда нужна первая машина.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_11_baltasi_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_11_baltasi_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_11_baltasi_3.jpg</t>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_17_varnavino_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_17_varnavino_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_17_varnavino_3.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_17_varnavino_4.jpg</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -17054,7 +17054,7 @@
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>Балтаси, Республика Татарстан, ул. Советская, 20</t>
+          <t>Варнавино, Нижегородская обл., ул. Советская, 1</t>
         </is>
       </c>
       <c r="O72" t="inlineStr">
@@ -17063,7 +17063,7 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>350</v>
+        <v>2450</v>
       </c>
       <c r="Q72" t="inlineStr">
         <is>
@@ -17097,7 +17097,7 @@
       </c>
       <c r="W72" t="inlineStr">
         <is>
-          <t>Берёза</t>
+          <t>Ель</t>
         </is>
       </c>
       <c r="X72" t="inlineStr">
@@ -17106,10 +17106,10 @@
         </is>
       </c>
       <c r="AB72" t="n">
-        <v>2000</v>
+        <v>6000</v>
       </c>
       <c r="AC72" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="AE72" t="inlineStr">
         <is>
@@ -17123,24 +17123,24 @@
       </c>
       <c r="AG72" t="inlineStr">
         <is>
-          <t>2026-10-17T09:40:00+03:00</t>
+          <t>2026-10-17T12:10:00+03:00</t>
         </is>
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
-          <t>2026-09-17T11:40:00+03:00</t>
+          <t>2026-09-17T14:10:00+03:00</t>
         </is>
       </c>
       <c r="AK72" t="inlineStr">
         <is>
-          <t>2026-10-17T09:40:00+03:00</t>
+          <t>2026-10-17T12:10:00+03:00</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>1944067370</t>
+          <t>4328655612</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -17155,17 +17155,17 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Ель пиловочник, ЭСД за 15 минут на рейс</t>
+          <t>Кряж берёзовый (декларация о сделке)</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;strong&gt;Документ на вывоз будет у вас в тот же день, когда вы напишете.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Берём вашу древесину на свой объём по договору купли-продажи, ставим кубатуру в ФГИС ЛК и выпускаем ЭСД с QR на рейс. Дальше подаём декларацию о сделке и закрываем отчёт 1-ИЛ.&lt;/p&gt;&lt;p&gt;Работаем удалённо по всей стране, от 2450 руб. Ни кабинета, ни подписи заводить не надо.&lt;/p&gt;&lt;p&gt;Еловый пиловочник 6 метров, диаметр от 20 см.&lt;/p&gt;&lt;p&gt;Варнавинский район, Нижегородская область.&lt;/p&gt;&lt;p&gt;Напишите, когда нужна первая машина.&lt;/p&gt;</t>
+          <t>&lt;p&gt;&lt;strong&gt;Сделка станет видимой в системе, и вы перестанете зависеть от того, проверят вас или нет.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Заводим вашу древесину через договор купли-продажи от нашего объёма, подаём декларацию о сделке в ФГИС ЛК и выпускаем ЭСД с QR на каждую отгрузку за 15 минут.&lt;/p&gt;&lt;p&gt;Работаем удалённо, кабинет и подпись заводить не нужно. Работа от 620 руб.&lt;/p&gt;&lt;p&gt;Берёзовый кряж 3 и 4 метра, диаметр от 16 см.&lt;/p&gt;&lt;p&gt;Кузоватовский район, Ульяновская область.&lt;/p&gt;&lt;p&gt;Напишите объём и породу.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_17_varnavino_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_17_varnavino_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_17_varnavino_3.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_17_varnavino_4.jpg</t>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_05_kuzovatovo_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_05_kuzovatovo_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_05_kuzovatovo_3.jpg</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -17180,7 +17180,7 @@
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>Варнавино, Нижегородская обл., ул. Советская, 1</t>
+          <t>Кузоватово, Ульяновская обл., ул. Октябрьская, 4</t>
         </is>
       </c>
       <c r="O73" t="inlineStr">
@@ -17189,7 +17189,7 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>2450</v>
+        <v>620</v>
       </c>
       <c r="Q73" t="inlineStr">
         <is>
@@ -17223,7 +17223,7 @@
       </c>
       <c r="W73" t="inlineStr">
         <is>
-          <t>Ель</t>
+          <t>Берёза</t>
         </is>
       </c>
       <c r="X73" t="inlineStr">
@@ -17232,10 +17232,10 @@
         </is>
       </c>
       <c r="AB73" t="n">
-        <v>6000</v>
+        <v>4000</v>
       </c>
       <c r="AC73" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="AE73" t="inlineStr">
         <is>
@@ -17249,24 +17249,24 @@
       </c>
       <c r="AG73" t="inlineStr">
         <is>
-          <t>2026-10-17T12:10:00+03:00</t>
+          <t>2026-10-17T14:30:00+03:00</t>
         </is>
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>2026-09-17T14:10:00+03:00</t>
+          <t>2026-09-17T16:30:00+03:00</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
         <is>
-          <t>2026-10-17T12:10:00+03:00</t>
+          <t>2026-10-17T14:30:00+03:00</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>4328655612</t>
+          <t>2873722762</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -17281,17 +17281,17 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Кряж берёзовый (декларация о сделке)</t>
+          <t>Лес кругляк сосна, документы ФГИС ЛК</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;strong&gt;Сделка станет видимой в системе, и вы перестанете зависеть от того, проверят вас или нет.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Заводим вашу древесину через договор купли-продажи от нашего объёма, подаём декларацию о сделке в ФГИС ЛК и выпускаем ЭСД с QR на каждую отгрузку за 15 минут.&lt;/p&gt;&lt;p&gt;Работаем удалённо, кабинет и подпись заводить не нужно. Работа от 620 руб.&lt;/p&gt;&lt;p&gt;Берёзовый кряж 3 и 4 метра, диаметр от 16 см.&lt;/p&gt;&lt;p&gt;Кузоватовский район, Ульяновская область.&lt;/p&gt;&lt;p&gt;Напишите объём и породу.&lt;/p&gt;</t>
+          <t>&lt;p&gt;&lt;strong&gt;Купили лес у населения или взяли по билету, а в системе пусто: доведём партию до законной отгрузки.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Оформляем происхождение древесины договором купли-продажи от нашего объёма, заводим кубатуру в ФГИС ЛК, выдаём ЭСД с QR на рейс за 15 минут, подаём декларацию и закрываем отчёт 1-ИЛ.&lt;/p&gt;&lt;p&gt;Кабинет в системе вам заводить не надо, работа от 750 руб.&lt;/p&gt;&lt;p&gt;Сосновый кругляк 4 и 6 метров, диаметр от 18 см.&lt;/p&gt;&lt;p&gt;Зубово-Полянский район, Мордовия.&lt;/p&gt;&lt;p&gt;Напишите, откуда древесина.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_05_kuzovatovo_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_05_kuzovatovo_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_05_kuzovatovo_3.jpg</t>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_07_zubovapolyana_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_07_zubovapolyana_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_07_zubovapolyana_3.jpg</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -17306,7 +17306,7 @@
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>Кузоватово, Ульяновская обл., ул. Октябрьская, 4</t>
+          <t>Зубова Поляна, Республика Мордовия, ул. Ленина, 6</t>
         </is>
       </c>
       <c r="O74" t="inlineStr">
@@ -17315,7 +17315,7 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>620</v>
+        <v>750</v>
       </c>
       <c r="Q74" t="inlineStr">
         <is>
@@ -17349,7 +17349,7 @@
       </c>
       <c r="W74" t="inlineStr">
         <is>
-          <t>Берёза</t>
+          <t>Сосна</t>
         </is>
       </c>
       <c r="X74" t="inlineStr">
@@ -17358,10 +17358,10 @@
         </is>
       </c>
       <c r="AB74" t="n">
-        <v>4000</v>
+        <v>6000</v>
       </c>
       <c r="AC74" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AE74" t="inlineStr">
         <is>
@@ -17375,24 +17375,24 @@
       </c>
       <c r="AG74" t="inlineStr">
         <is>
-          <t>2026-10-17T14:30:00+03:00</t>
+          <t>2026-10-18T07:20:00+03:00</t>
         </is>
       </c>
       <c r="AJ74" t="inlineStr">
         <is>
-          <t>2026-09-17T16:30:00+03:00</t>
+          <t>2026-09-18T09:20:00+03:00</t>
         </is>
       </c>
       <c r="AK74" t="inlineStr">
         <is>
-          <t>2026-10-17T14:30:00+03:00</t>
+          <t>2026-10-18T07:20:00+03:00</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2873722762</t>
+          <t>2564555725</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -17407,17 +17407,17 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Лес кругляк сосна, документы ФГИС ЛК</t>
+          <t>Доска обрезная сосна, QR код на вывоз</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;strong&gt;Купили лес у населения или взяли по билету, а в системе пусто: доведём партию до законной отгрузки.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Оформляем происхождение древесины договором купли-продажи от нашего объёма, заводим кубатуру в ФГИС ЛК, выдаём ЭСД с QR на рейс за 15 минут, подаём декларацию и закрываем отчёт 1-ИЛ.&lt;/p&gt;&lt;p&gt;Кабинет в системе вам заводить не надо, работа от 750 руб.&lt;/p&gt;&lt;p&gt;Сосновый кругляк 4 и 6 метров, диаметр от 18 см.&lt;/p&gt;&lt;p&gt;Зубово-Полянский район, Мордовия.&lt;/p&gt;&lt;p&gt;Напишите, откуда древесина.&lt;/p&gt;</t>
+          <t>&lt;p&gt;&lt;strong&gt;Покупатель заберёт партию спокойно: по бумагам древесина чистая и учтённая.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Заводим ваш объём в ФГИС ЛК через договор купли-продажи от нашей компании и выдаём документ с QR на каждую машину. Делаем за 15 минут, дальше декларация о сделке и отчёт 1-ИЛ на нас.&lt;/p&gt;&lt;p&gt;Кабинет и подпись не нужны, работа от 480 руб.&lt;/p&gt;&lt;p&gt;Сосновая доска и кругляк 4 и 6 метров, диаметр от 18 см.&lt;/p&gt;&lt;p&gt;Шиловский район, Рязанская область.&lt;/p&gt;&lt;p&gt;Напишите, какой объём и куда везёте.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_07_zubovapolyana_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_07_zubovapolyana_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_07_zubovapolyana_3.jpg</t>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_09_shilovo_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_09_shilovo_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_09_shilovo_3.jpg</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -17432,7 +17432,7 @@
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>Зубова Поляна, Республика Мордовия, ул. Ленина, 6</t>
+          <t>Шилово, Рязанская обл., ул. Советская, 14</t>
         </is>
       </c>
       <c r="O75" t="inlineStr">
@@ -17441,7 +17441,7 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>750</v>
+        <v>480</v>
       </c>
       <c r="Q75" t="inlineStr">
         <is>
@@ -17501,24 +17501,24 @@
       </c>
       <c r="AG75" t="inlineStr">
         <is>
-          <t>2026-10-18T07:20:00+03:00</t>
+          <t>2026-10-18T09:40:00+03:00</t>
         </is>
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>2026-09-18T09:20:00+03:00</t>
+          <t>2026-09-18T11:40:00+03:00</t>
         </is>
       </c>
       <c r="AK75" t="inlineStr">
         <is>
-          <t>2026-10-18T07:20:00+03:00</t>
+          <t>2026-10-18T09:40:00+03:00</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2564555725</t>
+          <t>3700275644</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -17533,17 +17533,17 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Доска обрезная сосна, QR код на вывоз</t>
+          <t>Лес кругляк хвоя (QR на перевозку леса)</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;strong&gt;Покупатель заберёт партию спокойно: по бумагам древесина чистая и учтённая.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Заводим ваш объём в ФГИС ЛК через договор купли-продажи от нашей компании и выдаём документ с QR на каждую машину. Делаем за 15 минут, дальше декларация о сделке и отчёт 1-ИЛ на нас.&lt;/p&gt;&lt;p&gt;Кабинет и подпись не нужны, работа от 480 руб.&lt;/p&gt;&lt;p&gt;Сосновая доска и кругляк 4 и 6 метров, диаметр от 18 см.&lt;/p&gt;&lt;p&gt;Шиловский район, Рязанская область.&lt;/p&gt;&lt;p&gt;Напишите, какой объём и куда везёте.&lt;/p&gt;</t>
+          <t>&lt;p&gt;&lt;strong&gt;Машина с нашим QR доезжает до покупателя без разворотов на дороге.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Оформляем вашу древесину на наш объём по договору купли-продажи, заводим кубатуру в ФГИС ЛК и выдаём электронный сопроводительный документ на каждый рейс. 15 минут на документ, дальше декларация и 1-ИЛ.&lt;/p&gt;&lt;p&gt;Свой кабинет в системе не нужен, работа от 690 руб.&lt;/p&gt;&lt;p&gt;Хвойный кругляк 4 и 6 метров, диаметр от 16 см.&lt;/p&gt;&lt;p&gt;Тисульский район, Кемеровская область.&lt;/p&gt;&lt;p&gt;Напишите маршрут и объём.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_09_shilovo_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_09_shilovo_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_09_shilovo_3.jpg</t>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_13_tisul_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_13_tisul_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_13_tisul_3.jpg</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -17558,7 +17558,7 @@
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>Шилово, Рязанская обл., ул. Советская, 14</t>
+          <t>Тисуль, Кемеровская обл., ул. Ленина, 53</t>
         </is>
       </c>
       <c r="O76" t="inlineStr">
@@ -17567,7 +17567,7 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>480</v>
+        <v>690</v>
       </c>
       <c r="Q76" t="inlineStr">
         <is>
@@ -17613,7 +17613,7 @@
         <v>6000</v>
       </c>
       <c r="AC76" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AE76" t="inlineStr">
         <is>
@@ -17627,24 +17627,24 @@
       </c>
       <c r="AG76" t="inlineStr">
         <is>
-          <t>2026-10-18T09:40:00+03:00</t>
+          <t>2026-10-18T12:10:00+03:00</t>
         </is>
       </c>
       <c r="AJ76" t="inlineStr">
         <is>
-          <t>2026-09-18T11:40:00+03:00</t>
+          <t>2026-09-18T14:10:00+03:00</t>
         </is>
       </c>
       <c r="AK76" t="inlineStr">
         <is>
-          <t>2026-10-18T09:40:00+03:00</t>
+          <t>2026-10-18T12:10:00+03:00</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>3700275644</t>
+          <t>5906342724</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -17659,17 +17659,17 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Лес кругляк хвоя (QR на перевозку леса)</t>
+          <t>Лес кругляк сосна, склад и учёт объёма</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;strong&gt;Машина с нашим QR доезжает до покупателя без разворотов на дороге.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Оформляем вашу древесину на наш объём по договору купли-продажи, заводим кубатуру в ФГИС ЛК и выдаём электронный сопроводительный документ на каждый рейс. 15 минут на документ, дальше декларация и 1-ИЛ.&lt;/p&gt;&lt;p&gt;Свой кабинет в системе не нужен, работа от 690 руб.&lt;/p&gt;&lt;p&gt;Хвойный кругляк 4 и 6 метров, диаметр от 16 см.&lt;/p&gt;&lt;p&gt;Тисульский район, Кемеровская область.&lt;/p&gt;&lt;p&gt;Напишите маршрут и объём.&lt;/p&gt;</t>
+          <t>&lt;p&gt;&lt;strong&gt;Штабель на площадке перестанет быть проблемой: он встанет в систему как ваш законный объём.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Оформляем места складирования в ФГИС ЛК, заводим кубатуру договором купли-продажи от нашего объёма, выдаём ЭСД с QR на вывоз за 15 минут и подаём декларацию о сделке.&lt;/p&gt;&lt;p&gt;От вас адрес площадки, порода и объём, работа от 820 руб. Кабинет не нужен.&lt;/p&gt;&lt;p&gt;Сосновый кругляк 4 и 6 метров, диаметр от 18 см.&lt;/p&gt;&lt;p&gt;Нязепетровский район, Челябинская область.&lt;/p&gt;&lt;p&gt;Напишите, сколько кубов лежит.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_13_tisul_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_13_tisul_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_13_tisul_3.jpg</t>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_16_nyazepetrovsk_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_16_nyazepetrovsk_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_16_nyazepetrovsk_3.jpg</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -17684,7 +17684,7 @@
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>Тисуль, Кемеровская обл., ул. Ленина, 53</t>
+          <t>Нязепетровск, Челябинская обл., ул. Свердлова, 8</t>
         </is>
       </c>
       <c r="O77" t="inlineStr">
@@ -17693,7 +17693,7 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>690</v>
+        <v>820</v>
       </c>
       <c r="Q77" t="inlineStr">
         <is>
@@ -17739,7 +17739,7 @@
         <v>6000</v>
       </c>
       <c r="AC77" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AE77" t="inlineStr">
         <is>
@@ -17753,24 +17753,24 @@
       </c>
       <c r="AG77" t="inlineStr">
         <is>
-          <t>2026-10-18T12:10:00+03:00</t>
+          <t>2026-10-18T14:30:00+03:00</t>
         </is>
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>2026-09-18T14:10:00+03:00</t>
+          <t>2026-09-18T16:30:00+03:00</t>
         </is>
       </c>
       <c r="AK77" t="inlineStr">
         <is>
-          <t>2026-10-18T12:10:00+03:00</t>
+          <t>2026-10-18T14:30:00+03:00</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>5906342724</t>
+          <t>6811895387</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -17785,17 +17785,17 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Лес кругляк сосна, склад и учёт объёма</t>
+          <t>Сосна пиловочник, отчёт 1-ИЛ и ЭСД</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;strong&gt;Штабель на площадке перестанет быть проблемой: он встанет в систему как ваш законный объём.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Оформляем места складирования в ФГИС ЛК, заводим кубатуру договором купли-продажи от нашего объёма, выдаём ЭСД с QR на вывоз за 15 минут и подаём декларацию о сделке.&lt;/p&gt;&lt;p&gt;От вас адрес площадки, порода и объём, работа от 820 руб. Кабинет не нужен.&lt;/p&gt;&lt;p&gt;Сосновый кругляк 4 и 6 метров, диаметр от 18 см.&lt;/p&gt;&lt;p&gt;Нязепетровский район, Челябинская область.&lt;/p&gt;&lt;p&gt;Напишите, сколько кубов лежит.&lt;/p&gt;</t>
+          <t>&lt;p&gt;&lt;strong&gt;Отчётность по лесу перестанет висеть на вас: сдадим сами и в срок.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Заводим вашу древесину в ФГИС ЛК договором купли-продажи от нашего объёма, выписываем ЭСД с QR на каждый рейс, подаём декларацию о сделке, закрываем отчёт 1-ИЛ и оформляем места складирования.&lt;/p&gt;&lt;p&gt;Кабинет и электронная подпись вам не нужны, от 1250 руб.&lt;/p&gt;&lt;p&gt;Сосновый пиловочник 4 и 6 метров, диаметр от 18 см.&lt;/p&gt;&lt;p&gt;Заринский район, Алтайский край.&lt;/p&gt;&lt;p&gt;Напишите, за какой период нужен отчёт.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_16_nyazepetrovsk_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_16_nyazepetrovsk_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_16_nyazepetrovsk_3.jpg</t>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_12_zarinsk_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_12_zarinsk_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_12_zarinsk_3.jpg</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -17810,7 +17810,7 @@
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>Нязепетровск, Челябинская обл., ул. Свердлова, 8</t>
+          <t>Заринск, Алтайский край, ул. Ленина, 2</t>
         </is>
       </c>
       <c r="O78" t="inlineStr">
@@ -17819,7 +17819,7 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>820</v>
+        <v>1250</v>
       </c>
       <c r="Q78" t="inlineStr">
         <is>
@@ -17879,24 +17879,24 @@
       </c>
       <c r="AG78" t="inlineStr">
         <is>
-          <t>2026-10-18T14:30:00+03:00</t>
+          <t>2026-10-19T07:20:00+03:00</t>
         </is>
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
-          <t>2026-09-18T16:30:00+03:00</t>
+          <t>2026-09-19T09:20:00+03:00</t>
         </is>
       </c>
       <c r="AK78" t="inlineStr">
         <is>
-          <t>2026-10-18T14:30:00+03:00</t>
+          <t>2026-10-19T07:20:00+03:00</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>6811895387</t>
+          <t>2189870291</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -17911,17 +17911,17 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Сосна пиловочник, отчёт 1-ИЛ и ЭСД</t>
+          <t>Сосна баланс, накладная на перевозку</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;strong&gt;Отчётность по лесу перестанет висеть на вас: сдадим сами и в срок.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Заводим вашу древесину в ФГИС ЛК договором купли-продажи от нашего объёма, выписываем ЭСД с QR на каждый рейс, подаём декларацию о сделке, закрываем отчёт 1-ИЛ и оформляем места складирования.&lt;/p&gt;&lt;p&gt;Кабинет и электронная подпись вам не нужны, от 1250 руб.&lt;/p&gt;&lt;p&gt;Сосновый пиловочник 4 и 6 метров, диаметр от 18 см.&lt;/p&gt;&lt;p&gt;Заринский район, Алтайский край.&lt;/p&gt;&lt;p&gt;Напишите, за какой период нужен отчёт.&lt;/p&gt;</t>
+          <t>&lt;p&gt;&lt;strong&gt;Отдадим водителю бумагу, по которой груз примут на комбинате без споров.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Ставим вашу древесину на учёт в ФГИС ЛК через договор купли-продажи от нашего объёма и выписываем накладную с QR на рейс за 15 минут. Декларацию о сделке и отчёт 1-ИЛ берём на себя.&lt;/p&gt;&lt;p&gt;От вас порода, объём и маршрут, от 540 руб. Электронная подпись не нужна.&lt;/p&gt;&lt;p&gt;Сосновый баланс 2 и 3 метра, диаметр от 6 см.&lt;/p&gt;&lt;p&gt;Земетчинский район, Пензенская область.&lt;/p&gt;&lt;p&gt;Напишите, куда отгружаете.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_12_zarinsk_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_12_zarinsk_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_12_zarinsk_3.jpg</t>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_14_zemetchino_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_14_zemetchino_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_14_zemetchino_3.jpg</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -17936,7 +17936,7 @@
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>Заринск, Алтайский край, ул. Ленина, 2</t>
+          <t>Земетчино, Пензенская обл., ул. Первомайская, 2</t>
         </is>
       </c>
       <c r="O79" t="inlineStr">
@@ -17945,7 +17945,7 @@
         </is>
       </c>
       <c r="P79" t="n">
-        <v>1250</v>
+        <v>540</v>
       </c>
       <c r="Q79" t="inlineStr">
         <is>
@@ -17988,10 +17988,10 @@
         </is>
       </c>
       <c r="AB79" t="n">
-        <v>6000</v>
+        <v>3000</v>
       </c>
       <c r="AC79" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="AE79" t="inlineStr">
         <is>
@@ -18005,24 +18005,24 @@
       </c>
       <c r="AG79" t="inlineStr">
         <is>
-          <t>2026-10-19T07:20:00+03:00</t>
+          <t>2026-10-19T09:40:00+03:00</t>
         </is>
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>2026-09-19T09:20:00+03:00</t>
+          <t>2026-09-19T11:40:00+03:00</t>
         </is>
       </c>
       <c r="AK79" t="inlineStr">
         <is>
-          <t>2026-10-19T07:20:00+03:00</t>
+          <t>2026-10-19T09:40:00+03:00</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2189870291</t>
+          <t>3309045417</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -18037,17 +18037,17 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Сосна баланс, накладная на перевозку</t>
+          <t>Баланс хвойный (декларация о сделке)</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;strong&gt;Отдадим водителю бумагу, по которой груз примут на комбинате без споров.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Ставим вашу древесину на учёт в ФГИС ЛК через договор купли-продажи от нашего объёма и выписываем накладную с QR на рейс за 15 минут. Декларацию о сделке и отчёт 1-ИЛ берём на себя.&lt;/p&gt;&lt;p&gt;От вас порода, объём и маршрут, от 540 руб. Электронная подпись не нужна.&lt;/p&gt;&lt;p&gt;Сосновый баланс 2 и 3 метра, диаметр от 6 см.&lt;/p&gt;&lt;p&gt;Земетчинский район, Пензенская область.&lt;/p&gt;&lt;p&gt;Напишите, куда отгружаете.&lt;/p&gt;</t>
+          <t>&lt;p&gt;&lt;strong&gt;Сделку проведём так, чтобы к вам не было вопросов ни у покупателя, ни у проверяющих.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Оформляем вашу древесину через договор купли-продажи от нашего объёма, подаём декларацию о сделке в ФГИС ЛК, выписываем ЭСД с QR на каждый рейс за 15 минут и закрываем отчёт 1-ИЛ.&lt;/p&gt;&lt;p&gt;Электронная подпись вам не нужна, работа от 420 руб.&lt;/p&gt;&lt;p&gt;Хвойный баланс 2 и 3 метра, диаметр от 6 см.&lt;/p&gt;&lt;p&gt;Тоншаевский район, Нижегородская область.&lt;/p&gt;&lt;p&gt;Напишите объём и покупателя.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_14_zemetchino_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_14_zemetchino_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_14_zemetchino_3.jpg</t>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_18_tonshaevo_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_18_tonshaevo_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_18_tonshaevo_3.jpg</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -18062,7 +18062,7 @@
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>Земетчино, Пензенская обл., ул. Первомайская, 2</t>
+          <t>Тоншаево, Нижегородская обл., ул. Ленина, 3</t>
         </is>
       </c>
       <c r="O80" t="inlineStr">
@@ -18071,7 +18071,7 @@
         </is>
       </c>
       <c r="P80" t="n">
-        <v>540</v>
+        <v>420</v>
       </c>
       <c r="Q80" t="inlineStr">
         <is>
@@ -18131,24 +18131,24 @@
       </c>
       <c r="AG80" t="inlineStr">
         <is>
-          <t>2026-10-19T09:40:00+03:00</t>
+          <t>2026-10-19T12:10:00+03:00</t>
         </is>
       </c>
       <c r="AJ80" t="inlineStr">
         <is>
-          <t>2026-09-19T11:40:00+03:00</t>
+          <t>2026-09-19T14:10:00+03:00</t>
         </is>
       </c>
       <c r="AK80" t="inlineStr">
         <is>
-          <t>2026-10-19T09:40:00+03:00</t>
+          <t>2026-10-19T12:10:00+03:00</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>3309045417</t>
+          <t>5040251653</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -18163,17 +18163,17 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Баланс хвойный (декларация о сделке)</t>
+          <t>Кругляк берёза (QR код на вывоз партии)</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;strong&gt;Сделку проведём так, чтобы к вам не было вопросов ни у покупателя, ни у проверяющих.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Оформляем вашу древесину через договор купли-продажи от нашего объёма, подаём декларацию о сделке в ФГИС ЛК, выписываем ЭСД с QR на каждый рейс за 15 минут и закрываем отчёт 1-ИЛ.&lt;/p&gt;&lt;p&gt;Электронная подпись вам не нужна, работа от 420 руб.&lt;/p&gt;&lt;p&gt;Хвойный баланс 2 и 3 метра, диаметр от 6 см.&lt;/p&gt;&lt;p&gt;Тоншаевский район, Нижегородская область.&lt;/p&gt;&lt;p&gt;Напишите объём и покупателя.&lt;/p&gt;</t>
+          <t>&lt;p&gt;&lt;strong&gt;Партия уедет с площадки законно, с живым QR на каждой машине.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Заводим вашу древесину в ФГИС ЛК через договор купли-продажи от нашего объёма и выдаём документ с QR на рейс за 15 минут. Декларацию о сделке подаём сами, отчёт 1-ИЛ закрываем тоже.&lt;/p&gt;&lt;p&gt;От вас порода, объём и маршрут, от 2700 руб. Кабинет в системе не нужен.&lt;/p&gt;&lt;p&gt;Берёзовый кругляк 3 и 4 метра, диаметр от 16 см.&lt;/p&gt;&lt;p&gt;Ибресинский район, Чувашия.&lt;/p&gt;&lt;p&gt;Напишите, сколько машин готовите.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_18_tonshaevo_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_18_tonshaevo_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_18_tonshaevo_3.jpg</t>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_20_ibresi_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_20_ibresi_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_20_ibresi_3.jpg</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -18188,7 +18188,7 @@
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>Тоншаево, Нижегородская обл., ул. Ленина, 3</t>
+          <t>Ибреси, Чувашская Республика, ул. Ленина, 26</t>
         </is>
       </c>
       <c r="O81" t="inlineStr">
@@ -18197,7 +18197,7 @@
         </is>
       </c>
       <c r="P81" t="n">
-        <v>420</v>
+        <v>2700</v>
       </c>
       <c r="Q81" t="inlineStr">
         <is>
@@ -18231,7 +18231,7 @@
       </c>
       <c r="W81" t="inlineStr">
         <is>
-          <t>Сосна</t>
+          <t>Берёза</t>
         </is>
       </c>
       <c r="X81" t="inlineStr">
@@ -18240,10 +18240,10 @@
         </is>
       </c>
       <c r="AB81" t="n">
-        <v>3000</v>
+        <v>4000</v>
       </c>
       <c r="AC81" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="AE81" t="inlineStr">
         <is>
@@ -18257,141 +18257,15 @@
       </c>
       <c r="AG81" t="inlineStr">
         <is>
-          <t>2026-10-19T12:10:00+03:00</t>
+          <t>2026-10-19T14:30:00+03:00</t>
         </is>
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>2026-09-19T14:10:00+03:00</t>
+          <t>2026-09-19T16:30:00+03:00</t>
         </is>
       </c>
       <c r="AK81" t="inlineStr">
-        <is>
-          <t>2026-10-19T12:10:00+03:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>5040251653</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>BBL</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t>79852671426</t>
-        </is>
-      </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>Кругляк берёза (QR код на вывоз партии)</t>
-        </is>
-      </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>&lt;p&gt;&lt;strong&gt;Партия уедет с площадки законно, с живым QR на каждой машине.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Заводим вашу древесину в ФГИС ЛК через договор купли-продажи от нашего объёма и выдаём документ с QR на рейс за 15 минут. Декларацию о сделке подаём сами, отчёт 1-ИЛ закрываем тоже.&lt;/p&gt;&lt;p&gt;От вас порода, объём и маршрут, от 2700 руб. Кабинет в системе не нужен.&lt;/p&gt;&lt;p&gt;Берёзовый кругляк 3 и 4 метра, диаметр от 16 см.&lt;/p&gt;&lt;p&gt;Ибресинский район, Чувашия.&lt;/p&gt;&lt;p&gt;Напишите, сколько машин готовите.&lt;/p&gt;</t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_20_ibresi_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_20_ibresi_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_20_ibresi_3.jpg</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t>В сообщениях</t>
-        </is>
-      </c>
-      <c r="J82" t="inlineStr">
-        <is>
-          <t>Ремонт и строительство</t>
-        </is>
-      </c>
-      <c r="K82" t="inlineStr">
-        <is>
-          <t>Ибреси, Чувашская Республика, ул. Ленина, 26</t>
-        </is>
-      </c>
-      <c r="O82" t="inlineStr">
-        <is>
-          <t>ПВЗ</t>
-        </is>
-      </c>
-      <c r="P82" t="n">
-        <v>2700</v>
-      </c>
-      <c r="Q82" t="inlineStr">
-        <is>
-          <t>Стройматериалы</t>
-        </is>
-      </c>
-      <c r="R82" t="inlineStr">
-        <is>
-          <t>Товар приобретен на продажу</t>
-        </is>
-      </c>
-      <c r="S82" t="inlineStr">
-        <is>
-          <t>Новое</t>
-        </is>
-      </c>
-      <c r="T82" t="inlineStr">
-        <is>
-          <t>В наличии</t>
-        </is>
-      </c>
-      <c r="U82" t="inlineStr">
-        <is>
-          <t>Пиломатериалы</t>
-        </is>
-      </c>
-      <c r="V82" t="inlineStr">
-        <is>
-          <t>Лес-кругляк</t>
-        </is>
-      </c>
-      <c r="W82" t="inlineStr">
-        <is>
-          <t>Берёза</t>
-        </is>
-      </c>
-      <c r="X82" t="inlineStr">
-        <is>
-          <t>Да</t>
-        </is>
-      </c>
-      <c r="AB82" t="n">
-        <v>4000</v>
-      </c>
-      <c r="AC82" t="n">
-        <v>16</v>
-      </c>
-      <c r="AE82" t="inlineStr">
-        <is>
-          <t>orbizona-shop@yandex.ru</t>
-        </is>
-      </c>
-      <c r="AF82" t="inlineStr">
-        <is>
-          <t>ЕГАИС ЛЕС документация</t>
-        </is>
-      </c>
-      <c r="AG82" t="inlineStr">
-        <is>
-          <t>2026-10-19T14:30:00+03:00</t>
-        </is>
-      </c>
-      <c r="AJ82" t="inlineStr">
-        <is>
-          <t>2026-09-19T16:30:00+03:00</t>
-        </is>
-      </c>
-      <c r="AK82" t="inlineStr">
         <is>
           <t>2026-10-19T14:30:00+03:00</t>
         </is>

--- a/egais.xlsx
+++ b/egais.xlsx
@@ -7820,7 +7820,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK81"/>
+  <dimension ref="A1:AK91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28.33" customWidth="1" min="1" max="1"/>
@@ -15754,7 +15754,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>7772328806</t>
+          <t>2666553242</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -15769,12 +15769,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Сосна пиловочник, ЭСД выдаём за 15 минут</t>
+          <t>Сосна пиловочник (ЭСД за 15 минут)</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;strong&gt;Лес у вас есть, а в системе его нет: сделаем так, чтобы партию можно было вывезти и продать.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Оформляем вашу древесину договором купли-продажи от нашего объёма, заводим кубатуру в ФГИС ЛК и выписываем ЭСД с QR на каждый рейс. На документ уходит 15 минут.&lt;/p&gt;&lt;p&gt;Кабинет в системе и электронная подпись вам не нужны, от вас только порода, объём и маршрут. Работа от 1400 руб.&lt;/p&gt;&lt;p&gt;Сосновый пиловочник 4 и 6 метров, диаметр от 18 см.&lt;/p&gt;&lt;p&gt;Южский район, Ивановская область.&lt;/p&gt;&lt;p&gt;Напишите, сколько машин в неделю.&lt;/p&gt;</t>
+          <t>&lt;p&gt;&lt;strong&gt;Лес во дворе лежит, а машину без QR с площадки никто не выпустит.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Оформим вашу древесину договором купли-продажи, поставим кубатуру в ФГИС ЛК и выпишем ЭСД с QR на каждый рейс.&lt;/p&gt;&lt;p&gt;Кабинет в системе и электронная подпись от вас не нужны, нужны порода, объём и маршрут. От 1400 руб, документ на машину готов за 15 минут.&lt;/p&gt;&lt;p&gt;Сосновый пиловочник 4 и 6 метров, диаметр от 18 см.&lt;/p&gt;&lt;p&gt;Южский район, Ивановская область. Напишите, сколько машин в неделю.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -15880,7 +15880,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>9833881860</t>
+          <t>5323514222</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -15895,12 +15895,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Баланс берёзовый, накладная на перевозку</t>
+          <t>Баланс берёзовый, накладная с QR на рейс</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;strong&gt;Довезём вашу партию до покупателя по бумагам, которые он примет без вопросов.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Что делаем:&lt;br&gt;- договор купли-продажи от нашего объёма на вашу древесину&lt;br&gt;- постановка кубатуры в ФГИС ЛК&lt;br&gt;- накладная с QR на каждую машину, 15 минут на документ&lt;br&gt;- декларация о сделке и отчёт 1-ИЛ&lt;/p&gt;&lt;p&gt;От вас порода, объём и маршрут, от 950 руб. Электронная подпись не понадобится.&lt;/p&gt;&lt;p&gt;Берёзовый баланс 2 и 3 метра, диаметр от 6 см.&lt;/p&gt;&lt;p&gt;Меленковский район, Владимирская область.&lt;/p&gt;&lt;p&gt;Напишите, сколько кубов набирается.&lt;/p&gt;</t>
+          <t>&lt;p&gt;&lt;strong&gt;Покупатель берёт баланс, но просит бумагу на происхождение, и сделка встаёт.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Сделаем документы, с которыми партию можно спокойно продать: договор купли-продажи на древесину и накладная с QR на каждый рейс.&lt;/p&gt;&lt;p&gt;От вас порода, кубатура и маршрут, остальное наша забота. От 950 руб, ЭСД на машину выписываем за 15 минут.&lt;/p&gt;&lt;p&gt;Берёзовый баланс 2 и 3 метра, диаметр от 6 см.&lt;/p&gt;&lt;p&gt;Меленковский район, Владимирская область. Напишите объём, ответим сразу.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -16006,7 +16006,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>4102655995</t>
+          <t>5289293410</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -16026,7 +16026,7 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;strong&gt;На руках будет комплект, с которым партию принимают и на комбинате, и на посту.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Оформляем вашу древесину договором купли-продажи от нашего объёма, ставим её на учёт в ФГИС ЛК и выписываем ЭСД с QR на рейс за 15 минут. Декларацию о сделке и отчёт 1-ИЛ закрываем сами.&lt;/p&gt;&lt;p&gt;Работаем удалённо, от 2000 руб. Свой кабинет заводить не нужно.&lt;/p&gt;&lt;p&gt;Сосновый пиловочник 6 метров, диаметр от 20 см.&lt;/p&gt;&lt;p&gt;Кукморский район, Татарстан.&lt;/p&gt;&lt;p&gt;Напишите, сколько машин в неделю.&lt;/p&gt;</t>
+          <t>&lt;p&gt;&lt;strong&gt;Партия ждёт отгрузки, а вопрос с документами так и не решён.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Берём бумажную часть на себя: договор купли-продажи на древесину, кубатура в ФГИС ЛК, ЭСД с QR на каждый рейс.&lt;/p&gt;&lt;p&gt;Ни кабинета, ни электронной подписи от вас не нужно, только порода, объём и маршрут. От 2000 руб.&lt;/p&gt;&lt;p&gt;Сосновый пиловочник 6 метров, диаметр от 20 см.&lt;/p&gt;&lt;p&gt;Кукморский район, Татарстан. Напишите, какой объём отгружаете.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -16132,7 +16132,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>9814763638</t>
+          <t>5715368817</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -16152,7 +16152,7 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;strong&gt;Работаем с теми, кто пилит сам: доведём вашу заготовку до бумаг, с которыми её купят.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Оформляем древесину договором купли-продажи от нашего объёма, ставим кубатуру в ФГИС ЛК и выдаём ЭСД с QR на рейс за 15 минут. Декларация о сделке и отчёт 1-ИЛ на нас.&lt;/p&gt;&lt;p&gt;Свой кабинет и подпись заводить не нужно, от 1850 руб.&lt;/p&gt;&lt;p&gt;Сосновый пиловочник 4 и 6 метров, диаметр от 18 см.&lt;/p&gt;&lt;p&gt;Караидельский район, Башкортостан.&lt;/p&gt;&lt;p&gt;Напишите, какой объём пилите в месяц.&lt;/p&gt;</t>
+          <t>&lt;p&gt;&lt;strong&gt;Заготовили сами, а продать по-белому не получается.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Сделаем древесину законным товаром: договор купли-продажи от нашего объёма, кубатура в ФГИС ЛК, ЭСД с QR на отгрузку.&lt;/p&gt;&lt;p&gt;Всё оформление на нас, от вас порода, объём и маршрут. От 1850 руб.&lt;/p&gt;&lt;p&gt;Сосновый пиловочник 4 и 6 метров, диаметр от 18 см.&lt;/p&gt;&lt;p&gt;Караидельский район, Башкортостан. Напишите, что за лес и сколько его.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -16258,7 +16258,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>4647399772</t>
+          <t>2399797215</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -16273,17 +16273,17 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Лес кругляк ель (QR код на каждый рейс)</t>
+          <t>Сосна пиловочник, QR код на перевозку</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;strong&gt;Машина уедет с площадки только с рабочим QR, и ни один пост её не развернёт.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Берём вашу древесину на свой объём по договору купли-продажи, ставим кубатуру в ФГИС ЛК и выдаём электронный сопроводительный документ на рейс. QR живой, проверяется телефоном за пару секунд.&lt;/p&gt;&lt;p&gt;Ни кабинета, ни подписи заводить не надо, работа от 850 руб.&lt;/p&gt;&lt;p&gt;Еловый кругляк 4 и 6 метров, диаметр от 14 см.&lt;/p&gt;&lt;p&gt;Пестяковский район, Ивановская область.&lt;/p&gt;&lt;p&gt;Напишите, куда идёт груз.&lt;/p&gt;</t>
+          <t>&lt;p&gt;&lt;strong&gt;Пиловочник лежит, покупатель найден, а подтвердить происхождение нечем.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Оформим договор купли-продажи на партию, заведём кубатуру в ФГИС ЛК, выпишем ЭСД с QR на перевозку.&lt;/p&gt;&lt;p&gt;От вас порода, объём и маршрут, кабинет и подпись не нужны. От 1490 руб.&lt;/p&gt;&lt;p&gt;Сосновый пиловочник 4 и 6 метров, диаметр от 18 см.&lt;/p&gt;&lt;p&gt;Заволжский район, Ивановская область. Напишите, сколько пиловочника.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_02_pestyaki_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_02_pestyaki_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_02_pestyaki_3.jpg</t>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-20/w2009_21_zavolzhsk_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-20/w2009_21_zavolzhsk_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-20/w2009_21_zavolzhsk_3.jpg</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -16298,7 +16298,7 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>Пестяки, Ивановская обл., ул. Ленина, 14</t>
+          <t>Заволжск, Ивановская обл., ул. Мира, 15</t>
         </is>
       </c>
       <c r="O66" t="inlineStr">
@@ -16307,7 +16307,7 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>850</v>
+        <v>1490</v>
       </c>
       <c r="Q66" t="inlineStr">
         <is>
@@ -16341,7 +16341,7 @@
       </c>
       <c r="W66" t="inlineStr">
         <is>
-          <t>Ель</t>
+          <t>Сосна</t>
         </is>
       </c>
       <c r="X66" t="inlineStr">
@@ -16353,7 +16353,7 @@
         <v>6000</v>
       </c>
       <c r="AC66" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="AE66" t="inlineStr">
         <is>
@@ -16367,24 +16367,24 @@
       </c>
       <c r="AG66" t="inlineStr">
         <is>
-          <t>2026-10-16T07:20:00+03:00</t>
+          <t>2026-10-15T16:40:00+03:00</t>
         </is>
       </c>
       <c r="AJ66" t="inlineStr">
         <is>
-          <t>2026-09-16T09:20:00+03:00</t>
+          <t>2026-09-15T18:40:00+03:00</t>
         </is>
       </c>
       <c r="AK66" t="inlineStr">
         <is>
-          <t>2026-10-16T07:20:00+03:00</t>
+          <t>2026-10-15T16:40:00+03:00</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>5381421624</t>
+          <t>1987889847</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -16399,17 +16399,17 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Пиловочник сосна, заведём объём в ФГИС ЛК</t>
+          <t>Лес кругляк ель (QR код на каждый рейс)</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;strong&gt;Кубатура начнёт числиться за вами, и партию можно будет спокойно продавать.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Разбираем ситуацию в день обращения, оформляем древесину договором купли-продажи от нашего объёма и заводим её в ФГИС ЛК. Дальше выписываем ЭСД на рейсы, подаём декларацию о сделке и закрываем отчёт 1-ИЛ.&lt;/p&gt;&lt;p&gt;Свой кабинет вам не нужен, от 1700 руб. Срок по учёту называем после разбора ситуации.&lt;/p&gt;&lt;p&gt;Сосновый пиловочник 6 метров, диаметр от 20 см.&lt;/p&gt;&lt;p&gt;Судогодский район, Владимирская область.&lt;/p&gt;&lt;p&gt;Напишите, что уже есть по документам.&lt;/p&gt;</t>
+          <t>&lt;p&gt;&lt;strong&gt;Водитель на погрузке спрашивает документ на груз, а показать нечего.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Дадим на рейс электронный сопроводительный документ с QR, а на партию договор купли-продажи, по которому лес числится за вами.&lt;/p&gt;&lt;p&gt;Вам не нужен ни кабинет в ФГИС ЛК, ни подпись: скажите породу, кубатуру и куда идёт лесовоз. От 850 руб.&lt;/p&gt;&lt;p&gt;Еловый кругляк 4 и 6 метров, диаметр от 14 см.&lt;/p&gt;&lt;p&gt;Пестяковский район, Ивановская область. Напишите, когда ближайшая отгрузка.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_04_sudogda_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_04_sudogda_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_04_sudogda_3.jpg</t>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_02_pestyaki_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_02_pestyaki_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_02_pestyaki_3.jpg</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -16424,7 +16424,7 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>Судогда, Владимирская обл., ул. Ленина, 40</t>
+          <t>Пестяки, Ивановская обл., ул. Ленина, 14</t>
         </is>
       </c>
       <c r="O67" t="inlineStr">
@@ -16433,7 +16433,7 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>1700</v>
+        <v>850</v>
       </c>
       <c r="Q67" t="inlineStr">
         <is>
@@ -16467,7 +16467,7 @@
       </c>
       <c r="W67" t="inlineStr">
         <is>
-          <t>Сосна</t>
+          <t>Ель</t>
         </is>
       </c>
       <c r="X67" t="inlineStr">
@@ -16479,7 +16479,7 @@
         <v>6000</v>
       </c>
       <c r="AC67" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="AE67" t="inlineStr">
         <is>
@@ -16493,24 +16493,24 @@
       </c>
       <c r="AG67" t="inlineStr">
         <is>
-          <t>2026-10-16T09:40:00+03:00</t>
+          <t>2026-10-16T07:20:00+03:00</t>
         </is>
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>2026-09-16T11:40:00+03:00</t>
+          <t>2026-09-16T09:20:00+03:00</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
         <is>
-          <t>2026-10-16T09:40:00+03:00</t>
+          <t>2026-10-16T07:20:00+03:00</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>7245708048</t>
+          <t>3815885267</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -16525,17 +16525,17 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Балансы еловые (объём встанет на баланс)</t>
+          <t>Пиловочник сосна (документация ФГИС ЛК)</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;strong&gt;Кубы, которых сейчас за вами нет, появятся на балансе и станут товаром.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Работаем так: договор купли-продажи от нашего объёма на вашу древесину, постановка в ФГИС ЛК, ЭСД с QR на каждый рейс за 15 минут, декларация о сделке, отчёт 1-ИЛ и места складирования.&lt;/p&gt;&lt;p&gt;Электронная подпись и свой кабинет не понадобятся, от 900 руб.&lt;/p&gt;&lt;p&gt;Еловый баланс 2 и 3 метра, диаметр от 6 см.&lt;/p&gt;&lt;p&gt;Кезский район, Удмуртия.&lt;/p&gt;&lt;p&gt;Напишите, сколько кубов на руках.&lt;/p&gt;</t>
+          <t>&lt;p&gt;&lt;strong&gt;В ФГИС ЛК по вашему лесу пусто, а вывозить надо уже на этой неделе.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Заведём кубатуру в ФГИС ЛК, оформим древесину договором купли-продажи и выпишем ЭСД с QR на каждую машину.&lt;/p&gt;&lt;p&gt;Всю возню с системой берём на себя, от вас порода, объём и маршрут. От 1700 руб.&lt;/p&gt;&lt;p&gt;Сосновый пиловочник 6 метров, диаметр от 20 см.&lt;/p&gt;&lt;p&gt;Судогодский район, Владимирская область. Напишите, сколько кубов и куда везёте.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_08_kez_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_08_kez_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_08_kez_3.jpg</t>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_04_sudogda_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_04_sudogda_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_04_sudogda_3.jpg</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -16550,7 +16550,7 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>Кез, Удмуртская Республика, ул. Кирова, 10</t>
+          <t>Судогда, Владимирская обл., ул. Ленина, 40</t>
         </is>
       </c>
       <c r="O68" t="inlineStr">
@@ -16559,7 +16559,7 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>900</v>
+        <v>1700</v>
       </c>
       <c r="Q68" t="inlineStr">
         <is>
@@ -16593,7 +16593,7 @@
       </c>
       <c r="W68" t="inlineStr">
         <is>
-          <t>Ель</t>
+          <t>Сосна</t>
         </is>
       </c>
       <c r="X68" t="inlineStr">
@@ -16602,10 +16602,10 @@
         </is>
       </c>
       <c r="AB68" t="n">
-        <v>3000</v>
+        <v>6000</v>
       </c>
       <c r="AC68" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="AE68" t="inlineStr">
         <is>
@@ -16619,24 +16619,24 @@
       </c>
       <c r="AG68" t="inlineStr">
         <is>
-          <t>2026-10-16T12:10:00+03:00</t>
+          <t>2026-10-16T09:40:00+03:00</t>
         </is>
       </c>
       <c r="AJ68" t="inlineStr">
         <is>
-          <t>2026-09-16T14:10:00+03:00</t>
+          <t>2026-09-16T11:40:00+03:00</t>
         </is>
       </c>
       <c r="AK68" t="inlineStr">
         <is>
-          <t>2026-10-16T12:10:00+03:00</t>
+          <t>2026-10-16T09:40:00+03:00</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>3846915680</t>
+          <t>1375199930</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -16651,17 +16651,17 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Пиловочник ель (ЭСД на каждую машину)</t>
+          <t>Балансы еловые (учёт объёма в ФГИС ЛК)</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;strong&gt;Сколько машин уйдёт, столько документов и будет, задержек по бумагам не случится.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Оформляем вашу древесину договором купли-продажи от нашего объёма, заводим в ФГИС ЛК и выписываем ЭСД с QR на рейс за 15 минут. Декларация о сделке и отчёт 1-ИЛ на нас.&lt;/p&gt;&lt;p&gt;Кабинет и электронная подпись вам не понадобятся, от 1550 руб.&lt;/p&gt;&lt;p&gt;Еловый пиловочник 4 и 6 метров, диаметр от 16 см.&lt;/p&gt;&lt;p&gt;Маслянинский район, Новосибирская область.&lt;/p&gt;&lt;p&gt;Напишите, сколько рейсов в неделю.&lt;/p&gt;</t>
+          <t>&lt;p&gt;&lt;strong&gt;Объём есть, а числится он ни за кем, и на комбинат с таким не заедешь.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Поставим кубатуру в ФГИС ЛК за вами, оформим договор купли-продажи и дадим ЭСД с QR на отгрузку.&lt;/p&gt;&lt;p&gt;Разбираться в системе не придётся, работаем и с одной машиной, и с потоком. От 900 руб.&lt;/p&gt;&lt;p&gt;Еловый баланс 2 и 3 метра, диаметр от 6 см.&lt;/p&gt;&lt;p&gt;Кезский район, Удмуртия. Напишите, сколько кубов балансов.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_15_maslyanino_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_15_maslyanino_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_15_maslyanino_3.jpg</t>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_08_kez_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_08_kez_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_08_kez_3.jpg</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -16676,7 +16676,7 @@
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>Маслянино, Новосибирская обл., ул. Коммунистическая, 3</t>
+          <t>Кез, Удмуртская Республика, ул. Кирова, 10</t>
         </is>
       </c>
       <c r="O69" t="inlineStr">
@@ -16685,7 +16685,7 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>1550</v>
+        <v>900</v>
       </c>
       <c r="Q69" t="inlineStr">
         <is>
@@ -16728,10 +16728,10 @@
         </is>
       </c>
       <c r="AB69" t="n">
-        <v>6000</v>
+        <v>3000</v>
       </c>
       <c r="AC69" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="AE69" t="inlineStr">
         <is>
@@ -16745,24 +16745,24 @@
       </c>
       <c r="AG69" t="inlineStr">
         <is>
-          <t>2026-10-16T14:30:00+03:00</t>
+          <t>2026-10-16T12:10:00+03:00</t>
         </is>
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>2026-09-16T16:30:00+03:00</t>
+          <t>2026-09-16T14:10:00+03:00</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
         <is>
-          <t>2026-10-16T14:30:00+03:00</t>
+          <t>2026-10-16T12:10:00+03:00</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>1403662800</t>
+          <t>6850310008</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -16777,17 +16777,17 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Ель пиловочник, ЭСД на вывоз с площадки</t>
+          <t>Пиловочник ель (ЭСД на каждую машину)</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;strong&gt;Отгрузка не встанет из-за бумаг: документ на рейс будет у водителя раньше, чем он заведёт машину.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Оформляем вашу древесину на наш объём договором купли-продажи, ставим её в ФГИС ЛК и выписываем ЭСД с QR. На документ уходит 15 минут, дальше подаём декларацию о сделке и закрываем 1-ИЛ.&lt;/p&gt;&lt;p&gt;От вас порода, объём и маршрут, от 1100 руб. Подпись и кабинет не нужны.&lt;/p&gt;&lt;p&gt;Еловый пиловочник 4 и 6 метров, диаметр от 16 см.&lt;/p&gt;&lt;p&gt;Западнодвинский округ, Тверская область.&lt;/p&gt;&lt;p&gt;Напишите, сколько машин в день.&lt;/p&gt;</t>
+          <t>&lt;p&gt;&lt;strong&gt;Отгрузка срывается каждый раз, когда просят документ на груз.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Выдадим ЭСД с QR на каждую машину и оформим древесину договором купли-продажи, чтобы её приняли на весовой.&lt;/p&gt;&lt;p&gt;Работу с ФГИС ЛК берём на себя, от вас порода, кубатура и маршрут. От 1550 руб.&lt;/p&gt;&lt;p&gt;Еловый пиловочник 4 и 6 метров, диаметр от 16 см.&lt;/p&gt;&lt;p&gt;Маслянинский район, Новосибирская область. Напишите, сколько машин в неделю.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_06_zapdvina_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_06_zapdvina_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_06_zapdvina_3.jpg</t>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_15_maslyanino_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_15_maslyanino_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_15_maslyanino_3.jpg</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -16802,7 +16802,7 @@
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>Западная Двина, Тверская обл., ул. Кирова, 10</t>
+          <t>Маслянино, Новосибирская обл., ул. Коммунистическая, 3</t>
         </is>
       </c>
       <c r="O70" t="inlineStr">
@@ -16811,7 +16811,7 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>1100</v>
+        <v>1550</v>
       </c>
       <c r="Q70" t="inlineStr">
         <is>
@@ -16871,24 +16871,24 @@
       </c>
       <c r="AG70" t="inlineStr">
         <is>
-          <t>2026-10-17T07:20:00+03:00</t>
+          <t>2026-10-16T14:30:00+03:00</t>
         </is>
       </c>
       <c r="AJ70" t="inlineStr">
         <is>
-          <t>2026-09-17T09:20:00+03:00</t>
+          <t>2026-09-16T16:30:00+03:00</t>
         </is>
       </c>
       <c r="AK70" t="inlineStr">
         <is>
-          <t>2026-10-17T07:20:00+03:00</t>
+          <t>2026-10-16T14:30:00+03:00</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>3459366177</t>
+          <t>4351555607</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -16903,17 +16903,17 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Берёза дровяная (поставим на учёт в ЛК)</t>
+          <t>Лес кругляк ель (документация ФГИС)</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;strong&gt;Даже дровяная древесина должна числиться за вами, иначе её не продать и не вывезти.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Ставим вашу кубатуру в ФГИС ЛК через договор купли-продажи от нашего объёма, выписываем ЭСД с QR на рейс за 15 минут и подаём декларацию о сделке.&lt;/p&gt;&lt;p&gt;От вас порода, объём и маршрут, работа от 350 руб. Подпись и кабинет не понадобятся.&lt;/p&gt;&lt;p&gt;Берёзовые дрова и баланс 1 и 2 метра, диаметр от 6 см.&lt;/p&gt;&lt;p&gt;Балтасинский район, Татарстан.&lt;/p&gt;&lt;p&gt;Напишите, сколько кубов.&lt;/p&gt;</t>
+          <t>&lt;p&gt;&lt;strong&gt;Вся беда в бумагах: лес ваш, а доказать это нечем.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Договор купли-продажи закрепит древесину за вами, кубатура встанет в ФГИС ЛК, а на рейсы пойдёт ЭСД с QR.&lt;/p&gt;&lt;p&gt;Документами занимаемся мы целиком, вам грузить и получать деньги. От 2490 руб.&lt;/p&gt;&lt;p&gt;Еловый кругляк 4 и 6 метров, диаметр от 16 см.&lt;/p&gt;&lt;p&gt;Гороховецкий район, Владимирская область. Напишите, когда отгрузка.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_11_baltasi_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_11_baltasi_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_11_baltasi_3.jpg</t>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-20/w2009_22_gorohovets_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-20/w2009_22_gorohovets_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-20/w2009_22_gorohovets_3.jpg</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -16928,7 +16928,7 @@
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>Балтаси, Республика Татарстан, ул. Советская, 20</t>
+          <t>Гороховец, Владимирская обл., ул. Ленина, 93</t>
         </is>
       </c>
       <c r="O71" t="inlineStr">
@@ -16937,7 +16937,7 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>350</v>
+        <v>2490</v>
       </c>
       <c r="Q71" t="inlineStr">
         <is>
@@ -16971,7 +16971,7 @@
       </c>
       <c r="W71" t="inlineStr">
         <is>
-          <t>Берёза</t>
+          <t>Ель</t>
         </is>
       </c>
       <c r="X71" t="inlineStr">
@@ -16980,10 +16980,10 @@
         </is>
       </c>
       <c r="AB71" t="n">
-        <v>2000</v>
+        <v>6000</v>
       </c>
       <c r="AC71" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="AE71" t="inlineStr">
         <is>
@@ -16997,24 +16997,24 @@
       </c>
       <c r="AG71" t="inlineStr">
         <is>
-          <t>2026-10-17T09:40:00+03:00</t>
+          <t>2026-10-16T16:40:00+03:00</t>
         </is>
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>2026-09-17T11:40:00+03:00</t>
+          <t>2026-09-16T18:40:00+03:00</t>
         </is>
       </c>
       <c r="AK71" t="inlineStr">
         <is>
-          <t>2026-10-17T09:40:00+03:00</t>
+          <t>2026-10-16T16:40:00+03:00</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>1944067370</t>
+          <t>1487549445</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -17029,17 +17029,17 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Ель пиловочник, ЭСД за 15 минут на рейс</t>
+          <t>Ель пиловочник, документы на вывоз леса</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;strong&gt;Документ на вывоз будет у вас в тот же день, когда вы напишете.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Берём вашу древесину на свой объём по договору купли-продажи, ставим кубатуру в ФГИС ЛК и выпускаем ЭСД с QR на рейс. Дальше подаём декларацию о сделке и закрываем отчёт 1-ИЛ.&lt;/p&gt;&lt;p&gt;Работаем удалённо по всей стране, от 2450 руб. Ни кабинета, ни подписи заводить не надо.&lt;/p&gt;&lt;p&gt;Еловый пиловочник 6 метров, диаметр от 20 см.&lt;/p&gt;&lt;p&gt;Варнавинский район, Нижегородская область.&lt;/p&gt;&lt;p&gt;Напишите, когда нужна первая машина.&lt;/p&gt;</t>
+          <t>&lt;p&gt;&lt;strong&gt;Лесовоз загружен, а выехать с площадки нельзя, ЭСД на груз нет.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Выпишем электронный сопроводительный документ с QR на рейс и оформим договор купли-продажи, по которому древесина ваша.&lt;/p&gt;&lt;p&gt;Ни кабинета, ни подписи не потребуется, назовите породу, кубатуру и маршрут. От 1100 руб, ЭСД готов за 15 минут.&lt;/p&gt;&lt;p&gt;Еловый пиловочник 4 и 6 метров, диаметр от 16 см.&lt;/p&gt;&lt;p&gt;Западнодвинский округ, Тверская область. Напишите, когда грузите.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_17_varnavino_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_17_varnavino_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_17_varnavino_3.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_17_varnavino_4.jpg</t>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_06_zapdvina_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_06_zapdvina_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_06_zapdvina_3.jpg</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -17054,7 +17054,7 @@
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>Варнавино, Нижегородская обл., ул. Советская, 1</t>
+          <t>Западная Двина, Тверская обл., ул. Кирова, 10</t>
         </is>
       </c>
       <c r="O72" t="inlineStr">
@@ -17063,7 +17063,7 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>2450</v>
+        <v>1100</v>
       </c>
       <c r="Q72" t="inlineStr">
         <is>
@@ -17109,7 +17109,7 @@
         <v>6000</v>
       </c>
       <c r="AC72" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="AE72" t="inlineStr">
         <is>
@@ -17123,24 +17123,24 @@
       </c>
       <c r="AG72" t="inlineStr">
         <is>
-          <t>2026-10-17T12:10:00+03:00</t>
+          <t>2026-10-17T07:20:00+03:00</t>
         </is>
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
-          <t>2026-09-17T14:10:00+03:00</t>
+          <t>2026-09-17T09:20:00+03:00</t>
         </is>
       </c>
       <c r="AK72" t="inlineStr">
         <is>
-          <t>2026-10-17T12:10:00+03:00</t>
+          <t>2026-10-17T07:20:00+03:00</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>4328655612</t>
+          <t>7549099851</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -17155,17 +17155,17 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Кряж берёзовый (декларация о сделке)</t>
+          <t>Берёза дровяная (учёт в ФГИС ЛК)</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;strong&gt;Сделка станет видимой в системе, и вы перестанете зависеть от того, проверят вас или нет.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Заводим вашу древесину через договор купли-продажи от нашего объёма, подаём декларацию о сделке в ФГИС ЛК и выпускаем ЭСД с QR на каждую отгрузку за 15 минут.&lt;/p&gt;&lt;p&gt;Работаем удалённо, кабинет и подпись заводить не нужно. Работа от 620 руб.&lt;/p&gt;&lt;p&gt;Берёзовый кряж 3 и 4 метра, диаметр от 16 см.&lt;/p&gt;&lt;p&gt;Кузоватовский район, Ульяновская область.&lt;/p&gt;&lt;p&gt;Напишите объём и породу.&lt;/p&gt;</t>
+          <t>&lt;p&gt;&lt;strong&gt;Дровяная берёза лежит, а по системе её у вас как будто нет.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Оформим объём за вами в ФГИС ЛК, дадим договор купли-продажи и ЭСД с QR на вывоз.&lt;/p&gt;&lt;p&gt;Проще некуда: назвали породу и кубатуру, получили документ на машину. От 350 руб.&lt;/p&gt;&lt;p&gt;Берёзовые дрова и баланс 1 и 2 метра, диаметр от 6 см.&lt;/p&gt;&lt;p&gt;Балтасинский район, Татарстан. Напишите, сколько кубов дров.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_05_kuzovatovo_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_05_kuzovatovo_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_05_kuzovatovo_3.jpg</t>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_11_baltasi_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_11_baltasi_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_11_baltasi_3.jpg</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -17180,7 +17180,7 @@
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>Кузоватово, Ульяновская обл., ул. Октябрьская, 4</t>
+          <t>Балтаси, Республика Татарстан, ул. Советская, 20</t>
         </is>
       </c>
       <c r="O73" t="inlineStr">
@@ -17189,7 +17189,7 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>620</v>
+        <v>350</v>
       </c>
       <c r="Q73" t="inlineStr">
         <is>
@@ -17232,10 +17232,10 @@
         </is>
       </c>
       <c r="AB73" t="n">
-        <v>4000</v>
+        <v>2000</v>
       </c>
       <c r="AC73" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="AE73" t="inlineStr">
         <is>
@@ -17249,24 +17249,24 @@
       </c>
       <c r="AG73" t="inlineStr">
         <is>
-          <t>2026-10-17T14:30:00+03:00</t>
+          <t>2026-10-17T09:40:00+03:00</t>
         </is>
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>2026-09-17T16:30:00+03:00</t>
+          <t>2026-09-17T11:40:00+03:00</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
         <is>
-          <t>2026-10-17T14:30:00+03:00</t>
+          <t>2026-10-17T09:40:00+03:00</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2873722762</t>
+          <t>2571643288</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -17281,17 +17281,17 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Лес кругляк сосна, документы ФГИС ЛК</t>
+          <t>Ель пиловочник, ЭСД за 15 минут на рейс</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;strong&gt;Купили лес у населения или взяли по билету, а в системе пусто: доведём партию до законной отгрузки.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Оформляем происхождение древесины договором купли-продажи от нашего объёма, заводим кубатуру в ФГИС ЛК, выдаём ЭСД с QR на рейс за 15 минут, подаём декларацию и закрываем отчёт 1-ИЛ.&lt;/p&gt;&lt;p&gt;Кабинет в системе вам заводить не надо, работа от 750 руб.&lt;/p&gt;&lt;p&gt;Сосновый кругляк 4 и 6 метров, диаметр от 18 см.&lt;/p&gt;&lt;p&gt;Зубово-Полянский район, Мордовия.&lt;/p&gt;&lt;p&gt;Напишите, откуда древесина.&lt;/p&gt;</t>
+          <t>&lt;p&gt;&lt;strong&gt;Рейсы стоят, потому что ЭСД на груз выписать некому.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Будем выписывать ЭСД с QR за 15 минут на каждый рейс, а партию закроем договором купли-продажи.&lt;/p&gt;&lt;p&gt;Всю работу с системой ведём мы, вам остаётся грузить лесовозы. От 2450 руб.&lt;/p&gt;&lt;p&gt;Еловый пиловочник 6 метров, диаметр от 20 см.&lt;/p&gt;&lt;p&gt;Варнавинский район, Нижегородская область. Напишите, сколько рейсов в месяц.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_07_zubovapolyana_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_07_zubovapolyana_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_07_zubovapolyana_3.jpg</t>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_17_varnavino_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_17_varnavino_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_17_varnavino_3.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_17_varnavino_4.jpg</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -17306,7 +17306,7 @@
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>Зубова Поляна, Республика Мордовия, ул. Ленина, 6</t>
+          <t>Варнавино, Нижегородская обл., ул. Советская, 1</t>
         </is>
       </c>
       <c r="O74" t="inlineStr">
@@ -17315,7 +17315,7 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>750</v>
+        <v>2450</v>
       </c>
       <c r="Q74" t="inlineStr">
         <is>
@@ -17349,7 +17349,7 @@
       </c>
       <c r="W74" t="inlineStr">
         <is>
-          <t>Сосна</t>
+          <t>Ель</t>
         </is>
       </c>
       <c r="X74" t="inlineStr">
@@ -17361,7 +17361,7 @@
         <v>6000</v>
       </c>
       <c r="AC74" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AE74" t="inlineStr">
         <is>
@@ -17375,24 +17375,24 @@
       </c>
       <c r="AG74" t="inlineStr">
         <is>
-          <t>2026-10-18T07:20:00+03:00</t>
+          <t>2026-10-17T12:10:00+03:00</t>
         </is>
       </c>
       <c r="AJ74" t="inlineStr">
         <is>
-          <t>2026-09-18T09:20:00+03:00</t>
+          <t>2026-09-17T14:10:00+03:00</t>
         </is>
       </c>
       <c r="AK74" t="inlineStr">
         <is>
-          <t>2026-10-18T07:20:00+03:00</t>
+          <t>2026-10-17T12:10:00+03:00</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2564555725</t>
+          <t>9160676187</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -17407,17 +17407,17 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Доска обрезная сосна, QR код на вывоз</t>
+          <t>Кряж берёзовый (декларация о сделке)</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;strong&gt;Покупатель заберёт партию спокойно: по бумагам древесина чистая и учтённая.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Заводим ваш объём в ФГИС ЛК через договор купли-продажи от нашей компании и выдаём документ с QR на каждую машину. Делаем за 15 минут, дальше декларация о сделке и отчёт 1-ИЛ на нас.&lt;/p&gt;&lt;p&gt;Кабинет и подпись не нужны, работа от 480 руб.&lt;/p&gt;&lt;p&gt;Сосновая доска и кругляк 4 и 6 метров, диаметр от 18 см.&lt;/p&gt;&lt;p&gt;Шиловский район, Рязанская область.&lt;/p&gt;&lt;p&gt;Напишите, какой объём и куда везёте.&lt;/p&gt;</t>
+          <t>&lt;p&gt;&lt;strong&gt;Кряж заготовлен, а продать не выходит: подтвердить происхождение нечем.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Оформим партию договором купли-продажи и закроем её декларацией, а на вывоз дадим ЭСД с QR.&lt;/p&gt;&lt;p&gt;Всё просто, берём любой объём: хоть одна машина, хоть двадцать. От 620 руб.&lt;/p&gt;&lt;p&gt;Берёзовый кряж 3 и 4 метра, диаметр от 16 см.&lt;/p&gt;&lt;p&gt;Кузоватовский район, Ульяновская область. Напишите, сколько кряжа лежит.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_09_shilovo_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_09_shilovo_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_09_shilovo_3.jpg</t>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_05_kuzovatovo_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_05_kuzovatovo_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_05_kuzovatovo_3.jpg</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -17432,7 +17432,7 @@
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>Шилово, Рязанская обл., ул. Советская, 14</t>
+          <t>Кузоватово, Ульяновская обл., ул. Октябрьская, 4</t>
         </is>
       </c>
       <c r="O75" t="inlineStr">
@@ -17441,7 +17441,7 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>480</v>
+        <v>620</v>
       </c>
       <c r="Q75" t="inlineStr">
         <is>
@@ -17475,7 +17475,7 @@
       </c>
       <c r="W75" t="inlineStr">
         <is>
-          <t>Сосна</t>
+          <t>Берёза</t>
         </is>
       </c>
       <c r="X75" t="inlineStr">
@@ -17484,10 +17484,10 @@
         </is>
       </c>
       <c r="AB75" t="n">
-        <v>6000</v>
+        <v>4000</v>
       </c>
       <c r="AC75" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AE75" t="inlineStr">
         <is>
@@ -17501,24 +17501,24 @@
       </c>
       <c r="AG75" t="inlineStr">
         <is>
-          <t>2026-10-18T09:40:00+03:00</t>
+          <t>2026-10-17T14:30:00+03:00</t>
         </is>
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>2026-09-18T11:40:00+03:00</t>
+          <t>2026-09-17T16:30:00+03:00</t>
         </is>
       </c>
       <c r="AK75" t="inlineStr">
         <is>
-          <t>2026-10-18T09:40:00+03:00</t>
+          <t>2026-10-17T14:30:00+03:00</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>3700275644</t>
+          <t>8164161808</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -17533,17 +17533,17 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Лес кругляк хвоя (QR на перевозку леса)</t>
+          <t>Баланс берёзовый, QR код на каждый рейс</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;strong&gt;Машина с нашим QR доезжает до покупателя без разворотов на дороге.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Оформляем вашу древесину на наш объём по договору купли-продажи, заводим кубатуру в ФГИС ЛК и выдаём электронный сопроводительный документ на каждый рейс. 15 минут на документ, дальше декларация и 1-ИЛ.&lt;/p&gt;&lt;p&gt;Свой кабинет в системе не нужен, работа от 690 руб.&lt;/p&gt;&lt;p&gt;Хвойный кругляк 4 и 6 метров, диаметр от 16 см.&lt;/p&gt;&lt;p&gt;Тисульский район, Кемеровская область.&lt;/p&gt;&lt;p&gt;Напишите маршрут и объём.&lt;/p&gt;</t>
+          <t>&lt;p&gt;&lt;strong&gt;Баланс уходит на комбинат, а на весовую без документа не пустят.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Дадим ЭСД с QR на каждый рейс и договор купли-продажи на партию, с ними груз принимают.&lt;/p&gt;&lt;p&gt;Всё по переписке, объём любой. От 990 руб, документ на машину за 15 минут.&lt;/p&gt;&lt;p&gt;Берёзовый баланс 2 и 3 метра, диаметр от 6 см.&lt;/p&gt;&lt;p&gt;Сурский район, Ульяновская область. Напишите, сколько баланса.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_13_tisul_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_13_tisul_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_13_tisul_3.jpg</t>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-20/w2009_23_surskoe_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-20/w2009_23_surskoe_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-20/w2009_23_surskoe_3.jpg</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -17558,7 +17558,7 @@
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>Тисуль, Кемеровская обл., ул. Ленина, 53</t>
+          <t>Сурское, Ульяновская обл., ул. Советская, 35</t>
         </is>
       </c>
       <c r="O76" t="inlineStr">
@@ -17567,7 +17567,7 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>690</v>
+        <v>990</v>
       </c>
       <c r="Q76" t="inlineStr">
         <is>
@@ -17601,7 +17601,7 @@
       </c>
       <c r="W76" t="inlineStr">
         <is>
-          <t>Сосна</t>
+          <t>Берёза</t>
         </is>
       </c>
       <c r="X76" t="inlineStr">
@@ -17610,10 +17610,10 @@
         </is>
       </c>
       <c r="AB76" t="n">
-        <v>6000</v>
+        <v>3000</v>
       </c>
       <c r="AC76" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="AE76" t="inlineStr">
         <is>
@@ -17627,24 +17627,24 @@
       </c>
       <c r="AG76" t="inlineStr">
         <is>
-          <t>2026-10-18T12:10:00+03:00</t>
+          <t>2026-10-17T16:40:00+03:00</t>
         </is>
       </c>
       <c r="AJ76" t="inlineStr">
         <is>
-          <t>2026-09-18T14:10:00+03:00</t>
+          <t>2026-09-17T18:40:00+03:00</t>
         </is>
       </c>
       <c r="AK76" t="inlineStr">
         <is>
-          <t>2026-10-18T12:10:00+03:00</t>
+          <t>2026-10-17T16:40:00+03:00</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>5906342724</t>
+          <t>6290188818</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -17659,17 +17659,17 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Лес кругляк сосна, склад и учёт объёма</t>
+          <t>Лес кругляк сосна, документы ФГИС ЛК</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;strong&gt;Штабель на площадке перестанет быть проблемой: он встанет в систему как ваш законный объём.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Оформляем места складирования в ФГИС ЛК, заводим кубатуру договором купли-продажи от нашего объёма, выдаём ЭСД с QR на вывоз за 15 минут и подаём декларацию о сделке.&lt;/p&gt;&lt;p&gt;От вас адрес площадки, порода и объём, работа от 820 руб. Кабинет не нужен.&lt;/p&gt;&lt;p&gt;Сосновый кругляк 4 и 6 метров, диаметр от 18 см.&lt;/p&gt;&lt;p&gt;Нязепетровский район, Челябинская область.&lt;/p&gt;&lt;p&gt;Напишите, сколько кубов лежит.&lt;/p&gt;</t>
+          <t>&lt;p&gt;&lt;strong&gt;Купили лес у населения, а бумаг на него вам никто не дал.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Сделаем так, чтобы древесина стала законным товаром: договор купли-продажи на партию, кубатура в ФГИС ЛК, QR-код на перевозку.&lt;/p&gt;&lt;p&gt;От вас только порода и объём, дальше уже не ваша забота. От 750 руб.&lt;/p&gt;&lt;p&gt;Сосновый кругляк 4 и 6 метров, диаметр от 18 см.&lt;/p&gt;&lt;p&gt;Зубово-Полянский район, Мордовия. Напишите, сколько машин планируете.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_16_nyazepetrovsk_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_16_nyazepetrovsk_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_16_nyazepetrovsk_3.jpg</t>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_07_zubovapolyana_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_07_zubovapolyana_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_07_zubovapolyana_3.jpg</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -17684,7 +17684,7 @@
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>Нязепетровск, Челябинская обл., ул. Свердлова, 8</t>
+          <t>Зубова Поляна, Республика Мордовия, ул. Ленина, 6</t>
         </is>
       </c>
       <c r="O77" t="inlineStr">
@@ -17693,7 +17693,7 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>820</v>
+        <v>750</v>
       </c>
       <c r="Q77" t="inlineStr">
         <is>
@@ -17753,24 +17753,24 @@
       </c>
       <c r="AG77" t="inlineStr">
         <is>
-          <t>2026-10-18T14:30:00+03:00</t>
+          <t>2026-10-18T07:20:00+03:00</t>
         </is>
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>2026-09-18T16:30:00+03:00</t>
+          <t>2026-09-18T09:20:00+03:00</t>
         </is>
       </c>
       <c r="AK77" t="inlineStr">
         <is>
-          <t>2026-10-18T14:30:00+03:00</t>
+          <t>2026-10-18T07:20:00+03:00</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>6811895387</t>
+          <t>6949649199</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -17785,17 +17785,17 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Сосна пиловочник, отчёт 1-ИЛ и ЭСД</t>
+          <t>Доска обрезная сосна, QR код на вывоз</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;strong&gt;Отчётность по лесу перестанет висеть на вас: сдадим сами и в срок.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Заводим вашу древесину в ФГИС ЛК договором купли-продажи от нашего объёма, выписываем ЭСД с QR на каждый рейс, подаём декларацию о сделке, закрываем отчёт 1-ИЛ и оформляем места складирования.&lt;/p&gt;&lt;p&gt;Кабинет и электронная подпись вам не нужны, от 1250 руб.&lt;/p&gt;&lt;p&gt;Сосновый пиловочник 4 и 6 метров, диаметр от 18 см.&lt;/p&gt;&lt;p&gt;Заринский район, Алтайский край.&lt;/p&gt;&lt;p&gt;Напишите, за какой период нужен отчёт.&lt;/p&gt;</t>
+          <t>&lt;p&gt;&lt;strong&gt;Доска готова к отгрузке, а перевозчик без QR за рейс не берётся.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Дадим QR-код на перевозку и договор купли-продажи, чтобы груз приняли без лишних вопросов.&lt;/p&gt;&lt;p&gt;Заявка занимает пару минут: порода, кубатура, маршрут. Документ на рейс за 15 минут, от 480 руб.&lt;/p&gt;&lt;p&gt;Сосновая доска и кругляк 4 и 6 метров, диаметр от 18 см.&lt;/p&gt;&lt;p&gt;Шиловский район, Рязанская область. Напишите, сколько рейсов нужно закрыть.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_12_zarinsk_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_12_zarinsk_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_12_zarinsk_3.jpg</t>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_09_shilovo_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_09_shilovo_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_09_shilovo_3.jpg</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -17810,7 +17810,7 @@
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>Заринск, Алтайский край, ул. Ленина, 2</t>
+          <t>Шилово, Рязанская обл., ул. Советская, 14</t>
         </is>
       </c>
       <c r="O78" t="inlineStr">
@@ -17819,7 +17819,7 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>1250</v>
+        <v>480</v>
       </c>
       <c r="Q78" t="inlineStr">
         <is>
@@ -17879,24 +17879,24 @@
       </c>
       <c r="AG78" t="inlineStr">
         <is>
-          <t>2026-10-19T07:20:00+03:00</t>
+          <t>2026-10-18T09:40:00+03:00</t>
         </is>
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
-          <t>2026-09-19T09:20:00+03:00</t>
+          <t>2026-09-18T11:40:00+03:00</t>
         </is>
       </c>
       <c r="AK78" t="inlineStr">
         <is>
-          <t>2026-10-19T07:20:00+03:00</t>
+          <t>2026-10-18T09:40:00+03:00</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2189870291</t>
+          <t>7061487276</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -17911,17 +17911,17 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Сосна баланс, накладная на перевозку</t>
+          <t>Лес кругляк хвоя (QR на перевозку леса)</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;strong&gt;Отдадим водителю бумагу, по которой груз примут на комбинате без споров.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Ставим вашу древесину на учёт в ФГИС ЛК через договор купли-продажи от нашего объёма и выписываем накладную с QR на рейс за 15 минут. Декларацию о сделке и отчёт 1-ИЛ берём на себя.&lt;/p&gt;&lt;p&gt;От вас порода, объём и маршрут, от 540 руб. Электронная подпись не нужна.&lt;/p&gt;&lt;p&gt;Сосновый баланс 2 и 3 метра, диаметр от 6 см.&lt;/p&gt;&lt;p&gt;Земетчинский район, Пензенская область.&lt;/p&gt;&lt;p&gt;Напишите, куда отгружаете.&lt;/p&gt;</t>
+          <t>&lt;p&gt;&lt;strong&gt;Кругляк грузите, а везёте на свой страх, QR-кода на рейс нет.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Закроем рейсы электронным сопроводительным документом с QR, а партию оформим договором купли-продажи.&lt;/p&gt;&lt;p&gt;Всё делается по переписке, объём любой, хоть одна машина. От 690 руб.&lt;/p&gt;&lt;p&gt;Хвойный кругляк 4 и 6 метров, диаметр от 16 см.&lt;/p&gt;&lt;p&gt;Тисульский район, Кемеровская область. Напишите, сколько кругляка.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_14_zemetchino_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_14_zemetchino_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_14_zemetchino_3.jpg</t>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_13_tisul_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_13_tisul_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_13_tisul_3.jpg</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -17936,7 +17936,7 @@
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>Земетчино, Пензенская обл., ул. Первомайская, 2</t>
+          <t>Тисуль, Кемеровская обл., ул. Ленина, 53</t>
         </is>
       </c>
       <c r="O79" t="inlineStr">
@@ -17945,7 +17945,7 @@
         </is>
       </c>
       <c r="P79" t="n">
-        <v>540</v>
+        <v>690</v>
       </c>
       <c r="Q79" t="inlineStr">
         <is>
@@ -17988,10 +17988,10 @@
         </is>
       </c>
       <c r="AB79" t="n">
-        <v>3000</v>
+        <v>6000</v>
       </c>
       <c r="AC79" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="AE79" t="inlineStr">
         <is>
@@ -18005,24 +18005,24 @@
       </c>
       <c r="AG79" t="inlineStr">
         <is>
-          <t>2026-10-19T09:40:00+03:00</t>
+          <t>2026-10-18T12:10:00+03:00</t>
         </is>
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>2026-09-19T11:40:00+03:00</t>
+          <t>2026-09-18T14:10:00+03:00</t>
         </is>
       </c>
       <c r="AK79" t="inlineStr">
         <is>
-          <t>2026-10-19T09:40:00+03:00</t>
+          <t>2026-10-18T12:10:00+03:00</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>3309045417</t>
+          <t>3485114965</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -18037,17 +18037,17 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Баланс хвойный (декларация о сделке)</t>
+          <t>Лес кругляк сосна (места складирования)</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;strong&gt;Сделку проведём так, чтобы к вам не было вопросов ни у покупателя, ни у проверяющих.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Оформляем вашу древесину через договор купли-продажи от нашего объёма, подаём декларацию о сделке в ФГИС ЛК, выписываем ЭСД с QR на каждый рейс за 15 минут и закрываем отчёт 1-ИЛ.&lt;/p&gt;&lt;p&gt;Электронная подпись вам не нужна, работа от 420 руб.&lt;/p&gt;&lt;p&gt;Хвойный баланс 2 и 3 метра, диаметр от 6 см.&lt;/p&gt;&lt;p&gt;Тоншаевский район, Нижегородская область.&lt;/p&gt;&lt;p&gt;Напишите объём и покупателя.&lt;/p&gt;</t>
+          <t>&lt;p&gt;&lt;strong&gt;Лес складирован на площадке, а сама площадка нигде не заявлена.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Заявим место складирования, поставим кубатуру в ФГИС ЛК и дадим ЭСД с QR на вывоз.&lt;/p&gt;&lt;p&gt;Ни кабинета, ни подписи: пишете породу и объём, получаете документы. От 820 руб.&lt;/p&gt;&lt;p&gt;Сосновый кругляк 4 и 6 метров, диаметр от 18 см.&lt;/p&gt;&lt;p&gt;Нязепетровский район, Челябинская область. Напишите, где лежит лес.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_18_tonshaevo_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_18_tonshaevo_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_18_tonshaevo_3.jpg</t>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_16_nyazepetrovsk_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_16_nyazepetrovsk_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_16_nyazepetrovsk_3.jpg</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -18062,7 +18062,7 @@
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>Тоншаево, Нижегородская обл., ул. Ленина, 3</t>
+          <t>Нязепетровск, Челябинская обл., ул. Свердлова, 8</t>
         </is>
       </c>
       <c r="O80" t="inlineStr">
@@ -18071,7 +18071,7 @@
         </is>
       </c>
       <c r="P80" t="n">
-        <v>420</v>
+        <v>820</v>
       </c>
       <c r="Q80" t="inlineStr">
         <is>
@@ -18114,10 +18114,10 @@
         </is>
       </c>
       <c r="AB80" t="n">
-        <v>3000</v>
+        <v>6000</v>
       </c>
       <c r="AC80" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="AE80" t="inlineStr">
         <is>
@@ -18131,24 +18131,24 @@
       </c>
       <c r="AG80" t="inlineStr">
         <is>
-          <t>2026-10-19T12:10:00+03:00</t>
+          <t>2026-10-18T14:30:00+03:00</t>
         </is>
       </c>
       <c r="AJ80" t="inlineStr">
         <is>
-          <t>2026-09-19T14:10:00+03:00</t>
+          <t>2026-09-18T16:30:00+03:00</t>
         </is>
       </c>
       <c r="AK80" t="inlineStr">
         <is>
-          <t>2026-10-19T12:10:00+03:00</t>
+          <t>2026-10-18T14:30:00+03:00</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>5040251653</t>
+          <t>4165300953</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -18163,111 +18163,1371 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
+          <t>Ель пиловочник (QR код на вывоз леса)</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;&lt;strong&gt;Каждый рейс как лотерея, пока на груз нет электронного документа.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Каждая машина поедет с ЭСД и QR, а партия будет закрыта договором купли-продажи.&lt;/p&gt;&lt;p&gt;Систему берём на себя, от вас порода, кубатура и маршрут. От 1990 руб.&lt;/p&gt;&lt;p&gt;Еловый пиловочник 6 метров, диаметр от 20 см.&lt;/p&gt;&lt;p&gt;Торопецкий район, Тверская область. Напишите, сколько машин уходит.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-20/w2009_24_toropets_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-20/w2009_24_toropets_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-20/w2009_24_toropets_3.jpg</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>В сообщениях</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>Торопец, Тверская обл., ул. Октябрьская, 40</t>
+        </is>
+      </c>
+      <c r="O81" t="inlineStr">
+        <is>
+          <t>ПВЗ</t>
+        </is>
+      </c>
+      <c r="P81" t="n">
+        <v>1990</v>
+      </c>
+      <c r="Q81" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R81" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S81" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>Ель</t>
+        </is>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB81" t="n">
+        <v>6000</v>
+      </c>
+      <c r="AC81" t="n">
+        <v>20</v>
+      </c>
+      <c r="AE81" t="inlineStr">
+        <is>
+          <t>orbizona-shop@yandex.ru</t>
+        </is>
+      </c>
+      <c r="AF81" t="inlineStr">
+        <is>
+          <t>ЕГАИС ЛЕС документация</t>
+        </is>
+      </c>
+      <c r="AG81" t="inlineStr">
+        <is>
+          <t>2026-10-18T16:40:00+03:00</t>
+        </is>
+      </c>
+      <c r="AJ81" t="inlineStr">
+        <is>
+          <t>2026-09-18T18:40:00+03:00</t>
+        </is>
+      </c>
+      <c r="AK81" t="inlineStr">
+        <is>
+          <t>2026-10-18T16:40:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>8938051818</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>79852671426</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>Сосна пиловочник (ЭСД и отчёт 1-ИЛ)</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;&lt;strong&gt;Машину развернули на трассе, потому что предъявить было нечего.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Чтобы такое не повторялось: ЭСД с QR на каждую машину, договор купли-продажи на партию, кубатура в ФГИС ЛК.&lt;/p&gt;&lt;p&gt;От вас порода, объём и маршрут, остальное делаем мы. От 1250 руб, документ за 15 минут.&lt;/p&gt;&lt;p&gt;Сосновый пиловочник 4 и 6 метров, диаметр от 18 см.&lt;/p&gt;&lt;p&gt;Заринский район, Алтайский край. Напишите, куда идут машины.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_12_zarinsk_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_12_zarinsk_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_12_zarinsk_3.jpg</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>В сообщениях</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>Заринск, Алтайский край, ул. Ленина, 2</t>
+        </is>
+      </c>
+      <c r="O82" t="inlineStr">
+        <is>
+          <t>ПВЗ</t>
+        </is>
+      </c>
+      <c r="P82" t="n">
+        <v>1250</v>
+      </c>
+      <c r="Q82" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R82" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S82" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>Сосна</t>
+        </is>
+      </c>
+      <c r="X82" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB82" t="n">
+        <v>6000</v>
+      </c>
+      <c r="AC82" t="n">
+        <v>18</v>
+      </c>
+      <c r="AE82" t="inlineStr">
+        <is>
+          <t>orbizona-shop@yandex.ru</t>
+        </is>
+      </c>
+      <c r="AF82" t="inlineStr">
+        <is>
+          <t>ЕГАИС ЛЕС документация</t>
+        </is>
+      </c>
+      <c r="AG82" t="inlineStr">
+        <is>
+          <t>2026-10-19T07:20:00+03:00</t>
+        </is>
+      </c>
+      <c r="AJ82" t="inlineStr">
+        <is>
+          <t>2026-09-19T09:20:00+03:00</t>
+        </is>
+      </c>
+      <c r="AK82" t="inlineStr">
+        <is>
+          <t>2026-10-19T07:20:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>1621318393</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>79852671426</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>Сосна баланс, накладная на перевозку</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;&lt;strong&gt;Нужна накладная на перевозку, а вы даже не знаете, с чего начать.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Начинать никуда не надо, напишите нам: дальше документ с QR на рейс, договор купли-продажи и кубатура в ФГИС ЛК.&lt;/p&gt;&lt;p&gt;Кабинет и подпись не нужны, от вас порода, объём и маршрут. От 540 руб.&lt;/p&gt;&lt;p&gt;Сосновый баланс 2 и 3 метра, диаметр от 6 см.&lt;/p&gt;&lt;p&gt;Земетчинский район, Пензенская область. Напишите, когда первая отгрузка.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_14_zemetchino_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_14_zemetchino_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_14_zemetchino_3.jpg</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>В сообщениях</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>Земетчино, Пензенская обл., ул. Первомайская, 2</t>
+        </is>
+      </c>
+      <c r="O83" t="inlineStr">
+        <is>
+          <t>ПВЗ</t>
+        </is>
+      </c>
+      <c r="P83" t="n">
+        <v>540</v>
+      </c>
+      <c r="Q83" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R83" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S83" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>Сосна</t>
+        </is>
+      </c>
+      <c r="X83" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB83" t="n">
+        <v>3000</v>
+      </c>
+      <c r="AC83" t="n">
+        <v>6</v>
+      </c>
+      <c r="AE83" t="inlineStr">
+        <is>
+          <t>orbizona-shop@yandex.ru</t>
+        </is>
+      </c>
+      <c r="AF83" t="inlineStr">
+        <is>
+          <t>ЕГАИС ЛЕС документация</t>
+        </is>
+      </c>
+      <c r="AG83" t="inlineStr">
+        <is>
+          <t>2026-10-19T09:40:00+03:00</t>
+        </is>
+      </c>
+      <c r="AJ83" t="inlineStr">
+        <is>
+          <t>2026-09-19T11:40:00+03:00</t>
+        </is>
+      </c>
+      <c r="AK83" t="inlineStr">
+        <is>
+          <t>2026-10-19T09:40:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>5972001039</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>79852671426</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>Баланс хвойный, декларация в ФГИС ЛК</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;&lt;strong&gt;Сделка есть, декларации по ней нет, и покупатель начинает нервничать.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Оформим всё как положено: договор купли-продажи, декларация, объём в ФГИС ЛК и QR-код на перевозку.&lt;/p&gt;&lt;p&gt;Берём даже одну машину, вникать ни во что не придётся. От 420 руб.&lt;/p&gt;&lt;p&gt;Хвойный баланс 2 и 3 метра, диаметр от 6 см.&lt;/p&gt;&lt;p&gt;Тоншаевский район, Нижегородская область. Напишите породу и кубатуру.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_18_tonshaevo_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_18_tonshaevo_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_18_tonshaevo_3.jpg</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>В сообщениях</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>Тоншаево, Нижегородская обл., ул. Ленина, 3</t>
+        </is>
+      </c>
+      <c r="O84" t="inlineStr">
+        <is>
+          <t>ПВЗ</t>
+        </is>
+      </c>
+      <c r="P84" t="n">
+        <v>420</v>
+      </c>
+      <c r="Q84" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R84" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S84" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W84" t="inlineStr">
+        <is>
+          <t>Сосна</t>
+        </is>
+      </c>
+      <c r="X84" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB84" t="n">
+        <v>3000</v>
+      </c>
+      <c r="AC84" t="n">
+        <v>6</v>
+      </c>
+      <c r="AE84" t="inlineStr">
+        <is>
+          <t>orbizona-shop@yandex.ru</t>
+        </is>
+      </c>
+      <c r="AF84" t="inlineStr">
+        <is>
+          <t>ЕГАИС ЛЕС документация</t>
+        </is>
+      </c>
+      <c r="AG84" t="inlineStr">
+        <is>
+          <t>2026-10-19T12:10:00+03:00</t>
+        </is>
+      </c>
+      <c r="AJ84" t="inlineStr">
+        <is>
+          <t>2026-09-19T14:10:00+03:00</t>
+        </is>
+      </c>
+      <c r="AK84" t="inlineStr">
+        <is>
+          <t>2026-10-19T12:10:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>2946271120</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>79852671426</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
           <t>Кругляк берёза (QR код на вывоз партии)</t>
         </is>
       </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>&lt;p&gt;&lt;strong&gt;Партия уедет с площадки законно, с живым QR на каждой машине.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Заводим вашу древесину в ФГИС ЛК через договор купли-продажи от нашего объёма и выдаём документ с QR на рейс за 15 минут. Декларацию о сделке подаём сами, отчёт 1-ИЛ закрываем тоже.&lt;/p&gt;&lt;p&gt;От вас порода, объём и маршрут, от 2700 руб. Кабинет в системе не нужен.&lt;/p&gt;&lt;p&gt;Берёзовый кругляк 3 и 4 метра, диаметр от 16 см.&lt;/p&gt;&lt;p&gt;Ибресинский район, Чувашия.&lt;/p&gt;&lt;p&gt;Напишите, сколько машин готовите.&lt;/p&gt;</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr">
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;&lt;strong&gt;Берёза продана, только вывезти её без QR на машину не выйдет.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Дадим QR-код на вывоз каждого рейса и договор купли-продажи, по которому партия ваша.&lt;/p&gt;&lt;p&gt;Возиться с ФГИС ЛК не придётся, всё берём на себя. От 2700 руб, ЭСД на рейс за 15 минут.&lt;/p&gt;&lt;p&gt;Берёзовый кругляк 3 и 4 метра, диаметр от 16 см.&lt;/p&gt;&lt;p&gt;Ибресинский район, Чувашия. Напишите, какой объём вывозите.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
         <is>
           <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_20_ibresi_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_20_ibresi_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_20_ibresi_3.jpg</t>
         </is>
       </c>
-      <c r="I81" t="inlineStr">
+      <c r="I85" t="inlineStr">
         <is>
           <t>В сообщениях</t>
         </is>
       </c>
-      <c r="J81" t="inlineStr">
+      <c r="J85" t="inlineStr">
         <is>
           <t>Ремонт и строительство</t>
         </is>
       </c>
-      <c r="K81" t="inlineStr">
+      <c r="K85" t="inlineStr">
         <is>
           <t>Ибреси, Чувашская Республика, ул. Ленина, 26</t>
         </is>
       </c>
-      <c r="O81" t="inlineStr">
+      <c r="O85" t="inlineStr">
         <is>
           <t>ПВЗ</t>
         </is>
       </c>
-      <c r="P81" t="n">
+      <c r="P85" t="n">
         <v>2700</v>
       </c>
-      <c r="Q81" t="inlineStr">
+      <c r="Q85" t="inlineStr">
         <is>
           <t>Стройматериалы</t>
         </is>
       </c>
-      <c r="R81" t="inlineStr">
+      <c r="R85" t="inlineStr">
         <is>
           <t>Товар приобретен на продажу</t>
         </is>
       </c>
-      <c r="S81" t="inlineStr">
+      <c r="S85" t="inlineStr">
         <is>
           <t>Новое</t>
         </is>
       </c>
-      <c r="T81" t="inlineStr">
+      <c r="T85" t="inlineStr">
         <is>
           <t>В наличии</t>
         </is>
       </c>
-      <c r="U81" t="inlineStr">
+      <c r="U85" t="inlineStr">
         <is>
           <t>Пиломатериалы</t>
         </is>
       </c>
-      <c r="V81" t="inlineStr">
+      <c r="V85" t="inlineStr">
         <is>
           <t>Лес-кругляк</t>
         </is>
       </c>
-      <c r="W81" t="inlineStr">
+      <c r="W85" t="inlineStr">
         <is>
           <t>Берёза</t>
         </is>
       </c>
-      <c r="X81" t="inlineStr">
+      <c r="X85" t="inlineStr">
         <is>
           <t>Да</t>
         </is>
       </c>
-      <c r="AB81" t="n">
+      <c r="AB85" t="n">
         <v>4000</v>
       </c>
-      <c r="AC81" t="n">
+      <c r="AC85" t="n">
         <v>16</v>
       </c>
-      <c r="AE81" t="inlineStr">
+      <c r="AE85" t="inlineStr">
         <is>
           <t>orbizona-shop@yandex.ru</t>
         </is>
       </c>
-      <c r="AF81" t="inlineStr">
+      <c r="AF85" t="inlineStr">
         <is>
           <t>ЕГАИС ЛЕС документация</t>
         </is>
       </c>
-      <c r="AG81" t="inlineStr">
+      <c r="AG85" t="inlineStr">
         <is>
           <t>2026-10-19T14:30:00+03:00</t>
         </is>
       </c>
-      <c r="AJ81" t="inlineStr">
+      <c r="AJ85" t="inlineStr">
         <is>
           <t>2026-09-19T16:30:00+03:00</t>
         </is>
       </c>
-      <c r="AK81" t="inlineStr">
+      <c r="AK85" t="inlineStr">
         <is>
           <t>2026-10-19T14:30:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>4887726982</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>79852671426</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>Дрова берёзовые, документы на перевозку</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;&lt;strong&gt;Дрова готовы, покупатель ждёт, а никаких бумаг на них нет.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Оформим древесину договором купли-продажи и дадим документ с QR на перевозку.&lt;/p&gt;&lt;p&gt;Проще некуда: пишете объём и куда везёте, получаете ЭСД. От 490 руб.&lt;/p&gt;&lt;p&gt;Берёзовые дрова и баланс 1 и 2 метра, диаметр от 6 см.&lt;/p&gt;&lt;p&gt;Темниковский район, Мордовия. Напишите, сколько кубов дров и куда.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-20/w2009_25_temnikov_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-20/w2009_25_temnikov_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-20/w2009_25_temnikov_3.jpg</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>В сообщениях</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>Темников, Республика Мордовия, ул. Ленина, 25</t>
+        </is>
+      </c>
+      <c r="O86" t="inlineStr">
+        <is>
+          <t>ПВЗ</t>
+        </is>
+      </c>
+      <c r="P86" t="n">
+        <v>490</v>
+      </c>
+      <c r="Q86" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R86" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S86" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W86" t="inlineStr">
+        <is>
+          <t>Берёза</t>
+        </is>
+      </c>
+      <c r="X86" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB86" t="n">
+        <v>2000</v>
+      </c>
+      <c r="AC86" t="n">
+        <v>6</v>
+      </c>
+      <c r="AE86" t="inlineStr">
+        <is>
+          <t>orbizona-shop@yandex.ru</t>
+        </is>
+      </c>
+      <c r="AF86" t="inlineStr">
+        <is>
+          <t>ЕГАИС ЛЕС документация</t>
+        </is>
+      </c>
+      <c r="AG86" t="inlineStr">
+        <is>
+          <t>2026-10-19T16:40:00+03:00</t>
+        </is>
+      </c>
+      <c r="AJ86" t="inlineStr">
+        <is>
+          <t>2026-09-19T18:40:00+03:00</t>
+        </is>
+      </c>
+      <c r="AK86" t="inlineStr">
+        <is>
+          <t>2026-10-19T16:40:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>4076806619</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>79852671426</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>Кругляк хвойный (документация ФГИС ЛК)</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;&lt;strong&gt;Хвоя лежит на площадке, а в ФГИС ЛК за вами она не числится.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Поставим объём за вами в системе, оформим договор купли-продажи и выпишем ЭСД с QR на каждую машину.&lt;/p&gt;&lt;p&gt;Ни кабинета, ни подписи, от вас порода, кубатура и маршрут. От 1150 руб.&lt;/p&gt;&lt;p&gt;Хвойный кругляк 4 и 6 метров, диаметр от 16 см.&lt;/p&gt;&lt;p&gt;Увинский район, Удмуртия. Напишите, сколько кругляка лежит.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-20/w2009_26_uva_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-20/w2009_26_uva_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-20/w2009_26_uva_3.jpg</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>В сообщениях</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>Ува, Удмуртская Республика, ул. Калинина, 15</t>
+        </is>
+      </c>
+      <c r="O87" t="inlineStr">
+        <is>
+          <t>ПВЗ</t>
+        </is>
+      </c>
+      <c r="P87" t="n">
+        <v>1150</v>
+      </c>
+      <c r="Q87" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R87" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S87" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W87" t="inlineStr">
+        <is>
+          <t>Сосна</t>
+        </is>
+      </c>
+      <c r="X87" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB87" t="n">
+        <v>6000</v>
+      </c>
+      <c r="AC87" t="n">
+        <v>16</v>
+      </c>
+      <c r="AE87" t="inlineStr">
+        <is>
+          <t>orbizona-shop@yandex.ru</t>
+        </is>
+      </c>
+      <c r="AF87" t="inlineStr">
+        <is>
+          <t>ЕГАИС ЛЕС документация</t>
+        </is>
+      </c>
+      <c r="AG87" t="inlineStr">
+        <is>
+          <t>2026-10-20T07:20:00+03:00</t>
+        </is>
+      </c>
+      <c r="AJ87" t="inlineStr">
+        <is>
+          <t>2026-09-20T09:20:00+03:00</t>
+        </is>
+      </c>
+      <c r="AK87" t="inlineStr">
+        <is>
+          <t>2026-10-20T07:20:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>1036432555</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>79852671426</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>Берёза баланс, QR на вывоз древесины</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;&lt;strong&gt;Берёзовый баланс копится, а вывозить его без документов боязно.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Дадим QR на вывоз древесины и договор купли-продажи, чтобы партию можно было продать.&lt;/p&gt;&lt;p&gt;Дешевле всего и без хлопот, объём любой: хоть одна машина в месяц. От 290 руб.&lt;/p&gt;&lt;p&gt;Берёзовый баланс 2 и 3 метра, диаметр от 6 см.&lt;/p&gt;&lt;p&gt;Кадомский район, Рязанская область. Напишите, сколько баланса накопилось.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-20/w2009_27_kadom_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-20/w2009_27_kadom_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-20/w2009_27_kadom_3.jpg</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>В сообщениях</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>Кадом, Рязанская обл., ул. Ленина, 37</t>
+        </is>
+      </c>
+      <c r="O88" t="inlineStr">
+        <is>
+          <t>ПВЗ</t>
+        </is>
+      </c>
+      <c r="P88" t="n">
+        <v>290</v>
+      </c>
+      <c r="Q88" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R88" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S88" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V88" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W88" t="inlineStr">
+        <is>
+          <t>Берёза</t>
+        </is>
+      </c>
+      <c r="X88" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB88" t="n">
+        <v>3000</v>
+      </c>
+      <c r="AC88" t="n">
+        <v>6</v>
+      </c>
+      <c r="AE88" t="inlineStr">
+        <is>
+          <t>orbizona-shop@yandex.ru</t>
+        </is>
+      </c>
+      <c r="AF88" t="inlineStr">
+        <is>
+          <t>ЕГАИС ЛЕС документация</t>
+        </is>
+      </c>
+      <c r="AG88" t="inlineStr">
+        <is>
+          <t>2026-10-20T09:40:00+03:00</t>
+        </is>
+      </c>
+      <c r="AJ88" t="inlineStr">
+        <is>
+          <t>2026-09-20T11:40:00+03:00</t>
+        </is>
+      </c>
+      <c r="AK88" t="inlineStr">
+        <is>
+          <t>2026-10-20T09:40:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>3344417490</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>79852671426</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>Пиловочник сосна (договор и ЭСД)</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;&lt;strong&gt;Крупная партия, серьёзный покупатель, и ни одной бумаги на древесину.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Сделаем всё разом: договор купли-продажи на объём, кубатура в ФГИС ЛК, ЭСД с QR на каждый рейс.&lt;/p&gt;&lt;p&gt;Вам не придётся ни во что вникать, бумажную сторону закрываем сами. От 2990 руб.&lt;/p&gt;&lt;p&gt;Сосновый пиловочник 6 метров, диаметр от 20 см.&lt;/p&gt;&lt;p&gt;Сабинский район, Татарстан. Напишите объём партии и сроки.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-20/w2009_28_saby_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-20/w2009_28_saby_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-20/w2009_28_saby_3.jpg</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>В сообщениях</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>Богатые Сабы, Республика Татарстан, ул. Ленина, 2</t>
+        </is>
+      </c>
+      <c r="O89" t="inlineStr">
+        <is>
+          <t>ПВЗ</t>
+        </is>
+      </c>
+      <c r="P89" t="n">
+        <v>2990</v>
+      </c>
+      <c r="Q89" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R89" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S89" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V89" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W89" t="inlineStr">
+        <is>
+          <t>Сосна</t>
+        </is>
+      </c>
+      <c r="X89" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB89" t="n">
+        <v>6000</v>
+      </c>
+      <c r="AC89" t="n">
+        <v>20</v>
+      </c>
+      <c r="AE89" t="inlineStr">
+        <is>
+          <t>orbizona-shop@yandex.ru</t>
+        </is>
+      </c>
+      <c r="AF89" t="inlineStr">
+        <is>
+          <t>ЕГАИС ЛЕС документация</t>
+        </is>
+      </c>
+      <c r="AG89" t="inlineStr">
+        <is>
+          <t>2026-10-20T12:10:00+03:00</t>
+        </is>
+      </c>
+      <c r="AJ89" t="inlineStr">
+        <is>
+          <t>2026-09-20T14:10:00+03:00</t>
+        </is>
+      </c>
+      <c r="AK89" t="inlineStr">
+        <is>
+          <t>2026-10-20T12:10:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>2562904083</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>79852671426</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>Лес кругляк сосна, документы на продажу</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;&lt;strong&gt;Продать лес готовы хоть завтра, если будет чем подтвердить, что он ваш.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Подтвердит договор купли-продажи: древесина станет вашим товаром, объём встанет в ФГИС ЛК, на вывоз пойдёт ЭСД с QR.&lt;/p&gt;&lt;p&gt;Оформление целиком на нас, от вас порода, кубатура и маршрут. От 1750 руб.&lt;/p&gt;&lt;p&gt;Сосновый кругляк 4 и 6 метров, диаметр от 18 см.&lt;/p&gt;&lt;p&gt;Залесовский округ, Алтайский край. Напишите, кому продаёте и сколько.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-20/w2009_29_zalesovo_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-20/w2009_29_zalesovo_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-20/w2009_29_zalesovo_3.jpg</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>В сообщениях</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>Залесово, Алтайский край, ул. Ленина, 12</t>
+        </is>
+      </c>
+      <c r="O90" t="inlineStr">
+        <is>
+          <t>ПВЗ</t>
+        </is>
+      </c>
+      <c r="P90" t="n">
+        <v>1750</v>
+      </c>
+      <c r="Q90" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R90" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S90" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V90" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W90" t="inlineStr">
+        <is>
+          <t>Сосна</t>
+        </is>
+      </c>
+      <c r="X90" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB90" t="n">
+        <v>6000</v>
+      </c>
+      <c r="AC90" t="n">
+        <v>18</v>
+      </c>
+      <c r="AE90" t="inlineStr">
+        <is>
+          <t>orbizona-shop@yandex.ru</t>
+        </is>
+      </c>
+      <c r="AF90" t="inlineStr">
+        <is>
+          <t>ЕГАИС ЛЕС документация</t>
+        </is>
+      </c>
+      <c r="AG90" t="inlineStr">
+        <is>
+          <t>2026-10-20T14:30:00+03:00</t>
+        </is>
+      </c>
+      <c r="AJ90" t="inlineStr">
+        <is>
+          <t>2026-09-20T16:30:00+03:00</t>
+        </is>
+      </c>
+      <c r="AK90" t="inlineStr">
+        <is>
+          <t>2026-10-20T14:30:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>9982483217</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>79852671426</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>Сосна пиловочник (ЭСД с QR на рейс)</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;&lt;strong&gt;Работаете на объёме, а документы на груз каждый раз головная боль.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Снимем эту заботу: ЭСД с QR на каждый рейс за 15 минут, договор купли-продажи на партию, кубатура в ФГИС ЛК.&lt;/p&gt;&lt;p&gt;Поток машин ведём сами, от вас порода, объём и маршрут. От 3500 руб.&lt;/p&gt;&lt;p&gt;Сосновый пиловочник 4 и 6 метров, диаметр от 18 см.&lt;/p&gt;&lt;p&gt;Сузунский район, Новосибирская область. Напишите, сколько рейсов в неделю.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-20/w2009_30_suzun_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-20/w2009_30_suzun_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-20/w2009_30_suzun_3.jpg</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>В сообщениях</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>Сузун, Новосибирская обл., ул. Ленина, 51</t>
+        </is>
+      </c>
+      <c r="O91" t="inlineStr">
+        <is>
+          <t>ПВЗ</t>
+        </is>
+      </c>
+      <c r="P91" t="n">
+        <v>3500</v>
+      </c>
+      <c r="Q91" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R91" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S91" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V91" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W91" t="inlineStr">
+        <is>
+          <t>Сосна</t>
+        </is>
+      </c>
+      <c r="X91" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB91" t="n">
+        <v>6000</v>
+      </c>
+      <c r="AC91" t="n">
+        <v>18</v>
+      </c>
+      <c r="AE91" t="inlineStr">
+        <is>
+          <t>orbizona-shop@yandex.ru</t>
+        </is>
+      </c>
+      <c r="AF91" t="inlineStr">
+        <is>
+          <t>ЕГАИС ЛЕС документация</t>
+        </is>
+      </c>
+      <c r="AG91" t="inlineStr">
+        <is>
+          <t>2026-10-20T16:40:00+03:00</t>
+        </is>
+      </c>
+      <c r="AJ91" t="inlineStr">
+        <is>
+          <t>2026-09-20T18:40:00+03:00</t>
+        </is>
+      </c>
+      <c r="AK91" t="inlineStr">
+        <is>
+          <t>2026-10-20T16:40:00+03:00</t>
         </is>
       </c>
     </row>

--- a/egais.xlsx
+++ b/egais.xlsx
@@ -15754,7 +15754,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2666553242</t>
+          <t>8179360744</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -15774,7 +15774,7 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;strong&gt;Лес во дворе лежит, а машину без QR с площадки никто не выпустит.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Оформим вашу древесину договором купли-продажи, поставим кубатуру в ФГИС ЛК и выпишем ЭСД с QR на каждый рейс.&lt;/p&gt;&lt;p&gt;Кабинет в системе и электронная подпись от вас не нужны, нужны порода, объём и маршрут. От 1400 руб, документ на машину готов за 15 минут.&lt;/p&gt;&lt;p&gt;Сосновый пиловочник 4 и 6 метров, диаметр от 18 см.&lt;/p&gt;&lt;p&gt;Южский район, Ивановская область. Напишите, сколько машин в неделю.&lt;/p&gt;</t>
+          <t>&lt;p&gt;&lt;strong&gt;Оформляем документы на древесину.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Даём ЭСД с QR на каждый рейс: лесовоз едет спокойно. И договор купли-продажи, по которому древесина числится за вами.&lt;/p&gt;&lt;p&gt;Кабинет в ФГИС ЛК и электронная подпись не нужны, от вас порода, объём и маршрут. От 1400 руб, документ на машину за 15 минут.&lt;/p&gt;&lt;p&gt;Сосновый пиловочник 4 и 6 метров, диаметр от 18 см.&lt;/p&gt;&lt;p&gt;Южский район, Ивановская область. Напишите, сколько машин в неделю.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -15880,7 +15880,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>5323514222</t>
+          <t>7661728126</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -15900,7 +15900,7 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;strong&gt;Покупатель берёт баланс, но просит бумагу на происхождение, и сделка встаёт.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Сделаем документы, с которыми партию можно спокойно продать: договор купли-продажи на древесину и накладная с QR на каждый рейс.&lt;/p&gt;&lt;p&gt;От вас порода, кубатура и маршрут, остальное наша забота. От 950 руб, ЭСД на машину выписываем за 15 минут.&lt;/p&gt;&lt;p&gt;Берёзовый баланс 2 и 3 метра, диаметр от 6 см.&lt;/p&gt;&lt;p&gt;Меленковский район, Владимирская область. Напишите объём, ответим сразу.&lt;/p&gt;</t>
+          <t>&lt;p&gt;&lt;strong&gt;Делаем накладную с QR на перевозку древесины.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Документ на рейс за 15 минут, водитель показывает его на посту и на весовой. Договор купли-продажи закрепляет баланс за вами, и партию можно продать.&lt;/p&gt;&lt;p&gt;От вас порода, кубатура и маршрут, остальное на нас. От 950 руб.&lt;/p&gt;&lt;p&gt;Берёзовый баланс 2 и 3 метра, диаметр от 6 см.&lt;/p&gt;&lt;p&gt;Меленковский район, Владимирская область. Напишите, сколько кубов набирается.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -16006,7 +16006,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>5289293410</t>
+          <t>6738021087</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -16026,7 +16026,7 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;strong&gt;Партия ждёт отгрузки, а вопрос с документами так и не решён.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Берём бумажную часть на себя: договор купли-продажи на древесину, кубатура в ФГИС ЛК, ЭСД с QR на каждый рейс.&lt;/p&gt;&lt;p&gt;Ни кабинета, ни электронной подписи от вас не нужно, только порода, объём и маршрут. От 2000 руб.&lt;/p&gt;&lt;p&gt;Сосновый пиловочник 6 метров, диаметр от 20 см.&lt;/p&gt;&lt;p&gt;Кукморский район, Татарстан. Напишите, какой объём отгружаете.&lt;/p&gt;</t>
+          <t>&lt;p&gt;&lt;strong&gt;Оформляем договор и ЭСД на груз.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Договор купли-продажи на древесину и электронный сопроводительный документ с QR на каждый рейс. С ними партию принимают на комбинате.&lt;/p&gt;&lt;p&gt;Бумажную часть ведём мы, от вас порода, объём и маршрут. От 2000 руб.&lt;/p&gt;&lt;p&gt;Сосновый пиловочник 6 метров, диаметр от 20 см.&lt;/p&gt;&lt;p&gt;Кукморский район, Татарстан. Напишите, какой объём отгружаете.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -16132,7 +16132,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>5715368817</t>
+          <t>7065474569</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -16152,7 +16152,7 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;strong&gt;Заготовили сами, а продать по-белому не получается.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Сделаем древесину законным товаром: договор купли-продажи от нашего объёма, кубатура в ФГИС ЛК, ЭСД с QR на отгрузку.&lt;/p&gt;&lt;p&gt;Всё оформление на нас, от вас порода, объём и маршрут. От 1850 руб.&lt;/p&gt;&lt;p&gt;Сосновый пиловочник 4 и 6 метров, диаметр от 18 см.&lt;/p&gt;&lt;p&gt;Караидельский район, Башкортостан. Напишите, что за лес и сколько его.&lt;/p&gt;</t>
+          <t>&lt;p&gt;&lt;strong&gt;Оформляем документы тем, кто пилит сам.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Заготовка становится товаром: договор купли-продажи, кубатура в ФГИС ЛК, ЭСД с QR на отгрузку.&lt;/p&gt;&lt;p&gt;Оформление целиком на нас, от вас порода, объём и маршрут. От 1850 руб, документ на рейс за 15 минут.&lt;/p&gt;&lt;p&gt;Сосновый пиловочник 4 и 6 метров, диаметр от 18 см.&lt;/p&gt;&lt;p&gt;Караидельский район, Башкортостан. Напишите, что за лес и сколько его.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -16258,7 +16258,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2399797215</t>
+          <t>9518632923</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -16278,7 +16278,7 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;strong&gt;Пиловочник лежит, покупатель найден, а подтвердить происхождение нечем.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Оформим договор купли-продажи на партию, заведём кубатуру в ФГИС ЛК, выпишем ЭСД с QR на перевозку.&lt;/p&gt;&lt;p&gt;От вас порода, объём и маршрут, кабинет и подпись не нужны. От 1490 руб.&lt;/p&gt;&lt;p&gt;Сосновый пиловочник 4 и 6 метров, диаметр от 18 см.&lt;/p&gt;&lt;p&gt;Заволжский район, Ивановская область. Напишите, сколько пиловочника.&lt;/p&gt;</t>
+          <t>&lt;p&gt;&lt;strong&gt;Оформляем QR-код на перевозку леса.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;На каждый рейс свой ЭСД, на партию договор купли-продажи, кубатура встаёт в ФГИС ЛК за вами.&lt;/p&gt;&lt;p&gt;От вас порода, объём и маршрут, кабинет и электронная подпись не нужны. От 1490 руб.&lt;/p&gt;&lt;p&gt;Сосновый пиловочник 4 и 6 метров, диаметр от 18 см.&lt;/p&gt;&lt;p&gt;Заволжский район, Ивановская область. Напишите, сколько пиловочника.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -16384,7 +16384,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>1987889847</t>
+          <t>2697992858</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -16404,7 +16404,7 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;strong&gt;Водитель на погрузке спрашивает документ на груз, а показать нечего.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Дадим на рейс электронный сопроводительный документ с QR, а на партию договор купли-продажи, по которому лес числится за вами.&lt;/p&gt;&lt;p&gt;Вам не нужен ни кабинет в ФГИС ЛК, ни подпись: скажите породу, кубатуру и куда идёт лесовоз. От 850 руб.&lt;/p&gt;&lt;p&gt;Еловый кругляк 4 и 6 метров, диаметр от 14 см.&lt;/p&gt;&lt;p&gt;Пестяковский район, Ивановская область. Напишите, когда ближайшая отгрузка.&lt;/p&gt;</t>
+          <t>&lt;p&gt;&lt;strong&gt;Выдаём QR-код на перевозку леса.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;На каждый рейс электронный сопроводительный документ, QR проверяется телефоном за пару секунд. На партию договор купли-продажи.&lt;/p&gt;&lt;p&gt;Работаем по переписке, свой кабинет в ФГИС ЛК заводить не надо. От вас порода, кубатура и куда везёте. От 850 руб.&lt;/p&gt;&lt;p&gt;Еловый кругляк 4 и 6 метров, диаметр от 14 см.&lt;/p&gt;&lt;p&gt;Пестяковский район, Ивановская область. Напишите, когда ближайшая отгрузка.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -16510,7 +16510,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>3815885267</t>
+          <t>8630019576</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -16530,7 +16530,7 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;strong&gt;В ФГИС ЛК по вашему лесу пусто, а вывозить надо уже на этой неделе.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Заведём кубатуру в ФГИС ЛК, оформим древесину договором купли-продажи и выпишем ЭСД с QR на каждую машину.&lt;/p&gt;&lt;p&gt;Всю возню с системой берём на себя, от вас порода, объём и маршрут. От 1700 руб.&lt;/p&gt;&lt;p&gt;Сосновый пиловочник 6 метров, диаметр от 20 см.&lt;/p&gt;&lt;p&gt;Судогодский район, Владимирская область. Напишите, сколько кубов и куда везёте.&lt;/p&gt;</t>
+          <t>&lt;p&gt;&lt;strong&gt;Ставим древесину на учёт в ФГИС ЛК.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Кубатура начинает числиться за вами. Дальше договор купли-продажи на партию и ЭСД с QR на каждую машину.&lt;/p&gt;&lt;p&gt;Всю возню с системой берём на себя, свой кабинет и подпись вам не нужны. От вас порода, объём и маршрут. От 1700 руб.&lt;/p&gt;&lt;p&gt;Сосновый пиловочник 6 метров, диаметр от 20 см.&lt;/p&gt;&lt;p&gt;Судогодский район, Владимирская область. Напишите, сколько кубов и куда везёте.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -16636,7 +16636,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>1375199930</t>
+          <t>2140473788</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -16656,7 +16656,7 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;strong&gt;Объём есть, а числится он ни за кем, и на комбинат с таким не заедешь.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Поставим кубатуру в ФГИС ЛК за вами, оформим договор купли-продажи и дадим ЭСД с QR на отгрузку.&lt;/p&gt;&lt;p&gt;Разбираться в системе не придётся, работаем и с одной машиной, и с потоком. От 900 руб.&lt;/p&gt;&lt;p&gt;Еловый баланс 2 и 3 метра, диаметр от 6 см.&lt;/p&gt;&lt;p&gt;Кезский район, Удмуртия. Напишите, сколько кубов балансов.&lt;/p&gt;</t>
+          <t>&lt;p&gt;&lt;strong&gt;Заводим вашу кубатуру в ФГИС ЛК.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Объём встаёт на баланс за вами, на партию идёт договор купли-продажи, на отгрузку ЭСД с QR.&lt;/p&gt;&lt;p&gt;Разбираться в системе не придётся, работаем и с одной машиной, и с потоком. От 900 руб.&lt;/p&gt;&lt;p&gt;Еловый баланс 2 и 3 метра, диаметр от 6 см.&lt;/p&gt;&lt;p&gt;Кезский район, Удмуртия. Напишите, сколько кубов балансов.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -16762,7 +16762,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>6850310008</t>
+          <t>6038274710</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -16782,7 +16782,7 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;strong&gt;Отгрузка срывается каждый раз, когда просят документ на груз.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Выдадим ЭСД с QR на каждую машину и оформим древесину договором купли-продажи, чтобы её приняли на весовой.&lt;/p&gt;&lt;p&gt;Работу с ФГИС ЛК берём на себя, от вас порода, кубатура и маршрут. От 1550 руб.&lt;/p&gt;&lt;p&gt;Еловый пиловочник 4 и 6 метров, диаметр от 16 см.&lt;/p&gt;&lt;p&gt;Маслянинский район, Новосибирская область. Напишите, сколько машин в неделю.&lt;/p&gt;</t>
+          <t>&lt;p&gt;&lt;strong&gt;Выписываем ЭСД на каждую машину.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Сколько лесовозов уходит, столько документов с QR. И договор купли-продажи, по которому древесину принимают на весовой.&lt;/p&gt;&lt;p&gt;Работу с ФГИС ЛК берём на себя, от вас порода, кубатура и маршрут. От 1550 руб.&lt;/p&gt;&lt;p&gt;Еловый пиловочник 4 и 6 метров, диаметр от 16 см.&lt;/p&gt;&lt;p&gt;Маслянинский район, Новосибирская область. Напишите, сколько машин в неделю.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -16888,7 +16888,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>4351555607</t>
+          <t>8464900540</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -16908,7 +16908,7 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;strong&gt;Вся беда в бумагах: лес ваш, а доказать это нечем.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Договор купли-продажи закрепит древесину за вами, кубатура встанет в ФГИС ЛК, а на рейсы пойдёт ЭСД с QR.&lt;/p&gt;&lt;p&gt;Документами занимаемся мы целиком, вам грузить и получать деньги. От 2490 руб.&lt;/p&gt;&lt;p&gt;Еловый кругляк 4 и 6 метров, диаметр от 16 см.&lt;/p&gt;&lt;p&gt;Гороховецкий район, Владимирская область. Напишите, когда отгрузка.&lt;/p&gt;</t>
+          <t>&lt;p&gt;&lt;strong&gt;Делаем документы на древесину в ФГИС ЛК.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Договор купли-продажи закрепляет лес за вами, кубатура числится в системе, на рейсы идёт ЭСД с QR.&lt;/p&gt;&lt;p&gt;Документами занимаемся мы целиком, вам грузить и получать деньги. От 2490 руб.&lt;/p&gt;&lt;p&gt;Еловый кругляк 4 и 6 метров, диаметр от 16 см.&lt;/p&gt;&lt;p&gt;Гороховецкий район, Владимирская область. Напишите, когда отгрузка.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -17014,7 +17014,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>1487549445</t>
+          <t>9832978840</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -17034,7 +17034,7 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;strong&gt;Лесовоз загружен, а выехать с площадки нельзя, ЭСД на груз нет.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Выпишем электронный сопроводительный документ с QR на рейс и оформим договор купли-продажи, по которому древесина ваша.&lt;/p&gt;&lt;p&gt;Ни кабинета, ни подписи не потребуется, назовите породу, кубатуру и маршрут. От 1100 руб, ЭСД готов за 15 минут.&lt;/p&gt;&lt;p&gt;Еловый пиловочник 4 и 6 метров, диаметр от 16 см.&lt;/p&gt;&lt;p&gt;Западнодвинский округ, Тверская область. Напишите, когда грузите.&lt;/p&gt;</t>
+          <t>&lt;p&gt;&lt;strong&gt;Выписываем ЭСД на вывоз леса.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Электронный сопроводительный документ с QR готов за 15 минут, на каждый рейс свой. И договор купли-продажи на древесину.&lt;/p&gt;&lt;p&gt;Ни кабинета, ни электронной подписи от вас. Назовите породу, кубатуру и маршрут. От 1100 руб.&lt;/p&gt;&lt;p&gt;Еловый пиловочник 4 и 6 метров, диаметр от 16 см.&lt;/p&gt;&lt;p&gt;Западнодвинский округ, Тверская область. Напишите, когда грузите лесовоз.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -17140,7 +17140,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>7549099851</t>
+          <t>1273554299</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -17160,7 +17160,7 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;strong&gt;Дровяная берёза лежит, а по системе её у вас как будто нет.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Оформим объём за вами в ФГИС ЛК, дадим договор купли-продажи и ЭСД с QR на вывоз.&lt;/p&gt;&lt;p&gt;Проще некуда: назвали породу и кубатуру, получили документ на машину. От 350 руб.&lt;/p&gt;&lt;p&gt;Берёзовые дрова и баланс 1 и 2 метра, диаметр от 6 см.&lt;/p&gt;&lt;p&gt;Балтасинский район, Татарстан. Напишите, сколько кубов дров.&lt;/p&gt;</t>
+          <t>&lt;p&gt;&lt;strong&gt;Ставим берёзу на учёт в ФГИС ЛК.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Объём числится за вами, на руках договор купли-продажи и ЭСД с QR на вывоз.&lt;/p&gt;&lt;p&gt;Проще некуда: назвали породу и кубатуру, получили документ на машину. Подпись и кабинет не нужны. От 350 руб.&lt;/p&gt;&lt;p&gt;Берёзовые дрова и баланс 1 и 2 метра, диаметр от 6 см.&lt;/p&gt;&lt;p&gt;Балтасинский район, Татарстан. Напишите, сколько кубов дров.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -17266,7 +17266,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2571643288</t>
+          <t>7154914119</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -17286,7 +17286,7 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;strong&gt;Рейсы стоят, потому что ЭСД на груз выписать некому.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Будем выписывать ЭСД с QR за 15 минут на каждый рейс, а партию закроем договором купли-продажи.&lt;/p&gt;&lt;p&gt;Всю работу с системой ведём мы, вам остаётся грузить лесовозы. От 2450 руб.&lt;/p&gt;&lt;p&gt;Еловый пиловочник 6 метров, диаметр от 20 см.&lt;/p&gt;&lt;p&gt;Варнавинский район, Нижегородская область. Напишите, сколько рейсов в месяц.&lt;/p&gt;</t>
+          <t>&lt;p&gt;&lt;strong&gt;Выдаём ЭСД с QR за 15 минут.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Документ на рейс приходит в тот же день, когда написали. Партия закрыта договором купли-продажи, кубатура стоит в ФГИС ЛК.&lt;/p&gt;&lt;p&gt;Всю работу с системой ведём мы, вам остаётся грузить лесовозы. От 2450 руб.&lt;/p&gt;&lt;p&gt;Еловый пиловочник 6 метров, диаметр от 20 см.&lt;/p&gt;&lt;p&gt;Варнавинский район, Нижегородская область. Напишите, сколько рейсов в месяц.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -17392,7 +17392,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>9160676187</t>
+          <t>5708797610</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -17412,7 +17412,7 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;strong&gt;Кряж заготовлен, а продать не выходит: подтвердить происхождение нечем.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Оформим партию договором купли-продажи и закроем её декларацией, а на вывоз дадим ЭСД с QR.&lt;/p&gt;&lt;p&gt;Всё просто, берём любой объём: хоть одна машина, хоть двадцать. От 620 руб.&lt;/p&gt;&lt;p&gt;Берёзовый кряж 3 и 4 метра, диаметр от 16 см.&lt;/p&gt;&lt;p&gt;Кузоватовский район, Ульяновская область. Напишите, сколько кряжа лежит.&lt;/p&gt;</t>
+          <t>&lt;p&gt;&lt;strong&gt;Оформляем документы на продажу леса.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Договор купли-продажи, по которому кряж становится вашим товаром. Сделка проведена в ФГИС ЛК, на вывоз ЭСД с QR.&lt;/p&gt;&lt;p&gt;Берём любой объём: хоть одна машина, хоть двадцать. Вникать ни во что не придётся. От 620 руб.&lt;/p&gt;&lt;p&gt;Берёзовый кряж 3 и 4 метра, диаметр от 16 см.&lt;/p&gt;&lt;p&gt;Кузоватовский район, Ульяновская область. Напишите, сколько кряжа лежит.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -17518,7 +17518,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>8164161808</t>
+          <t>7235918048</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -17538,7 +17538,7 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;strong&gt;Баланс уходит на комбинат, а на весовую без документа не пустят.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Дадим ЭСД с QR на каждый рейс и договор купли-продажи на партию, с ними груз принимают.&lt;/p&gt;&lt;p&gt;Всё по переписке, объём любой. От 990 руб, документ на машину за 15 минут.&lt;/p&gt;&lt;p&gt;Берёзовый баланс 2 и 3 метра, диаметр от 6 см.&lt;/p&gt;&lt;p&gt;Сурский район, Ульяновская область. Напишите, сколько баланса.&lt;/p&gt;</t>
+          <t>&lt;p&gt;&lt;strong&gt;Выдаём документ с QR на каждый рейс.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;С ним баланс принимают на весовой и на комбинате. Договор купли-продажи на партию тоже будет у вас на руках.&lt;/p&gt;&lt;p&gt;Всё по переписке, объём любой. От 990 руб, документ на машину за 15 минут.&lt;/p&gt;&lt;p&gt;Берёзовый баланс 2 и 3 метра, диаметр от 6 см.&lt;/p&gt;&lt;p&gt;Сурский район, Ульяновская область. Напишите, сколько баланса.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -17644,7 +17644,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>6290188818</t>
+          <t>3891490310</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -17664,7 +17664,7 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;strong&gt;Купили лес у населения, а бумаг на него вам никто не дал.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Сделаем так, чтобы древесина стала законным товаром: договор купли-продажи на партию, кубатура в ФГИС ЛК, QR-код на перевозку.&lt;/p&gt;&lt;p&gt;От вас только порода и объём, дальше уже не ваша забота. От 750 руб.&lt;/p&gt;&lt;p&gt;Сосновый кругляк 4 и 6 метров, диаметр от 18 см.&lt;/p&gt;&lt;p&gt;Зубово-Полянский район, Мордовия. Напишите, сколько машин планируете.&lt;/p&gt;</t>
+          <t>&lt;p&gt;&lt;strong&gt;Делаем документы на лес, купленный у населения.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Древесина становится законным товаром: договор купли-продажи на партию, кубатура в ФГИС ЛК, QR-код на перевозку.&lt;/p&gt;&lt;p&gt;От вас порода и объём, дальше уже не ваша забота. От 750 руб, ЭСД на рейс за 15 минут.&lt;/p&gt;&lt;p&gt;Сосновый кругляк 4 и 6 метров, диаметр от 18 см.&lt;/p&gt;&lt;p&gt;Зубово-Полянский район, Мордовия. Напишите, сколько машин планируете.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -17770,7 +17770,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>6949649199</t>
+          <t>8653558262</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -17790,7 +17790,7 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;strong&gt;Доска готова к отгрузке, а перевозчик без QR за рейс не берётся.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Дадим QR-код на перевозку и договор купли-продажи, чтобы груз приняли без лишних вопросов.&lt;/p&gt;&lt;p&gt;Заявка занимает пару минут: порода, кубатура, маршрут. Документ на рейс за 15 минут, от 480 руб.&lt;/p&gt;&lt;p&gt;Сосновая доска и кругляк 4 и 6 метров, диаметр от 18 см.&lt;/p&gt;&lt;p&gt;Шиловский район, Рязанская область. Напишите, сколько рейсов нужно закрыть.&lt;/p&gt;</t>
+          <t>&lt;p&gt;&lt;strong&gt;Даём QR-код на вывоз партии.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Документ на рейс за 15 минут, перевозчик берётся за груз без вопросов. Договор купли-продажи подтверждает, что древесина ваша.&lt;/p&gt;&lt;p&gt;Заявка на пару минут: порода, кубатура, маршрут. Кабинет в ФГИС ЛК не нужен. От 480 руб.&lt;/p&gt;&lt;p&gt;Сосновая доска и кругляк 4 и 6 метров, диаметр от 18 см.&lt;/p&gt;&lt;p&gt;Шиловский район, Рязанская область. Напишите, сколько рейсов надо закрыть.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -17896,7 +17896,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>7061487276</t>
+          <t>7088644908</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -17916,7 +17916,7 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;strong&gt;Кругляк грузите, а везёте на свой страх, QR-кода на рейс нет.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Закроем рейсы электронным сопроводительным документом с QR, а партию оформим договором купли-продажи.&lt;/p&gt;&lt;p&gt;Всё делается по переписке, объём любой, хоть одна машина. От 690 руб.&lt;/p&gt;&lt;p&gt;Хвойный кругляк 4 и 6 метров, диаметр от 16 см.&lt;/p&gt;&lt;p&gt;Тисульский район, Кемеровская область. Напишите, сколько кругляка.&lt;/p&gt;</t>
+          <t>&lt;p&gt;&lt;strong&gt;Закрываем рейсы документом с QR.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;ЭСД на каждую машину, QR живой, проверяется прямо на посту. Партия при этом оформлена договором купли-продажи.&lt;/p&gt;&lt;p&gt;Всё по переписке, объём любой, хоть одна машина в месяц. От 690 руб.&lt;/p&gt;&lt;p&gt;Хвойный кругляк 4 и 6 метров, диаметр от 16 см.&lt;/p&gt;&lt;p&gt;Тисульский район, Кемеровская область. Напишите, сколько кругляка.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -18022,7 +18022,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>3485114965</t>
+          <t>4175583854</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -18042,7 +18042,7 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;strong&gt;Лес складирован на площадке, а сама площадка нигде не заявлена.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Заявим место складирования, поставим кубатуру в ФГИС ЛК и дадим ЭСД с QR на вывоз.&lt;/p&gt;&lt;p&gt;Ни кабинета, ни подписи: пишете породу и объём, получаете документы. От 820 руб.&lt;/p&gt;&lt;p&gt;Сосновый кругляк 4 и 6 метров, диаметр от 18 см.&lt;/p&gt;&lt;p&gt;Нязепетровский район, Челябинская область. Напишите, где лежит лес.&lt;/p&gt;</t>
+          <t>&lt;p&gt;&lt;strong&gt;Оформляем места складирования и вывоз древесины.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Площадка заявлена, кубатура стоит в ФГИС ЛК за вами, на каждый рейс ЭСД с QR.&lt;/p&gt;&lt;p&gt;Ни кабинета, ни подписи: пишете адрес площадки, породу и объём. От 820 руб, документ на машину за 15 минут.&lt;/p&gt;&lt;p&gt;Сосновый кругляк 4 и 6 метров, диаметр от 18 см.&lt;/p&gt;&lt;p&gt;Нязепетровский район, Челябинская область. Напишите, сколько кубов лежит.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -18148,7 +18148,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>4165300953</t>
+          <t>1385322760</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -18168,7 +18168,7 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;strong&gt;Каждый рейс как лотерея, пока на груз нет электронного документа.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Каждая машина поедет с ЭСД и QR, а партия будет закрыта договором купли-продажи.&lt;/p&gt;&lt;p&gt;Систему берём на себя, от вас порода, кубатура и маршрут. От 1990 руб.&lt;/p&gt;&lt;p&gt;Еловый пиловочник 6 метров, диаметр от 20 см.&lt;/p&gt;&lt;p&gt;Торопецкий район, Тверская область. Напишите, сколько машин уходит.&lt;/p&gt;</t>
+          <t>&lt;p&gt;&lt;strong&gt;Оформляем вывоз леса по документам с QR.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Каждая машина едет со своим ЭСД. Партия закрыта договором купли-продажи, кубатура в ФГИС ЛК числится за вами.&lt;/p&gt;&lt;p&gt;Систему берём на себя, от вас порода, кубатура и маршрут. От 1990 руб.&lt;/p&gt;&lt;p&gt;Еловый пиловочник 6 метров, диаметр от 20 см.&lt;/p&gt;&lt;p&gt;Торопецкий район, Тверская область. Напишите, сколько машин уходит.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -18274,7 +18274,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>8938051818</t>
+          <t>1517789134</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -18294,7 +18294,7 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;strong&gt;Машину развернули на трассе, потому что предъявить было нечего.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Чтобы такое не повторялось: ЭСД с QR на каждую машину, договор купли-продажи на партию, кубатура в ФГИС ЛК.&lt;/p&gt;&lt;p&gt;От вас порода, объём и маршрут, остальное делаем мы. От 1250 руб, документ за 15 минут.&lt;/p&gt;&lt;p&gt;Сосновый пиловочник 4 и 6 метров, диаметр от 18 см.&lt;/p&gt;&lt;p&gt;Заринский район, Алтайский край. Напишите, куда идут машины.&lt;/p&gt;</t>
+          <t>&lt;p&gt;&lt;strong&gt;Оформляем документы на древесину и отчётность по ней.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;ЭСД с QR на каждую машину, договор купли-продажи на партию, кубатура в ФГИС ЛК. Отчёт 1-ИЛ закрываем сами.&lt;/p&gt;&lt;p&gt;От вас порода, объём и маршрут. От 1250 руб, документ на рейс за 15 минут.&lt;/p&gt;&lt;p&gt;Сосновый пиловочник 4 и 6 метров, диаметр от 18 см.&lt;/p&gt;&lt;p&gt;Заринский район, Алтайский край. Напишите, куда идут машины.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
@@ -18400,7 +18400,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>1621318393</t>
+          <t>5495184664</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -18420,7 +18420,7 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;strong&gt;Нужна накладная на перевозку, а вы даже не знаете, с чего начать.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Начинать никуда не надо, напишите нам: дальше документ с QR на рейс, договор купли-продажи и кубатура в ФГИС ЛК.&lt;/p&gt;&lt;p&gt;Кабинет и подпись не нужны, от вас порода, объём и маршрут. От 540 руб.&lt;/p&gt;&lt;p&gt;Сосновый баланс 2 и 3 метра, диаметр от 6 см.&lt;/p&gt;&lt;p&gt;Земетчинский район, Пензенская область. Напишите, когда первая отгрузка.&lt;/p&gt;</t>
+          <t>&lt;p&gt;&lt;strong&gt;Делаем документы на перевозку древесины.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Накладная с QR на рейс, договор купли-продажи на партию, кубатура в ФГИС ЛК за вами.&lt;/p&gt;&lt;p&gt;Начинать никуда не надо, просто напишите. Кабинет и подпись не нужны, от вас порода, объём и маршрут. От 540 руб.&lt;/p&gt;&lt;p&gt;Сосновый баланс 2 и 3 метра, диаметр от 6 см.&lt;/p&gt;&lt;p&gt;Земетчинский район, Пензенская область. Напишите, когда первая отгрузка.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -18526,7 +18526,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>5972001039</t>
+          <t>7017657555</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -18546,7 +18546,7 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;strong&gt;Сделка есть, декларации по ней нет, и покупатель начинает нервничать.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Оформим всё как положено: договор купли-продажи, декларация, объём в ФГИС ЛК и QR-код на перевозку.&lt;/p&gt;&lt;p&gt;Берём даже одну машину, вникать ни во что не придётся. От 420 руб.&lt;/p&gt;&lt;p&gt;Хвойный баланс 2 и 3 метра, диаметр от 6 см.&lt;/p&gt;&lt;p&gt;Тоншаевский район, Нижегородская область. Напишите породу и кубатуру.&lt;/p&gt;</t>
+          <t>&lt;p&gt;&lt;strong&gt;Проводим сделку по древесине в ФГИС ЛК.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Договор купли-продажи на партию, объём за вами в системе, QR-код на перевозку каждой машины.&lt;/p&gt;&lt;p&gt;Берём даже одну машину, вникать ни во что не придётся. От 420 руб, ЭСД на рейс за 15 минут.&lt;/p&gt;&lt;p&gt;Хвойный баланс 2 и 3 метра, диаметр от 6 см.&lt;/p&gt;&lt;p&gt;Тоншаевский район, Нижегородская область. Напишите породу и кубатуру.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
@@ -18652,7 +18652,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2946271120</t>
+          <t>4896481532</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -18672,7 +18672,7 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;strong&gt;Берёза продана, только вывезти её без QR на машину не выйдет.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Дадим QR-код на вывоз каждого рейса и договор купли-продажи, по которому партия ваша.&lt;/p&gt;&lt;p&gt;Возиться с ФГИС ЛК не придётся, всё берём на себя. От 2700 руб, ЭСД на рейс за 15 минут.&lt;/p&gt;&lt;p&gt;Берёзовый кругляк 3 и 4 метра, диаметр от 16 см.&lt;/p&gt;&lt;p&gt;Ибресинский район, Чувашия. Напишите, какой объём вывозите.&lt;/p&gt;</t>
+          <t>&lt;p&gt;&lt;strong&gt;Выписываем документ с QR на каждый лесовоз.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;ЭСД на рейс за 15 минут и договор купли-продажи, по которому партия ваша.&lt;/p&gt;&lt;p&gt;Возиться с ФГИС ЛК не придётся, всё делаем сами. От вас порода, кубатура и маршрут. От 2700 руб.&lt;/p&gt;&lt;p&gt;Берёзовый кругляк 3 и 4 метра, диаметр от 16 см.&lt;/p&gt;&lt;p&gt;Ибресинский район, Чувашия. Напишите, какой объём вывозите.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
@@ -18778,7 +18778,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>4887726982</t>
+          <t>6437459772</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -18798,7 +18798,7 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;strong&gt;Дрова готовы, покупатель ждёт, а никаких бумаг на них нет.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Оформим древесину договором купли-продажи и дадим документ с QR на перевозку.&lt;/p&gt;&lt;p&gt;Проще некуда: пишете объём и куда везёте, получаете ЭСД. От 490 руб.&lt;/p&gt;&lt;p&gt;Берёзовые дрова и баланс 1 и 2 метра, диаметр от 6 см.&lt;/p&gt;&lt;p&gt;Темниковский район, Мордовия. Напишите, сколько кубов дров и куда.&lt;/p&gt;</t>
+          <t>&lt;p&gt;&lt;strong&gt;Делаем документы на перевозку дров и баланса.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;ЭСД с QR на рейс и договор купли-продажи, по которому древесина ваша.&lt;/p&gt;&lt;p&gt;Проще некуда: пишете объём и куда везёте, получаете документ за 15 минут. От 490 руб.&lt;/p&gt;&lt;p&gt;Берёзовые дрова и баланс 1 и 2 метра, диаметр от 6 см.&lt;/p&gt;&lt;p&gt;Темниковский район, Мордовия. Напишите, сколько кубов дров и куда.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
@@ -18904,7 +18904,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>4076806619</t>
+          <t>2579967049</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -18924,7 +18924,7 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;strong&gt;Хвоя лежит на площадке, а в ФГИС ЛК за вами она не числится.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Поставим объём за вами в системе, оформим договор купли-продажи и выпишем ЭСД с QR на каждую машину.&lt;/p&gt;&lt;p&gt;Ни кабинета, ни подписи, от вас порода, кубатура и маршрут. От 1150 руб.&lt;/p&gt;&lt;p&gt;Хвойный кругляк 4 и 6 метров, диаметр от 16 см.&lt;/p&gt;&lt;p&gt;Увинский район, Удмуртия. Напишите, сколько кругляка лежит.&lt;/p&gt;</t>
+          <t>&lt;p&gt;&lt;strong&gt;Ставим объём в ФГИС ЛК и даём QR на рейс.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Кругляк числится за вами, на партию договор купли-продажи, на каждую машину ЭСД.&lt;/p&gt;&lt;p&gt;Ни кабинета, ни электронной подписи. От вас порода, кубатура и маршрут. От 1150 руб.&lt;/p&gt;&lt;p&gt;Хвойный кругляк 4 и 6 метров, диаметр от 16 см.&lt;/p&gt;&lt;p&gt;Увинский район, Удмуртия. Напишите, сколько кругляка лежит.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
@@ -19030,7 +19030,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>1036432555</t>
+          <t>8626117472</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -19050,7 +19050,7 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;strong&gt;Берёзовый баланс копится, а вывозить его без документов боязно.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Дадим QR на вывоз древесины и договор купли-продажи, чтобы партию можно было продать.&lt;/p&gt;&lt;p&gt;Дешевле всего и без хлопот, объём любой: хоть одна машина в месяц. От 290 руб.&lt;/p&gt;&lt;p&gt;Берёзовый баланс 2 и 3 метра, диаметр от 6 см.&lt;/p&gt;&lt;p&gt;Кадомский район, Рязанская область. Напишите, сколько баланса накопилось.&lt;/p&gt;</t>
+          <t>&lt;p&gt;&lt;strong&gt;Выписываем QR на вывоз древесины.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Документ на каждый рейс и договор купли-продажи, чтобы партию можно было продать.&lt;/p&gt;&lt;p&gt;Без хлопот и недорого, объём любой: хоть одна машина в месяц. От 290 руб, ЭСД за 15 минут.&lt;/p&gt;&lt;p&gt;Берёзовый баланс 2 и 3 метра, диаметр от 6 см.&lt;/p&gt;&lt;p&gt;Кадомский район, Рязанская область. Напишите, сколько баланса накопилось.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
@@ -19156,7 +19156,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>3344417490</t>
+          <t>2624373461</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -19176,7 +19176,7 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;strong&gt;Крупная партия, серьёзный покупатель, и ни одной бумаги на древесину.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Сделаем всё разом: договор купли-продажи на объём, кубатура в ФГИС ЛК, ЭСД с QR на каждый рейс.&lt;/p&gt;&lt;p&gt;Вам не придётся ни во что вникать, бумажную сторону закрываем сами. От 2990 руб.&lt;/p&gt;&lt;p&gt;Сосновый пиловочник 6 метров, диаметр от 20 см.&lt;/p&gt;&lt;p&gt;Сабинский район, Татарстан. Напишите объём партии и сроки.&lt;/p&gt;</t>
+          <t>&lt;p&gt;&lt;strong&gt;Оформляем договор купли-продажи и ЭСД на партию.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Древесина становится вашим товаром, кубатура встаёт в ФГИС ЛК, на каждый рейс документ с QR.&lt;/p&gt;&lt;p&gt;Вникать ни во что не придётся, бумажную сторону закрываем сами. От 2990 руб.&lt;/p&gt;&lt;p&gt;Сосновый пиловочник 6 метров, диаметр от 20 см.&lt;/p&gt;&lt;p&gt;Сабинский район, Татарстан. Напишите объём партии и сроки.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
@@ -19282,7 +19282,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2562904083</t>
+          <t>8485702559</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -19302,7 +19302,7 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;strong&gt;Продать лес готовы хоть завтра, если будет чем подтвердить, что он ваш.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Подтвердит договор купли-продажи: древесина станет вашим товаром, объём встанет в ФГИС ЛК, на вывоз пойдёт ЭСД с QR.&lt;/p&gt;&lt;p&gt;Оформление целиком на нас, от вас порода, кубатура и маршрут. От 1750 руб.&lt;/p&gt;&lt;p&gt;Сосновый кругляк 4 и 6 метров, диаметр от 18 см.&lt;/p&gt;&lt;p&gt;Залесовский округ, Алтайский край. Напишите, кому продаёте и сколько.&lt;/p&gt;</t>
+          <t>&lt;p&gt;&lt;strong&gt;Делаем документы, по которым лес можно продать.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Договор купли-продажи на древесину, кубатура за вами в ФГИС ЛК, ЭСД с QR на вывоз.&lt;/p&gt;&lt;p&gt;Работаем по переписке. От вас порода, объём и куда везёте. От 1750 руб, документ на рейс за 15 минут.&lt;/p&gt;&lt;p&gt;Сосновый кругляк 4 и 6 метров, диаметр от 18 см.&lt;/p&gt;&lt;p&gt;Залесовский округ, Алтайский край. Напишите, кому продаёте и сколько.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -19408,7 +19408,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>9982483217</t>
+          <t>7528664312</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -19428,7 +19428,7 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;strong&gt;Работаете на объёме, а документы на груз каждый раз головная боль.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Снимем эту заботу: ЭСД с QR на каждый рейс за 15 минут, договор купли-продажи на партию, кубатура в ФГИС ЛК.&lt;/p&gt;&lt;p&gt;Поток машин ведём сами, от вас порода, объём и маршрут. От 3500 руб.&lt;/p&gt;&lt;p&gt;Сосновый пиловочник 4 и 6 метров, диаметр от 18 см.&lt;/p&gt;&lt;p&gt;Сузунский район, Новосибирская область. Напишите, сколько рейсов в неделю.&lt;/p&gt;</t>
+          <t>&lt;p&gt;&lt;strong&gt;Оформляем отгрузку лесовозов по ЭСД с QR.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;На каждый рейс документ за 15 минут, на партию договор купли-продажи, кубатура в ФГИС ЛК за вами.&lt;/p&gt;&lt;p&gt;Поток машин ведём сами, от вас порода, объём и маршрут. От 3500 руб.&lt;/p&gt;&lt;p&gt;Сосновый пиловочник 4 и 6 метров, диаметр от 18 см.&lt;/p&gt;&lt;p&gt;Сузунский район, Новосибирская область. Напишите, сколько рейсов в неделю.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">

--- a/egais.xlsx
+++ b/egais.xlsx
@@ -15754,7 +15754,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>8179360744</t>
+          <t>8072318046</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -15774,7 +15774,7 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;strong&gt;Оформляем документы на древесину.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Даём ЭСД с QR на каждый рейс: лесовоз едет спокойно. И договор купли-продажи, по которому древесина числится за вами.&lt;/p&gt;&lt;p&gt;Кабинет в ФГИС ЛК и электронная подпись не нужны, от вас порода, объём и маршрут. От 1400 руб, документ на машину за 15 минут.&lt;/p&gt;&lt;p&gt;Сосновый пиловочник 4 и 6 метров, диаметр от 18 см.&lt;/p&gt;&lt;p&gt;Южский район, Ивановская область. Напишите, сколько машин в неделю.&lt;/p&gt;</t>
+          <t>&lt;p&gt;&lt;strong&gt;Оформляем документы на древесину.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Даём электронный сопроводительный документ и QR-код на перевозку древесины. Водитель показывает его на посту и на весовой.&lt;/p&gt;&lt;p&gt;Сосновый пиловочник проводим договором купли-продажи, кубатура встаёт в ФГИС ЛК за вами. Декларацию о сделке подаём сами.&lt;/p&gt;&lt;p&gt;Кабинет в ЛесЕГАИС не нужен, от вас порода, объём и маршрут. От 1400 руб, ЭСД на рейс за 15 минут.&lt;/p&gt;&lt;p&gt;Сосновый пиловочник 4 и 6 метров, диаметр от 18 см.&lt;/p&gt;&lt;p&gt;Южа, Южский район, Ивановская область. Напишите, сколько машин в неделю.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -15880,7 +15880,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>7661728126</t>
+          <t>5628990094</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -15900,7 +15900,7 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;strong&gt;Делаем накладную с QR на перевозку древесины.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Документ на рейс за 15 минут, водитель показывает его на посту и на весовой. Договор купли-продажи закрепляет баланс за вами, и партию можно продать.&lt;/p&gt;&lt;p&gt;От вас порода, кубатура и маршрут, остальное на нас. От 950 руб.&lt;/p&gt;&lt;p&gt;Берёзовый баланс 2 и 3 метра, диаметр от 6 см.&lt;/p&gt;&lt;p&gt;Меленковский район, Владимирская область. Напишите, сколько кубов набирается.&lt;/p&gt;</t>
+          <t>&lt;p&gt;&lt;strong&gt;Делаем накладную с QR на перевозку древесины.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Документ готов за 15 минут. Что будет у вас на руках:&lt;br&gt;- электронный сопроводительный документ на рейс&lt;br&gt;- QR-код на перевозку древесины&lt;br&gt;- договор купли-продажи на берёзовый баланс&lt;br&gt;- кубатура в ФГИС ЛК за вами&lt;br&gt;- отчёт 1-ИЛ закрываем сами&lt;/p&gt;&lt;p&gt;Кабинет в ЛесЕГАИС и электронная подпись не нужны. От вас порода, объём и маршрут, от 950 руб.&lt;/p&gt;&lt;p&gt;Берёзовый баланс 2 и 3 метра, диаметр от 6 см.&lt;/p&gt;&lt;p&gt;Меленки, Меленковский район, Владимирская область. Напишите, сколько кубов набирается.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -16006,7 +16006,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>6738021087</t>
+          <t>6560689748</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -16026,7 +16026,7 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;strong&gt;Оформляем договор и ЭСД на груз.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Договор купли-продажи на древесину и электронный сопроводительный документ с QR на каждый рейс. С ними партию принимают на комбинате.&lt;/p&gt;&lt;p&gt;Бумажную часть ведём мы, от вас порода, объём и маршрут. От 2000 руб.&lt;/p&gt;&lt;p&gt;Сосновый пиловочник 6 метров, диаметр от 20 см.&lt;/p&gt;&lt;p&gt;Кукморский район, Татарстан. Напишите, какой объём отгружаете.&lt;/p&gt;</t>
+          <t>&lt;p&gt;&lt;strong&gt;Оформляем договор и ЭСД на груз.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Электронный сопроводительный документ выписываем на каждую машину, QR-код на перевозку древесины в нём уже есть. С ним партию принимают на комбинате и на весовой.&lt;/p&gt;&lt;p&gt;Сосновый пиловочник закрепляем за вами договором купли-продажи, кубатуру ставим в ФГИС ЛК, отчёт 1-ИЛ закрываем сами. Кабинет в ЛесЕГАИС не нужен, от 2000 руб.&lt;/p&gt;&lt;p&gt;Сосновый пиловочник 6 метров, диаметр от 20 см.&lt;/p&gt;&lt;p&gt;Кукмор, Кукморский район, Татарстан. Напишите, какой объём отгружаете.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -16132,7 +16132,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>7065474569</t>
+          <t>4519088530</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -16152,7 +16152,7 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;strong&gt;Оформляем документы тем, кто пилит сам.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Заготовка становится товаром: договор купли-продажи, кубатура в ФГИС ЛК, ЭСД с QR на отгрузку.&lt;/p&gt;&lt;p&gt;Оформление целиком на нас, от вас порода, объём и маршрут. От 1850 руб, документ на рейс за 15 минут.&lt;/p&gt;&lt;p&gt;Сосновый пиловочник 4 и 6 метров, диаметр от 18 см.&lt;/p&gt;&lt;p&gt;Караидельский район, Башкортостан. Напишите, что за лес и сколько его.&lt;/p&gt;</t>
+          <t>&lt;p&gt;&lt;strong&gt;Оформляем документы тем, кто пилит сам.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Пилите сами: заготовку ставим на учёт в ФГИС ЛК, сосновый пиловочник начинает числиться за вами.&lt;/p&gt;&lt;p&gt;Продаёте: договор купли-продажи делает древесину товаром. Везёте: электронный сопроводительный документ и QR-код на перевозку древесины на каждый рейс.&lt;/p&gt;&lt;p&gt;Кабинет в ЛесЕГАИС и подпись не нужны, от 1850 руб.&lt;/p&gt;&lt;p&gt;Сосновый пиловочник 4 и 6 метров, диаметр от 18 см.&lt;/p&gt;&lt;p&gt;Караидель, Караидельский район, Башкортостан. Напишите, что за лес и сколько его.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -16258,7 +16258,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>9518632923</t>
+          <t>7366509820</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -16278,7 +16278,7 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;strong&gt;Оформляем QR-код на перевозку леса.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;На каждый рейс свой ЭСД, на партию договор купли-продажи, кубатура встаёт в ФГИС ЛК за вами.&lt;/p&gt;&lt;p&gt;От вас порода, объём и маршрут, кабинет и электронная подпись не нужны. От 1490 руб.&lt;/p&gt;&lt;p&gt;Сосновый пиловочник 4 и 6 метров, диаметр от 18 см.&lt;/p&gt;&lt;p&gt;Заволжский район, Ивановская область. Напишите, сколько пиловочника.&lt;/p&gt;</t>
+          <t>&lt;p&gt;&lt;strong&gt;Оформляем QR-код на перевозку леса.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Электронный сопроводительный документ выписываем на рейс, QR-код на перевозку древесины уже внутри. Водитель показывает его с телефона на посту.&lt;/p&gt;&lt;p&gt;Сосновый пиловочник закрепляем договором купли-продажи, кубатура идёт в ФГИС ЛК за вами, декларацию о сделке подаём сами.&lt;/p&gt;&lt;p&gt;Кабинет в ЛесЕГАИС и подпись не нужны, от 1490 руб за рейс.&lt;/p&gt;&lt;p&gt;Сосновый пиловочник 4 и 6 метров, диаметр от 18 см.&lt;/p&gt;&lt;p&gt;Заволжск, Заволжский район, Ивановская область. Напишите, сколько пиловочника.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -16384,7 +16384,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2697992858</t>
+          <t>7840079321</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -16404,7 +16404,7 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;strong&gt;Выдаём QR-код на перевозку леса.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;На каждый рейс электронный сопроводительный документ, QR проверяется телефоном за пару секунд. На партию договор купли-продажи.&lt;/p&gt;&lt;p&gt;Работаем по переписке, свой кабинет в ФГИС ЛК заводить не надо. От вас порода, кубатура и куда везёте. От 850 руб.&lt;/p&gt;&lt;p&gt;Еловый кругляк 4 и 6 метров, диаметр от 14 см.&lt;/p&gt;&lt;p&gt;Пестяковский район, Ивановская область. Напишите, когда ближайшая отгрузка.&lt;/p&gt;</t>
+          <t>&lt;p&gt;&lt;strong&gt;Выдаём QR-код на перевозку леса.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Электронный сопроводительный документ на рейс, а в нём QR-код на перевозку древесины. Инспектор на посту сканирует его телефоном за пару секунд.&lt;/p&gt;&lt;p&gt;Еловый кругляк оформляем договором купли-продажи и ставим на учёт в ФГИС ЛК, объём числится за вами.&lt;/p&gt;&lt;p&gt;Свой кабинет в ЛесЕГАИС заводить не надо, работаем по переписке. От 850 руб за рейс.&lt;/p&gt;&lt;p&gt;Еловый кругляк 4 и 6 метров, диаметр от 14 см.&lt;/p&gt;&lt;p&gt;Пестяки, Пестяковский район, Ивановская область. Напишите, когда ближайшая отгрузка.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -16510,7 +16510,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>8630019576</t>
+          <t>4731301322</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -16530,7 +16530,7 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;strong&gt;Ставим древесину на учёт в ФГИС ЛК.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Кубатура начинает числиться за вами. Дальше договор купли-продажи на партию и ЭСД с QR на каждую машину.&lt;/p&gt;&lt;p&gt;Всю возню с системой берём на себя, свой кабинет и подпись вам не нужны. От вас порода, объём и маршрут. От 1700 руб.&lt;/p&gt;&lt;p&gt;Сосновый пиловочник 6 метров, диаметр от 20 см.&lt;/p&gt;&lt;p&gt;Судогодский район, Владимирская область. Напишите, сколько кубов и куда везёте.&lt;/p&gt;</t>
+          <t>&lt;p&gt;&lt;strong&gt;Ставим древесину на учёт в ФГИС ЛК.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Сосновый пиловочник встаёт на учёт, и кубатура числится за вами. Дальше по списку:&lt;br&gt;- договор купли-продажи на вашу древесину&lt;br&gt;- QR-код на перевозку древесины на каждый рейс&lt;br&gt;- электронный сопроводительный документ за 15 минут&lt;/p&gt;&lt;p&gt;Свой кабинет в ЛесЕГАИС вам не нужен. От вас порода, объём и маршрут, от 1700 руб.&lt;/p&gt;&lt;p&gt;Сосновый пиловочник 6 метров, диаметр от 20 см.&lt;/p&gt;&lt;p&gt;Судогда, Судогодский район, Владимирская область. Напишите, сколько кубов и куда везёте.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -16636,7 +16636,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2140473788</t>
+          <t>1156126848</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -16656,7 +16656,7 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;strong&gt;Заводим вашу кубатуру в ФГИС ЛК.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Объём встаёт на баланс за вами, на партию идёт договор купли-продажи, на отгрузку ЭСД с QR.&lt;/p&gt;&lt;p&gt;Разбираться в системе не придётся, работаем и с одной машиной, и с потоком. От 900 руб.&lt;/p&gt;&lt;p&gt;Еловый баланс 2 и 3 метра, диаметр от 6 см.&lt;/p&gt;&lt;p&gt;Кезский район, Удмуртия. Напишите, сколько кубов балансов.&lt;/p&gt;</t>
+          <t>&lt;p&gt;&lt;strong&gt;Заводим вашу кубатуру в ФГИС ЛК.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Продаёте партию: договор купли-продажи делает древесину вашим товаром, кубатура встаёт на баланс в ФГИС ЛК.&lt;/p&gt;&lt;p&gt;Везёте сами: на рейс идёт электронный сопроводительный документ, в нём QR-код на перевозку древесины.&lt;/p&gt;&lt;p&gt;Свой кабинет в ЛесЕГАИС и подпись не нужны, еловый баланс берём любым объёмом. От 900 руб, документ на рейс за 15 минут.&lt;/p&gt;&lt;p&gt;Еловый баланс 2 и 3 метра, диаметр от 6 см.&lt;/p&gt;&lt;p&gt;Кез, Кезский район, Удмуртия. Напишите, сколько кубов балансов.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -16762,7 +16762,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>6038274710</t>
+          <t>8543140206</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -16782,7 +16782,7 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;strong&gt;Выписываем ЭСД на каждую машину.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Сколько лесовозов уходит, столько документов с QR. И договор купли-продажи, по которому древесину принимают на весовой.&lt;/p&gt;&lt;p&gt;Работу с ФГИС ЛК берём на себя, от вас порода, кубатура и маршрут. От 1550 руб.&lt;/p&gt;&lt;p&gt;Еловый пиловочник 4 и 6 метров, диаметр от 16 см.&lt;/p&gt;&lt;p&gt;Маслянинский район, Новосибирская область. Напишите, сколько машин в неделю.&lt;/p&gt;</t>
+          <t>&lt;p&gt;&lt;strong&gt;Выписываем ЭСД на каждую машину.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Электронный сопроводительный документ делаем на каждый лесовоз. В каждом свой QR-код на перевозку древесины, 15 минут на документ.&lt;/p&gt;&lt;p&gt;Еловый пиловочник закрываем договором купли-продажи, декларацию о сделке в ФГИС ЛК подаём сами.&lt;/p&gt;&lt;p&gt;Кабинет в ЛесЕГАИС и электронная подпись вам не нужны, от вас порода, кубатура и маршрут. От 1550 руб.&lt;/p&gt;&lt;p&gt;Еловый пиловочник 4 и 6 метров, диаметр от 16 см.&lt;/p&gt;&lt;p&gt;Маслянино, Маслянинский район, Новосибирская область. Напишите, сколько рейсов в неделю.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -16888,7 +16888,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>8464900540</t>
+          <t>7187686177</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -16908,7 +16908,7 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;strong&gt;Делаем документы на древесину в ФГИС ЛК.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Договор купли-продажи закрепляет лес за вами, кубатура числится в системе, на рейсы идёт ЭСД с QR.&lt;/p&gt;&lt;p&gt;Документами занимаемся мы целиком, вам грузить и получать деньги. От 2490 руб.&lt;/p&gt;&lt;p&gt;Еловый кругляк 4 и 6 метров, диаметр от 16 см.&lt;/p&gt;&lt;p&gt;Гороховецкий район, Владимирская область. Напишите, когда отгрузка.&lt;/p&gt;</t>
+          <t>&lt;p&gt;&lt;strong&gt;Делаем документы на древесину в ФГИС ЛК.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Еловый кругляк становится учтённым товаром. По списку:&lt;br&gt;- постановка древесины на учёт в ФГИС ЛК&lt;br&gt;- договор купли-продажи, по нему лес ваш&lt;br&gt;- электронный сопроводительный документ на каждый рейс&lt;br&gt;- QR-код на перевозку древесины для водителя&lt;/p&gt;&lt;p&gt;Работу берём на себя, кабинет в ЛесЕГАИС и подпись вам не нужны. От 2490 руб.&lt;/p&gt;&lt;p&gt;Еловый кругляк 4 и 6 метров, диаметр от 16 см.&lt;/p&gt;&lt;p&gt;Гороховец, Гороховецкий район, Владимирская область. Напишите, когда отгрузка.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -17014,7 +17014,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>9832978840</t>
+          <t>6082650913</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -17034,7 +17034,7 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;strong&gt;Выписываем ЭСД на вывоз леса.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Электронный сопроводительный документ с QR готов за 15 минут, на каждый рейс свой. И договор купли-продажи на древесину.&lt;/p&gt;&lt;p&gt;Ни кабинета, ни электронной подписи от вас. Назовите породу, кубатуру и маршрут. От 1100 руб.&lt;/p&gt;&lt;p&gt;Еловый пиловочник 4 и 6 метров, диаметр от 16 см.&lt;/p&gt;&lt;p&gt;Западнодвинский округ, Тверская область. Напишите, когда грузите лесовоз.&lt;/p&gt;</t>
+          <t>&lt;p&gt;&lt;strong&gt;Выписываем ЭСД на вывоз леса.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Электронный сопроводительный документ делаем на каждый рейс, в нём QR-код на перевозку древесины. Водитель показывает его на посту, груз едет дальше.&lt;/p&gt;&lt;p&gt;Еловый пиловочник закрепляем договором купли-продажи, кубатуру ставим в ФГИС ЛК, оформляем места складирования. Кабинет в ЛесЕГАИС не нужен, от 1100 руб.&lt;/p&gt;&lt;p&gt;Еловый пиловочник 4 и 6 метров, диаметр от 16 см.&lt;/p&gt;&lt;p&gt;Западная Двина, Западнодвинский округ, Тверская область. Напишите, когда грузите лесовоз.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -17140,7 +17140,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>1273554299</t>
+          <t>4846480914</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -17160,7 +17160,7 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;strong&gt;Ставим берёзу на учёт в ФГИС ЛК.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Объём числится за вами, на руках договор купли-продажи и ЭСД с QR на вывоз.&lt;/p&gt;&lt;p&gt;Проще некуда: назвали породу и кубатуру, получили документ на машину. Подпись и кабинет не нужны. От 350 руб.&lt;/p&gt;&lt;p&gt;Берёзовые дрова и баланс 1 и 2 метра, диаметр от 6 см.&lt;/p&gt;&lt;p&gt;Балтасинский район, Татарстан. Напишите, сколько кубов дров.&lt;/p&gt;</t>
+          <t>&lt;p&gt;&lt;strong&gt;Ставим берёзу на учёт в ФГИС ЛК.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Берёзовые дрова тоже должны числиться за вами. Делаем так:&lt;br&gt;- постановка кубатуры на учёт в ФГИС ЛК&lt;br&gt;- договор купли-продажи на вашу древесину&lt;br&gt;- QR-код на перевозку древесины на каждый рейс&lt;/p&gt;&lt;p&gt;Электронный сопроводительный документ готов за 15 минут. Ни кабинета в ЛесЕГАИС, ни подписи от вас, от 350 руб.&lt;/p&gt;&lt;p&gt;Берёзовые дрова и баланс 1 и 2 метра, диаметр от 6 см.&lt;/p&gt;&lt;p&gt;Балтаси, Балтасинский район, Татарстан. Напишите, сколько кубов дров.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -17266,7 +17266,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>7154914119</t>
+          <t>8373658504</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -17286,7 +17286,7 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;strong&gt;Выдаём ЭСД с QR за 15 минут.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Документ на рейс приходит в тот же день, когда написали. Партия закрыта договором купли-продажи, кубатура стоит в ФГИС ЛК.&lt;/p&gt;&lt;p&gt;Всю работу с системой ведём мы, вам остаётся грузить лесовозы. От 2450 руб.&lt;/p&gt;&lt;p&gt;Еловый пиловочник 6 метров, диаметр от 20 см.&lt;/p&gt;&lt;p&gt;Варнавинский район, Нижегородская область. Напишите, сколько рейсов в месяц.&lt;/p&gt;</t>
+          <t>&lt;p&gt;&lt;strong&gt;Выдаём ЭСД с QR за 15 минут.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Электронный сопроводительный документ на рейс делаем за 15 минут, в тот же день, когда написали. В нём QR-код на перевозку древесины, машина едет спокойно.&lt;/p&gt;&lt;p&gt;Еловый пиловочник закрыт договором купли-продажи, кубатура стоит в ФГИС ЛК за вами, отчёт 1-ИЛ сдаём сами. Кабинет в ЛесЕГАИС не нужен, от 2450 руб.&lt;/p&gt;&lt;p&gt;Еловый пиловочник 6 метров, диаметр от 20 см.&lt;/p&gt;&lt;p&gt;Варнавино, Варнавинский район, Нижегородская область. Напишите, сколько рейсов в месяц.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -17392,7 +17392,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>5708797610</t>
+          <t>3234945559</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -17412,7 +17412,7 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;strong&gt;Оформляем документы на продажу леса.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Договор купли-продажи, по которому кряж становится вашим товаром. Сделка проведена в ФГИС ЛК, на вывоз ЭСД с QR.&lt;/p&gt;&lt;p&gt;Берём любой объём: хоть одна машина, хоть двадцать. Вникать ни во что не придётся. От 620 руб.&lt;/p&gt;&lt;p&gt;Берёзовый кряж 3 и 4 метра, диаметр от 16 см.&lt;/p&gt;&lt;p&gt;Кузоватовский район, Ульяновская область. Напишите, сколько кряжа лежит.&lt;/p&gt;</t>
+          <t>&lt;p&gt;&lt;strong&gt;Оформляем документы на продажу леса.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Возите сами: даём электронный сопроводительный документ и QR-код на перевозку древесины на каждый рейс.&lt;/p&gt;&lt;p&gt;Продаёте партию: оформляем договор купли-продажи на берёзовый кряж и подаём декларацию о сделке в ФГИС ЛК.&lt;/p&gt;&lt;p&gt;Кабинет в ЛесЕГАИС и подпись не нужны, всё по переписке. От 620 руб, документ на рейс за 15 минут.&lt;/p&gt;&lt;p&gt;Берёзовый кряж 3 и 4 метра, диаметр от 16 см.&lt;/p&gt;&lt;p&gt;Кузоватово, Кузоватовский район, Ульяновская область. Напишите, сколько кряжа лежит.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -17518,7 +17518,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>7235918048</t>
+          <t>4789650607</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -17538,7 +17538,7 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;strong&gt;Выдаём документ с QR на каждый рейс.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;С ним баланс принимают на весовой и на комбинате. Договор купли-продажи на партию тоже будет у вас на руках.&lt;/p&gt;&lt;p&gt;Всё по переписке, объём любой. От 990 руб, документ на машину за 15 минут.&lt;/p&gt;&lt;p&gt;Берёзовый баланс 2 и 3 метра, диаметр от 6 см.&lt;/p&gt;&lt;p&gt;Сурский район, Ульяновская область. Напишите, сколько баланса.&lt;/p&gt;</t>
+          <t>&lt;p&gt;&lt;strong&gt;Выдаём документ с QR на каждый рейс.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;На машину идёт электронный сопроводительный документ, в нём QR-код на перевозку древесины. С ним берёзовый баланс принимают на весовой и на комбинате.&lt;/p&gt;&lt;p&gt;Партию закрываем договором купли-продажи, кубатура числится за вами в ФГИС ЛК, отчёт 1-ИЛ сдаём сами. Кабинет в ЛесЕГАИС не нужен, от 990 руб за рейс.&lt;/p&gt;&lt;p&gt;Берёзовый баланс 2 и 3 метра, диаметр от 6 см.&lt;/p&gt;&lt;p&gt;Сурское, Сурский район, Ульяновская область. Напишите, сколько баланса.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -17644,7 +17644,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>3891490310</t>
+          <t>6664165510</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -17664,7 +17664,7 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;strong&gt;Делаем документы на лес, купленный у населения.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Древесина становится законным товаром: договор купли-продажи на партию, кубатура в ФГИС ЛК, QR-код на перевозку.&lt;/p&gt;&lt;p&gt;От вас порода и объём, дальше уже не ваша забота. От 750 руб, ЭСД на рейс за 15 минут.&lt;/p&gt;&lt;p&gt;Сосновый кругляк 4 и 6 метров, диаметр от 18 см.&lt;/p&gt;&lt;p&gt;Зубово-Полянский район, Мордовия. Напишите, сколько машин планируете.&lt;/p&gt;</t>
+          <t>&lt;p&gt;&lt;strong&gt;Делаем документы на лес, купленный у населения.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Древесина от населения становится законным товаром. На руках будет:&lt;br&gt;- договор купли-продажи на сосновый кругляк&lt;br&gt;- кубатура на балансе в ФГИС ЛК за вами&lt;br&gt;- ЭСД и QR-код на перевозку древесины&lt;/p&gt;&lt;p&gt;Кабинет в ЛесЕГАИС заводить не придётся. Электронный сопроводительный документ выдаём за 15 минут, от 750 руб.&lt;/p&gt;&lt;p&gt;Сосновый кругляк 4 и 6 метров, диаметр от 18 см.&lt;/p&gt;&lt;p&gt;Зубова Поляна, Зубово-Полянский район, Мордовия. Напишите, сколько машин планируете.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -17770,7 +17770,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>8653558262</t>
+          <t>7326838900</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -17790,7 +17790,7 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;strong&gt;Даём QR-код на вывоз партии.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Документ на рейс за 15 минут, перевозчик берётся за груз без вопросов. Договор купли-продажи подтверждает, что древесина ваша.&lt;/p&gt;&lt;p&gt;Заявка на пару минут: порода, кубатура, маршрут. Кабинет в ФГИС ЛК не нужен. От 480 руб.&lt;/p&gt;&lt;p&gt;Сосновая доска и кругляк 4 и 6 метров, диаметр от 18 см.&lt;/p&gt;&lt;p&gt;Шиловский район, Рязанская область. Напишите, сколько рейсов надо закрыть.&lt;/p&gt;</t>
+          <t>&lt;p&gt;&lt;strong&gt;Даём QR-код на вывоз партии.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;QR-код на перевозку древесины идёт на каждую машину. Документ электронный, водитель показывает его с телефона на посту.&lt;/p&gt;&lt;p&gt;Сосновую доску и кругляк проводим договором купли-продажи, декларацию о сделке в ФГИС ЛК подаём сами.&lt;/p&gt;&lt;p&gt;Кабинет в ЛесЕГАИС не нужен, от вас порода, объём и маршрут. От 480 руб, электронный сопроводительный документ за 15 минут.&lt;/p&gt;&lt;p&gt;Сосновая доска и кругляк 4 и 6 метров, диаметр от 18 см.&lt;/p&gt;&lt;p&gt;Шилово, Шиловский район, Рязанская область. Напишите, сколько рейсов надо закрыть.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -17896,7 +17896,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>7088644908</t>
+          <t>8006364040</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -17916,7 +17916,7 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;strong&gt;Закрываем рейсы документом с QR.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;ЭСД на каждую машину, QR живой, проверяется прямо на посту. Партия при этом оформлена договором купли-продажи.&lt;/p&gt;&lt;p&gt;Всё по переписке, объём любой, хоть одна машина в месяц. От 690 руб.&lt;/p&gt;&lt;p&gt;Хвойный кругляк 4 и 6 метров, диаметр от 16 см.&lt;/p&gt;&lt;p&gt;Тисульский район, Кемеровская область. Напишите, сколько кругляка.&lt;/p&gt;</t>
+          <t>&lt;p&gt;&lt;strong&gt;Закрываем рейсы документом с QR.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;QR-код на перевозку древесины сканируют прямо на посту, он живой и привязан к рейсу. Выдаём электронный сопроводительный документ за 15 минут.&lt;/p&gt;&lt;p&gt;Хвойный кругляк оформляем договором купли-продажи, кубатура в ФГИС ЛК за вами, места складирования заявляем сами.&lt;/p&gt;&lt;p&gt;Кабинет в ЛесЕГАИС не нужен, объём любой, хоть одна машина в месяц. От 690 руб.&lt;/p&gt;&lt;p&gt;Хвойный кругляк 4 и 6 метров, диаметр от 16 см.&lt;/p&gt;&lt;p&gt;Тисуль, Тисульский район, Кемеровская область. Напишите, сколько кругляка.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -18022,7 +18022,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>4175583854</t>
+          <t>2714757754</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -18042,7 +18042,7 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;strong&gt;Оформляем места складирования и вывоз древесины.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Площадка заявлена, кубатура стоит в ФГИС ЛК за вами, на каждый рейс ЭСД с QR.&lt;/p&gt;&lt;p&gt;Ни кабинета, ни подписи: пишете адрес площадки, породу и объём. От 820 руб, документ на машину за 15 минут.&lt;/p&gt;&lt;p&gt;Сосновый кругляк 4 и 6 метров, диаметр от 18 см.&lt;/p&gt;&lt;p&gt;Нязепетровский район, Челябинская область. Напишите, сколько кубов лежит.&lt;/p&gt;</t>
+          <t>&lt;p&gt;&lt;strong&gt;Оформляем места складирования и вывоз древесины.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Штабель на площадке встаёт в систему как ваш объём. Что делаем:&lt;br&gt;- места складирования в ФГИС ЛК&lt;br&gt;- договор купли-продажи на сосновый кругляк&lt;br&gt;- электронный сопроводительный документ на вывоз&lt;br&gt;- QR-код на перевозку древесины на каждый рейс&lt;/p&gt;&lt;p&gt;От вас адрес площадки, порода и объём, кабинет в ЛесЕГАИС не нужен. От 820 руб.&lt;/p&gt;&lt;p&gt;Сосновый кругляк 4 и 6 метров, диаметр от 18 см.&lt;/p&gt;&lt;p&gt;Нязепетровск, Нязепетровский район, Челябинская область. Напишите, сколько кубов лежит.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -18148,7 +18148,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>1385322760</t>
+          <t>3358334445</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -18168,7 +18168,7 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;strong&gt;Оформляем вывоз леса по документам с QR.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Каждая машина едет со своим ЭСД. Партия закрыта договором купли-продажи, кубатура в ФГИС ЛК числится за вами.&lt;/p&gt;&lt;p&gt;Систему берём на себя, от вас порода, кубатура и маршрут. От 1990 руб.&lt;/p&gt;&lt;p&gt;Еловый пиловочник 6 метров, диаметр от 20 см.&lt;/p&gt;&lt;p&gt;Торопецкий район, Тверская область. Напишите, сколько машин уходит.&lt;/p&gt;</t>
+          <t>&lt;p&gt;&lt;strong&gt;Оформляем вывоз леса по документам с QR.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;QR-код на перевозку древесины идёт на каждую машину, отдельно на рейс. Сканируют его на посту, груз не задерживают.&lt;/p&gt;&lt;p&gt;Сам электронный сопроводительный документ готов за 15 минут. Еловый пиловочник закрыт договором купли-продажи, кубатура и места складирования стоят в ФГИС ЛК.&lt;/p&gt;&lt;p&gt;Кабинет в ЛесЕГАИС не нужен, от 1990 руб.&lt;/p&gt;&lt;p&gt;Еловый пиловочник 6 метров, диаметр от 20 см.&lt;/p&gt;&lt;p&gt;Торопец, Торопецкий район, Тверская область. Напишите, сколько машин уходит.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -18274,7 +18274,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>1517789134</t>
+          <t>8001567780</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -18294,7 +18294,7 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;strong&gt;Оформляем документы на древесину и отчётность по ней.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;ЭСД с QR на каждую машину, договор купли-продажи на партию, кубатура в ФГИС ЛК. Отчёт 1-ИЛ закрываем сами.&lt;/p&gt;&lt;p&gt;От вас порода, объём и маршрут. От 1250 руб, документ на рейс за 15 минут.&lt;/p&gt;&lt;p&gt;Сосновый пиловочник 4 и 6 метров, диаметр от 18 см.&lt;/p&gt;&lt;p&gt;Заринский район, Алтайский край. Напишите, куда идут машины.&lt;/p&gt;</t>
+          <t>&lt;p&gt;&lt;strong&gt;Оформляем документы на древесину и отчётность по ней.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Берём на себя бумажную часть по сосновому пиловочнику:&lt;br&gt;- электронный сопроводительный документ на рейс за 15 минут&lt;br&gt;- QR-код на перевозку древесины для водителя&lt;br&gt;- договор купли-продажи, кубатура в ФГИС ЛК за вами&lt;br&gt;- отчёт 1-ИЛ сдаём сами&lt;/p&gt;&lt;p&gt;Кабинет в ЛесЕГАИС вам не понадобится, от 1250 руб.&lt;/p&gt;&lt;p&gt;Сосновый пиловочник 4 и 6 метров, диаметр от 18 см.&lt;/p&gt;&lt;p&gt;Заринск, Заринский район, Алтайский край. Напишите, куда идут машины.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
@@ -18400,7 +18400,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>5495184664</t>
+          <t>1370253181</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -18420,7 +18420,7 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;strong&gt;Делаем документы на перевозку древесины.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Накладная с QR на рейс, договор купли-продажи на партию, кубатура в ФГИС ЛК за вами.&lt;/p&gt;&lt;p&gt;Начинать никуда не надо, просто напишите. Кабинет и подпись не нужны, от вас порода, объём и маршрут. От 540 руб.&lt;/p&gt;&lt;p&gt;Сосновый баланс 2 и 3 метра, диаметр от 6 см.&lt;/p&gt;&lt;p&gt;Земетчинский район, Пензенская область. Напишите, когда первая отгрузка.&lt;/p&gt;</t>
+          <t>&lt;p&gt;&lt;strong&gt;Делаем документы на перевозку древесины.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Накладная на машину, это электронный сопроводительный документ. В нём QR-код на перевозку древесины, водителю хватает телефона.&lt;/p&gt;&lt;p&gt;Сосновый баланс закрепляем договором купли-продажи, кубатура встаёт на баланс в ФГИС ЛК и числится за вами. Кабинет в ЛесЕГАИС заводить не надо.&lt;/p&gt;&lt;p&gt;От вас порода, объём и маршрут. От 540 руб, документ за 15 минут.&lt;/p&gt;&lt;p&gt;Сосновый баланс 2 и 3 метра, диаметр от 6 см.&lt;/p&gt;&lt;p&gt;Земетчино, Земетчинский район, Пензенская область. Напишите, когда первая отгрузка.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -18526,7 +18526,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>7017657555</t>
+          <t>7657398596</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -18546,7 +18546,7 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;strong&gt;Проводим сделку по древесине в ФГИС ЛК.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Договор купли-продажи на партию, объём за вами в системе, QR-код на перевозку каждой машины.&lt;/p&gt;&lt;p&gt;Берём даже одну машину, вникать ни во что не придётся. От 420 руб, ЭСД на рейс за 15 минут.&lt;/p&gt;&lt;p&gt;Хвойный баланс 2 и 3 метра, диаметр от 6 см.&lt;/p&gt;&lt;p&gt;Тоншаевский район, Нижегородская область. Напишите породу и кубатуру.&lt;/p&gt;</t>
+          <t>&lt;p&gt;&lt;strong&gt;Проводим сделку по древесине в ФГИС ЛК.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Продаёте партию: договор купли-продажи делает хвойный баланс вашим товаром, декларация о сделке проходит в ФГИС ЛК.&lt;/p&gt;&lt;p&gt;Везёте сами: на машину выписываем электронный сопроводительный документ и QR-код на перевозку древесины.&lt;/p&gt;&lt;p&gt;Берём даже одну машину, кабинет в ЛесЕГАИС не нужен. От 420 руб, документ за 15 минут.&lt;/p&gt;&lt;p&gt;Хвойный баланс 2 и 3 метра, диаметр от 6 см.&lt;/p&gt;&lt;p&gt;Тоншаево, Тоншаевский район, Нижегородская область. Напишите породу и кубатуру.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
@@ -18652,7 +18652,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>4896481532</t>
+          <t>8344104479</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -18672,7 +18672,7 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;strong&gt;Выписываем документ с QR на каждый лесовоз.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;ЭСД на рейс за 15 минут и договор купли-продажи, по которому партия ваша.&lt;/p&gt;&lt;p&gt;Возиться с ФГИС ЛК не придётся, всё делаем сами. От вас порода, кубатура и маршрут. От 2700 руб.&lt;/p&gt;&lt;p&gt;Берёзовый кругляк 3 и 4 метра, диаметр от 16 см.&lt;/p&gt;&lt;p&gt;Ибресинский район, Чувашия. Напишите, какой объём вывозите.&lt;/p&gt;</t>
+          <t>&lt;p&gt;&lt;strong&gt;Выписываем документ с QR на каждый лесовоз.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;QR-код на перевозку древесины идёт на каждую машину. Проверяется телефоном за пару секунд, разворотов на трассе не будет.&lt;/p&gt;&lt;p&gt;Электронный сопроводительный документ на рейс готов за 15 минут. Берёзовый кругляк проводим договором купли-продажи, кубатура встаёт на баланс в ФГИС ЛК.&lt;/p&gt;&lt;p&gt;Кабинет в ЛесЕГАИС не нужен, от 2700 руб.&lt;/p&gt;&lt;p&gt;Берёзовый кругляк 3 и 4 метра, диаметр от 16 см.&lt;/p&gt;&lt;p&gt;Ибреси, Ибресинский район, Чувашия. Напишите, какой объём вывозите.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
@@ -18778,7 +18778,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>6437459772</t>
+          <t>4176535762</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -18798,7 +18798,7 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;strong&gt;Делаем документы на перевозку дров и баланса.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;ЭСД с QR на рейс и договор купли-продажи, по которому древесина ваша.&lt;/p&gt;&lt;p&gt;Проще некуда: пишете объём и куда везёте, получаете документ за 15 минут. От 490 руб.&lt;/p&gt;&lt;p&gt;Берёзовые дрова и баланс 1 и 2 метра, диаметр от 6 см.&lt;/p&gt;&lt;p&gt;Темниковский район, Мордовия. Напишите, сколько кубов дров и куда.&lt;/p&gt;</t>
+          <t>&lt;p&gt;&lt;strong&gt;Делаем документы на перевозку дров и баланса.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;На каждый рейс выписываем электронный сопроводительный документ, в нём QR-код на перевозку древесины. Груз едет законно.&lt;/p&gt;&lt;p&gt;Берёзовые дрова проводим договором купли-продажи, кубатура встаёт на баланс в ФГИС ЛК за вами. Кабинет в ЛесЕГАИС заводить не надо, от 490 руб, документ за 15 минут.&lt;/p&gt;&lt;p&gt;Берёзовые дрова и баланс 1 и 2 метра, диаметр от 6 см.&lt;/p&gt;&lt;p&gt;Темников, Темниковский район, Мордовия. Напишите объём и маршрут.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
@@ -18904,7 +18904,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2579967049</t>
+          <t>2760809937</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -18924,7 +18924,7 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;strong&gt;Ставим объём в ФГИС ЛК и даём QR на рейс.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Кругляк числится за вами, на партию договор купли-продажи, на каждую машину ЭСД.&lt;/p&gt;&lt;p&gt;Ни кабинета, ни электронной подписи. От вас порода, кубатура и маршрут. От 1150 руб.&lt;/p&gt;&lt;p&gt;Хвойный кругляк 4 и 6 метров, диаметр от 16 см.&lt;/p&gt;&lt;p&gt;Увинский район, Удмуртия. Напишите, сколько кругляка лежит.&lt;/p&gt;</t>
+          <t>&lt;p&gt;&lt;strong&gt;Ставим объём в ФГИС ЛК и даём QR на рейс.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Хвойный кругляк заводим в систему и закрываем бумагами. По порядку:&lt;br&gt;- постановка кубатуры на учёт в ФГИС ЛК&lt;br&gt;- договор купли-продажи на вашу древесину&lt;br&gt;- электронный сопроводительный документ за 15 минут&lt;br&gt;- QR-код на перевозку древесины на каждый рейс&lt;/p&gt;&lt;p&gt;Свой кабинет в ЛесЕГАИС и электронная подпись не нужны, от 1150 руб.&lt;/p&gt;&lt;p&gt;Хвойный кругляк 4 и 6 метров, диаметр от 16 см.&lt;/p&gt;&lt;p&gt;Ува, Увинский район, Удмуртия. Напишите, сколько кругляка лежит.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
@@ -19030,7 +19030,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>8626117472</t>
+          <t>7380042033</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -19050,7 +19050,7 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;strong&gt;Выписываем QR на вывоз древесины.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Документ на каждый рейс и договор купли-продажи, чтобы партию можно было продать.&lt;/p&gt;&lt;p&gt;Без хлопот и недорого, объём любой: хоть одна машина в месяц. От 290 руб, ЭСД за 15 минут.&lt;/p&gt;&lt;p&gt;Берёзовый баланс 2 и 3 метра, диаметр от 6 см.&lt;/p&gt;&lt;p&gt;Кадомский район, Рязанская область. Напишите, сколько баланса накопилось.&lt;/p&gt;</t>
+          <t>&lt;p&gt;&lt;strong&gt;Выписываем QR на вывоз древесины.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Везёте сами: на каждый рейс электронный сопроводительный документ, в нём QR-код на перевозку древесины.&lt;/p&gt;&lt;p&gt;Продаёте берёзовый баланс: договор купли-продажи и декларация о сделке в ФГИС ЛК, кубатура числится за вами.&lt;/p&gt;&lt;p&gt;Кабинет в ЛесЕГАИС не нужен, объём любой, хоть одна машина. От 290 руб, документ за 15 минут.&lt;/p&gt;&lt;p&gt;Берёзовый баланс 2 и 3 метра, диаметр от 6 см.&lt;/p&gt;&lt;p&gt;Кадом, Кадомский район, Рязанская область. Напишите, сколько баланса накопилось.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
@@ -19156,7 +19156,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2624373461</t>
+          <t>3281078406</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -19176,7 +19176,7 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;strong&gt;Оформляем договор купли-продажи и ЭСД на партию.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Древесина становится вашим товаром, кубатура встаёт в ФГИС ЛК, на каждый рейс документ с QR.&lt;/p&gt;&lt;p&gt;Вникать ни во что не придётся, бумажную сторону закрываем сами. От 2990 руб.&lt;/p&gt;&lt;p&gt;Сосновый пиловочник 6 метров, диаметр от 20 см.&lt;/p&gt;&lt;p&gt;Сабинский район, Татарстан. Напишите объём партии и сроки.&lt;/p&gt;</t>
+          <t>&lt;p&gt;&lt;strong&gt;Оформляем договор купли-продажи и ЭСД на партию.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Продаёте: договор купли-продажи делает сосновый пиловочник вашим товаром, кубатура встаёт в ФГИС ЛК.&lt;/p&gt;&lt;p&gt;Везёте: на каждую машину электронный сопроводительный документ и QR-код на перевозку древесины, 15 минут на рейс.&lt;/p&gt;&lt;p&gt;Отчёт 1-ИЛ сдаём сами, кабинет в ЛесЕГАИС вам не нужен. От 2990 руб.&lt;/p&gt;&lt;p&gt;Сосновый пиловочник 6 метров, диаметр от 20 см.&lt;/p&gt;&lt;p&gt;Богатые Сабы, Сабинский район, Татарстан. Напишите объём партии и сроки.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
@@ -19282,7 +19282,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>8485702559</t>
+          <t>4811004277</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -19302,7 +19302,7 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;strong&gt;Делаем документы, по которым лес можно продать.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Договор купли-продажи на древесину, кубатура за вами в ФГИС ЛК, ЭСД с QR на вывоз.&lt;/p&gt;&lt;p&gt;Работаем по переписке. От вас порода, объём и куда везёте. От 1750 руб, документ на рейс за 15 минут.&lt;/p&gt;&lt;p&gt;Сосновый кругляк 4 и 6 метров, диаметр от 18 см.&lt;/p&gt;&lt;p&gt;Залесовский округ, Алтайский край. Напишите, кому продаёте и сколько.&lt;/p&gt;</t>
+          <t>&lt;p&gt;&lt;strong&gt;Делаем документы, по которым лес можно продать.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Продаёте: договор купли-продажи закрепляет сосновый кругляк за вами, и партию можно выставлять покупателю.&lt;/p&gt;&lt;p&gt;Везёте: электронный сопроводительный документ на рейс и QR-код на перевозку древесины, 15 минут на машину.&lt;/p&gt;&lt;p&gt;Кубатура и места складирования стоят в ФГИС ЛК, кабинет в ЛесЕГАИС не нужен. От 1750 руб.&lt;/p&gt;&lt;p&gt;Сосновый кругляк 4 и 6 метров, диаметр от 18 см.&lt;/p&gt;&lt;p&gt;Залесово, Залесовский округ, Алтайский край. Напишите, кому продаёте и сколько.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -19408,7 +19408,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>7528664312</t>
+          <t>7740261188</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -19428,7 +19428,7 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;strong&gt;Оформляем отгрузку лесовозов по ЭСД с QR.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;На каждый рейс документ за 15 минут, на партию договор купли-продажи, кубатура в ФГИС ЛК за вами.&lt;/p&gt;&lt;p&gt;Поток машин ведём сами, от вас порода, объём и маршрут. От 3500 руб.&lt;/p&gt;&lt;p&gt;Сосновый пиловочник 4 и 6 метров, диаметр от 18 см.&lt;/p&gt;&lt;p&gt;Сузунский район, Новосибирская область. Напишите, сколько рейсов в неделю.&lt;/p&gt;</t>
+          <t>&lt;p&gt;&lt;strong&gt;Оформляем отгрузку лесовозов по ЭСД с QR.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;На каждый лесовоз выписываем электронный сопроводительный документ, в нём QR-код на перевозку древесины. Поток машин ведём сами, документ за 15 минут.&lt;/p&gt;&lt;p&gt;Сосновый пиловочник проводим договором купли-продажи, кубатура встаёт на баланс в ФГИС ЛК за вами. Кабинет в ЛесЕГАИС и подпись не нужны, от 3500 руб.&lt;/p&gt;&lt;p&gt;Сосновый пиловочник 4 и 6 метров, диаметр от 18 см.&lt;/p&gt;&lt;p&gt;Сузун, Сузунский район, Новосибирская область. Напишите, сколько машин в день.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">

--- a/egais.xlsx
+++ b/egais.xlsx
@@ -15754,7 +15754,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>8072318046</t>
+          <t>4434093629</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -15774,7 +15774,7 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;strong&gt;Оформляем документы на древесину.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Даём электронный сопроводительный документ и QR-код на перевозку древесины. Водитель показывает его на посту и на весовой.&lt;/p&gt;&lt;p&gt;Сосновый пиловочник проводим договором купли-продажи, кубатура встаёт в ФГИС ЛК за вами. Декларацию о сделке подаём сами.&lt;/p&gt;&lt;p&gt;Кабинет в ЛесЕГАИС не нужен, от вас порода, объём и маршрут. От 1400 руб, ЭСД на рейс за 15 минут.&lt;/p&gt;&lt;p&gt;Сосновый пиловочник 4 и 6 метров, диаметр от 18 см.&lt;/p&gt;&lt;p&gt;Южа, Южский район, Ивановская область. Напишите, сколько машин в неделю.&lt;/p&gt;</t>
+          <t>&lt;p&gt;&lt;strong&gt;Оформляем документы на древесину.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Даём электронный сопроводительный документ и QR-код на перевозку древесины. Водитель показывает его на посту и на весовой.&lt;/p&gt;&lt;p&gt;Сосновый пиловочник проводим договором купли-продажи, кубатура встаёт в ФГИС ЛК за вами. Декларацию о сделке подаём сами.&lt;/p&gt;&lt;p&gt;Кабинет в ЛесЕГАИС не нужен, от вас порода, объём и маршрут. ЭСД на рейс делаем за 15 минут.&lt;/p&gt;&lt;p&gt;Сосновый пиловочник 4 и 6 метров, диаметр от 18 см.&lt;/p&gt;&lt;p&gt;Южа, Южский район, Ивановская область. Напишите, сколько машин в неделю уходит, посчитаем.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -15863,24 +15863,24 @@
       </c>
       <c r="AG62" t="inlineStr">
         <is>
-          <t>2026-10-15T07:20:00+03:00</t>
+          <t>2026-10-15T08:30:00+03:00</t>
         </is>
       </c>
       <c r="AJ62" t="inlineStr">
         <is>
-          <t>2026-09-15T09:20:00+03:00</t>
+          <t>2026-09-15T10:30:00+03:00</t>
         </is>
       </c>
       <c r="AK62" t="inlineStr">
         <is>
-          <t>2026-10-15T07:20:00+03:00</t>
+          <t>2026-10-15T08:30:00+03:00</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>5628990094</t>
+          <t>4732648717</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -15895,17 +15895,17 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Баланс берёзовый, накладная с QR на рейс</t>
+          <t>Лес кругляк ель (документация ФГИС)</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;strong&gt;Делаем накладную с QR на перевозку древесины.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Документ готов за 15 минут. Что будет у вас на руках:&lt;br&gt;- электронный сопроводительный документ на рейс&lt;br&gt;- QR-код на перевозку древесины&lt;br&gt;- договор купли-продажи на берёзовый баланс&lt;br&gt;- кубатура в ФГИС ЛК за вами&lt;br&gt;- отчёт 1-ИЛ закрываем сами&lt;/p&gt;&lt;p&gt;Кабинет в ЛесЕГАИС и электронная подпись не нужны. От вас порода, объём и маршрут, от 950 руб.&lt;/p&gt;&lt;p&gt;Берёзовый баланс 2 и 3 метра, диаметр от 6 см.&lt;/p&gt;&lt;p&gt;Меленки, Меленковский район, Владимирская область. Напишите, сколько кубов набирается.&lt;/p&gt;</t>
+          <t>&lt;p&gt;&lt;strong&gt;Делаем документы на древесину в ФГИС ЛК.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Еловый кругляк становится учтённым товаром. По списку:&lt;br&gt;- постановка древесины на учёт в ФГИС ЛК&lt;br&gt;- договор купли-продажи, по нему лес ваш&lt;br&gt;- электронный сопроводительный документ на каждый рейс&lt;br&gt;- QR-код на перевозку древесины для водителя&lt;/p&gt;&lt;p&gt;Работу берём на себя, кабинет в ЛесЕГАИС и подпись вам не нужны.&lt;/p&gt;&lt;p&gt;Еловый кругляк 4 и 6 метров, диаметр от 16 см.&lt;/p&gt;&lt;p&gt;Гороховец, Гороховецкий район, Владимирская область. Напишите, когда отгрузка и сколько кубов.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_03_melenki_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_03_melenki_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_03_melenki_3.jpg</t>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-20/w2009_22_gorohovets_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-20/w2009_22_gorohovets_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-20/w2009_22_gorohovets_3.jpg</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -15920,7 +15920,7 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>Меленки, Владимирская обл., ул. Первомайская, 108</t>
+          <t>Гороховец, Владимирская обл., ул. Ленина, 93</t>
         </is>
       </c>
       <c r="O63" t="inlineStr">
@@ -15929,7 +15929,7 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>950</v>
+        <v>2490</v>
       </c>
       <c r="Q63" t="inlineStr">
         <is>
@@ -15963,7 +15963,7 @@
       </c>
       <c r="W63" t="inlineStr">
         <is>
-          <t>Берёза</t>
+          <t>Ель</t>
         </is>
       </c>
       <c r="X63" t="inlineStr">
@@ -15972,10 +15972,10 @@
         </is>
       </c>
       <c r="AB63" t="n">
-        <v>3000</v>
+        <v>6000</v>
       </c>
       <c r="AC63" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="AE63" t="inlineStr">
         <is>
@@ -15989,24 +15989,24 @@
       </c>
       <c r="AG63" t="inlineStr">
         <is>
-          <t>2026-10-15T09:40:00+03:00</t>
+          <t>2026-10-15T11:30:00+03:00</t>
         </is>
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>2026-09-15T11:40:00+03:00</t>
+          <t>2026-09-15T13:30:00+03:00</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
         <is>
-          <t>2026-10-15T09:40:00+03:00</t>
+          <t>2026-10-15T11:30:00+03:00</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>6560689748</t>
+          <t>5711102696</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -16021,17 +16021,17 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Пиловочник сосна, ЭСД и договор на груз</t>
+          <t>Пиловочник сосна (договор и ЭСД)</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;strong&gt;Оформляем договор и ЭСД на груз.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Электронный сопроводительный документ выписываем на каждую машину, QR-код на перевозку древесины в нём уже есть. С ним партию принимают на комбинате и на весовой.&lt;/p&gt;&lt;p&gt;Сосновый пиловочник закрепляем за вами договором купли-продажи, кубатуру ставим в ФГИС ЛК, отчёт 1-ИЛ закрываем сами. Кабинет в ЛесЕГАИС не нужен, от 2000 руб.&lt;/p&gt;&lt;p&gt;Сосновый пиловочник 6 метров, диаметр от 20 см.&lt;/p&gt;&lt;p&gt;Кукмор, Кукморский район, Татарстан. Напишите, какой объём отгружаете.&lt;/p&gt;</t>
+          <t>&lt;p&gt;&lt;strong&gt;Оформляем договор купли-продажи и ЭСД на партию.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Продаёте: договор купли-продажи делает сосновый пиловочник вашим товаром, кубатура встаёт в ФГИС ЛК.&lt;/p&gt;&lt;p&gt;Везёте: на каждую машину электронный сопроводительный документ и QR-код на перевозку древесины, 15 минут на рейс.&lt;/p&gt;&lt;p&gt;Отчёт 1-ИЛ сдаём сами, кабинет в ЛесЕГАИС и подпись вам не нужны.&lt;/p&gt;&lt;p&gt;Сосновый пиловочник 6 метров, диаметр от 20 см.&lt;/p&gt;&lt;p&gt;Богатые Сабы, Сабинский район, Татарстан. Напишите объём партии и сроки, подготовим документы.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_10_kukmor_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_10_kukmor_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_10_kukmor_3.jpg</t>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-20/w2009_28_saby_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-20/w2009_28_saby_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-20/w2009_28_saby_3.jpg</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -16046,7 +16046,7 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>Кукмор, Республика Татарстан, ул. Ленина, 15</t>
+          <t>Богатые Сабы, Республика Татарстан, ул. Ленина, 2</t>
         </is>
       </c>
       <c r="O64" t="inlineStr">
@@ -16055,7 +16055,7 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>2000</v>
+        <v>2990</v>
       </c>
       <c r="Q64" t="inlineStr">
         <is>
@@ -16115,24 +16115,24 @@
       </c>
       <c r="AG64" t="inlineStr">
         <is>
-          <t>2026-10-15T12:10:00+03:00</t>
+          <t>2026-10-15T14:30:00+03:00</t>
         </is>
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
-          <t>2026-09-15T14:10:00+03:00</t>
+          <t>2026-09-15T16:30:00+03:00</t>
         </is>
       </c>
       <c r="AK64" t="inlineStr">
         <is>
-          <t>2026-10-15T12:10:00+03:00</t>
+          <t>2026-10-15T14:30:00+03:00</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>4519088530</t>
+          <t>8180586755</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -16147,17 +16147,17 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Пиловочник сосна от заготовителя, ЭСД</t>
+          <t>Кряж берёзовый (декларация о сделке)</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;strong&gt;Оформляем документы тем, кто пилит сам.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Пилите сами: заготовку ставим на учёт в ФГИС ЛК, сосновый пиловочник начинает числиться за вами.&lt;/p&gt;&lt;p&gt;Продаёте: договор купли-продажи делает древесину товаром. Везёте: электронный сопроводительный документ и QR-код на перевозку древесины на каждый рейс.&lt;/p&gt;&lt;p&gt;Кабинет в ЛесЕГАИС и подпись не нужны, от 1850 руб.&lt;/p&gt;&lt;p&gt;Сосновый пиловочник 4 и 6 метров, диаметр от 18 см.&lt;/p&gt;&lt;p&gt;Караидель, Караидельский район, Башкортостан. Напишите, что за лес и сколько его.&lt;/p&gt;</t>
+          <t>&lt;p&gt;&lt;strong&gt;Оформляем документы на продажу леса.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Возите сами: даём электронный сопроводительный документ и QR-код на перевозку древесины на каждый рейс.&lt;/p&gt;&lt;p&gt;Продаёте партию: оформляем договор купли-продажи на берёзовый кряж и подаём декларацию о сделке в ФГИС ЛК.&lt;/p&gt;&lt;p&gt;Кабинет в ЛесЕГАИС и подпись не нужны, всё по переписке. Документ на рейс за 15 минут.&lt;/p&gt;&lt;p&gt;Берёзовый кряж 3 и 4 метра, диаметр от 16 см.&lt;/p&gt;&lt;p&gt;Кузоватово, Кузоватовский район, Ульяновская область. Напишите, сколько кряжа лежит, прикинем по документам.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_19_karaidel_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_19_karaidel_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_19_karaidel_3.jpg</t>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_05_kuzovatovo_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_05_kuzovatovo_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_05_kuzovatovo_3.jpg</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -16172,7 +16172,7 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>Караидель, Республика Башкортостан, ул. Ленина, 24</t>
+          <t>Кузоватово, Ульяновская обл., ул. Октябрьская, 4</t>
         </is>
       </c>
       <c r="O65" t="inlineStr">
@@ -16181,7 +16181,7 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>1850</v>
+        <v>620</v>
       </c>
       <c r="Q65" t="inlineStr">
         <is>
@@ -16215,7 +16215,7 @@
       </c>
       <c r="W65" t="inlineStr">
         <is>
-          <t>Сосна</t>
+          <t>Берёза</t>
         </is>
       </c>
       <c r="X65" t="inlineStr">
@@ -16224,10 +16224,10 @@
         </is>
       </c>
       <c r="AB65" t="n">
-        <v>6000</v>
+        <v>4000</v>
       </c>
       <c r="AC65" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AE65" t="inlineStr">
         <is>
@@ -16241,24 +16241,24 @@
       </c>
       <c r="AG65" t="inlineStr">
         <is>
-          <t>2026-10-15T14:30:00+03:00</t>
+          <t>2026-10-15T17:30:00+03:00</t>
         </is>
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>2026-09-15T16:30:00+03:00</t>
+          <t>2026-09-15T19:30:00+03:00</t>
         </is>
       </c>
       <c r="AK65" t="inlineStr">
         <is>
-          <t>2026-10-15T14:30:00+03:00</t>
+          <t>2026-10-15T17:30:00+03:00</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>7366509820</t>
+          <t>4646089948</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -16273,17 +16273,17 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Сосна пиловочник, QR код на перевозку</t>
+          <t>Ель пиловочник (QR код на вывоз леса)</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;strong&gt;Оформляем QR-код на перевозку леса.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Электронный сопроводительный документ выписываем на рейс, QR-код на перевозку древесины уже внутри. Водитель показывает его с телефона на посту.&lt;/p&gt;&lt;p&gt;Сосновый пиловочник закрепляем договором купли-продажи, кубатура идёт в ФГИС ЛК за вами, декларацию о сделке подаём сами.&lt;/p&gt;&lt;p&gt;Кабинет в ЛесЕГАИС и подпись не нужны, от 1490 руб за рейс.&lt;/p&gt;&lt;p&gt;Сосновый пиловочник 4 и 6 метров, диаметр от 18 см.&lt;/p&gt;&lt;p&gt;Заволжск, Заволжский район, Ивановская область. Напишите, сколько пиловочника.&lt;/p&gt;</t>
+          <t>&lt;p&gt;&lt;strong&gt;Оформляем вывоз леса по документам с QR.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;QR-код на перевозку древесины идёт на каждую машину, отдельно на рейс. Сканируют его на посту, груз не задерживают.&lt;/p&gt;&lt;p&gt;Сам электронный сопроводительный документ готов за 15 минут. Еловый пиловочник закрыт договором купли-продажи, кубатура и места складирования стоят в ФГИС ЛК.&lt;/p&gt;&lt;p&gt;Кабинет в ЛесЕГАИС не нужен.&lt;/p&gt;&lt;p&gt;Еловый пиловочник 6 метров, диаметр от 20 см.&lt;/p&gt;&lt;p&gt;Торопец, Торопецкий район, Тверская область. Напишите, сколько машин уходит, ответим в сообщениях.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-20/w2009_21_zavolzhsk_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-20/w2009_21_zavolzhsk_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-20/w2009_21_zavolzhsk_3.jpg</t>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-20/w2009_24_toropets_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-20/w2009_24_toropets_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-20/w2009_24_toropets_3.jpg</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -16298,7 +16298,7 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>Заволжск, Ивановская обл., ул. Мира, 15</t>
+          <t>Торопец, Тверская обл., ул. Октябрьская, 40</t>
         </is>
       </c>
       <c r="O66" t="inlineStr">
@@ -16307,7 +16307,7 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>1490</v>
+        <v>1990</v>
       </c>
       <c r="Q66" t="inlineStr">
         <is>
@@ -16341,7 +16341,7 @@
       </c>
       <c r="W66" t="inlineStr">
         <is>
-          <t>Сосна</t>
+          <t>Ель</t>
         </is>
       </c>
       <c r="X66" t="inlineStr">
@@ -16353,7 +16353,7 @@
         <v>6000</v>
       </c>
       <c r="AC66" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AE66" t="inlineStr">
         <is>
@@ -16367,24 +16367,24 @@
       </c>
       <c r="AG66" t="inlineStr">
         <is>
-          <t>2026-10-15T16:40:00+03:00</t>
+          <t>2026-10-16T03:30:00+03:00</t>
         </is>
       </c>
       <c r="AJ66" t="inlineStr">
         <is>
-          <t>2026-09-15T18:40:00+03:00</t>
+          <t>2026-09-16T05:30:00+03:00</t>
         </is>
       </c>
       <c r="AK66" t="inlineStr">
         <is>
-          <t>2026-10-15T16:40:00+03:00</t>
+          <t>2026-10-16T03:30:00+03:00</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>7840079321</t>
+          <t>1725681496</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -16399,17 +16399,17 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Лес кругляк ель (QR код на каждый рейс)</t>
+          <t>Лес кругляк сосна, документы ФГИС ЛК</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;strong&gt;Выдаём QR-код на перевозку леса.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Электронный сопроводительный документ на рейс, а в нём QR-код на перевозку древесины. Инспектор на посту сканирует его телефоном за пару секунд.&lt;/p&gt;&lt;p&gt;Еловый кругляк оформляем договором купли-продажи и ставим на учёт в ФГИС ЛК, объём числится за вами.&lt;/p&gt;&lt;p&gt;Свой кабинет в ЛесЕГАИС заводить не надо, работаем по переписке. От 850 руб за рейс.&lt;/p&gt;&lt;p&gt;Еловый кругляк 4 и 6 метров, диаметр от 14 см.&lt;/p&gt;&lt;p&gt;Пестяки, Пестяковский район, Ивановская область. Напишите, когда ближайшая отгрузка.&lt;/p&gt;</t>
+          <t>&lt;p&gt;&lt;strong&gt;Делаем документы на лес, купленный у населения.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Древесина от населения становится законным товаром. На руках будет:&lt;br&gt;- договор купли-продажи на сосновый кругляк&lt;br&gt;- кубатура на балансе в ФГИС ЛК за вами&lt;br&gt;- ЭСД и QR-код на перевозку древесины&lt;/p&gt;&lt;p&gt;Кабинет в ЛесЕГАИС заводить не придётся. Электронный сопроводительный документ выдаём за 15 минут.&lt;/p&gt;&lt;p&gt;Сосновый кругляк 4 и 6 метров, диаметр от 18 см.&lt;/p&gt;&lt;p&gt;Зубова Поляна, Зубово-Полянский район, Мордовия. Напишите, сколько машин планируете, скажем, что понадобится.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_02_pestyaki_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_02_pestyaki_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_02_pestyaki_3.jpg</t>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_07_zubovapolyana_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_07_zubovapolyana_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_07_zubovapolyana_3.jpg</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -16424,7 +16424,7 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>Пестяки, Ивановская обл., ул. Ленина, 14</t>
+          <t>Зубова Поляна, Республика Мордовия, ул. Ленина, 6</t>
         </is>
       </c>
       <c r="O67" t="inlineStr">
@@ -16433,7 +16433,7 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>850</v>
+        <v>750</v>
       </c>
       <c r="Q67" t="inlineStr">
         <is>
@@ -16467,7 +16467,7 @@
       </c>
       <c r="W67" t="inlineStr">
         <is>
-          <t>Ель</t>
+          <t>Сосна</t>
         </is>
       </c>
       <c r="X67" t="inlineStr">
@@ -16479,7 +16479,7 @@
         <v>6000</v>
       </c>
       <c r="AC67" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="AE67" t="inlineStr">
         <is>
@@ -16493,24 +16493,24 @@
       </c>
       <c r="AG67" t="inlineStr">
         <is>
-          <t>2026-10-16T07:20:00+03:00</t>
+          <t>2026-10-16T06:30:00+03:00</t>
         </is>
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>2026-09-16T09:20:00+03:00</t>
+          <t>2026-09-16T08:30:00+03:00</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
         <is>
-          <t>2026-10-16T07:20:00+03:00</t>
+          <t>2026-10-16T06:30:00+03:00</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>4731301322</t>
+          <t>5685246725</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -16525,17 +16525,17 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Пиловочник сосна (документация ФГИС ЛК)</t>
+          <t>Кругляк хвойный (документация ФГИС ЛК)</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;strong&gt;Ставим древесину на учёт в ФГИС ЛК.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Сосновый пиловочник встаёт на учёт, и кубатура числится за вами. Дальше по списку:&lt;br&gt;- договор купли-продажи на вашу древесину&lt;br&gt;- QR-код на перевозку древесины на каждый рейс&lt;br&gt;- электронный сопроводительный документ за 15 минут&lt;/p&gt;&lt;p&gt;Свой кабинет в ЛесЕГАИС вам не нужен. От вас порода, объём и маршрут, от 1700 руб.&lt;/p&gt;&lt;p&gt;Сосновый пиловочник 6 метров, диаметр от 20 см.&lt;/p&gt;&lt;p&gt;Судогда, Судогодский район, Владимирская область. Напишите, сколько кубов и куда везёте.&lt;/p&gt;</t>
+          <t>&lt;p&gt;&lt;strong&gt;Ставим объём в ФГИС ЛК и даём QR на рейс.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Хвойный кругляк заводим в систему и закрываем бумагами. По порядку:&lt;br&gt;- постановка кубатуры на учёт в ФГИС ЛК&lt;br&gt;- договор купли-продажи на вашу древесину&lt;br&gt;- электронный сопроводительный документ за 15 минут&lt;br&gt;- QR-код на перевозку древесины на каждый рейс&lt;/p&gt;&lt;p&gt;Свой кабинет в ЛесЕГАИС и электронная подпись не нужны, от вас порода, объём и маршрут.&lt;/p&gt;&lt;p&gt;Хвойный кругляк 4 и 6 метров, диаметр от 16 см.&lt;/p&gt;&lt;p&gt;Ува, Увинский район, Удмуртия. Напишите, сколько кругляка лежит и куда идёт.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_04_sudogda_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_04_sudogda_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_04_sudogda_3.jpg</t>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-20/w2009_26_uva_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-20/w2009_26_uva_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-20/w2009_26_uva_3.jpg</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -16550,7 +16550,7 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>Судогда, Владимирская обл., ул. Ленина, 40</t>
+          <t>Ува, Удмуртская Республика, ул. Калинина, 15</t>
         </is>
       </c>
       <c r="O68" t="inlineStr">
@@ -16559,7 +16559,7 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>1700</v>
+        <v>1150</v>
       </c>
       <c r="Q68" t="inlineStr">
         <is>
@@ -16605,7 +16605,7 @@
         <v>6000</v>
       </c>
       <c r="AC68" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="AE68" t="inlineStr">
         <is>
@@ -16619,24 +16619,24 @@
       </c>
       <c r="AG68" t="inlineStr">
         <is>
-          <t>2026-10-16T09:40:00+03:00</t>
+          <t>2026-10-16T09:30:00+03:00</t>
         </is>
       </c>
       <c r="AJ68" t="inlineStr">
         <is>
-          <t>2026-09-16T11:40:00+03:00</t>
+          <t>2026-09-16T11:30:00+03:00</t>
         </is>
       </c>
       <c r="AK68" t="inlineStr">
         <is>
-          <t>2026-10-16T09:40:00+03:00</t>
+          <t>2026-10-16T09:30:00+03:00</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>1156126848</t>
+          <t>6048366115</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -16651,17 +16651,17 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Балансы еловые (учёт объёма в ФГИС ЛК)</t>
+          <t>Доска обрезная сосна, QR код на вывоз</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;strong&gt;Заводим вашу кубатуру в ФГИС ЛК.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Продаёте партию: договор купли-продажи делает древесину вашим товаром, кубатура встаёт на баланс в ФГИС ЛК.&lt;/p&gt;&lt;p&gt;Везёте сами: на рейс идёт электронный сопроводительный документ, в нём QR-код на перевозку древесины.&lt;/p&gt;&lt;p&gt;Свой кабинет в ЛесЕГАИС и подпись не нужны, еловый баланс берём любым объёмом. От 900 руб, документ на рейс за 15 минут.&lt;/p&gt;&lt;p&gt;Еловый баланс 2 и 3 метра, диаметр от 6 см.&lt;/p&gt;&lt;p&gt;Кез, Кезский район, Удмуртия. Напишите, сколько кубов балансов.&lt;/p&gt;</t>
+          <t>&lt;p&gt;&lt;strong&gt;Даём QR-код на вывоз партии.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;QR-код на перевозку древесины идёт на каждую машину. Документ электронный, водитель показывает его с телефона.&lt;/p&gt;&lt;p&gt;Сосновую доску и кругляк проводим договором купли-продажи, декларацию о сделке в ФГИС ЛК подаём сами.&lt;/p&gt;&lt;p&gt;Кабинет в ЛесЕГАИС не нужен, работаем по переписке. Электронный сопроводительный документ за 15 минут.&lt;/p&gt;&lt;p&gt;Сосновая доска и кругляк 4 и 6 метров, диаметр от 18 см.&lt;/p&gt;&lt;p&gt;Шилово, Шиловский район, Рязанская область. Напишите, сколько рейсов надо закрыть, разберём вашу ситуацию.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_08_kez_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_08_kez_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_08_kez_3.jpg</t>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_09_shilovo_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_09_shilovo_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_09_shilovo_3.jpg</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -16676,7 +16676,7 @@
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>Кез, Удмуртская Республика, ул. Кирова, 10</t>
+          <t>Шилово, Рязанская обл., ул. Советская, 14</t>
         </is>
       </c>
       <c r="O69" t="inlineStr">
@@ -16685,7 +16685,7 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>900</v>
+        <v>480</v>
       </c>
       <c r="Q69" t="inlineStr">
         <is>
@@ -16719,7 +16719,7 @@
       </c>
       <c r="W69" t="inlineStr">
         <is>
-          <t>Ель</t>
+          <t>Сосна</t>
         </is>
       </c>
       <c r="X69" t="inlineStr">
@@ -16728,10 +16728,10 @@
         </is>
       </c>
       <c r="AB69" t="n">
-        <v>3000</v>
+        <v>6000</v>
       </c>
       <c r="AC69" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="AE69" t="inlineStr">
         <is>
@@ -16745,24 +16745,24 @@
       </c>
       <c r="AG69" t="inlineStr">
         <is>
-          <t>2026-10-16T12:10:00+03:00</t>
+          <t>2026-10-16T12:30:00+03:00</t>
         </is>
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>2026-09-16T14:10:00+03:00</t>
+          <t>2026-09-16T14:30:00+03:00</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
         <is>
-          <t>2026-10-16T12:10:00+03:00</t>
+          <t>2026-10-16T12:30:00+03:00</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>8543140206</t>
+          <t>2939061244</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -16777,17 +16777,17 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Пиловочник ель (ЭСД на каждую машину)</t>
+          <t>Сосна пиловочник (ЭСД и отчёт 1-ИЛ)</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;strong&gt;Выписываем ЭСД на каждую машину.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Электронный сопроводительный документ делаем на каждый лесовоз. В каждом свой QR-код на перевозку древесины, 15 минут на документ.&lt;/p&gt;&lt;p&gt;Еловый пиловочник закрываем договором купли-продажи, декларацию о сделке в ФГИС ЛК подаём сами.&lt;/p&gt;&lt;p&gt;Кабинет в ЛесЕГАИС и электронная подпись вам не нужны, от вас порода, кубатура и маршрут. От 1550 руб.&lt;/p&gt;&lt;p&gt;Еловый пиловочник 4 и 6 метров, диаметр от 16 см.&lt;/p&gt;&lt;p&gt;Маслянино, Маслянинский район, Новосибирская область. Напишите, сколько рейсов в неделю.&lt;/p&gt;</t>
+          <t>&lt;p&gt;&lt;strong&gt;Оформляем документы на древесину и отчётность по ней.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Берём на себя бумажную часть по сосновому пиловочнику:&lt;br&gt;- электронный сопроводительный документ на рейс за 15 минут&lt;br&gt;- QR-код на перевозку древесины для водителя&lt;br&gt;- договор купли-продажи, кубатура в ФГИС ЛК за вами&lt;br&gt;- отчёт 1-ИЛ сдаём сами&lt;/p&gt;&lt;p&gt;Кабинет в ЛесЕГАИС вам не понадобится, от вас порода, объём и маршрут.&lt;/p&gt;&lt;p&gt;Сосновый пиловочник 4 и 6 метров, диаметр от 18 см.&lt;/p&gt;&lt;p&gt;Заринск, Заринский район, Алтайский край. Напишите, куда идут машины, подберём документы.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_15_maslyanino_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_15_maslyanino_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_15_maslyanino_3.jpg</t>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_12_zarinsk_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_12_zarinsk_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_12_zarinsk_3.jpg</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -16802,7 +16802,7 @@
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>Маслянино, Новосибирская обл., ул. Коммунистическая, 3</t>
+          <t>Заринск, Алтайский край, ул. Ленина, 2</t>
         </is>
       </c>
       <c r="O70" t="inlineStr">
@@ -16811,7 +16811,7 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>1550</v>
+        <v>1250</v>
       </c>
       <c r="Q70" t="inlineStr">
         <is>
@@ -16845,7 +16845,7 @@
       </c>
       <c r="W70" t="inlineStr">
         <is>
-          <t>Ель</t>
+          <t>Сосна</t>
         </is>
       </c>
       <c r="X70" t="inlineStr">
@@ -16857,7 +16857,7 @@
         <v>6000</v>
       </c>
       <c r="AC70" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AE70" t="inlineStr">
         <is>
@@ -16871,24 +16871,24 @@
       </c>
       <c r="AG70" t="inlineStr">
         <is>
-          <t>2026-10-16T14:30:00+03:00</t>
+          <t>2026-10-16T15:30:00+03:00</t>
         </is>
       </c>
       <c r="AJ70" t="inlineStr">
         <is>
-          <t>2026-09-16T16:30:00+03:00</t>
+          <t>2026-09-16T17:30:00+03:00</t>
         </is>
       </c>
       <c r="AK70" t="inlineStr">
         <is>
-          <t>2026-10-16T14:30:00+03:00</t>
+          <t>2026-10-16T15:30:00+03:00</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>7187686177</t>
+          <t>3172035112</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -16903,17 +16903,17 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Лес кругляк ель (документация ФГИС)</t>
+          <t>Сосна пиловочник (ЭСД с QR на рейс)</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;strong&gt;Делаем документы на древесину в ФГИС ЛК.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Еловый кругляк становится учтённым товаром. По списку:&lt;br&gt;- постановка древесины на учёт в ФГИС ЛК&lt;br&gt;- договор купли-продажи, по нему лес ваш&lt;br&gt;- электронный сопроводительный документ на каждый рейс&lt;br&gt;- QR-код на перевозку древесины для водителя&lt;/p&gt;&lt;p&gt;Работу берём на себя, кабинет в ЛесЕГАИС и подпись вам не нужны. От 2490 руб.&lt;/p&gt;&lt;p&gt;Еловый кругляк 4 и 6 метров, диаметр от 16 см.&lt;/p&gt;&lt;p&gt;Гороховец, Гороховецкий район, Владимирская область. Напишите, когда отгрузка.&lt;/p&gt;</t>
+          <t>&lt;p&gt;&lt;strong&gt;Оформляем отгрузку лесовозов по ЭСД с QR.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;На каждый лесовоз выписываем электронный сопроводительный документ, в нём QR-код на перевозку древесины. Поток машин ведём сами, документ за 15 минут.&lt;/p&gt;&lt;p&gt;Сосновый пиловочник проводим договором купли-продажи, кубатура встаёт на баланс в ФГИС ЛК за вами.&lt;/p&gt;&lt;p&gt;Кабинет в ЛесЕГАИС и подпись не нужны.&lt;/p&gt;&lt;p&gt;Сосновый пиловочник 4 и 6 метров, диаметр от 18 см.&lt;/p&gt;&lt;p&gt;Сузун, Сузунский район, Новосибирская область. Напишите, сколько машин в день, подстроимся под ваш график.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-20/w2009_22_gorohovets_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-20/w2009_22_gorohovets_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-20/w2009_22_gorohovets_3.jpg</t>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-20/w2009_30_suzun_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-20/w2009_30_suzun_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-20/w2009_30_suzun_3.jpg</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -16928,7 +16928,7 @@
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>Гороховец, Владимирская обл., ул. Ленина, 93</t>
+          <t>Сузун, Новосибирская обл., ул. Ленина, 51</t>
         </is>
       </c>
       <c r="O71" t="inlineStr">
@@ -16937,7 +16937,7 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>2490</v>
+        <v>3500</v>
       </c>
       <c r="Q71" t="inlineStr">
         <is>
@@ -16971,7 +16971,7 @@
       </c>
       <c r="W71" t="inlineStr">
         <is>
-          <t>Ель</t>
+          <t>Сосна</t>
         </is>
       </c>
       <c r="X71" t="inlineStr">
@@ -16983,7 +16983,7 @@
         <v>6000</v>
       </c>
       <c r="AC71" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AE71" t="inlineStr">
         <is>
@@ -16997,24 +16997,24 @@
       </c>
       <c r="AG71" t="inlineStr">
         <is>
-          <t>2026-10-16T16:40:00+03:00</t>
+          <t>2026-10-17T03:30:00+03:00</t>
         </is>
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>2026-09-16T18:40:00+03:00</t>
+          <t>2026-09-17T05:30:00+03:00</t>
         </is>
       </c>
       <c r="AK71" t="inlineStr">
         <is>
-          <t>2026-10-16T16:40:00+03:00</t>
+          <t>2026-10-17T03:30:00+03:00</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>6082650913</t>
+          <t>5915329752</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -17029,17 +17029,17 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Ель пиловочник, документы на вывоз леса</t>
+          <t>Баланс хвойный, декларация в ФГИС ЛК</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;strong&gt;Выписываем ЭСД на вывоз леса.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Электронный сопроводительный документ делаем на каждый рейс, в нём QR-код на перевозку древесины. Водитель показывает его на посту, груз едет дальше.&lt;/p&gt;&lt;p&gt;Еловый пиловочник закрепляем договором купли-продажи, кубатуру ставим в ФГИС ЛК, оформляем места складирования. Кабинет в ЛесЕГАИС не нужен, от 1100 руб.&lt;/p&gt;&lt;p&gt;Еловый пиловочник 4 и 6 метров, диаметр от 16 см.&lt;/p&gt;&lt;p&gt;Западная Двина, Западнодвинский округ, Тверская область. Напишите, когда грузите лесовоз.&lt;/p&gt;</t>
+          <t>&lt;p&gt;&lt;strong&gt;Проводим сделку по древесине в ФГИС ЛК.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Продаёте партию: договор купли-продажи делает хвойный баланс вашим товаром, декларация о сделке проходит в ФГИС ЛК.&lt;/p&gt;&lt;p&gt;Везёте сами: на машину выписываем электронный сопроводительный документ и QR-код на перевозку древесины.&lt;/p&gt;&lt;p&gt;Берём даже одну машину, кабинет в ЛесЕГАИС не нужен. Документ за 15 минут.&lt;/p&gt;&lt;p&gt;Хвойный баланс 2 и 3 метра, диаметр от 6 см.&lt;/p&gt;&lt;p&gt;Тоншаево, Тоншаевский район, Нижегородская область. Напишите породу и кубатуру, ответим, что нужно оформить.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_06_zapdvina_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_06_zapdvina_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_06_zapdvina_3.jpg</t>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_18_tonshaevo_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_18_tonshaevo_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_18_tonshaevo_3.jpg</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -17054,7 +17054,7 @@
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>Западная Двина, Тверская обл., ул. Кирова, 10</t>
+          <t>Тоншаево, Нижегородская обл., ул. Ленина, 3</t>
         </is>
       </c>
       <c r="O72" t="inlineStr">
@@ -17063,7 +17063,7 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>1100</v>
+        <v>420</v>
       </c>
       <c r="Q72" t="inlineStr">
         <is>
@@ -17097,7 +17097,7 @@
       </c>
       <c r="W72" t="inlineStr">
         <is>
-          <t>Ель</t>
+          <t>Сосна</t>
         </is>
       </c>
       <c r="X72" t="inlineStr">
@@ -17106,10 +17106,10 @@
         </is>
       </c>
       <c r="AB72" t="n">
-        <v>6000</v>
+        <v>3000</v>
       </c>
       <c r="AC72" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="AE72" t="inlineStr">
         <is>
@@ -17123,24 +17123,24 @@
       </c>
       <c r="AG72" t="inlineStr">
         <is>
-          <t>2026-10-17T07:20:00+03:00</t>
+          <t>2026-10-17T06:30:00+03:00</t>
         </is>
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
-          <t>2026-09-17T09:20:00+03:00</t>
+          <t>2026-09-17T08:30:00+03:00</t>
         </is>
       </c>
       <c r="AK72" t="inlineStr">
         <is>
-          <t>2026-10-17T07:20:00+03:00</t>
+          <t>2026-10-17T06:30:00+03:00</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>4846480914</t>
+          <t>1203904869</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -17155,17 +17155,17 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Берёза дровяная (учёт в ФГИС ЛК)</t>
+          <t>Лес кругляк хвоя (QR на перевозку леса)</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;strong&gt;Ставим берёзу на учёт в ФГИС ЛК.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Берёзовые дрова тоже должны числиться за вами. Делаем так:&lt;br&gt;- постановка кубатуры на учёт в ФГИС ЛК&lt;br&gt;- договор купли-продажи на вашу древесину&lt;br&gt;- QR-код на перевозку древесины на каждый рейс&lt;/p&gt;&lt;p&gt;Электронный сопроводительный документ готов за 15 минут. Ни кабинета в ЛесЕГАИС, ни подписи от вас, от 350 руб.&lt;/p&gt;&lt;p&gt;Берёзовые дрова и баланс 1 и 2 метра, диаметр от 6 см.&lt;/p&gt;&lt;p&gt;Балтаси, Балтасинский район, Татарстан. Напишите, сколько кубов дров.&lt;/p&gt;</t>
+          <t>&lt;p&gt;&lt;strong&gt;Закрываем рейсы документом с QR.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;QR-код на перевозку древесины сканируют прямо на посту, он привязан к рейсу. Электронный сопроводительный документ выдаём за 15 минут.&lt;/p&gt;&lt;p&gt;Хвойный кругляк оформляем договором купли-продажи, кубатура в ФГИС ЛК за вами, места складирования заявляем сами.&lt;/p&gt;&lt;p&gt;Кабинет в ЛесЕГАИС не нужен, объём любой, хоть одна машина в месяц.&lt;/p&gt;&lt;p&gt;Хвойный кругляк 4 и 6 метров, диаметр от 16 см.&lt;/p&gt;&lt;p&gt;Тисуль, Тисульский район, Кемеровская область. Напишите, сколько кругляка и куда везёте.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_11_baltasi_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_11_baltasi_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_11_baltasi_3.jpg</t>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_13_tisul_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_13_tisul_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_13_tisul_3.jpg</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -17180,7 +17180,7 @@
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>Балтаси, Республика Татарстан, ул. Советская, 20</t>
+          <t>Тисуль, Кемеровская обл., ул. Ленина, 53</t>
         </is>
       </c>
       <c r="O73" t="inlineStr">
@@ -17189,7 +17189,7 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>350</v>
+        <v>690</v>
       </c>
       <c r="Q73" t="inlineStr">
         <is>
@@ -17223,7 +17223,7 @@
       </c>
       <c r="W73" t="inlineStr">
         <is>
-          <t>Берёза</t>
+          <t>Сосна</t>
         </is>
       </c>
       <c r="X73" t="inlineStr">
@@ -17232,10 +17232,10 @@
         </is>
       </c>
       <c r="AB73" t="n">
-        <v>2000</v>
+        <v>6000</v>
       </c>
       <c r="AC73" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="AE73" t="inlineStr">
         <is>
@@ -17249,24 +17249,24 @@
       </c>
       <c r="AG73" t="inlineStr">
         <is>
-          <t>2026-10-17T09:40:00+03:00</t>
+          <t>2026-10-17T09:30:00+03:00</t>
         </is>
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>2026-09-17T11:40:00+03:00</t>
+          <t>2026-09-17T11:30:00+03:00</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
         <is>
-          <t>2026-10-17T09:40:00+03:00</t>
+          <t>2026-10-17T09:30:00+03:00</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>8373658504</t>
+          <t>4684029782</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -17281,17 +17281,17 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Ель пиловочник, ЭСД за 15 минут на рейс</t>
+          <t>Сосна баланс, накладная на перевозку</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;strong&gt;Выдаём ЭСД с QR за 15 минут.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Электронный сопроводительный документ на рейс делаем за 15 минут, в тот же день, когда написали. В нём QR-код на перевозку древесины, машина едет спокойно.&lt;/p&gt;&lt;p&gt;Еловый пиловочник закрыт договором купли-продажи, кубатура стоит в ФГИС ЛК за вами, отчёт 1-ИЛ сдаём сами. Кабинет в ЛесЕГАИС не нужен, от 2450 руб.&lt;/p&gt;&lt;p&gt;Еловый пиловочник 6 метров, диаметр от 20 см.&lt;/p&gt;&lt;p&gt;Варнавино, Варнавинский район, Нижегородская область. Напишите, сколько рейсов в месяц.&lt;/p&gt;</t>
+          <t>&lt;p&gt;&lt;strong&gt;Делаем документы на перевозку древесины.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Накладная на машину, это электронный сопроводительный документ. В нём QR-код на перевозку древесины, водителю хватает телефона.&lt;/p&gt;&lt;p&gt;Сосновый баланс закрепляем договором купли-продажи, кубатура встаёт на баланс в ФГИС ЛК и числится за вами.&lt;/p&gt;&lt;p&gt;Кабинет в ЛесЕГАИС заводить не надо, документ на рейс за 15 минут.&lt;/p&gt;&lt;p&gt;Сосновый баланс 2 и 3 метра, диаметр от 6 см.&lt;/p&gt;&lt;p&gt;Земетчино, Земетчинский район, Пензенская область. Напишите, когда первая отгрузка, подготовимся заранее.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_17_varnavino_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_17_varnavino_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_17_varnavino_3.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_17_varnavino_4.jpg</t>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_14_zemetchino_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_14_zemetchino_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_14_zemetchino_3.jpg</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -17306,7 +17306,7 @@
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>Варнавино, Нижегородская обл., ул. Советская, 1</t>
+          <t>Земетчино, Пензенская обл., ул. Первомайская, 2</t>
         </is>
       </c>
       <c r="O74" t="inlineStr">
@@ -17315,7 +17315,7 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>2450</v>
+        <v>540</v>
       </c>
       <c r="Q74" t="inlineStr">
         <is>
@@ -17349,7 +17349,7 @@
       </c>
       <c r="W74" t="inlineStr">
         <is>
-          <t>Ель</t>
+          <t>Сосна</t>
         </is>
       </c>
       <c r="X74" t="inlineStr">
@@ -17358,10 +17358,10 @@
         </is>
       </c>
       <c r="AB74" t="n">
-        <v>6000</v>
+        <v>3000</v>
       </c>
       <c r="AC74" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="AE74" t="inlineStr">
         <is>
@@ -17375,24 +17375,24 @@
       </c>
       <c r="AG74" t="inlineStr">
         <is>
-          <t>2026-10-17T12:10:00+03:00</t>
+          <t>2026-10-17T12:30:00+03:00</t>
         </is>
       </c>
       <c r="AJ74" t="inlineStr">
         <is>
-          <t>2026-09-17T14:10:00+03:00</t>
+          <t>2026-09-17T14:30:00+03:00</t>
         </is>
       </c>
       <c r="AK74" t="inlineStr">
         <is>
-          <t>2026-10-17T12:10:00+03:00</t>
+          <t>2026-10-17T12:30:00+03:00</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>3234945559</t>
+          <t>1926895206</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -17407,17 +17407,17 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Кряж берёзовый (декларация о сделке)</t>
+          <t>Лес кругляк сосна (места складирования)</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;strong&gt;Оформляем документы на продажу леса.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Возите сами: даём электронный сопроводительный документ и QR-код на перевозку древесины на каждый рейс.&lt;/p&gt;&lt;p&gt;Продаёте партию: оформляем договор купли-продажи на берёзовый кряж и подаём декларацию о сделке в ФГИС ЛК.&lt;/p&gt;&lt;p&gt;Кабинет в ЛесЕГАИС и подпись не нужны, всё по переписке. От 620 руб, документ на рейс за 15 минут.&lt;/p&gt;&lt;p&gt;Берёзовый кряж 3 и 4 метра, диаметр от 16 см.&lt;/p&gt;&lt;p&gt;Кузоватово, Кузоватовский район, Ульяновская область. Напишите, сколько кряжа лежит.&lt;/p&gt;</t>
+          <t>&lt;p&gt;&lt;strong&gt;Оформляем места складирования и вывоз древесины.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Штабель на площадке встаёт в систему как ваш объём. Что делаем:&lt;br&gt;- места складирования в ФГИС ЛК&lt;br&gt;- договор купли-продажи на сосновый кругляк&lt;br&gt;- электронный сопроводительный документ на вывоз&lt;br&gt;- QR-код на перевозку древесины на каждый рейс&lt;/p&gt;&lt;p&gt;От вас адрес площадки, порода и объём, кабинет в ЛесЕГАИС не нужен.&lt;/p&gt;&lt;p&gt;Сосновый кругляк 4 и 6 метров, диаметр от 18 см.&lt;/p&gt;&lt;p&gt;Нязепетровск, Нязепетровский район, Челябинская область. Напишите, сколько кубов лежит на площадке.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_05_kuzovatovo_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_05_kuzovatovo_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_05_kuzovatovo_3.jpg</t>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_16_nyazepetrovsk_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_16_nyazepetrovsk_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_16_nyazepetrovsk_3.jpg</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -17432,7 +17432,7 @@
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>Кузоватово, Ульяновская обл., ул. Октябрьская, 4</t>
+          <t>Нязепетровск, Челябинская обл., ул. Свердлова, 8</t>
         </is>
       </c>
       <c r="O75" t="inlineStr">
@@ -17441,7 +17441,7 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>620</v>
+        <v>820</v>
       </c>
       <c r="Q75" t="inlineStr">
         <is>
@@ -17475,7 +17475,7 @@
       </c>
       <c r="W75" t="inlineStr">
         <is>
-          <t>Берёза</t>
+          <t>Сосна</t>
         </is>
       </c>
       <c r="X75" t="inlineStr">
@@ -17484,10 +17484,10 @@
         </is>
       </c>
       <c r="AB75" t="n">
-        <v>4000</v>
+        <v>6000</v>
       </c>
       <c r="AC75" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AE75" t="inlineStr">
         <is>
@@ -17501,24 +17501,24 @@
       </c>
       <c r="AG75" t="inlineStr">
         <is>
-          <t>2026-10-17T14:30:00+03:00</t>
+          <t>2026-10-17T15:30:00+03:00</t>
         </is>
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>2026-09-17T16:30:00+03:00</t>
+          <t>2026-09-17T17:30:00+03:00</t>
         </is>
       </c>
       <c r="AK75" t="inlineStr">
         <is>
-          <t>2026-10-17T14:30:00+03:00</t>
+          <t>2026-10-17T15:30:00+03:00</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>4789650607</t>
+          <t>3032852513</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -17533,17 +17533,17 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Баланс берёзовый, QR код на каждый рейс</t>
+          <t>Пиловочник сосна от заготовителя, ЭСД</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;strong&gt;Выдаём документ с QR на каждый рейс.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;На машину идёт электронный сопроводительный документ, в нём QR-код на перевозку древесины. С ним берёзовый баланс принимают на весовой и на комбинате.&lt;/p&gt;&lt;p&gt;Партию закрываем договором купли-продажи, кубатура числится за вами в ФГИС ЛК, отчёт 1-ИЛ сдаём сами. Кабинет в ЛесЕГАИС не нужен, от 990 руб за рейс.&lt;/p&gt;&lt;p&gt;Берёзовый баланс 2 и 3 метра, диаметр от 6 см.&lt;/p&gt;&lt;p&gt;Сурское, Сурский район, Ульяновская область. Напишите, сколько баланса.&lt;/p&gt;</t>
+          <t>&lt;p&gt;&lt;strong&gt;Оформляем документы тем, кто пилит сам.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Пилите сами: заготовку ставим на учёт в ФГИС ЛК, сосновый пиловочник начинает числиться за вами.&lt;/p&gt;&lt;p&gt;Продаёте: договор купли-продажи делает древесину товаром. Везёте: электронный сопроводительный документ и QR-код на перевозку древесины на каждый рейс.&lt;/p&gt;&lt;p&gt;Кабинет в ЛесЕГАИС и подпись не нужны, ЭСД за 15 минут.&lt;/p&gt;&lt;p&gt;Сосновый пиловочник 4 и 6 метров, диаметр от 18 см.&lt;/p&gt;&lt;p&gt;Караидель, Караидельский район, Башкортостан. Напишите, что за лес и сколько его, скажем, чего не хватает.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-20/w2009_23_surskoe_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-20/w2009_23_surskoe_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-20/w2009_23_surskoe_3.jpg</t>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_19_karaidel_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_19_karaidel_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_19_karaidel_3.jpg</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -17558,7 +17558,7 @@
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>Сурское, Ульяновская обл., ул. Советская, 35</t>
+          <t>Караидель, Республика Башкортостан, ул. Ленина, 24</t>
         </is>
       </c>
       <c r="O76" t="inlineStr">
@@ -17567,7 +17567,7 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>990</v>
+        <v>1850</v>
       </c>
       <c r="Q76" t="inlineStr">
         <is>
@@ -17601,7 +17601,7 @@
       </c>
       <c r="W76" t="inlineStr">
         <is>
-          <t>Берёза</t>
+          <t>Сосна</t>
         </is>
       </c>
       <c r="X76" t="inlineStr">
@@ -17610,10 +17610,10 @@
         </is>
       </c>
       <c r="AB76" t="n">
-        <v>3000</v>
+        <v>6000</v>
       </c>
       <c r="AC76" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="AE76" t="inlineStr">
         <is>
@@ -17627,24 +17627,24 @@
       </c>
       <c r="AG76" t="inlineStr">
         <is>
-          <t>2026-10-17T16:40:00+03:00</t>
+          <t>2026-10-18T03:30:00+03:00</t>
         </is>
       </c>
       <c r="AJ76" t="inlineStr">
         <is>
-          <t>2026-09-17T18:40:00+03:00</t>
+          <t>2026-09-18T05:30:00+03:00</t>
         </is>
       </c>
       <c r="AK76" t="inlineStr">
         <is>
-          <t>2026-10-17T16:40:00+03:00</t>
+          <t>2026-10-18T03:30:00+03:00</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>6664165510</t>
+          <t>1563154543</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -17659,17 +17659,17 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Лес кругляк сосна, документы ФГИС ЛК</t>
+          <t>Кругляк берёза (QR код на вывоз партии)</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;strong&gt;Делаем документы на лес, купленный у населения.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Древесина от населения становится законным товаром. На руках будет:&lt;br&gt;- договор купли-продажи на сосновый кругляк&lt;br&gt;- кубатура на балансе в ФГИС ЛК за вами&lt;br&gt;- ЭСД и QR-код на перевозку древесины&lt;/p&gt;&lt;p&gt;Кабинет в ЛесЕГАИС заводить не придётся. Электронный сопроводительный документ выдаём за 15 минут, от 750 руб.&lt;/p&gt;&lt;p&gt;Сосновый кругляк 4 и 6 метров, диаметр от 18 см.&lt;/p&gt;&lt;p&gt;Зубова Поляна, Зубово-Полянский район, Мордовия. Напишите, сколько машин планируете.&lt;/p&gt;</t>
+          <t>&lt;p&gt;&lt;strong&gt;Выписываем документ с QR на каждый лесовоз.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;QR-код на перевозку древесины идёт на каждую машину. Проверяют его телефоном за пару секунд, разворотов на трассе не будет.&lt;/p&gt;&lt;p&gt;Электронный сопроводительный документ на рейс готов за 15 минут. Берёзовый кругляк проводим договором купли-продажи, кубатура встаёт на баланс в ФГИС ЛК.&lt;/p&gt;&lt;p&gt;Кабинет в ЛесЕГАИС не нужен.&lt;/p&gt;&lt;p&gt;Берёзовый кругляк 3 и 4 метра, диаметр от 16 см.&lt;/p&gt;&lt;p&gt;Ибреси, Ибресинский район, Чувашия. Напишите, какой объём вывозите, прикинем документы.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_07_zubovapolyana_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_07_zubovapolyana_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_07_zubovapolyana_3.jpg</t>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_20_ibresi_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_20_ibresi_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_20_ibresi_3.jpg</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -17684,7 +17684,7 @@
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>Зубова Поляна, Республика Мордовия, ул. Ленина, 6</t>
+          <t>Ибреси, Чувашская Республика, ул. Ленина, 26</t>
         </is>
       </c>
       <c r="O77" t="inlineStr">
@@ -17693,7 +17693,7 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>750</v>
+        <v>2700</v>
       </c>
       <c r="Q77" t="inlineStr">
         <is>
@@ -17727,7 +17727,7 @@
       </c>
       <c r="W77" t="inlineStr">
         <is>
-          <t>Сосна</t>
+          <t>Берёза</t>
         </is>
       </c>
       <c r="X77" t="inlineStr">
@@ -17736,10 +17736,10 @@
         </is>
       </c>
       <c r="AB77" t="n">
-        <v>6000</v>
+        <v>4000</v>
       </c>
       <c r="AC77" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AE77" t="inlineStr">
         <is>
@@ -17753,24 +17753,24 @@
       </c>
       <c r="AG77" t="inlineStr">
         <is>
-          <t>2026-10-18T07:20:00+03:00</t>
+          <t>2026-10-18T06:30:00+03:00</t>
         </is>
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>2026-09-18T09:20:00+03:00</t>
+          <t>2026-09-18T08:30:00+03:00</t>
         </is>
       </c>
       <c r="AK77" t="inlineStr">
         <is>
-          <t>2026-10-18T07:20:00+03:00</t>
+          <t>2026-10-18T06:30:00+03:00</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>7326838900</t>
+          <t>9371494926</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -17785,17 +17785,17 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Доска обрезная сосна, QR код на вывоз</t>
+          <t>Лес кругляк ель (QR код на каждый рейс)</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;strong&gt;Даём QR-код на вывоз партии.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;QR-код на перевозку древесины идёт на каждую машину. Документ электронный, водитель показывает его с телефона на посту.&lt;/p&gt;&lt;p&gt;Сосновую доску и кругляк проводим договором купли-продажи, декларацию о сделке в ФГИС ЛК подаём сами.&lt;/p&gt;&lt;p&gt;Кабинет в ЛесЕГАИС не нужен, от вас порода, объём и маршрут. От 480 руб, электронный сопроводительный документ за 15 минут.&lt;/p&gt;&lt;p&gt;Сосновая доска и кругляк 4 и 6 метров, диаметр от 18 см.&lt;/p&gt;&lt;p&gt;Шилово, Шиловский район, Рязанская область. Напишите, сколько рейсов надо закрыть.&lt;/p&gt;</t>
+          <t>&lt;p&gt;&lt;strong&gt;Выдаём QR-код на перевозку леса.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Электронный сопроводительный документ на рейс, в нём QR-код на перевозку древесины. Инспектор сканирует его на посту телефоном.&lt;/p&gt;&lt;p&gt;Еловый кругляк оформляем договором купли-продажи, объём встаёт в ФГИС ЛК и числится за вами.&lt;/p&gt;&lt;p&gt;Кабинет в ЛесЕГАИС заводить не надо, работаем по переписке. Документ на рейс готов за 15 минут.&lt;/p&gt;&lt;p&gt;Еловый кругляк 4 и 6 метров, диаметр от 14 см.&lt;/p&gt;&lt;p&gt;Пестяки, Пестяковский район, Ивановская область. Напишите, когда ближайшая отгрузка, подготовим документы к ней.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_09_shilovo_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_09_shilovo_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_09_shilovo_3.jpg</t>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_02_pestyaki_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_02_pestyaki_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_02_pestyaki_3.jpg</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -17810,7 +17810,7 @@
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>Шилово, Рязанская обл., ул. Советская, 14</t>
+          <t>Пестяки, Ивановская обл., ул. Ленина, 14</t>
         </is>
       </c>
       <c r="O78" t="inlineStr">
@@ -17819,7 +17819,7 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>480</v>
+        <v>850</v>
       </c>
       <c r="Q78" t="inlineStr">
         <is>
@@ -17853,7 +17853,7 @@
       </c>
       <c r="W78" t="inlineStr">
         <is>
-          <t>Сосна</t>
+          <t>Ель</t>
         </is>
       </c>
       <c r="X78" t="inlineStr">
@@ -17865,7 +17865,7 @@
         <v>6000</v>
       </c>
       <c r="AC78" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="AE78" t="inlineStr">
         <is>
@@ -17879,24 +17879,24 @@
       </c>
       <c r="AG78" t="inlineStr">
         <is>
-          <t>2026-10-18T09:40:00+03:00</t>
+          <t>2026-10-18T09:30:00+03:00</t>
         </is>
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
-          <t>2026-09-18T11:40:00+03:00</t>
+          <t>2026-09-18T11:30:00+03:00</t>
         </is>
       </c>
       <c r="AK78" t="inlineStr">
         <is>
-          <t>2026-10-18T09:40:00+03:00</t>
+          <t>2026-10-18T09:30:00+03:00</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>8006364040</t>
+          <t>7532374004</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -17911,17 +17911,17 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Лес кругляк хвоя (QR на перевозку леса)</t>
+          <t>Пиловочник сосна (документация ФГИС ЛК)</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;strong&gt;Закрываем рейсы документом с QR.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;QR-код на перевозку древесины сканируют прямо на посту, он живой и привязан к рейсу. Выдаём электронный сопроводительный документ за 15 минут.&lt;/p&gt;&lt;p&gt;Хвойный кругляк оформляем договором купли-продажи, кубатура в ФГИС ЛК за вами, места складирования заявляем сами.&lt;/p&gt;&lt;p&gt;Кабинет в ЛесЕГАИС не нужен, объём любой, хоть одна машина в месяц. От 690 руб.&lt;/p&gt;&lt;p&gt;Хвойный кругляк 4 и 6 метров, диаметр от 16 см.&lt;/p&gt;&lt;p&gt;Тисуль, Тисульский район, Кемеровская область. Напишите, сколько кругляка.&lt;/p&gt;</t>
+          <t>&lt;p&gt;&lt;strong&gt;Ставим древесину на учёт в ФГИС ЛК.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Сосновый пиловочник встаёт на учёт, и кубатура числится за вами. Дальше по списку:&lt;br&gt;- договор купли-продажи на вашу древесину&lt;br&gt;- QR-код на перевозку древесины на каждый рейс&lt;br&gt;- электронный сопроводительный документ за 15 минут&lt;/p&gt;&lt;p&gt;Свой кабинет в ЛесЕГАИС вам не нужен, от вас порода, объём и маршрут.&lt;/p&gt;&lt;p&gt;Сосновый пиловочник 6 метров, диаметр от 20 см.&lt;/p&gt;&lt;p&gt;Судогда, Судогодский район, Владимирская область. Напишите, сколько кубов и куда везёте, подскажем, какие документы нужны.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_13_tisul_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_13_tisul_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_13_tisul_3.jpg</t>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_04_sudogda_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_04_sudogda_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_04_sudogda_3.jpg</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -17936,7 +17936,7 @@
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>Тисуль, Кемеровская обл., ул. Ленина, 53</t>
+          <t>Судогда, Владимирская обл., ул. Ленина, 40</t>
         </is>
       </c>
       <c r="O79" t="inlineStr">
@@ -17945,7 +17945,7 @@
         </is>
       </c>
       <c r="P79" t="n">
-        <v>690</v>
+        <v>1700</v>
       </c>
       <c r="Q79" t="inlineStr">
         <is>
@@ -17991,7 +17991,7 @@
         <v>6000</v>
       </c>
       <c r="AC79" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="AE79" t="inlineStr">
         <is>
@@ -18005,24 +18005,24 @@
       </c>
       <c r="AG79" t="inlineStr">
         <is>
-          <t>2026-10-18T12:10:00+03:00</t>
+          <t>2026-10-18T12:30:00+03:00</t>
         </is>
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>2026-09-18T14:10:00+03:00</t>
+          <t>2026-09-18T14:30:00+03:00</t>
         </is>
       </c>
       <c r="AK79" t="inlineStr">
         <is>
-          <t>2026-10-18T12:10:00+03:00</t>
+          <t>2026-10-18T12:30:00+03:00</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2714757754</t>
+          <t>2489770520</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -18037,17 +18037,17 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Лес кругляк сосна (места складирования)</t>
+          <t>Берёза дровяная (учёт в ФГИС ЛК)</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;strong&gt;Оформляем места складирования и вывоз древесины.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Штабель на площадке встаёт в систему как ваш объём. Что делаем:&lt;br&gt;- места складирования в ФГИС ЛК&lt;br&gt;- договор купли-продажи на сосновый кругляк&lt;br&gt;- электронный сопроводительный документ на вывоз&lt;br&gt;- QR-код на перевозку древесины на каждый рейс&lt;/p&gt;&lt;p&gt;От вас адрес площадки, порода и объём, кабинет в ЛесЕГАИС не нужен. От 820 руб.&lt;/p&gt;&lt;p&gt;Сосновый кругляк 4 и 6 метров, диаметр от 18 см.&lt;/p&gt;&lt;p&gt;Нязепетровск, Нязепетровский район, Челябинская область. Напишите, сколько кубов лежит.&lt;/p&gt;</t>
+          <t>&lt;p&gt;&lt;strong&gt;Ставим берёзу на учёт в ФГИС ЛК.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Берёзовые дрова тоже должны числиться за вами. Делаем так:&lt;br&gt;- постановка кубатуры на учёт в ФГИС ЛК&lt;br&gt;- договор купли-продажи на вашу древесину&lt;br&gt;- QR-код на перевозку древесины на каждый рейс&lt;/p&gt;&lt;p&gt;Электронный сопроводительный документ готов за 15 минут. Ни кабинета в ЛесЕГАИС, ни подписи от вас не понадобится.&lt;/p&gt;&lt;p&gt;Берёзовые дрова и баланс 1 и 2 метра, диаметр от 6 см.&lt;/p&gt;&lt;p&gt;Балтаси, Балтасинский район, Татарстан. Напишите, сколько кубов дров, ответим, что нужно для оформления.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_16_nyazepetrovsk_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_16_nyazepetrovsk_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_16_nyazepetrovsk_3.jpg</t>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_11_baltasi_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_11_baltasi_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_11_baltasi_3.jpg</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -18062,7 +18062,7 @@
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>Нязепетровск, Челябинская обл., ул. Свердлова, 8</t>
+          <t>Балтаси, Республика Татарстан, ул. Советская, 20</t>
         </is>
       </c>
       <c r="O80" t="inlineStr">
@@ -18071,7 +18071,7 @@
         </is>
       </c>
       <c r="P80" t="n">
-        <v>820</v>
+        <v>350</v>
       </c>
       <c r="Q80" t="inlineStr">
         <is>
@@ -18105,7 +18105,7 @@
       </c>
       <c r="W80" t="inlineStr">
         <is>
-          <t>Сосна</t>
+          <t>Берёза</t>
         </is>
       </c>
       <c r="X80" t="inlineStr">
@@ -18114,10 +18114,10 @@
         </is>
       </c>
       <c r="AB80" t="n">
-        <v>6000</v>
+        <v>2000</v>
       </c>
       <c r="AC80" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="AE80" t="inlineStr">
         <is>
@@ -18131,24 +18131,24 @@
       </c>
       <c r="AG80" t="inlineStr">
         <is>
-          <t>2026-10-18T14:30:00+03:00</t>
+          <t>2026-10-18T15:30:00+03:00</t>
         </is>
       </c>
       <c r="AJ80" t="inlineStr">
         <is>
-          <t>2026-09-18T16:30:00+03:00</t>
+          <t>2026-09-18T17:30:00+03:00</t>
         </is>
       </c>
       <c r="AK80" t="inlineStr">
         <is>
-          <t>2026-10-18T14:30:00+03:00</t>
+          <t>2026-10-18T15:30:00+03:00</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>3358334445</t>
+          <t>7021894670</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -18163,17 +18163,17 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Ель пиловочник (QR код на вывоз леса)</t>
+          <t>Баланс берёзовый, QR код на каждый рейс</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;strong&gt;Оформляем вывоз леса по документам с QR.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;QR-код на перевозку древесины идёт на каждую машину, отдельно на рейс. Сканируют его на посту, груз не задерживают.&lt;/p&gt;&lt;p&gt;Сам электронный сопроводительный документ готов за 15 минут. Еловый пиловочник закрыт договором купли-продажи, кубатура и места складирования стоят в ФГИС ЛК.&lt;/p&gt;&lt;p&gt;Кабинет в ЛесЕГАИС не нужен, от 1990 руб.&lt;/p&gt;&lt;p&gt;Еловый пиловочник 6 метров, диаметр от 20 см.&lt;/p&gt;&lt;p&gt;Торопец, Торопецкий район, Тверская область. Напишите, сколько машин уходит.&lt;/p&gt;</t>
+          <t>&lt;p&gt;&lt;strong&gt;Выдаём документ с QR на каждый рейс.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;На машину идёт электронный сопроводительный документ, в нём QR-код на перевозку древесины. С ним берёзовый баланс принимают на весовой и на комбинате.&lt;/p&gt;&lt;p&gt;Партию закрываем договором купли-продажи, кубатура числится за вами в ФГИС ЛК, отчёт 1-ИЛ сдаём сами.&lt;/p&gt;&lt;p&gt;Кабинет в ЛесЕГАИС не нужен, документ за 15 минут.&lt;/p&gt;&lt;p&gt;Берёзовый баланс 2 и 3 метра, диаметр от 6 см.&lt;/p&gt;&lt;p&gt;Сурское, Сурский район, Ульяновская область. Напишите, сколько баланса и куда везёте, дальше наша забота.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-20/w2009_24_toropets_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-20/w2009_24_toropets_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-20/w2009_24_toropets_3.jpg</t>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-20/w2009_23_surskoe_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-20/w2009_23_surskoe_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-20/w2009_23_surskoe_3.jpg</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -18188,7 +18188,7 @@
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>Торопец, Тверская обл., ул. Октябрьская, 40</t>
+          <t>Сурское, Ульяновская обл., ул. Советская, 35</t>
         </is>
       </c>
       <c r="O81" t="inlineStr">
@@ -18197,7 +18197,7 @@
         </is>
       </c>
       <c r="P81" t="n">
-        <v>1990</v>
+        <v>990</v>
       </c>
       <c r="Q81" t="inlineStr">
         <is>
@@ -18231,7 +18231,7 @@
       </c>
       <c r="W81" t="inlineStr">
         <is>
-          <t>Ель</t>
+          <t>Берёза</t>
         </is>
       </c>
       <c r="X81" t="inlineStr">
@@ -18240,10 +18240,10 @@
         </is>
       </c>
       <c r="AB81" t="n">
-        <v>6000</v>
+        <v>3000</v>
       </c>
       <c r="AC81" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="AE81" t="inlineStr">
         <is>
@@ -18257,24 +18257,24 @@
       </c>
       <c r="AG81" t="inlineStr">
         <is>
-          <t>2026-10-18T16:40:00+03:00</t>
+          <t>2026-10-19T03:30:00+03:00</t>
         </is>
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>2026-09-18T18:40:00+03:00</t>
+          <t>2026-09-19T05:30:00+03:00</t>
         </is>
       </c>
       <c r="AK81" t="inlineStr">
         <is>
-          <t>2026-10-18T16:40:00+03:00</t>
+          <t>2026-10-19T03:30:00+03:00</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>8001567780</t>
+          <t>2304485694</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -18289,17 +18289,17 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Сосна пиловочник (ЭСД и отчёт 1-ИЛ)</t>
+          <t>Ель пиловочник, документы на вывоз леса</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;strong&gt;Оформляем документы на древесину и отчётность по ней.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Берём на себя бумажную часть по сосновому пиловочнику:&lt;br&gt;- электронный сопроводительный документ на рейс за 15 минут&lt;br&gt;- QR-код на перевозку древесины для водителя&lt;br&gt;- договор купли-продажи, кубатура в ФГИС ЛК за вами&lt;br&gt;- отчёт 1-ИЛ сдаём сами&lt;/p&gt;&lt;p&gt;Кабинет в ЛесЕГАИС вам не понадобится, от 1250 руб.&lt;/p&gt;&lt;p&gt;Сосновый пиловочник 4 и 6 метров, диаметр от 18 см.&lt;/p&gt;&lt;p&gt;Заринск, Заринский район, Алтайский край. Напишите, куда идут машины.&lt;/p&gt;</t>
+          <t>&lt;p&gt;&lt;strong&gt;Выписываем ЭСД на вывоз леса.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Электронный сопроводительный документ делаем на каждый рейс, в нём QR-код на перевозку древесины. Водитель показывает его на посту, груз едет дальше.&lt;/p&gt;&lt;p&gt;Еловый пиловочник закрепляем договором купли-продажи, кубатуру ставим в ФГИС ЛК, оформляем места складирования.&lt;/p&gt;&lt;p&gt;Кабинет в ЛесЕГАИС не нужен, ЭСД за 15 минут.&lt;/p&gt;&lt;p&gt;Еловый пиловочник 4 и 6 метров, диаметр от 16 см.&lt;/p&gt;&lt;p&gt;Западная Двина, Западнодвинский округ, Тверская область. Напишите, когда грузите лесовоз, успеем к погрузке.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_12_zarinsk_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_12_zarinsk_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_12_zarinsk_3.jpg</t>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_06_zapdvina_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_06_zapdvina_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_06_zapdvina_3.jpg</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -18314,7 +18314,7 @@
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>Заринск, Алтайский край, ул. Ленина, 2</t>
+          <t>Западная Двина, Тверская обл., ул. Кирова, 10</t>
         </is>
       </c>
       <c r="O82" t="inlineStr">
@@ -18323,7 +18323,7 @@
         </is>
       </c>
       <c r="P82" t="n">
-        <v>1250</v>
+        <v>1100</v>
       </c>
       <c r="Q82" t="inlineStr">
         <is>
@@ -18357,7 +18357,7 @@
       </c>
       <c r="W82" t="inlineStr">
         <is>
-          <t>Сосна</t>
+          <t>Ель</t>
         </is>
       </c>
       <c r="X82" t="inlineStr">
@@ -18369,7 +18369,7 @@
         <v>6000</v>
       </c>
       <c r="AC82" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AE82" t="inlineStr">
         <is>
@@ -18383,24 +18383,24 @@
       </c>
       <c r="AG82" t="inlineStr">
         <is>
-          <t>2026-10-19T07:20:00+03:00</t>
+          <t>2026-10-19T06:30:00+03:00</t>
         </is>
       </c>
       <c r="AJ82" t="inlineStr">
         <is>
-          <t>2026-09-19T09:20:00+03:00</t>
+          <t>2026-09-19T08:30:00+03:00</t>
         </is>
       </c>
       <c r="AK82" t="inlineStr">
         <is>
-          <t>2026-10-19T07:20:00+03:00</t>
+          <t>2026-10-19T06:30:00+03:00</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>1370253181</t>
+          <t>3882450127</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -18415,17 +18415,17 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Сосна баланс, накладная на перевозку</t>
+          <t>Дрова берёзовые, документы на перевозку</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;strong&gt;Делаем документы на перевозку древесины.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Накладная на машину, это электронный сопроводительный документ. В нём QR-код на перевозку древесины, водителю хватает телефона.&lt;/p&gt;&lt;p&gt;Сосновый баланс закрепляем договором купли-продажи, кубатура встаёт на баланс в ФГИС ЛК и числится за вами. Кабинет в ЛесЕГАИС заводить не надо.&lt;/p&gt;&lt;p&gt;От вас порода, объём и маршрут. От 540 руб, документ за 15 минут.&lt;/p&gt;&lt;p&gt;Сосновый баланс 2 и 3 метра, диаметр от 6 см.&lt;/p&gt;&lt;p&gt;Земетчино, Земетчинский район, Пензенская область. Напишите, когда первая отгрузка.&lt;/p&gt;</t>
+          <t>&lt;p&gt;&lt;strong&gt;Делаем документы на перевозку дров и баланса.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;На каждый рейс выписываем электронный сопроводительный документ, в нём QR-код на перевозку древесины. Груз едет законно, водителя не разворачивают.&lt;/p&gt;&lt;p&gt;Берёзовые дрова проводим договором купли-продажи, кубатура встаёт на баланс в ФГИС ЛК за вами.&lt;/p&gt;&lt;p&gt;Кабинет в ЛесЕГАИС заводить не надо, документ за 15 минут.&lt;/p&gt;&lt;p&gt;Берёзовые дрова и баланс 1 и 2 метра, диаметр от 6 см.&lt;/p&gt;&lt;p&gt;Темников, Темниковский район, Мордовия. Напишите объём и маршрут, скажем, что оформить.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_14_zemetchino_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_14_zemetchino_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_14_zemetchino_3.jpg</t>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-20/w2009_25_temnikov_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-20/w2009_25_temnikov_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-20/w2009_25_temnikov_3.jpg</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -18440,7 +18440,7 @@
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>Земетчино, Пензенская обл., ул. Первомайская, 2</t>
+          <t>Темников, Республика Мордовия, ул. Ленина, 25</t>
         </is>
       </c>
       <c r="O83" t="inlineStr">
@@ -18449,7 +18449,7 @@
         </is>
       </c>
       <c r="P83" t="n">
-        <v>540</v>
+        <v>490</v>
       </c>
       <c r="Q83" t="inlineStr">
         <is>
@@ -18483,7 +18483,7 @@
       </c>
       <c r="W83" t="inlineStr">
         <is>
-          <t>Сосна</t>
+          <t>Берёза</t>
         </is>
       </c>
       <c r="X83" t="inlineStr">
@@ -18492,7 +18492,7 @@
         </is>
       </c>
       <c r="AB83" t="n">
-        <v>3000</v>
+        <v>2000</v>
       </c>
       <c r="AC83" t="n">
         <v>6</v>
@@ -18509,24 +18509,24 @@
       </c>
       <c r="AG83" t="inlineStr">
         <is>
-          <t>2026-10-19T09:40:00+03:00</t>
+          <t>2026-10-19T09:30:00+03:00</t>
         </is>
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>2026-09-19T11:40:00+03:00</t>
+          <t>2026-09-19T11:30:00+03:00</t>
         </is>
       </c>
       <c r="AK83" t="inlineStr">
         <is>
-          <t>2026-10-19T09:40:00+03:00</t>
+          <t>2026-10-19T09:30:00+03:00</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>7657398596</t>
+          <t>5104488379</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -18541,17 +18541,17 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Баланс хвойный, декларация в ФГИС ЛК</t>
+          <t>Балансы еловые (учёт объёма в ФГИС ЛК)</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;strong&gt;Проводим сделку по древесине в ФГИС ЛК.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Продаёте партию: договор купли-продажи делает хвойный баланс вашим товаром, декларация о сделке проходит в ФГИС ЛК.&lt;/p&gt;&lt;p&gt;Везёте сами: на машину выписываем электронный сопроводительный документ и QR-код на перевозку древесины.&lt;/p&gt;&lt;p&gt;Берём даже одну машину, кабинет в ЛесЕГАИС не нужен. От 420 руб, документ за 15 минут.&lt;/p&gt;&lt;p&gt;Хвойный баланс 2 и 3 метра, диаметр от 6 см.&lt;/p&gt;&lt;p&gt;Тоншаево, Тоншаевский район, Нижегородская область. Напишите породу и кубатуру.&lt;/p&gt;</t>
+          <t>&lt;p&gt;&lt;strong&gt;Заводим вашу кубатуру в ФГИС ЛК.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Продаёте партию: договор купли-продажи делает древесину вашим товаром, кубатура встаёт на баланс в ФГИС ЛК.&lt;/p&gt;&lt;p&gt;Везёте сами: на рейс идёт электронный сопроводительный документ, в нём QR-код на перевозку древесины.&lt;/p&gt;&lt;p&gt;Свой кабинет в ЛесЕГАИС и подпись не нужны, еловый баланс берём любым объёмом. Документ на рейс за 15 минут.&lt;/p&gt;&lt;p&gt;Еловый баланс 2 и 3 метра, диаметр от 6 см.&lt;/p&gt;&lt;p&gt;Кез, Кезский район, Удмуртия. Напишите, сколько кубов балансов, возьмём в работу.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_18_tonshaevo_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_18_tonshaevo_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_18_tonshaevo_3.jpg</t>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_08_kez_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_08_kez_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_08_kez_3.jpg</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -18566,7 +18566,7 @@
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>Тоншаево, Нижегородская обл., ул. Ленина, 3</t>
+          <t>Кез, Удмуртская Республика, ул. Кирова, 10</t>
         </is>
       </c>
       <c r="O84" t="inlineStr">
@@ -18575,7 +18575,7 @@
         </is>
       </c>
       <c r="P84" t="n">
-        <v>420</v>
+        <v>900</v>
       </c>
       <c r="Q84" t="inlineStr">
         <is>
@@ -18609,7 +18609,7 @@
       </c>
       <c r="W84" t="inlineStr">
         <is>
-          <t>Сосна</t>
+          <t>Ель</t>
         </is>
       </c>
       <c r="X84" t="inlineStr">
@@ -18635,24 +18635,24 @@
       </c>
       <c r="AG84" t="inlineStr">
         <is>
-          <t>2026-10-19T12:10:00+03:00</t>
+          <t>2026-10-19T12:30:00+03:00</t>
         </is>
       </c>
       <c r="AJ84" t="inlineStr">
         <is>
-          <t>2026-09-19T14:10:00+03:00</t>
+          <t>2026-09-19T14:30:00+03:00</t>
         </is>
       </c>
       <c r="AK84" t="inlineStr">
         <is>
-          <t>2026-10-19T12:10:00+03:00</t>
+          <t>2026-10-19T12:30:00+03:00</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>8344104479</t>
+          <t>2686700654</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -18667,17 +18667,17 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Кругляк берёза (QR код на вывоз партии)</t>
+          <t>Берёза баланс, QR на вывоз древесины</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;strong&gt;Выписываем документ с QR на каждый лесовоз.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;QR-код на перевозку древесины идёт на каждую машину. Проверяется телефоном за пару секунд, разворотов на трассе не будет.&lt;/p&gt;&lt;p&gt;Электронный сопроводительный документ на рейс готов за 15 минут. Берёзовый кругляк проводим договором купли-продажи, кубатура встаёт на баланс в ФГИС ЛК.&lt;/p&gt;&lt;p&gt;Кабинет в ЛесЕГАИС не нужен, от 2700 руб.&lt;/p&gt;&lt;p&gt;Берёзовый кругляк 3 и 4 метра, диаметр от 16 см.&lt;/p&gt;&lt;p&gt;Ибреси, Ибресинский район, Чувашия. Напишите, какой объём вывозите.&lt;/p&gt;</t>
+          <t>&lt;p&gt;&lt;strong&gt;Выписываем QR на вывоз древесины.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Везёте сами: на каждый рейс электронный сопроводительный документ, в нём QR-код на перевозку древесины.&lt;/p&gt;&lt;p&gt;Продаёте берёзовый баланс: договор купли-продажи и декларация о сделке в ФГИС ЛК, кубатура числится за вами.&lt;/p&gt;&lt;p&gt;Кабинет в ЛесЕГАИС не нужен, объём любой, хоть одна машина. Документ за 15 минут.&lt;/p&gt;&lt;p&gt;Берёзовый баланс 2 и 3 метра, диаметр от 6 см.&lt;/p&gt;&lt;p&gt;Кадом, Кадомский район, Рязанская область. Напишите в сообщения, сколько баланса накопилось.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_20_ibresi_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_20_ibresi_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_20_ibresi_3.jpg</t>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-20/w2009_27_kadom_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-20/w2009_27_kadom_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-20/w2009_27_kadom_3.jpg</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -18692,7 +18692,7 @@
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>Ибреси, Чувашская Республика, ул. Ленина, 26</t>
+          <t>Кадом, Рязанская обл., ул. Ленина, 37</t>
         </is>
       </c>
       <c r="O85" t="inlineStr">
@@ -18701,7 +18701,7 @@
         </is>
       </c>
       <c r="P85" t="n">
-        <v>2700</v>
+        <v>290</v>
       </c>
       <c r="Q85" t="inlineStr">
         <is>
@@ -18744,10 +18744,10 @@
         </is>
       </c>
       <c r="AB85" t="n">
-        <v>4000</v>
+        <v>3000</v>
       </c>
       <c r="AC85" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="AE85" t="inlineStr">
         <is>
@@ -18761,24 +18761,24 @@
       </c>
       <c r="AG85" t="inlineStr">
         <is>
-          <t>2026-10-19T14:30:00+03:00</t>
+          <t>2026-10-19T15:30:00+03:00</t>
         </is>
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>2026-09-19T16:30:00+03:00</t>
+          <t>2026-09-19T17:30:00+03:00</t>
         </is>
       </c>
       <c r="AK85" t="inlineStr">
         <is>
-          <t>2026-10-19T14:30:00+03:00</t>
+          <t>2026-10-19T15:30:00+03:00</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>4176535762</t>
+          <t>6971388674</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -18793,17 +18793,17 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Дрова берёзовые, документы на перевозку</t>
+          <t>Лес кругляк сосна, документы на продажу</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;strong&gt;Делаем документы на перевозку дров и баланса.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;На каждый рейс выписываем электронный сопроводительный документ, в нём QR-код на перевозку древесины. Груз едет законно.&lt;/p&gt;&lt;p&gt;Берёзовые дрова проводим договором купли-продажи, кубатура встаёт на баланс в ФГИС ЛК за вами. Кабинет в ЛесЕГАИС заводить не надо, от 490 руб, документ за 15 минут.&lt;/p&gt;&lt;p&gt;Берёзовые дрова и баланс 1 и 2 метра, диаметр от 6 см.&lt;/p&gt;&lt;p&gt;Темников, Темниковский район, Мордовия. Напишите объём и маршрут.&lt;/p&gt;</t>
+          <t>&lt;p&gt;&lt;strong&gt;Делаем документы, по которым лес можно продать.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Продаёте: договор купли-продажи закрепляет сосновый кругляк за вами, и партию можно выставлять покупателю.&lt;/p&gt;&lt;p&gt;Везёте: электронный сопроводительный документ на рейс и QR-код на перевозку древесины, 15 минут на машину.&lt;/p&gt;&lt;p&gt;Кубатура и места складирования стоят в ФГИС ЛК, кабинет в ЛесЕГАИС не нужен.&lt;/p&gt;&lt;p&gt;Сосновый кругляк 4 и 6 метров, диаметр от 18 см.&lt;/p&gt;&lt;p&gt;Залесово, Залесовский округ, Алтайский край. Напишите, кому продаёте и сколько кубов.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-20/w2009_25_temnikov_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-20/w2009_25_temnikov_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-20/w2009_25_temnikov_3.jpg</t>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-20/w2009_29_zalesovo_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-20/w2009_29_zalesovo_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-20/w2009_29_zalesovo_3.jpg</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -18818,7 +18818,7 @@
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>Темников, Республика Мордовия, ул. Ленина, 25</t>
+          <t>Залесово, Алтайский край, ул. Ленина, 12</t>
         </is>
       </c>
       <c r="O86" t="inlineStr">
@@ -18827,7 +18827,7 @@
         </is>
       </c>
       <c r="P86" t="n">
-        <v>490</v>
+        <v>1750</v>
       </c>
       <c r="Q86" t="inlineStr">
         <is>
@@ -18861,7 +18861,7 @@
       </c>
       <c r="W86" t="inlineStr">
         <is>
-          <t>Берёза</t>
+          <t>Сосна</t>
         </is>
       </c>
       <c r="X86" t="inlineStr">
@@ -18870,10 +18870,10 @@
         </is>
       </c>
       <c r="AB86" t="n">
-        <v>2000</v>
+        <v>6000</v>
       </c>
       <c r="AC86" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="AE86" t="inlineStr">
         <is>
@@ -18887,24 +18887,24 @@
       </c>
       <c r="AG86" t="inlineStr">
         <is>
-          <t>2026-10-19T16:40:00+03:00</t>
+          <t>2026-10-20T03:30:00+03:00</t>
         </is>
       </c>
       <c r="AJ86" t="inlineStr">
         <is>
-          <t>2026-09-19T18:40:00+03:00</t>
+          <t>2026-09-20T05:30:00+03:00</t>
         </is>
       </c>
       <c r="AK86" t="inlineStr">
         <is>
-          <t>2026-10-19T16:40:00+03:00</t>
+          <t>2026-10-20T03:30:00+03:00</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2760809937</t>
+          <t>3034550951</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -18919,17 +18919,17 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Кругляк хвойный (документация ФГИС ЛК)</t>
+          <t>Пиловочник ель (ЭСД на каждую машину)</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;strong&gt;Ставим объём в ФГИС ЛК и даём QR на рейс.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Хвойный кругляк заводим в систему и закрываем бумагами. По порядку:&lt;br&gt;- постановка кубатуры на учёт в ФГИС ЛК&lt;br&gt;- договор купли-продажи на вашу древесину&lt;br&gt;- электронный сопроводительный документ за 15 минут&lt;br&gt;- QR-код на перевозку древесины на каждый рейс&lt;/p&gt;&lt;p&gt;Свой кабинет в ЛесЕГАИС и электронная подпись не нужны, от 1150 руб.&lt;/p&gt;&lt;p&gt;Хвойный кругляк 4 и 6 метров, диаметр от 16 см.&lt;/p&gt;&lt;p&gt;Ува, Увинский район, Удмуртия. Напишите, сколько кругляка лежит.&lt;/p&gt;</t>
+          <t>&lt;p&gt;&lt;strong&gt;Выписываем ЭСД на каждую машину.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Электронный сопроводительный документ делаем на каждый лесовоз. В каждом свой QR-код на перевозку древесины, 15 минут на документ.&lt;/p&gt;&lt;p&gt;Еловый пиловочник закрываем договором купли-продажи, декларацию о сделке в ФГИС ЛК подаём сами.&lt;/p&gt;&lt;p&gt;Кабинет в ЛесЕГАИС и электронная подпись вам не нужны, работаем по переписке.&lt;/p&gt;&lt;p&gt;Еловый пиловочник 4 и 6 метров, диаметр от 16 см.&lt;/p&gt;&lt;p&gt;Маслянино, Маслянинский район, Новосибирская область. Напишите, сколько рейсов в неделю, подскажем по оформлению.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-20/w2009_26_uva_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-20/w2009_26_uva_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-20/w2009_26_uva_3.jpg</t>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_15_maslyanino_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_15_maslyanino_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_15_maslyanino_3.jpg</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -18944,7 +18944,7 @@
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>Ува, Удмуртская Республика, ул. Калинина, 15</t>
+          <t>Маслянино, Новосибирская обл., ул. Коммунистическая, 3</t>
         </is>
       </c>
       <c r="O87" t="inlineStr">
@@ -18953,7 +18953,7 @@
         </is>
       </c>
       <c r="P87" t="n">
-        <v>1150</v>
+        <v>1550</v>
       </c>
       <c r="Q87" t="inlineStr">
         <is>
@@ -18987,7 +18987,7 @@
       </c>
       <c r="W87" t="inlineStr">
         <is>
-          <t>Сосна</t>
+          <t>Ель</t>
         </is>
       </c>
       <c r="X87" t="inlineStr">
@@ -19013,24 +19013,24 @@
       </c>
       <c r="AG87" t="inlineStr">
         <is>
-          <t>2026-10-20T07:20:00+03:00</t>
+          <t>2026-10-20T06:30:00+03:00</t>
         </is>
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>2026-09-20T09:20:00+03:00</t>
+          <t>2026-09-20T08:30:00+03:00</t>
         </is>
       </c>
       <c r="AK87" t="inlineStr">
         <is>
-          <t>2026-10-20T07:20:00+03:00</t>
+          <t>2026-10-20T06:30:00+03:00</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>7380042033</t>
+          <t>9739851912</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -19045,17 +19045,17 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Берёза баланс, QR на вывоз древесины</t>
+          <t>Ель пиловочник, ЭСД за 15 минут на рейс</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;strong&gt;Выписываем QR на вывоз древесины.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Везёте сами: на каждый рейс электронный сопроводительный документ, в нём QR-код на перевозку древесины.&lt;/p&gt;&lt;p&gt;Продаёте берёзовый баланс: договор купли-продажи и декларация о сделке в ФГИС ЛК, кубатура числится за вами.&lt;/p&gt;&lt;p&gt;Кабинет в ЛесЕГАИС не нужен, объём любой, хоть одна машина. От 290 руб, документ за 15 минут.&lt;/p&gt;&lt;p&gt;Берёзовый баланс 2 и 3 метра, диаметр от 6 см.&lt;/p&gt;&lt;p&gt;Кадом, Кадомский район, Рязанская область. Напишите, сколько баланса накопилось.&lt;/p&gt;</t>
+          <t>&lt;p&gt;&lt;strong&gt;Выдаём ЭСД с QR за 15 минут.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Электронный сопроводительный документ на рейс делаем за 15 минут, в тот же день. В нём QR-код на перевозку древесины, машина едет спокойно.&lt;/p&gt;&lt;p&gt;Еловый пиловочник закрыт договором купли-продажи, кубатура стоит в ФГИС ЛК за вами, отчёт 1-ИЛ сдаём сами.&lt;/p&gt;&lt;p&gt;Кабинет в ЛесЕГАИС и электронная подпись не нужны.&lt;/p&gt;&lt;p&gt;Еловый пиловочник 6 метров, диаметр от 20 см.&lt;/p&gt;&lt;p&gt;Варнавино, Варнавинский район, Нижегородская область. Напишите, сколько рейсов в месяц, разберём по документам.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-20/w2009_27_kadom_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-20/w2009_27_kadom_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-20/w2009_27_kadom_3.jpg</t>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_17_varnavino_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_17_varnavino_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_17_varnavino_3.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_17_varnavino_4.jpg</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -19070,7 +19070,7 @@
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>Кадом, Рязанская обл., ул. Ленина, 37</t>
+          <t>Варнавино, Нижегородская обл., ул. Советская, 1</t>
         </is>
       </c>
       <c r="O88" t="inlineStr">
@@ -19079,7 +19079,7 @@
         </is>
       </c>
       <c r="P88" t="n">
-        <v>290</v>
+        <v>2450</v>
       </c>
       <c r="Q88" t="inlineStr">
         <is>
@@ -19113,7 +19113,7 @@
       </c>
       <c r="W88" t="inlineStr">
         <is>
-          <t>Берёза</t>
+          <t>Ель</t>
         </is>
       </c>
       <c r="X88" t="inlineStr">
@@ -19122,10 +19122,10 @@
         </is>
       </c>
       <c r="AB88" t="n">
-        <v>3000</v>
+        <v>6000</v>
       </c>
       <c r="AC88" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="AE88" t="inlineStr">
         <is>
@@ -19139,24 +19139,24 @@
       </c>
       <c r="AG88" t="inlineStr">
         <is>
-          <t>2026-10-20T09:40:00+03:00</t>
+          <t>2026-10-20T09:30:00+03:00</t>
         </is>
       </c>
       <c r="AJ88" t="inlineStr">
         <is>
-          <t>2026-09-20T11:40:00+03:00</t>
+          <t>2026-09-20T11:30:00+03:00</t>
         </is>
       </c>
       <c r="AK88" t="inlineStr">
         <is>
-          <t>2026-10-20T09:40:00+03:00</t>
+          <t>2026-10-20T09:30:00+03:00</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>3281078406</t>
+          <t>4928424477</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -19171,17 +19171,17 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Пиловочник сосна (договор и ЭСД)</t>
+          <t>Сосна пиловочник, QR код на перевозку</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;strong&gt;Оформляем договор купли-продажи и ЭСД на партию.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Продаёте: договор купли-продажи делает сосновый пиловочник вашим товаром, кубатура встаёт в ФГИС ЛК.&lt;/p&gt;&lt;p&gt;Везёте: на каждую машину электронный сопроводительный документ и QR-код на перевозку древесины, 15 минут на рейс.&lt;/p&gt;&lt;p&gt;Отчёт 1-ИЛ сдаём сами, кабинет в ЛесЕГАИС вам не нужен. От 2990 руб.&lt;/p&gt;&lt;p&gt;Сосновый пиловочник 6 метров, диаметр от 20 см.&lt;/p&gt;&lt;p&gt;Богатые Сабы, Сабинский район, Татарстан. Напишите объём партии и сроки.&lt;/p&gt;</t>
+          <t>&lt;p&gt;&lt;strong&gt;Оформляем QR-код на перевозку леса.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Электронный сопроводительный документ выписываем на рейс, QR-код на перевозку древесины уже внутри. Водитель показывает его на посту.&lt;/p&gt;&lt;p&gt;Сосновый пиловочник закрепляем договором купли-продажи, кубатура идёт в ФГИС ЛК за вами, декларацию о сделке подаём сами.&lt;/p&gt;&lt;p&gt;Кабинет в ЛесЕГАИС и подпись не нужны, документ за 15 минут.&lt;/p&gt;&lt;p&gt;Сосновый пиловочник 4 и 6 метров, диаметр от 18 см.&lt;/p&gt;&lt;p&gt;Заволжск, Заволжский район, Ивановская область. Напишите, сколько пиловочника и куда идут машины.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-20/w2009_28_saby_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-20/w2009_28_saby_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-20/w2009_28_saby_3.jpg</t>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-20/w2009_21_zavolzhsk_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-20/w2009_21_zavolzhsk_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-20/w2009_21_zavolzhsk_3.jpg</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -19196,7 +19196,7 @@
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>Богатые Сабы, Республика Татарстан, ул. Ленина, 2</t>
+          <t>Заволжск, Ивановская обл., ул. Мира, 15</t>
         </is>
       </c>
       <c r="O89" t="inlineStr">
@@ -19205,7 +19205,7 @@
         </is>
       </c>
       <c r="P89" t="n">
-        <v>2990</v>
+        <v>1490</v>
       </c>
       <c r="Q89" t="inlineStr">
         <is>
@@ -19251,7 +19251,7 @@
         <v>6000</v>
       </c>
       <c r="AC89" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AE89" t="inlineStr">
         <is>
@@ -19265,24 +19265,24 @@
       </c>
       <c r="AG89" t="inlineStr">
         <is>
-          <t>2026-10-20T12:10:00+03:00</t>
+          <t>2026-10-20T12:30:00+03:00</t>
         </is>
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>2026-09-20T14:10:00+03:00</t>
+          <t>2026-09-20T14:30:00+03:00</t>
         </is>
       </c>
       <c r="AK89" t="inlineStr">
         <is>
-          <t>2026-10-20T12:10:00+03:00</t>
+          <t>2026-10-20T12:30:00+03:00</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>4811004277</t>
+          <t>5864261660</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -19297,17 +19297,17 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Лес кругляк сосна, документы на продажу</t>
+          <t>Баланс берёзовый, накладная с QR на рейс</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;strong&gt;Делаем документы, по которым лес можно продать.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Продаёте: договор купли-продажи закрепляет сосновый кругляк за вами, и партию можно выставлять покупателю.&lt;/p&gt;&lt;p&gt;Везёте: электронный сопроводительный документ на рейс и QR-код на перевозку древесины, 15 минут на машину.&lt;/p&gt;&lt;p&gt;Кубатура и места складирования стоят в ФГИС ЛК, кабинет в ЛесЕГАИС не нужен. От 1750 руб.&lt;/p&gt;&lt;p&gt;Сосновый кругляк 4 и 6 метров, диаметр от 18 см.&lt;/p&gt;&lt;p&gt;Залесово, Залесовский округ, Алтайский край. Напишите, кому продаёте и сколько.&lt;/p&gt;</t>
+          <t>&lt;p&gt;&lt;strong&gt;Делаем накладную с QR на перевозку древесины.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Документ готов за 15 минут. Что будет у вас на руках:&lt;br&gt;- электронный сопроводительный документ на рейс&lt;br&gt;- QR-код на перевозку древесины&lt;br&gt;- договор купли-продажи на берёзовый баланс&lt;br&gt;- кубатура в ФГИС ЛК за вами&lt;br&gt;- отчёт 1-ИЛ закрываем сами&lt;/p&gt;&lt;p&gt;Кабинет в ЛесЕГАИС и электронная подпись не нужны. От вас порода, объём и маршрут.&lt;/p&gt;&lt;p&gt;Берёзовый баланс 2 и 3 метра, диаметр от 6 см.&lt;/p&gt;&lt;p&gt;Меленки, Меленковский район, Владимирская область. Напишите, сколько кубов набирается, посчитаем.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-20/w2009_29_zalesovo_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-20/w2009_29_zalesovo_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-20/w2009_29_zalesovo_3.jpg</t>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_03_melenki_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_03_melenki_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_03_melenki_3.jpg</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -19322,7 +19322,7 @@
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>Залесово, Алтайский край, ул. Ленина, 12</t>
+          <t>Меленки, Владимирская обл., ул. Первомайская, 108</t>
         </is>
       </c>
       <c r="O90" t="inlineStr">
@@ -19331,7 +19331,7 @@
         </is>
       </c>
       <c r="P90" t="n">
-        <v>1750</v>
+        <v>950</v>
       </c>
       <c r="Q90" t="inlineStr">
         <is>
@@ -19365,7 +19365,7 @@
       </c>
       <c r="W90" t="inlineStr">
         <is>
-          <t>Сосна</t>
+          <t>Берёза</t>
         </is>
       </c>
       <c r="X90" t="inlineStr">
@@ -19374,10 +19374,10 @@
         </is>
       </c>
       <c r="AB90" t="n">
-        <v>6000</v>
+        <v>3000</v>
       </c>
       <c r="AC90" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="AE90" t="inlineStr">
         <is>
@@ -19391,24 +19391,24 @@
       </c>
       <c r="AG90" t="inlineStr">
         <is>
-          <t>2026-10-20T14:30:00+03:00</t>
+          <t>2026-10-20T15:30:00+03:00</t>
         </is>
       </c>
       <c r="AJ90" t="inlineStr">
         <is>
-          <t>2026-09-20T16:30:00+03:00</t>
+          <t>2026-09-20T17:30:00+03:00</t>
         </is>
       </c>
       <c r="AK90" t="inlineStr">
         <is>
-          <t>2026-10-20T14:30:00+03:00</t>
+          <t>2026-10-20T15:30:00+03:00</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>7740261188</t>
+          <t>8982309054</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -19423,17 +19423,17 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Сосна пиловочник (ЭСД с QR на рейс)</t>
+          <t>Пиловочник сосна, ЭСД и договор на груз</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;strong&gt;Оформляем отгрузку лесовозов по ЭСД с QR.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;На каждый лесовоз выписываем электронный сопроводительный документ, в нём QR-код на перевозку древесины. Поток машин ведём сами, документ за 15 минут.&lt;/p&gt;&lt;p&gt;Сосновый пиловочник проводим договором купли-продажи, кубатура встаёт на баланс в ФГИС ЛК за вами. Кабинет в ЛесЕГАИС и подпись не нужны, от 3500 руб.&lt;/p&gt;&lt;p&gt;Сосновый пиловочник 4 и 6 метров, диаметр от 18 см.&lt;/p&gt;&lt;p&gt;Сузун, Сузунский район, Новосибирская область. Напишите, сколько машин в день.&lt;/p&gt;</t>
+          <t>&lt;p&gt;&lt;strong&gt;Оформляем договор и ЭСД на груз.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Электронный сопроводительный документ выписываем на каждую машину, QR-код на перевозку древесины в нём уже есть. С ним партию принимают на комбинате и на весовой.&lt;/p&gt;&lt;p&gt;Сосновый пиловочник закрепляем за вами договором купли-продажи, кубатуру ставим в ФГИС ЛК, отчёт 1-ИЛ закрываем сами.&lt;/p&gt;&lt;p&gt;Кабинет в ЛесЕГАИС не нужен.&lt;/p&gt;&lt;p&gt;Сосновый пиловочник 6 метров, диаметр от 20 см.&lt;/p&gt;&lt;p&gt;Кукмор, Кукморский район, Татарстан. Напишите, какой объём отгружаете, скажем, какие документы нужны.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-20/w2009_30_suzun_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-20/w2009_30_suzun_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-20/w2009_30_suzun_3.jpg</t>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_10_kukmor_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_10_kukmor_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-15/w1509_10_kukmor_3.jpg</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -19448,7 +19448,7 @@
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>Сузун, Новосибирская обл., ул. Ленина, 51</t>
+          <t>Кукмор, Республика Татарстан, ул. Ленина, 15</t>
         </is>
       </c>
       <c r="O91" t="inlineStr">
@@ -19457,7 +19457,7 @@
         </is>
       </c>
       <c r="P91" t="n">
-        <v>3500</v>
+        <v>2000</v>
       </c>
       <c r="Q91" t="inlineStr">
         <is>
@@ -19503,7 +19503,7 @@
         <v>6000</v>
       </c>
       <c r="AC91" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AE91" t="inlineStr">
         <is>
@@ -19517,17 +19517,17 @@
       </c>
       <c r="AG91" t="inlineStr">
         <is>
-          <t>2026-10-20T16:40:00+03:00</t>
+          <t>2026-10-21T03:30:00+03:00</t>
         </is>
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>2026-09-20T18:40:00+03:00</t>
+          <t>2026-09-21T05:30:00+03:00</t>
         </is>
       </c>
       <c r="AK91" t="inlineStr">
         <is>
-          <t>2026-10-20T16:40:00+03:00</t>
+          <t>2026-10-21T03:30:00+03:00</t>
         </is>
       </c>
     </row>

--- a/egais.xlsx
+++ b/egais.xlsx
@@ -7820,7 +7820,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK91"/>
+  <dimension ref="A1:AK96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28.33" customWidth="1" min="1" max="1"/>
@@ -19528,6 +19528,636 @@
       <c r="AK91" t="inlineStr">
         <is>
           <t>2026-10-21T03:30:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>7258091766</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>79852671426</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>Лес кругляк сосна (документы на древесину)</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;&lt;strong&gt;Готовим документы на заготовленную древесину.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Сосновый кругляк ставим на учёт в ФГИС ЛК и закрываем договором купли-продажи: лес становится вашим товаром и его можно продать.&lt;/p&gt;&lt;p&gt;На рейс выписываем электронный сопроводительный документ, в нём QR-код на перевозку древесины. Водитель показывает его на посту.&lt;/p&gt;&lt;p&gt;Кабинет в ЛесЕГАИС не нужен, документ на рейс готов за 15 минут.&lt;/p&gt;&lt;p&gt;Сосновый кругляк 4 и 6 метров, диаметр от 18 см.&lt;/p&gt;&lt;p&gt;Палех, Палехский район, Ивановская область. Напишите, какие бумаги на лес есть, скажем, чего не хватает.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-22/w2209_31_palekh_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-22/w2209_31_palekh_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-22/w2209_31_palekh_3.jpg</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>В сообщениях</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>Палех, Ивановская обл., ул. Ленина, 22</t>
+        </is>
+      </c>
+      <c r="O92" t="inlineStr">
+        <is>
+          <t>ПВЗ</t>
+        </is>
+      </c>
+      <c r="P92" t="n">
+        <v>640</v>
+      </c>
+      <c r="Q92" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R92" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S92" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T92" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U92" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V92" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W92" t="inlineStr">
+        <is>
+          <t>Сосна</t>
+        </is>
+      </c>
+      <c r="X92" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB92" t="n">
+        <v>6000</v>
+      </c>
+      <c r="AC92" t="n">
+        <v>18</v>
+      </c>
+      <c r="AE92" t="inlineStr">
+        <is>
+          <t>orbizona-shop@yandex.ru</t>
+        </is>
+      </c>
+      <c r="AF92" t="inlineStr">
+        <is>
+          <t>ЕГАИС ЛЕС документация</t>
+        </is>
+      </c>
+      <c r="AG92" t="inlineStr">
+        <is>
+          <t>2026-10-22T07:30:00+03:00</t>
+        </is>
+      </c>
+      <c r="AJ92" t="inlineStr">
+        <is>
+          <t>2026-09-22T09:30:00+03:00</t>
+        </is>
+      </c>
+      <c r="AK92" t="inlineStr">
+        <is>
+          <t>2026-10-22T07:30:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>3358158653</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>79852671426</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>Баланс еловый (документация ФГИС ЛЕС)</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;&lt;strong&gt;Оформляем документацию на лес в ФГИС ЛК.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Еловый баланс становится учтённой древесиной. Что будет у вас:&lt;br&gt;- договор купли-продажи, по нему лес ваш товар&lt;br&gt;- электронный сопроводительный документ на каждый рейс&lt;br&gt;- QR-код на перевозку древесины для водителя&lt;br&gt;- отчёт 1-ИЛ сдаём сами&lt;/p&gt;&lt;p&gt;Кабинет в ЛесЕГАИС и подпись не нужны, документ на рейс за 15 минут.&lt;/p&gt;&lt;p&gt;Еловый баланс 2 и 3 метра, диаметр от 6 см.&lt;/p&gt;&lt;p&gt;Камешково, Камешковский район, Владимирская область. Напишите, чем сейчас закрываете отгрузки, посмотрим вместе.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-22/w2209_32_kameshkovo_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-22/w2209_32_kameshkovo_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-22/w2209_32_kameshkovo_3.jpg</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>В сообщениях</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>Камешково, Владимирская обл., ул. Свердлова, 10</t>
+        </is>
+      </c>
+      <c r="O93" t="inlineStr">
+        <is>
+          <t>ПВЗ</t>
+        </is>
+      </c>
+      <c r="P93" t="n">
+        <v>1320</v>
+      </c>
+      <c r="Q93" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R93" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S93" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T93" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U93" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V93" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W93" t="inlineStr">
+        <is>
+          <t>Ель</t>
+        </is>
+      </c>
+      <c r="X93" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB93" t="n">
+        <v>3000</v>
+      </c>
+      <c r="AC93" t="n">
+        <v>6</v>
+      </c>
+      <c r="AE93" t="inlineStr">
+        <is>
+          <t>orbizona-shop@yandex.ru</t>
+        </is>
+      </c>
+      <c r="AF93" t="inlineStr">
+        <is>
+          <t>ЕГАИС ЛЕС документация</t>
+        </is>
+      </c>
+      <c r="AG93" t="inlineStr">
+        <is>
+          <t>2026-10-22T09:30:00+03:00</t>
+        </is>
+      </c>
+      <c r="AJ93" t="inlineStr">
+        <is>
+          <t>2026-09-22T11:30:00+03:00</t>
+        </is>
+      </c>
+      <c r="AK93" t="inlineStr">
+        <is>
+          <t>2026-10-22T09:30:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>6160255461</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>79852671426</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>Берёза кругляк, документы на вывоз леса</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;&lt;strong&gt;Собираем документы на вывоз леса.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Продаёте партию: договор купли-продажи делает берёзовый кругляк вашим товаром, декларацию о сделке в ФГИС ЛК подаём сами.&lt;/p&gt;&lt;p&gt;Везёте сами: на машину выписываем электронный сопроводительный документ, в нём QR-код на перевозку древесины. Сканируют его прямо на посту.&lt;/p&gt;&lt;p&gt;Кабинет в ЛесЕГАИС заводить не надо, документ на рейс за 15 минут.&lt;/p&gt;&lt;p&gt;Берёзовый кругляк 3 и 4 метра, диаметр от 16 см.&lt;/p&gt;&lt;p&gt;Николаевка, Николаевский район, Ульяновская область. Напишите, кто покупатель и какой объём, соберём документы.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-22/w2209_33_nikolaevka_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-22/w2209_33_nikolaevka_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-22/w2209_33_nikolaevka_3.jpg</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>В сообщениях</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>Николаевка, Ульяновская обл., ул. Советская, 17</t>
+        </is>
+      </c>
+      <c r="O94" t="inlineStr">
+        <is>
+          <t>ПВЗ</t>
+        </is>
+      </c>
+      <c r="P94" t="n">
+        <v>1680</v>
+      </c>
+      <c r="Q94" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R94" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S94" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T94" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U94" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V94" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W94" t="inlineStr">
+        <is>
+          <t>Берёза</t>
+        </is>
+      </c>
+      <c r="X94" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB94" t="n">
+        <v>4000</v>
+      </c>
+      <c r="AC94" t="n">
+        <v>16</v>
+      </c>
+      <c r="AE94" t="inlineStr">
+        <is>
+          <t>orbizona-shop@yandex.ru</t>
+        </is>
+      </c>
+      <c r="AF94" t="inlineStr">
+        <is>
+          <t>ЕГАИС ЛЕС документация</t>
+        </is>
+      </c>
+      <c r="AG94" t="inlineStr">
+        <is>
+          <t>2026-10-22T11:30:00+03:00</t>
+        </is>
+      </c>
+      <c r="AJ94" t="inlineStr">
+        <is>
+          <t>2026-09-22T13:30:00+03:00</t>
+        </is>
+      </c>
+      <c r="AK94" t="inlineStr">
+        <is>
+          <t>2026-10-22T11:30:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>9333713925</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>79852671426</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>Пиловочник ель (документы на перевозку)</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;&lt;strong&gt;Выдаём водителю документ на перевозку леса.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Это электронный сопроводительный документ на рейс: в нём QR-код на перевозку древесины, порода, объём и маршрут. Инспектор сканирует код телефоном, груз едет дальше. Делаем его за 15 минут.&lt;/p&gt;&lt;p&gt;Еловый пиловочник закрепляем договором купли-продажи, кубатуру и места складирования ставим в ФГИС ЛК.&lt;/p&gt;&lt;p&gt;Свой кабинет в ЛесЕГАИС не нужен.&lt;/p&gt;&lt;p&gt;Еловый пиловочник 4 и 6 метров, диаметр от 16 см.&lt;/p&gt;&lt;p&gt;Бежецк, Бежецкий район, Тверская область. Напишите, куда идёт лесовоз и сколько в нём кубов.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-22/w2209_34_bezheck_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-22/w2209_34_bezheck_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-22/w2209_34_bezheck_3.jpg</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>В сообщениях</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>Бежецк, Тверская обл., ул. Первомайская, 28</t>
+        </is>
+      </c>
+      <c r="O95" t="inlineStr">
+        <is>
+          <t>ПВЗ</t>
+        </is>
+      </c>
+      <c r="P95" t="n">
+        <v>2240</v>
+      </c>
+      <c r="Q95" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R95" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S95" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T95" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U95" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V95" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W95" t="inlineStr">
+        <is>
+          <t>Ель</t>
+        </is>
+      </c>
+      <c r="X95" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB95" t="n">
+        <v>6000</v>
+      </c>
+      <c r="AC95" t="n">
+        <v>16</v>
+      </c>
+      <c r="AE95" t="inlineStr">
+        <is>
+          <t>orbizona-shop@yandex.ru</t>
+        </is>
+      </c>
+      <c r="AF95" t="inlineStr">
+        <is>
+          <t>ЕГАИС ЛЕС документация</t>
+        </is>
+      </c>
+      <c r="AG95" t="inlineStr">
+        <is>
+          <t>2026-10-22T13:30:00+03:00</t>
+        </is>
+      </c>
+      <c r="AJ95" t="inlineStr">
+        <is>
+          <t>2026-09-22T15:30:00+03:00</t>
+        </is>
+      </c>
+      <c r="AK95" t="inlineStr">
+        <is>
+          <t>2026-10-22T13:30:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>7953997959</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>79852671426</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>Сосна баланс, документация на древесину</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;&lt;strong&gt;Приводим документы на древесину в порядок.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Сосновый баланс оформляем договором купли-продажи: по документам лес становится вашим товаром, кубатура встаёт на баланс в ФГИС ЛК.&lt;/p&gt;&lt;p&gt;На каждый рейс выписываем электронный сопроводительный документ, в нём QR-код на перевозку древесины. Готов он за 15 минут.&lt;/p&gt;&lt;p&gt;Кабинет в ЛесЕГАИС и подпись вам не нужны, работаем по переписке.&lt;/p&gt;&lt;p&gt;Сосновый баланс 2 и 3 метра, диаметр от 6 см.&lt;/p&gt;&lt;p&gt;Якшур-Бодья, Якшур-Бодьинский район, Удмуртия. Напишите, сколько сосны во дворе, посчитаем, что оформить.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-22/w2209_35_yakshurbodya_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-22/w2209_35_yakshurbodya_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-22/w2209_35_yakshurbodya_3.jpg</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>В сообщениях</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>Якшур-Бодья, Удмуртская Республика, ул. Ленина, 10</t>
+        </is>
+      </c>
+      <c r="O96" t="inlineStr">
+        <is>
+          <t>ПВЗ</t>
+        </is>
+      </c>
+      <c r="P96" t="n">
+        <v>3100</v>
+      </c>
+      <c r="Q96" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R96" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S96" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T96" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U96" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V96" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W96" t="inlineStr">
+        <is>
+          <t>Сосна</t>
+        </is>
+      </c>
+      <c r="X96" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB96" t="n">
+        <v>3000</v>
+      </c>
+      <c r="AC96" t="n">
+        <v>6</v>
+      </c>
+      <c r="AE96" t="inlineStr">
+        <is>
+          <t>orbizona-shop@yandex.ru</t>
+        </is>
+      </c>
+      <c r="AF96" t="inlineStr">
+        <is>
+          <t>ЕГАИС ЛЕС документация</t>
+        </is>
+      </c>
+      <c r="AG96" t="inlineStr">
+        <is>
+          <t>2026-10-22T15:30:00+03:00</t>
+        </is>
+      </c>
+      <c r="AJ96" t="inlineStr">
+        <is>
+          <t>2026-09-22T17:30:00+03:00</t>
+        </is>
+      </c>
+      <c r="AK96" t="inlineStr">
+        <is>
+          <t>2026-10-22T15:30:00+03:00</t>
         </is>
       </c>
     </row>

--- a/egais.xlsx
+++ b/egais.xlsx
@@ -7820,7 +7820,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK96"/>
+  <dimension ref="A1:AK99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28.33" customWidth="1" min="1" max="1"/>
@@ -19660,7 +19660,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>3358158653</t>
+          <t>6160255461</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -19675,17 +19675,17 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Баланс еловый (документация ФГИС ЛЕС)</t>
+          <t>Берёза кругляк, документы на вывоз леса</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;strong&gt;Оформляем документацию на лес в ФГИС ЛК.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Еловый баланс становится учтённой древесиной. Что будет у вас:&lt;br&gt;- договор купли-продажи, по нему лес ваш товар&lt;br&gt;- электронный сопроводительный документ на каждый рейс&lt;br&gt;- QR-код на перевозку древесины для водителя&lt;br&gt;- отчёт 1-ИЛ сдаём сами&lt;/p&gt;&lt;p&gt;Кабинет в ЛесЕГАИС и подпись не нужны, документ на рейс за 15 минут.&lt;/p&gt;&lt;p&gt;Еловый баланс 2 и 3 метра, диаметр от 6 см.&lt;/p&gt;&lt;p&gt;Камешково, Камешковский район, Владимирская область. Напишите, чем сейчас закрываете отгрузки, посмотрим вместе.&lt;/p&gt;</t>
+          <t>&lt;p&gt;&lt;strong&gt;Собираем документы на вывоз леса.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Продаёте партию: договор купли-продажи делает берёзовый кругляк вашим товаром, декларацию о сделке в ФГИС ЛК подаём сами.&lt;/p&gt;&lt;p&gt;Везёте сами: на машину выписываем электронный сопроводительный документ, в нём QR-код на перевозку древесины. Сканируют его прямо на посту.&lt;/p&gt;&lt;p&gt;Кабинет в ЛесЕГАИС заводить не надо, документ на рейс за 15 минут.&lt;/p&gt;&lt;p&gt;Берёзовый кругляк 3 и 4 метра, диаметр от 16 см.&lt;/p&gt;&lt;p&gt;Николаевка, Николаевский район, Ульяновская область. Напишите, кто покупатель и какой объём, соберём документы.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-22/w2209_32_kameshkovo_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-22/w2209_32_kameshkovo_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-22/w2209_32_kameshkovo_3.jpg</t>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-22/w2209_33_nikolaevka_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-22/w2209_33_nikolaevka_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-22/w2209_33_nikolaevka_3.jpg</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -19700,7 +19700,7 @@
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>Камешково, Владимирская обл., ул. Свердлова, 10</t>
+          <t>Николаевка, Ульяновская обл., ул. Советская, 17</t>
         </is>
       </c>
       <c r="O93" t="inlineStr">
@@ -19709,7 +19709,7 @@
         </is>
       </c>
       <c r="P93" t="n">
-        <v>1320</v>
+        <v>1680</v>
       </c>
       <c r="Q93" t="inlineStr">
         <is>
@@ -19743,7 +19743,7 @@
       </c>
       <c r="W93" t="inlineStr">
         <is>
-          <t>Ель</t>
+          <t>Берёза</t>
         </is>
       </c>
       <c r="X93" t="inlineStr">
@@ -19752,10 +19752,10 @@
         </is>
       </c>
       <c r="AB93" t="n">
-        <v>3000</v>
+        <v>4000</v>
       </c>
       <c r="AC93" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="AE93" t="inlineStr">
         <is>
@@ -19769,24 +19769,24 @@
       </c>
       <c r="AG93" t="inlineStr">
         <is>
-          <t>2026-10-22T09:30:00+03:00</t>
+          <t>2026-10-22T11:30:00+03:00</t>
         </is>
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>2026-09-22T11:30:00+03:00</t>
+          <t>2026-09-22T13:30:00+03:00</t>
         </is>
       </c>
       <c r="AK93" t="inlineStr">
         <is>
-          <t>2026-10-22T09:30:00+03:00</t>
+          <t>2026-10-22T11:30:00+03:00</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>6160255461</t>
+          <t>9333713925</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -19801,17 +19801,17 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Берёза кругляк, документы на вывоз леса</t>
+          <t>Пиловочник ель (документы на перевозку)</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;strong&gt;Собираем документы на вывоз леса.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Продаёте партию: договор купли-продажи делает берёзовый кругляк вашим товаром, декларацию о сделке в ФГИС ЛК подаём сами.&lt;/p&gt;&lt;p&gt;Везёте сами: на машину выписываем электронный сопроводительный документ, в нём QR-код на перевозку древесины. Сканируют его прямо на посту.&lt;/p&gt;&lt;p&gt;Кабинет в ЛесЕГАИС заводить не надо, документ на рейс за 15 минут.&lt;/p&gt;&lt;p&gt;Берёзовый кругляк 3 и 4 метра, диаметр от 16 см.&lt;/p&gt;&lt;p&gt;Николаевка, Николаевский район, Ульяновская область. Напишите, кто покупатель и какой объём, соберём документы.&lt;/p&gt;</t>
+          <t>&lt;p&gt;&lt;strong&gt;Выдаём водителю документ на перевозку леса.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Это электронный сопроводительный документ на рейс: в нём QR-код на перевозку древесины, порода, объём и маршрут. Инспектор сканирует код телефоном, груз едет дальше. Делаем его за 15 минут.&lt;/p&gt;&lt;p&gt;Еловый пиловочник закрепляем договором купли-продажи, кубатуру и места складирования ставим в ФГИС ЛК.&lt;/p&gt;&lt;p&gt;Свой кабинет в ЛесЕГАИС не нужен.&lt;/p&gt;&lt;p&gt;Еловый пиловочник 4 и 6 метров, диаметр от 16 см.&lt;/p&gt;&lt;p&gt;Бежецк, Бежецкий район, Тверская область. Напишите, куда идёт лесовоз и сколько в нём кубов.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-22/w2209_33_nikolaevka_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-22/w2209_33_nikolaevka_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-22/w2209_33_nikolaevka_3.jpg</t>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-22/w2209_34_bezheck_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-22/w2209_34_bezheck_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-22/w2209_34_bezheck_3.jpg</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -19826,7 +19826,7 @@
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>Николаевка, Ульяновская обл., ул. Советская, 17</t>
+          <t>Бежецк, Тверская обл., ул. Первомайская, 28</t>
         </is>
       </c>
       <c r="O94" t="inlineStr">
@@ -19835,7 +19835,7 @@
         </is>
       </c>
       <c r="P94" t="n">
-        <v>1680</v>
+        <v>2240</v>
       </c>
       <c r="Q94" t="inlineStr">
         <is>
@@ -19869,7 +19869,7 @@
       </c>
       <c r="W94" t="inlineStr">
         <is>
-          <t>Берёза</t>
+          <t>Ель</t>
         </is>
       </c>
       <c r="X94" t="inlineStr">
@@ -19878,7 +19878,7 @@
         </is>
       </c>
       <c r="AB94" t="n">
-        <v>4000</v>
+        <v>6000</v>
       </c>
       <c r="AC94" t="n">
         <v>16</v>
@@ -19895,24 +19895,24 @@
       </c>
       <c r="AG94" t="inlineStr">
         <is>
-          <t>2026-10-22T11:30:00+03:00</t>
+          <t>2026-10-22T13:30:00+03:00</t>
         </is>
       </c>
       <c r="AJ94" t="inlineStr">
         <is>
-          <t>2026-09-22T13:30:00+03:00</t>
+          <t>2026-09-22T15:30:00+03:00</t>
         </is>
       </c>
       <c r="AK94" t="inlineStr">
         <is>
-          <t>2026-10-22T11:30:00+03:00</t>
+          <t>2026-10-22T13:30:00+03:00</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>9333713925</t>
+          <t>7953997959</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -19927,17 +19927,17 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Пиловочник ель (документы на перевозку)</t>
+          <t>Сосна баланс, документация на древесину</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;strong&gt;Выдаём водителю документ на перевозку леса.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Это электронный сопроводительный документ на рейс: в нём QR-код на перевозку древесины, порода, объём и маршрут. Инспектор сканирует код телефоном, груз едет дальше. Делаем его за 15 минут.&lt;/p&gt;&lt;p&gt;Еловый пиловочник закрепляем договором купли-продажи, кубатуру и места складирования ставим в ФГИС ЛК.&lt;/p&gt;&lt;p&gt;Свой кабинет в ЛесЕГАИС не нужен.&lt;/p&gt;&lt;p&gt;Еловый пиловочник 4 и 6 метров, диаметр от 16 см.&lt;/p&gt;&lt;p&gt;Бежецк, Бежецкий район, Тверская область. Напишите, куда идёт лесовоз и сколько в нём кубов.&lt;/p&gt;</t>
+          <t>&lt;p&gt;&lt;strong&gt;Приводим документы на древесину в порядок.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Сосновый баланс оформляем договором купли-продажи: по документам лес становится вашим товаром, кубатура встаёт на баланс в ФГИС ЛК.&lt;/p&gt;&lt;p&gt;На каждый рейс выписываем электронный сопроводительный документ, в нём QR-код на перевозку древесины. Готов он за 15 минут.&lt;/p&gt;&lt;p&gt;Кабинет в ЛесЕГАИС и подпись вам не нужны, работаем по переписке.&lt;/p&gt;&lt;p&gt;Сосновый баланс 2 и 3 метра, диаметр от 6 см.&lt;/p&gt;&lt;p&gt;Якшур-Бодья, Якшур-Бодьинский район, Удмуртия. Напишите, сколько сосны во дворе, посчитаем, что оформить.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-22/w2209_34_bezheck_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-22/w2209_34_bezheck_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-22/w2209_34_bezheck_3.jpg</t>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-22/w2209_35_yakshurbodya_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-22/w2209_35_yakshurbodya_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-22/w2209_35_yakshurbodya_3.jpg</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -19952,7 +19952,7 @@
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>Бежецк, Тверская обл., ул. Первомайская, 28</t>
+          <t>Якшур-Бодья, Удмуртская Республика, ул. Ленина, 10</t>
         </is>
       </c>
       <c r="O95" t="inlineStr">
@@ -19961,7 +19961,7 @@
         </is>
       </c>
       <c r="P95" t="n">
-        <v>2240</v>
+        <v>3100</v>
       </c>
       <c r="Q95" t="inlineStr">
         <is>
@@ -19995,7 +19995,7 @@
       </c>
       <c r="W95" t="inlineStr">
         <is>
-          <t>Ель</t>
+          <t>Сосна</t>
         </is>
       </c>
       <c r="X95" t="inlineStr">
@@ -20004,10 +20004,10 @@
         </is>
       </c>
       <c r="AB95" t="n">
-        <v>6000</v>
+        <v>3000</v>
       </c>
       <c r="AC95" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="AE95" t="inlineStr">
         <is>
@@ -20021,24 +20021,24 @@
       </c>
       <c r="AG95" t="inlineStr">
         <is>
-          <t>2026-10-22T13:30:00+03:00</t>
+          <t>2026-10-22T15:30:00+03:00</t>
         </is>
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>2026-09-22T15:30:00+03:00</t>
+          <t>2026-09-22T17:30:00+03:00</t>
         </is>
       </c>
       <c r="AK95" t="inlineStr">
         <is>
-          <t>2026-10-22T13:30:00+03:00</t>
+          <t>2026-10-22T15:30:00+03:00</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>7953997959</t>
+          <t>8715493315</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -20053,17 +20053,17 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Сосна баланс, документация на древесину</t>
+          <t>Сосна пиловочник (документы на вывоз)</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;strong&gt;Приводим документы на древесину в порядок.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Сосновый баланс оформляем договором купли-продажи: по документам лес становится вашим товаром, кубатура встаёт на баланс в ФГИС ЛК.&lt;/p&gt;&lt;p&gt;На каждый рейс выписываем электронный сопроводительный документ, в нём QR-код на перевозку древесины. Готов он за 15 минут.&lt;/p&gt;&lt;p&gt;Кабинет в ЛесЕГАИС и подпись вам не нужны, работаем по переписке.&lt;/p&gt;&lt;p&gt;Сосновый баланс 2 и 3 метра, диаметр от 6 см.&lt;/p&gt;&lt;p&gt;Якшур-Бодья, Якшур-Бодьинский район, Удмуртия. Напишите, сколько сосны во дворе, посчитаем, что оформить.&lt;/p&gt;</t>
+          <t>&lt;p&gt;&lt;strong&gt;Подтверждаем происхождение древесины документами.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Главный документ на вывоз, это электронный сопроводительный документ на рейс. В нём QR-код на перевозку древесины. Инспектор сканирует код на посту, приёмщик на весовой. Готов за 15 минут.&lt;/p&gt;&lt;p&gt;Сосновый пиловочник закрепляем договором купли-продажи, кубатура встаёт на баланс в ФГИС ЛК за вами. Кабинет в ЛесЕГАИС вам не нужен.&lt;/p&gt;&lt;p&gt;Сосновый пиловочник 4 и 6 метров, диаметр от 18 см.&lt;/p&gt;&lt;p&gt;Ельники, Ельниковский район, Мордовия. Напишите, сколько пиловочника уходит за рейс.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-22/w2209_35_yakshurbodya_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-22/w2209_35_yakshurbodya_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-22/w2209_35_yakshurbodya_3.jpg</t>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-23/w2309_36_elniki_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-23/w2309_36_elniki_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-23/w2309_36_elniki_3.jpg</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -20078,7 +20078,7 @@
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>Якшур-Бодья, Удмуртская Республика, ул. Ленина, 10</t>
+          <t>Ельники, Республика Мордовия, ул. Ленина, 20</t>
         </is>
       </c>
       <c r="O96" t="inlineStr">
@@ -20087,7 +20087,7 @@
         </is>
       </c>
       <c r="P96" t="n">
-        <v>3100</v>
+        <v>780</v>
       </c>
       <c r="Q96" t="inlineStr">
         <is>
@@ -20130,34 +20130,412 @@
         </is>
       </c>
       <c r="AB96" t="n">
+        <v>6000</v>
+      </c>
+      <c r="AC96" t="n">
+        <v>18</v>
+      </c>
+      <c r="AE96" t="inlineStr">
+        <is>
+          <t>orbizona-shop@yandex.ru</t>
+        </is>
+      </c>
+      <c r="AF96" t="inlineStr">
+        <is>
+          <t>ЕГАИС ЛЕС документация</t>
+        </is>
+      </c>
+      <c r="AG96" t="inlineStr">
+        <is>
+          <t>2026-10-23T09:30:00+03:00</t>
+        </is>
+      </c>
+      <c r="AJ96" t="inlineStr">
+        <is>
+          <t>2026-09-23T11:30:00+03:00</t>
+        </is>
+      </c>
+      <c r="AK96" t="inlineStr">
+        <is>
+          <t>2026-10-23T09:30:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>5356747191</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>79852671426</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>Берёза баланс, оформим документы на лес</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;&lt;strong&gt;Берём на себя документы на лес.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Берёзовый баланс становится вашим законным товаром. На руках у вас будет:&lt;br&gt;- договор купли-продажи, по нему древесина ваша&lt;br&gt;- электронный сопроводительный документ на каждый рейс&lt;br&gt;- QR-код на перевозку древесины для водителя&lt;br&gt;- отчёт 1-ИЛ в ФГИС ЛК сдаём сами&lt;/p&gt;&lt;p&gt;Кабинет в ЛесЕГАИС вам не нужен, от вас порода, объём и маршрут. ЭСД на рейс за 15 минут.&lt;/p&gt;&lt;p&gt;Берёзовый баланс 2 и 3 метра, диаметр от 6 см.&lt;/p&gt;&lt;p&gt;Ермишь, Ермишинский район, Рязанская область. Напишите, куда сдаёте баланс и каким объёмом.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-23/w2309_37_ermish_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-23/w2309_37_ermish_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-23/w2309_37_ermish_3.jpg</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>В сообщениях</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>Ермишь, Рязанская обл., ул. Советская, 12</t>
+        </is>
+      </c>
+      <c r="O97" t="inlineStr">
+        <is>
+          <t>ПВЗ</t>
+        </is>
+      </c>
+      <c r="P97" t="n">
+        <v>1450</v>
+      </c>
+      <c r="Q97" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R97" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S97" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T97" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U97" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V97" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W97" t="inlineStr">
+        <is>
+          <t>Берёза</t>
+        </is>
+      </c>
+      <c r="X97" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB97" t="n">
         <v>3000</v>
       </c>
-      <c r="AC96" t="n">
+      <c r="AC97" t="n">
         <v>6</v>
       </c>
-      <c r="AE96" t="inlineStr">
+      <c r="AE97" t="inlineStr">
         <is>
           <t>orbizona-shop@yandex.ru</t>
         </is>
       </c>
-      <c r="AF96" t="inlineStr">
+      <c r="AF97" t="inlineStr">
         <is>
           <t>ЕГАИС ЛЕС документация</t>
         </is>
       </c>
-      <c r="AG96" t="inlineStr">
-        <is>
-          <t>2026-10-22T15:30:00+03:00</t>
-        </is>
-      </c>
-      <c r="AJ96" t="inlineStr">
-        <is>
-          <t>2026-09-22T17:30:00+03:00</t>
-        </is>
-      </c>
-      <c r="AK96" t="inlineStr">
-        <is>
-          <t>2026-10-22T15:30:00+03:00</t>
+      <c r="AG97" t="inlineStr">
+        <is>
+          <t>2026-10-23T11:30:00+03:00</t>
+        </is>
+      </c>
+      <c r="AJ97" t="inlineStr">
+        <is>
+          <t>2026-09-23T13:30:00+03:00</t>
+        </is>
+      </c>
+      <c r="AK97" t="inlineStr">
+        <is>
+          <t>2026-10-23T11:30:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>6188959652</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>79852671426</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>Лес кругляк ель (документы для продажи)</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;&lt;strong&gt;Регистрируем древесину на вас.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Продаёте партию: договор купли-продажи делает еловый кругляк вашим товаром, декларация о сделке проходит в ФГИС ЛК. Покупателю есть чем подтвердить происхождение леса.&lt;/p&gt;&lt;p&gt;Везёте сами: на машину выписываем электронный сопроводительный документ, в нём QR-код на перевозку древесины. Готов за 15 минут.&lt;/p&gt;&lt;p&gt;Кабинет в ЛесЕГАИС и подпись не нужны.&lt;/p&gt;&lt;p&gt;Еловый кругляк 4 и 6 метров, диаметр от 16 см.&lt;/p&gt;&lt;p&gt;Арск, Арский район, Татарстан. Напишите, какой объём кругляка ждёт покупателя.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-23/w2309_38_arsk_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-23/w2309_38_arsk_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-23/w2309_38_arsk_3.jpg</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>В сообщениях</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>Арск, Республика Татарстан, ул. Ленина, 29</t>
+        </is>
+      </c>
+      <c r="O98" t="inlineStr">
+        <is>
+          <t>ПВЗ</t>
+        </is>
+      </c>
+      <c r="P98" t="n">
+        <v>2050</v>
+      </c>
+      <c r="Q98" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R98" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S98" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T98" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U98" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V98" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W98" t="inlineStr">
+        <is>
+          <t>Ель</t>
+        </is>
+      </c>
+      <c r="X98" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB98" t="n">
+        <v>6000</v>
+      </c>
+      <c r="AC98" t="n">
+        <v>16</v>
+      </c>
+      <c r="AE98" t="inlineStr">
+        <is>
+          <t>orbizona-shop@yandex.ru</t>
+        </is>
+      </c>
+      <c r="AF98" t="inlineStr">
+        <is>
+          <t>ЕГАИС ЛЕС документация</t>
+        </is>
+      </c>
+      <c r="AG98" t="inlineStr">
+        <is>
+          <t>2026-10-23T13:30:00+03:00</t>
+        </is>
+      </c>
+      <c r="AJ98" t="inlineStr">
+        <is>
+          <t>2026-09-23T15:30:00+03:00</t>
+        </is>
+      </c>
+      <c r="AK98" t="inlineStr">
+        <is>
+          <t>2026-10-23T13:30:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>1156339906</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>79852671426</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>Пиловочник сосна, документы на отгрузку</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;&lt;strong&gt;Заносим древесину в ФГИС ЛК на ваше имя.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Сосновый пиловочник встаёт на учёт и числится за вами. Договор купли-продажи делает его вашим товаром: партию можно продать или вывезти.&lt;/p&gt;&lt;p&gt;На каждый лесовоз идёт электронный сопроводительный документ, в нём QR-код на перевозку древесины. Водитель показывает его на посту и на весовой. Кабинет в ЛесЕГАИС не нужен, ЭСД за 15 минут.&lt;/p&gt;&lt;p&gt;Сосновый пиловочник 6 метров, диаметр от 20 см.&lt;/p&gt;&lt;p&gt;Тогучин, Тогучинский район, Новосибирская область. Напишите, на какой объём нужны документы.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-23/w2309_39_toguchin_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-23/w2309_39_toguchin_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-23/w2309_39_toguchin_3.jpg</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>В сообщениях</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>Тогучин, Новосибирская обл., ул. Комсомольская, 3</t>
+        </is>
+      </c>
+      <c r="O99" t="inlineStr">
+        <is>
+          <t>ПВЗ</t>
+        </is>
+      </c>
+      <c r="P99" t="n">
+        <v>2760</v>
+      </c>
+      <c r="Q99" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R99" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S99" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T99" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U99" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V99" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W99" t="inlineStr">
+        <is>
+          <t>Сосна</t>
+        </is>
+      </c>
+      <c r="X99" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB99" t="n">
+        <v>6000</v>
+      </c>
+      <c r="AC99" t="n">
+        <v>20</v>
+      </c>
+      <c r="AE99" t="inlineStr">
+        <is>
+          <t>orbizona-shop@yandex.ru</t>
+        </is>
+      </c>
+      <c r="AF99" t="inlineStr">
+        <is>
+          <t>ЕГАИС ЛЕС документация</t>
+        </is>
+      </c>
+      <c r="AG99" t="inlineStr">
+        <is>
+          <t>2026-10-23T15:30:00+03:00</t>
+        </is>
+      </c>
+      <c r="AJ99" t="inlineStr">
+        <is>
+          <t>2026-09-23T17:30:00+03:00</t>
+        </is>
+      </c>
+      <c r="AK99" t="inlineStr">
+        <is>
+          <t>2026-10-23T15:30:00+03:00</t>
         </is>
       </c>
     </row>

--- a/egais.xlsx
+++ b/egais.xlsx
@@ -7820,7 +7820,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK99"/>
+  <dimension ref="A1:AK103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28.33" customWidth="1" min="1" max="1"/>
@@ -20536,6 +20536,510 @@
       <c r="AK99" t="inlineStr">
         <is>
           <t>2026-10-23T15:30:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>5087198379</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>79852671426</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>Сосна баланс, документы для отгрузки</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;&lt;strong&gt;Присылаем документы на отгрузку древесины.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Работаем по переписке. Что вы получите:&lt;br&gt;- электронный сопроводительный документ на рейс, готов за 15 минут&lt;br&gt;- QR-код на перевозку древесины, его сканируют на посту&lt;br&gt;- договор купли-продажи, по нему сосновый баланс ваш товар&lt;br&gt;- места складирования в ФГИС ЛК по вашей площадке&lt;/p&gt;&lt;p&gt;Свой кабинет в ЛесЕГАИС заводить не придётся.&lt;/p&gt;&lt;p&gt;Сосновый баланс 2 и 3 метра, диаметр от 6 см.&lt;/p&gt;&lt;p&gt;Сосновоборск, Сосновоборский район, Пензенская область. Напишите, какой объём сосны лежит и когда грузите.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-24/w2409_40_sosnovoborsk_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-24/w2409_40_sosnovoborsk_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-24/w2409_40_sosnovoborsk_3.jpg</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>В сообщениях</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>Сосновоборск, Пензенская обл., ул. Ленина, 15</t>
+        </is>
+      </c>
+      <c r="O100" t="inlineStr">
+        <is>
+          <t>ПВЗ</t>
+        </is>
+      </c>
+      <c r="P100" t="n">
+        <v>870</v>
+      </c>
+      <c r="Q100" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R100" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S100" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T100" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U100" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V100" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W100" t="inlineStr">
+        <is>
+          <t>Сосна</t>
+        </is>
+      </c>
+      <c r="X100" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB100" t="n">
+        <v>3000</v>
+      </c>
+      <c r="AC100" t="n">
+        <v>6</v>
+      </c>
+      <c r="AE100" t="inlineStr">
+        <is>
+          <t>orbizona-shop@yandex.ru</t>
+        </is>
+      </c>
+      <c r="AF100" t="inlineStr">
+        <is>
+          <t>ЕГАИС ЛЕС документация</t>
+        </is>
+      </c>
+      <c r="AG100" t="inlineStr">
+        <is>
+          <t>2026-10-24T10:30:00+03:00</t>
+        </is>
+      </c>
+      <c r="AJ100" t="inlineStr">
+        <is>
+          <t>2026-09-24T12:30:00+03:00</t>
+        </is>
+      </c>
+      <c r="AK100" t="inlineStr">
+        <is>
+          <t>2026-10-24T10:30:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>1095859083</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>79852671426</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>Берёза кругляк (документы ФГИС ЛЕС)</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;&lt;strong&gt;Прописываем вашу древесину в ФГИС ЛК.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Постановка на учёт в ФГИС ЛК значит, что берёзовый кругляк числится за вами. Право на него даёт договор купли-продажи: по бумагам лес ваш товар.&lt;/p&gt;&lt;p&gt;На вывоз выписываем электронный сопроводительный документ, в нём QR-код на перевозку древесины. Инспектор сканирует код телефоном. Кабинет в ЛесЕГАИС не нужен, документ на рейс за 15 минут.&lt;/p&gt;&lt;p&gt;Берёзовый кругляк 3 и 4 метра, диаметр от 16 см.&lt;/p&gt;&lt;p&gt;Аскино, Аскинский район, Башкортостан. Напишите, сколько кубов берёзы и когда нужен документ.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-24/w2409_41_askino_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-24/w2409_41_askino_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-24/w2409_41_askino_3.jpg</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>В сообщениях</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>Аскино, Республика Башкортостан, ул. Советская, 21</t>
+        </is>
+      </c>
+      <c r="O101" t="inlineStr">
+        <is>
+          <t>ПВЗ</t>
+        </is>
+      </c>
+      <c r="P101" t="n">
+        <v>1590</v>
+      </c>
+      <c r="Q101" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R101" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S101" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T101" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U101" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V101" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W101" t="inlineStr">
+        <is>
+          <t>Берёза</t>
+        </is>
+      </c>
+      <c r="X101" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB101" t="n">
+        <v>4000</v>
+      </c>
+      <c r="AC101" t="n">
+        <v>16</v>
+      </c>
+      <c r="AE101" t="inlineStr">
+        <is>
+          <t>orbizona-shop@yandex.ru</t>
+        </is>
+      </c>
+      <c r="AF101" t="inlineStr">
+        <is>
+          <t>ЕГАИС ЛЕС документация</t>
+        </is>
+      </c>
+      <c r="AG101" t="inlineStr">
+        <is>
+          <t>2026-10-24T12:30:00+03:00</t>
+        </is>
+      </c>
+      <c r="AJ101" t="inlineStr">
+        <is>
+          <t>2026-09-24T14:30:00+03:00</t>
+        </is>
+      </c>
+      <c r="AK101" t="inlineStr">
+        <is>
+          <t>2026-10-24T12:30:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>8142281641</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>79852671426</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>Кругляк хвойный, оформим документацию</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;&lt;strong&gt;Закрепляем лес за вами по документам.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Продаёте: покупателю нужно подтверждение происхождения. Его даёт договор купли-продажи, декларацию о сделке в ФГИС ЛК подаём за вас.&lt;/p&gt;&lt;p&gt;Везёте: на машину идёт электронный сопроводительный документ, в нём QR-код на перевозку древесины. Хвойный кругляк проходит пост и весовую.&lt;/p&gt;&lt;p&gt;Кабинет в ЛесЕГАИС и подпись не нужны, ЭСД за 15 минут.&lt;/p&gt;&lt;p&gt;Хвойный кругляк 4 и 6 метров, диаметр от 16 см.&lt;/p&gt;&lt;p&gt;Яшкино, Яшкинский район, Кемеровская область. Напишите, что нужно закрыть по бумагам в первую очередь.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-24/w2409_42_yashkino_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-24/w2409_42_yashkino_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-24/w2409_42_yashkino_3.jpg</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>В сообщениях</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>Яшкино, Кемеровская обл., ул. Свердлова, 8</t>
+        </is>
+      </c>
+      <c r="O102" t="inlineStr">
+        <is>
+          <t>ПВЗ</t>
+        </is>
+      </c>
+      <c r="P102" t="n">
+        <v>2350</v>
+      </c>
+      <c r="Q102" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R102" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S102" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T102" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U102" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V102" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W102" t="inlineStr">
+        <is>
+          <t>Сосна</t>
+        </is>
+      </c>
+      <c r="X102" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB102" t="n">
+        <v>6000</v>
+      </c>
+      <c r="AC102" t="n">
+        <v>16</v>
+      </c>
+      <c r="AE102" t="inlineStr">
+        <is>
+          <t>orbizona-shop@yandex.ru</t>
+        </is>
+      </c>
+      <c r="AF102" t="inlineStr">
+        <is>
+          <t>ЕГАИС ЛЕС документация</t>
+        </is>
+      </c>
+      <c r="AG102" t="inlineStr">
+        <is>
+          <t>2026-10-24T14:30:00+03:00</t>
+        </is>
+      </c>
+      <c r="AJ102" t="inlineStr">
+        <is>
+          <t>2026-09-24T16:30:00+03:00</t>
+        </is>
+      </c>
+      <c r="AK102" t="inlineStr">
+        <is>
+          <t>2026-10-24T14:30:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>7875797135</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>79852671426</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>Баланс еловый, документы и учёт леса</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;&lt;strong&gt;Формируем документы на вывоз и учёт леса.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Ключевой документ, это договор купли-продажи. По нему еловый баланс становится вашим товаром, кубатура числится за вами в ФГИС ЛК, и партию можно продать или вывезти.&lt;/p&gt;&lt;p&gt;Дальше проще: на каждый рейс электронный сопроводительный документ, в нём QR-код на перевозку древесины. Отчёт 1-ИЛ сдаём сами, кабинет в ЛесЕГАИС не нужен, ЭСД за 15 минут.&lt;/p&gt;&lt;p&gt;Еловый баланс 2 и 3 метра, диаметр от 6 см.&lt;/p&gt;&lt;p&gt;Юрла, Юрлинский район, Пермский край. Напишите, сколько кубов лежит, посмотрим, что нужно.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-24/w2409_43_yurla_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-24/w2409_43_yurla_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-24/w2409_43_yurla_3.jpg</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>В сообщениях</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>Юрла, Пермский край, ул. Ленина, 15</t>
+        </is>
+      </c>
+      <c r="O103" t="inlineStr">
+        <is>
+          <t>ПВЗ</t>
+        </is>
+      </c>
+      <c r="P103" t="n">
+        <v>3300</v>
+      </c>
+      <c r="Q103" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R103" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S103" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T103" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U103" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V103" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W103" t="inlineStr">
+        <is>
+          <t>Ель</t>
+        </is>
+      </c>
+      <c r="X103" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB103" t="n">
+        <v>3000</v>
+      </c>
+      <c r="AC103" t="n">
+        <v>6</v>
+      </c>
+      <c r="AE103" t="inlineStr">
+        <is>
+          <t>orbizona-shop@yandex.ru</t>
+        </is>
+      </c>
+      <c r="AF103" t="inlineStr">
+        <is>
+          <t>ЕГАИС ЛЕС документация</t>
+        </is>
+      </c>
+      <c r="AG103" t="inlineStr">
+        <is>
+          <t>2026-10-24T16:30:00+03:00</t>
+        </is>
+      </c>
+      <c r="AJ103" t="inlineStr">
+        <is>
+          <t>2026-09-24T18:30:00+03:00</t>
+        </is>
+      </c>
+      <c r="AK103" t="inlineStr">
+        <is>
+          <t>2026-10-24T16:30:00+03:00</t>
         </is>
       </c>
     </row>
